--- a/Acervo_Jurisprudencial.xlsx
+++ b/Acervo_Jurisprudencial.xlsx
@@ -20,15 +20,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Penal" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Acervo (maestra)'!$A$1:$V$178</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Administrativo'!$A$1:$V$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Amparo'!$A$1:$V$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Acervo (maestra)'!$A$1:$V$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Administrativo'!$A$1:$V$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Amparo'!$A$1:$V$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Civil'!$A$1:$V$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Civil — Condominio'!$A$1:$V$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Constitucional - DDHH'!$A$1:$V$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Constitucional - DDHH'!$A$1:$V$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Fiscal'!$A$1:$V$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Laboral'!$A$1:$V$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Mercantil'!$A$1:$V$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Mercantil'!$A$1:$V$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Penal'!$A$1:$V$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -639,13 +639,13 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
@@ -655,11 +655,11 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Penal</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -782,7 +782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2064,7 +2064,7 @@
     <row r="14" ht="80" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>mer-eje-002</t>
+          <t>auto-2032557</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
@@ -2087,17 +2087,17 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Improcedencia — análisis oficioso en amparo directo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
@@ -2112,57 +2112,57 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
+          <t>COSTAS EN EL JUICIO EJECUTIVO MERCANTIL. LA EXCLUSIÓN DE CONCEPTOS DERIVADOS DEL TÍTULO DE CRÉDITO QUE NO FUERON RECLAMADOS COMO PRESTACIONES, NO CONFIGURA UN VENCIMIENTO PARCIAL.</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>2025924</t>
+          <t>2032557</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>viernes 28 de agosto de 2026 10:36 h</t>
         </is>
       </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="11" t="inlineStr">
         <is>
-          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S14" s="11" t="inlineStr">
         <is>
-          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T14" s="11" t="inlineStr"/>
       <c r="U14" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032557</t>
         </is>
       </c>
       <c r="V14" s="11" t="inlineStr">
         <is>
-          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="15" ht="80" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>mer-eje-003</t>
+          <t>mer-eje-002</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>Mora — fecha de actualización</t>
+          <t>Improcedencia — análisis oficioso en amparo directo</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I15" s="13" t="inlineStr">
@@ -2210,57 +2210,57 @@
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
+          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>2031591</t>
+          <t>2025924</t>
         </is>
       </c>
       <c r="M15" s="13" t="inlineStr"/>
       <c r="N15" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="O15" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P15" s="13" t="inlineStr"/>
       <c r="Q15" s="13" t="inlineStr">
         <is>
-          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
+          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
         </is>
       </c>
       <c r="R15" s="13" t="inlineStr">
         <is>
-          <t>Define desde cuándo corren intereses moratorios.</t>
+          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
         </is>
       </c>
       <c r="S15" s="13" t="inlineStr">
         <is>
-          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
+          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
         </is>
       </c>
       <c r="T15" s="13" t="inlineStr"/>
       <c r="U15" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
         </is>
       </c>
       <c r="V15" s="13" t="inlineStr">
         <is>
-          <t>mora · intereses moratorios · interpelación · 12a Época</t>
+          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
         </is>
       </c>
     </row>
     <row r="16" ht="80" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>mer-pag-002</t>
+          <t>mer-eje-003</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Títulos de crédito — pagaré</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>Acción causal — pagaré como prueba del contrato</t>
+          <t>Mora — fecha de actualización</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
@@ -2308,57 +2308,57 @@
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
+          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>2024056</t>
+          <t>2031591</t>
         </is>
       </c>
       <c r="M16" s="11" t="inlineStr"/>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O16" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P16" s="11" t="inlineStr"/>
       <c r="Q16" s="11" t="inlineStr">
         <is>
-          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
+          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
         </is>
       </c>
       <c r="R16" s="11" t="inlineStr">
         <is>
-          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
+          <t>Define desde cuándo corren intereses moratorios.</t>
         </is>
       </c>
       <c r="S16" s="11" t="inlineStr">
         <is>
-          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
+          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
         </is>
       </c>
       <c r="T16" s="11" t="inlineStr"/>
       <c r="U16" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
         </is>
       </c>
       <c r="V16" s="11" t="inlineStr">
         <is>
-          <t>pagaré · acción causal · ordinario mercantil</t>
+          <t>mora · intereses moratorios · interpelación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="17" ht="80" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>mer-pag-003</t>
+          <t>mer-pag-002</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>Pagarés seriados — lugar de pago</t>
+          <t>Acción causal — pagaré como prueba del contrato</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I17" s="13" t="inlineStr">
@@ -2406,18 +2406,18 @@
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
+          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
         </is>
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>2019464</t>
+          <t>2024056</t>
         </is>
       </c>
       <c r="M17" s="13" t="inlineStr"/>
       <c r="N17" s="13" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O17" s="13" t="inlineStr">
@@ -2428,33 +2428,131 @@
       <c r="P17" s="13" t="inlineStr"/>
       <c r="Q17" s="13" t="inlineStr">
         <is>
-          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
+          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
         </is>
       </c>
       <c r="R17" s="13" t="inlineStr">
         <is>
-          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
+          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
         </is>
       </c>
       <c r="S17" s="13" t="inlineStr">
         <is>
-          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
+          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
         </is>
       </c>
       <c r="T17" s="13" t="inlineStr"/>
       <c r="U17" s="13" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
+        </is>
+      </c>
+      <c r="V17" s="13" t="inlineStr">
+        <is>
+          <t>pagaré · acción causal · ordinario mercantil</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>mer-pag-003</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Mercantil</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Títulos de crédito — pagaré</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Pagarés seriados — lugar de pago</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Décima Época</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>2019464</t>
+        </is>
+      </c>
+      <c r="M18" s="11" t="inlineStr"/>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="O18" s="11" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P18" s="11" t="inlineStr"/>
+      <c r="Q18" s="11" t="inlineStr">
+        <is>
+          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
+        </is>
+      </c>
+      <c r="R18" s="11" t="inlineStr">
+        <is>
+          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
+        </is>
+      </c>
+      <c r="S18" s="11" t="inlineStr">
+        <is>
+          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
+        </is>
+      </c>
+      <c r="T18" s="11" t="inlineStr"/>
+      <c r="U18" s="11" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
         </is>
       </c>
-      <c r="V17" s="13" t="inlineStr">
+      <c r="V18" s="11" t="inlineStr">
         <is>
           <t>pagaré · pagarés seriados · lugar de pago</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V17"/>
+  <autoFilter ref="A1:V18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5516,7 +5614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V178"/>
+  <dimension ref="A1:V182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15008,7 +15106,7 @@
     <row r="101" ht="80" customHeight="1">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>amp-eje-001</t>
+          <t>auto-2032562</t>
         </is>
       </c>
       <c r="B101" s="13" t="n">
@@ -15021,17 +15119,17 @@
       </c>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>Amparo</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>Amparo contra normas generales</t>
+          <t>Responsabilidad administrativa de servidores públicos</t>
         </is>
       </c>
       <c r="F101" s="13" t="inlineStr">
         <is>
-          <t>Efectos reflejos del fallo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr">
@@ -15041,7 +15139,7 @@
       </c>
       <c r="H101" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I101" s="13" t="inlineStr">
@@ -15056,57 +15154,57 @@
       </c>
       <c r="K101" s="14" t="inlineStr">
         <is>
-          <t>AMPARO CONTRA NORMAS GENERALES. SU NEGATIVA VINCULA Y TIENE EFECTOS REFLEJOS EN OTROS LITIGIOS DONDE LA MISMA PERSONA SOLICITE, EN EJERCICIO DEL CONTROL DIFUSO O DE CONSTITUCIONALIDAD Y CONVENCIONALIDAD EX OFFICIO, LA INAPLICACIÓN DE AQUÉLLAS.</t>
+          <t>IMPUESTO SOBRE LA RENTA. NO PROCEDE SU DEDUCCIÓN POR EL PAGO DE PENAS CONVENCIONALES EN TÉRMINOS DEL ARTÍCULO 32, FRACCIÓN VI, DE LA LEY RELATIVA, CUANDO EXISTE UN MECANISMO CONTRACTUAL PARA EVITAR SU PAGO Y NO SE EJERCE (LEGISLACIÓN VIGENTE EN 2013).</t>
         </is>
       </c>
       <c r="L101" s="13" t="inlineStr">
         <is>
-          <t>2029745</t>
+          <t>2032562</t>
         </is>
       </c>
       <c r="M101" s="13" t="inlineStr"/>
       <c r="N101" s="13" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>viernes 28 de agosto de 2026 10:36 h</t>
         </is>
       </c>
       <c r="O101" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P101" s="13" t="inlineStr"/>
       <c r="Q101" s="13" t="inlineStr">
         <is>
-          <t>Si una persona pierde amparo contra norma general, esa cosa juzgada le aplica también en otros litigios donde pretenda inaplicación de la misma norma por control difuso.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R101" s="13" t="inlineStr">
         <is>
-          <t>Cierra puerta a relitigar inconstitucionalidad por vías paralelas.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S101" s="13" t="inlineStr">
         <is>
-          <t>Si ya perdiste amparo contra norma, no insistas vía control difuso en otro juicio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T101" s="13" t="inlineStr"/>
       <c r="U101" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029745</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032562</t>
         </is>
       </c>
       <c r="V101" s="13" t="inlineStr">
         <is>
-          <t>amparo normas · control difuso · efectos reflejos</t>
+          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="102" ht="80" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>auto-2032478</t>
+          <t>amp-eje-001</t>
         </is>
       </c>
       <c r="B102" s="11" t="n">
@@ -15124,12 +15222,12 @@
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>Procedencia del amparo</t>
+          <t>Amparo contra normas generales</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Efectos reflejos del fallo</t>
         </is>
       </c>
       <c r="G102" s="11" t="inlineStr">
@@ -15139,7 +15237,7 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
@@ -15154,57 +15252,57 @@
       </c>
       <c r="K102" s="12" t="inlineStr">
         <is>
-          <t>ACCIÓN PERSONAL PARA RECUPERAR LA POSESIÓN DE UN BIEN INMUEBLE ENTRE EXCONCUBINOS. ES IMPROCEDENTE CUANDO ÉSTE FORMA PARTE DEL DERECHO DE HABITACIÓN DE LAS PERSONAS ACREEDORAS ALIMENTARIAS.</t>
+          <t>AMPARO CONTRA NORMAS GENERALES. SU NEGATIVA VINCULA Y TIENE EFECTOS REFLEJOS EN OTROS LITIGIOS DONDE LA MISMA PERSONA SOLICITE, EN EJERCICIO DEL CONTROL DIFUSO O DE CONSTITUCIONALIDAD Y CONVENCIONALIDAD EX OFFICIO, LA INAPLICACIÓN DE AQUÉLLAS.</t>
         </is>
       </c>
       <c r="L102" s="11" t="inlineStr">
         <is>
-          <t>2032478</t>
+          <t>2029745</t>
         </is>
       </c>
       <c r="M102" s="11" t="inlineStr"/>
       <c r="N102" s="11" t="inlineStr">
         <is>
-          <t>viernes 14 de agosto de 2026 10:22 h</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O102" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P102" s="11" t="inlineStr"/>
       <c r="Q102" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Si una persona pierde amparo contra norma general, esa cosa juzgada le aplica también en otros litigios donde pretenda inaplicación de la misma norma por control difuso.</t>
         </is>
       </c>
       <c r="R102" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Cierra puerta a relitigar inconstitucionalidad por vías paralelas.</t>
         </is>
       </c>
       <c r="S102" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Si ya perdiste amparo contra norma, no insistas vía control difuso en otro juicio.</t>
         </is>
       </c>
       <c r="T102" s="11" t="inlineStr"/>
       <c r="U102" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032478</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029745</t>
         </is>
       </c>
       <c r="V102" s="11" t="inlineStr">
         <is>
-          <t>Procedencia del amparo · actualización automática</t>
+          <t>amparo normas · control difuso · efectos reflejos</t>
         </is>
       </c>
     </row>
     <row r="103" ht="80" customHeight="1">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>auto-2032523</t>
+          <t>auto-2032478</t>
         </is>
       </c>
       <c r="B103" s="13" t="n">
@@ -15252,18 +15350,18 @@
       </c>
       <c r="K103" s="14" t="inlineStr">
         <is>
-          <t>INTERÉS LEGÍTIMO EN AMPARO INDIRECTO. CONSTITUYE UN CONCEPTO ÍNTIMAMENTE VINCULADO CON LOS DERECHOS DE ACCESO A LA JUSTICIA Y DE PARTICIPACIÓN DEMOCRÁTICA PARA LA PROTECCIÓN EFECTIVA DE LOS DERECHOS HUMANOS.</t>
+          <t>ACCIÓN PERSONAL PARA RECUPERAR LA POSESIÓN DE UN BIEN INMUEBLE ENTRE EXCONCUBINOS. ES IMPROCEDENTE CUANDO ÉSTE FORMA PARTE DEL DERECHO DE HABITACIÓN DE LAS PERSONAS ACREEDORAS ALIMENTARIAS.</t>
         </is>
       </c>
       <c r="L103" s="13" t="inlineStr">
         <is>
-          <t>2032523</t>
+          <t>2032478</t>
         </is>
       </c>
       <c r="M103" s="13" t="inlineStr"/>
       <c r="N103" s="13" t="inlineStr">
         <is>
-          <t>viernes 21 de agosto de 2026 10:29 h</t>
+          <t>viernes 14 de agosto de 2026 10:22 h</t>
         </is>
       </c>
       <c r="O103" s="13" t="inlineStr">
@@ -15290,7 +15388,7 @@
       <c r="T103" s="13" t="inlineStr"/>
       <c r="U103" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032523</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032478</t>
         </is>
       </c>
       <c r="V103" s="13" t="inlineStr">
@@ -15302,7 +15400,7 @@
     <row r="104" ht="80" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>auto-2032525</t>
+          <t>auto-2032523</t>
         </is>
       </c>
       <c r="B104" s="11" t="n">
@@ -15350,12 +15448,12 @@
       </c>
       <c r="K104" s="12" t="inlineStr">
         <is>
-          <t>LEYES AUTOAPLICATIVAS. SU CONCEPCIÓN ACTUAL DEBE INTERPRETARSE A LA LUZ DEL INTERÉS LEGÍTIMO Y DEL DERECHO DE ACCESO A LA JUSTICIA.</t>
+          <t>INTERÉS LEGÍTIMO EN AMPARO INDIRECTO. CONSTITUYE UN CONCEPTO ÍNTIMAMENTE VINCULADO CON LOS DERECHOS DE ACCESO A LA JUSTICIA Y DE PARTICIPACIÓN DEMOCRÁTICA PARA LA PROTECCIÓN EFECTIVA DE LOS DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L104" s="11" t="inlineStr">
         <is>
-          <t>2032525</t>
+          <t>2032523</t>
         </is>
       </c>
       <c r="M104" s="11" t="inlineStr"/>
@@ -15388,7 +15486,7 @@
       <c r="T104" s="11" t="inlineStr"/>
       <c r="U104" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032525</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032523</t>
         </is>
       </c>
       <c r="V104" s="11" t="inlineStr">
@@ -15400,7 +15498,7 @@
     <row r="105" ht="80" customHeight="1">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>amp-sus-002</t>
+          <t>auto-2032525</t>
         </is>
       </c>
       <c r="B105" s="13" t="n">
@@ -15418,12 +15516,12 @@
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>Suspensión</t>
+          <t>Procedencia del amparo</t>
         </is>
       </c>
       <c r="F105" s="13" t="inlineStr">
         <is>
-          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G105" s="13" t="inlineStr">
@@ -15448,57 +15546,57 @@
       </c>
       <c r="K105" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
+          <t>LEYES AUTOAPLICATIVAS. SU CONCEPCIÓN ACTUAL DEBE INTERPRETARSE A LA LUZ DEL INTERÉS LEGÍTIMO Y DEL DERECHO DE ACCESO A LA JUSTICIA.</t>
         </is>
       </c>
       <c r="L105" s="13" t="inlineStr">
         <is>
-          <t>2032118</t>
+          <t>2032525</t>
         </is>
       </c>
       <c r="M105" s="13" t="inlineStr"/>
       <c r="N105" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 21 de agosto de 2026 10:29 h</t>
         </is>
       </c>
       <c r="O105" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P105" s="13" t="inlineStr"/>
       <c r="Q105" s="13" t="inlineStr">
         <is>
-          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R105" s="13" t="inlineStr">
         <is>
-          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S105" s="13" t="inlineStr">
         <is>
-          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T105" s="13" t="inlineStr"/>
       <c r="U105" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032525</t>
         </is>
       </c>
       <c r="V105" s="13" t="inlineStr">
         <is>
-          <t>suspensión amparo · medida cautelar · 12a Época</t>
+          <t>Procedencia del amparo · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="106" ht="80" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>amp-sus-003</t>
+          <t>amp-sus-002</t>
         </is>
       </c>
       <c r="B106" s="11" t="n">
@@ -15521,7 +15619,7 @@
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
+          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
         </is>
       </c>
       <c r="G106" s="11" t="inlineStr">
@@ -15546,12 +15644,12 @@
       </c>
       <c r="K106" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
+          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L106" s="11" t="inlineStr">
         <is>
-          <t>2032066</t>
+          <t>2032118</t>
         </is>
       </c>
       <c r="M106" s="11" t="inlineStr"/>
@@ -15568,35 +15666,35 @@
       <c r="P106" s="11" t="inlineStr"/>
       <c r="Q106" s="11" t="inlineStr">
         <is>
-          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
+          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
         </is>
       </c>
       <c r="R106" s="11" t="inlineStr">
         <is>
-          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
+          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
         </is>
       </c>
       <c r="S106" s="11" t="inlineStr">
         <is>
-          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
+          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
         </is>
       </c>
       <c r="T106" s="11" t="inlineStr"/>
       <c r="U106" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032066</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
         </is>
       </c>
       <c r="V106" s="11" t="inlineStr">
         <is>
-          <t>suspensión restitutoria · incapacidad médica · IMSS · 12a Época</t>
+          <t>suspensión amparo · medida cautelar · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="107" ht="80" customHeight="1">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>auto-2032354</t>
+          <t>amp-sus-003</t>
         </is>
       </c>
       <c r="B107" s="13" t="n">
@@ -15619,7 +15717,7 @@
       </c>
       <c r="F107" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
         </is>
       </c>
       <c r="G107" s="13" t="inlineStr">
@@ -15644,57 +15742,57 @@
       </c>
       <c r="K107" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. AL PROVEER SOBRE SU CONCESIÓN CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN, SE DEBE CONSIDERAR QUE LAS REPERCUSIONES NEGATIVAS DE LA BIOMETRÍA EMPEORAN GRAVEMENTE EN EL MODELO ECONÓMICO ACTUAL DEL CAPITALISMO DE VIGILANCIA.</t>
+          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
         </is>
       </c>
       <c r="L107" s="13" t="inlineStr">
         <is>
-          <t>2032354</t>
+          <t>2032066</t>
         </is>
       </c>
       <c r="M107" s="13" t="inlineStr"/>
       <c r="N107" s="13" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O107" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P107" s="13" t="inlineStr"/>
       <c r="Q107" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
         </is>
       </c>
       <c r="R107" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
         </is>
       </c>
       <c r="S107" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
         </is>
       </c>
       <c r="T107" s="13" t="inlineStr"/>
       <c r="U107" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032354</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032066</t>
         </is>
       </c>
       <c r="V107" s="13" t="inlineStr">
         <is>
-          <t>Suspensión · actualización automática</t>
+          <t>suspensión restitutoria · incapacidad médica · IMSS · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="108" ht="80" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>auto-2032355</t>
+          <t>auto-2032354</t>
         </is>
       </c>
       <c r="B108" s="11" t="n">
@@ -15742,18 +15840,18 @@
       </c>
       <c r="K108" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN QUE PREVÉ LA CREACIÓN DE LA CLAVE ÚNICA DE REGISTRO DE POBLACIÓN (CURP) BIOMÉTRICA.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. AL PROVEER SOBRE SU CONCESIÓN CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN, SE DEBE CONSIDERAR QUE LAS REPERCUSIONES NEGATIVAS DE LA BIOMETRÍA EMPEORAN GRAVEMENTE EN EL MODELO ECONÓMICO ACTUAL DEL CAPITALISMO DE VIGILANCIA.</t>
         </is>
       </c>
       <c r="L108" s="11" t="inlineStr">
         <is>
-          <t>2032355</t>
+          <t>2032354</t>
         </is>
       </c>
       <c r="M108" s="11" t="inlineStr"/>
       <c r="N108" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 26 de junio de 2026 10:</t>
         </is>
       </c>
       <c r="O108" s="11" t="inlineStr">
@@ -15780,7 +15878,7 @@
       <c r="T108" s="11" t="inlineStr"/>
       <c r="U108" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032355</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032354</t>
         </is>
       </c>
       <c r="V108" s="11" t="inlineStr">
@@ -15792,7 +15890,7 @@
     <row r="109" ht="80" customHeight="1">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>auto-2032475</t>
+          <t>auto-2032355</t>
         </is>
       </c>
       <c r="B109" s="13" t="n">
@@ -15840,18 +15938,18 @@
       </c>
       <c r="K109" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CON EFECTOS RESTITUTORIOS ANTICIPADOS CONTRA LA OMISIÓN DE PAGO CORRESPONDIENTE AL PROGRAMA PENSIÓN PARA EL BIENESTAR DE LAS PERSONAS CON DISCAPACIDAD PERMANENTE.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN QUE PREVÉ LA CREACIÓN DE LA CLAVE ÚNICA DE REGISTRO DE POBLACIÓN (CURP) BIOMÉTRICA.</t>
         </is>
       </c>
       <c r="L109" s="13" t="inlineStr">
         <is>
-          <t>2032475</t>
+          <t>2032355</t>
         </is>
       </c>
       <c r="M109" s="13" t="inlineStr"/>
       <c r="N109" s="13" t="inlineStr">
         <is>
-          <t>viernes 07 de agosto de 2026 10:15 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O109" s="13" t="inlineStr">
@@ -15878,7 +15976,7 @@
       <c r="T109" s="13" t="inlineStr"/>
       <c r="U109" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032475</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032355</t>
         </is>
       </c>
       <c r="V109" s="13" t="inlineStr">
@@ -15890,7 +15988,7 @@
     <row r="110" ht="80" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>auto-2032542</t>
+          <t>auto-2032475</t>
         </is>
       </c>
       <c r="B110" s="11" t="n">
@@ -15938,18 +16036,18 @@
       </c>
       <c r="K110" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN AMPARO INDIRECTO. ES IMPROCEDENTE CONTRA NORMAS RECLAMADAS COMO AUTOAPLICATIVAS, CUANDO EL PLAZO DE VACATIO LEGIS NO ACTUALIZA EL REQUISITO DE PELIGRO EN LA DEMORA.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CON EFECTOS RESTITUTORIOS ANTICIPADOS CONTRA LA OMISIÓN DE PAGO CORRESPONDIENTE AL PROGRAMA PENSIÓN PARA EL BIENESTAR DE LAS PERSONAS CON DISCAPACIDAD PERMANENTE.</t>
         </is>
       </c>
       <c r="L110" s="11" t="inlineStr">
         <is>
-          <t>2032542</t>
+          <t>2032475</t>
         </is>
       </c>
       <c r="M110" s="11" t="inlineStr"/>
       <c r="N110" s="11" t="inlineStr">
         <is>
-          <t>viernes 21 de agosto de 2026 10:29 h</t>
+          <t>viernes 07 de agosto de 2026 10:15 h</t>
         </is>
       </c>
       <c r="O110" s="11" t="inlineStr">
@@ -15976,7 +16074,7 @@
       <c r="T110" s="11" t="inlineStr"/>
       <c r="U110" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032542</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032475</t>
         </is>
       </c>
       <c r="V110" s="11" t="inlineStr">
@@ -15988,7 +16086,7 @@
     <row r="111" ht="80" customHeight="1">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>auto-2032544</t>
+          <t>auto-2032542</t>
         </is>
       </c>
       <c r="B111" s="13" t="n">
@@ -16036,12 +16134,12 @@
       </c>
       <c r="K111" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA LOS EFECTOS Y CONSECUENCIAS DEL ARTÍCULO 49 BIS DEL CÓDIGO FISCAL DE LA FEDERACIÓN.</t>
+          <t>SUSPENSIÓN EN AMPARO INDIRECTO. ES IMPROCEDENTE CONTRA NORMAS RECLAMADAS COMO AUTOAPLICATIVAS, CUANDO EL PLAZO DE VACATIO LEGIS NO ACTUALIZA EL REQUISITO DE PELIGRO EN LA DEMORA.</t>
         </is>
       </c>
       <c r="L111" s="13" t="inlineStr">
         <is>
-          <t>2032544</t>
+          <t>2032542</t>
         </is>
       </c>
       <c r="M111" s="13" t="inlineStr"/>
@@ -16074,7 +16172,7 @@
       <c r="T111" s="13" t="inlineStr"/>
       <c r="U111" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032544</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032542</t>
         </is>
       </c>
       <c r="V111" s="13" t="inlineStr">
@@ -16086,7 +16184,7 @@
     <row r="112" ht="80" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>auto-2032235</t>
+          <t>auto-2032544</t>
         </is>
       </c>
       <c r="B112" s="11" t="n">
@@ -16099,12 +16197,12 @@
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>Arrendamiento</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr">
@@ -16134,18 +16232,18 @@
       </c>
       <c r="K112" s="12" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE PAGO EN ARRENDAMIENTO DE BIENES INMUEBLES. NO SE ACTUALIZA CUANDO EN EL CONTRATO SE PACTAN MODALIDADES ESPECÍFICAS DE PAGO Y EL ARRENDATARIO LAS VARÍA DE MANERA UNILATERAL.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA LOS EFECTOS Y CONSECUENCIAS DEL ARTÍCULO 49 BIS DEL CÓDIGO FISCAL DE LA FEDERACIÓN.</t>
         </is>
       </c>
       <c r="L112" s="11" t="inlineStr">
         <is>
-          <t>2032235</t>
+          <t>2032544</t>
         </is>
       </c>
       <c r="M112" s="11" t="inlineStr"/>
       <c r="N112" s="11" t="inlineStr">
         <is>
-          <t>viernes 05 de junio de 2026 10:11 h</t>
+          <t>viernes 21 de agosto de 2026 10:29 h</t>
         </is>
       </c>
       <c r="O112" s="11" t="inlineStr">
@@ -16172,19 +16270,19 @@
       <c r="T112" s="11" t="inlineStr"/>
       <c r="U112" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032235</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032544</t>
         </is>
       </c>
       <c r="V112" s="11" t="inlineStr">
         <is>
-          <t>Arrendamiento · actualización automática</t>
+          <t>Suspensión · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="113" ht="80" customHeight="1">
       <c r="A113" s="13" t="inlineStr">
         <is>
-          <t>auto-2032255</t>
+          <t>auto-2032576</t>
         </is>
       </c>
       <c r="B113" s="13" t="n">
@@ -16197,12 +16295,12 @@
       </c>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>Arrendamiento</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F113" s="13" t="inlineStr">
@@ -16232,18 +16330,18 @@
       </c>
       <c r="K113" s="14" t="inlineStr">
         <is>
-          <t>CRÉDITOS CONTRA LA MASA EN EL CONCURSO MERCANTIL. SON LOS CONTRAÍDOS CON POSTERIORIDAD AL INICIO DEL CONCURSO MERCANTIL Y AL DICTADO DE LA SENTENCIA DE DECLARACIÓN, CON EXCEPCIÓN DE LOS CRÉDITOS LABORALES, FISCALES Y AQUELLOS CON GARANTÍA REAL.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA LA EXPULSIÓN DE UNA PERSONA ADOLESCENTE DE LA ESCUELA EN LA QUE CURSA LA EDUCACIÓN BÁSICA (SECUNDARIA) POR ACUMULAR FALTAS A SU REGLAMENTO.</t>
         </is>
       </c>
       <c r="L113" s="13" t="inlineStr">
         <is>
-          <t>2032255</t>
+          <t>2032576</t>
         </is>
       </c>
       <c r="M113" s="13" t="inlineStr"/>
       <c r="N113" s="13" t="inlineStr">
         <is>
-          <t>viernes 12 de junio de 2026 10:18 h</t>
+          <t>viernes 28 de agosto de 2026 10:36 h</t>
         </is>
       </c>
       <c r="O113" s="13" t="inlineStr">
@@ -16270,19 +16368,19 @@
       <c r="T113" s="13" t="inlineStr"/>
       <c r="U113" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032255</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032576</t>
         </is>
       </c>
       <c r="V113" s="13" t="inlineStr">
         <is>
-          <t>Arrendamiento · actualización automática</t>
+          <t>Suspensión · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="114" ht="80" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>auto-2032412</t>
+          <t>auto-2032235</t>
         </is>
       </c>
       <c r="B114" s="11" t="n">
@@ -16330,18 +16428,18 @@
       </c>
       <c r="K114" s="12" t="inlineStr">
         <is>
-          <t>DESECHAMIENTO DE LA DEMANDA EN EL JUICIO ORAL MERCANTIL. ES INVÁLIDO CUANDO SE BASA EN UNA APRECIACIÓN FORMAL DEL DESAHOGO DE LA PREVENCIÓN REALIZADA EN TÉRMINOS DEL ARTÍCULO 1390 BIS 12 DEL CÓDIGO DE COMERCIO.</t>
+          <t>PRESUNCIÓN DE PAGO EN ARRENDAMIENTO DE BIENES INMUEBLES. NO SE ACTUALIZA CUANDO EN EL CONTRATO SE PACTAN MODALIDADES ESPECÍFICAS DE PAGO Y EL ARRENDATARIO LAS VARÍA DE MANERA UNILATERAL.</t>
         </is>
       </c>
       <c r="L114" s="11" t="inlineStr">
         <is>
-          <t>2032412</t>
+          <t>2032235</t>
         </is>
       </c>
       <c r="M114" s="11" t="inlineStr"/>
       <c r="N114" s="11" t="inlineStr">
         <is>
-          <t>viernes 10 de julio de 2026 10:17 h</t>
+          <t>viernes 05 de junio de 2026 10:11 h</t>
         </is>
       </c>
       <c r="O114" s="11" t="inlineStr">
@@ -16368,7 +16466,7 @@
       <c r="T114" s="11" t="inlineStr"/>
       <c r="U114" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032412</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032235</t>
         </is>
       </c>
       <c r="V114" s="11" t="inlineStr">
@@ -16380,7 +16478,7 @@
     <row r="115" ht="80" customHeight="1">
       <c r="A115" s="13" t="inlineStr">
         <is>
-          <t>auto-2032524</t>
+          <t>auto-2032255</t>
         </is>
       </c>
       <c r="B115" s="13" t="n">
@@ -16428,18 +16526,18 @@
       </c>
       <c r="K115" s="14" t="inlineStr">
         <is>
-          <t>INTERÉS LEGÍTIMO EN AMPARO INDIRECTO. LO TIENEN LAS PERSONAS QUE ACREDITEN LA PROPIEDAD O POSESIÓN LEGAL DE INMUEBLES DESTINADOS A ESTANCIAS TURÍSTICAS EVENTUALES PARA RECLAMAR LA LEY DE TURISMO DE LA CIUDAD DE MÉXICO.</t>
+          <t>CRÉDITOS CONTRA LA MASA EN EL CONCURSO MERCANTIL. SON LOS CONTRAÍDOS CON POSTERIORIDAD AL INICIO DEL CONCURSO MERCANTIL Y AL DICTADO DE LA SENTENCIA DE DECLARACIÓN, CON EXCEPCIÓN DE LOS CRÉDITOS LABORALES, FISCALES Y AQUELLOS CON GARANTÍA REAL.</t>
         </is>
       </c>
       <c r="L115" s="13" t="inlineStr">
         <is>
-          <t>2032524</t>
+          <t>2032255</t>
         </is>
       </c>
       <c r="M115" s="13" t="inlineStr"/>
       <c r="N115" s="13" t="inlineStr">
         <is>
-          <t>viernes 21 de agosto de 2026 10:29 h</t>
+          <t>viernes 12 de junio de 2026 10:18 h</t>
         </is>
       </c>
       <c r="O115" s="13" t="inlineStr">
@@ -16466,7 +16564,7 @@
       <c r="T115" s="13" t="inlineStr"/>
       <c r="U115" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032524</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032255</t>
         </is>
       </c>
       <c r="V115" s="13" t="inlineStr">
@@ -16478,7 +16576,7 @@
     <row r="116" ht="80" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>civ-arr-003</t>
+          <t>auto-2032412</t>
         </is>
       </c>
       <c r="B116" s="11" t="n">
@@ -16501,7 +16599,7 @@
       </c>
       <c r="F116" s="11" t="inlineStr">
         <is>
-          <t>Tácita reconducción</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G116" s="11" t="inlineStr">
@@ -16511,7 +16609,7 @@
       </c>
       <c r="H116" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I116" s="11" t="inlineStr">
@@ -16521,54 +16619,62 @@
       </c>
       <c r="J116" s="11" t="inlineStr">
         <is>
-          <t>Federal — interpreta CCCDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K116" s="12" t="inlineStr">
         <is>
-          <t>TÁCITA RECONDUCCIÓN DEL ARRENDAMIENTO. SUS REQUISITOS Y EFECTOS CONFORME AL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL.</t>
+          <t>DESECHAMIENTO DE LA DEMANDA EN EL JUICIO ORAL MERCANTIL. ES INVÁLIDO CUANDO SE BASA EN UNA APRECIACIÓN FORMAL DEL DESAHOGO DE LA PREVENCIÓN REALIZADA EN TÉRMINOS DEL ARTÍCULO 1390 BIS 12 DEL CÓDIGO DE COMERCIO.</t>
         </is>
       </c>
       <c r="L116" s="11" t="inlineStr">
         <is>
-          <t>2017872</t>
+          <t>2032412</t>
         </is>
       </c>
       <c r="M116" s="11" t="inlineStr"/>
-      <c r="N116" s="11" t="inlineStr"/>
-      <c r="O116" s="11" t="inlineStr"/>
+      <c r="N116" s="11" t="inlineStr">
+        <is>
+          <t>viernes 10 de julio de 2026 10:17 h</t>
+        </is>
+      </c>
+      <c r="O116" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P116" s="11" t="inlineStr"/>
       <c r="Q116" s="11" t="inlineStr">
         <is>
-          <t>Vencido el contrato, si el arrendatario continúa en la posesión del bien con consentimiento del arrendador (recibos de renta o silencio) por más de 10 días, el contrato se considera renovado por tiempo indeterminado.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R116" s="11" t="inlineStr">
         <is>
-          <t>Trampa frecuente: el arrendador pierde plazo fijo por no actuar.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S116" s="11" t="inlineStr">
         <is>
-          <t>Al vencer el contrato, el arrendador debe requerir formalmente desocupación si no quiere renovación tácita. Recibir un solo pago posterior al vencimiento es indicio fuerte de reconducción.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T116" s="11" t="inlineStr"/>
       <c r="U116" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2017872</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032412</t>
         </is>
       </c>
       <c r="V116" s="11" t="inlineStr">
         <is>
-          <t>tácita reconducción · vencimiento · renovación</t>
+          <t>Arrendamiento · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="117" ht="80" customHeight="1">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>civ-arr-004</t>
+          <t>auto-2032524</t>
         </is>
       </c>
       <c r="B117" s="13" t="n">
@@ -16591,7 +16697,7 @@
       </c>
       <c r="F117" s="13" t="inlineStr">
         <is>
-          <t>Consignación de llaves no libera de pago</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G117" s="13" t="inlineStr">
@@ -16616,57 +16722,57 @@
       </c>
       <c r="K117" s="14" t="inlineStr">
         <is>
-          <t>ARRENDAMIENTO. LA CONSIGNACIÓN DE LLAVES DEL INMUEBLE ARRENDADO EXHIBIDAS MEDIANTE ESCRITO ANTE EL ÓRGANO JURISDICCIONAL NO LIBERA AL DEMANDADO DEL PAGO DE RENTAS, MANTENIMIENTO, SERVICIOS DE GAS Y AGUA, SI NO ACREDITA HABER IMPULSADO EL PROCEDIMIENTO.</t>
+          <t>INTERÉS LEGÍTIMO EN AMPARO INDIRECTO. LO TIENEN LAS PERSONAS QUE ACREDITEN LA PROPIEDAD O POSESIÓN LEGAL DE INMUEBLES DESTINADOS A ESTANCIAS TURÍSTICAS EVENTUALES PARA RECLAMAR LA LEY DE TURISMO DE LA CIUDAD DE MÉXICO.</t>
         </is>
       </c>
       <c r="L117" s="13" t="inlineStr">
         <is>
-          <t>2031626</t>
+          <t>2032524</t>
         </is>
       </c>
       <c r="M117" s="13" t="inlineStr"/>
       <c r="N117" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 21 de agosto de 2026 10:29 h</t>
         </is>
       </c>
       <c r="O117" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P117" s="13" t="inlineStr"/>
       <c r="Q117" s="13" t="inlineStr">
         <is>
-          <t>El arrendatario que pretende terminar el contrato consignando las llaves debe impulsar la notificación al arrendador. Sin ese impulso procesal, sigue obligado al pago de rentas y servicios.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R117" s="13" t="inlineStr">
         <is>
-          <t>Defensa del arrendador contra inquilinos que abandonan sin notificar.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S117" s="13" t="inlineStr">
         <is>
-          <t>Inquilino que entrega llaves debe pedir actuario para notificar, no basta exhibirlas. Arrendador puede seguir cobrando hasta que el procedimiento esté impulsado.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T117" s="13" t="inlineStr"/>
       <c r="U117" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031626</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032524</t>
         </is>
       </c>
       <c r="V117" s="13" t="inlineStr">
         <is>
-          <t>arrendamiento · consignación llaves · 12a Época</t>
+          <t>Arrendamiento · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="118" ht="80" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>civ-arr-005</t>
+          <t>civ-arr-003</t>
         </is>
       </c>
       <c r="B118" s="11" t="n">
@@ -16689,7 +16795,7 @@
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
-          <t>Aviso de terminación — cómputo de plazo</t>
+          <t>Tácita reconducción</t>
         </is>
       </c>
       <c r="G118" s="11" t="inlineStr">
@@ -16699,7 +16805,7 @@
       </c>
       <c r="H118" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I118" s="11" t="inlineStr">
@@ -16709,62 +16815,54 @@
       </c>
       <c r="J118" s="11" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal — interpreta CCCDMX</t>
         </is>
       </c>
       <c r="K118" s="12" t="inlineStr">
         <is>
-          <t>CONTRATO DE ARRENDAMIENTO POR TIEMPO INDETERMINADO PARA PREDIOS URBANOS. LA OPORTUNIDAD DEL AVISO PARA DARLO POR CONCLUIDO DEBE COMPUTARSE EN DÍAS HÁBILES, A MENOS QUE LAS PARTES RENUNCIEN A ESE DERECHO.</t>
+          <t>TÁCITA RECONDUCCIÓN DEL ARRENDAMIENTO. SUS REQUISITOS Y EFECTOS CONFORME AL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL.</t>
         </is>
       </c>
       <c r="L118" s="11" t="inlineStr">
         <is>
-          <t>2024563</t>
+          <t>2017872</t>
         </is>
       </c>
       <c r="M118" s="11" t="inlineStr"/>
-      <c r="N118" s="11" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="O118" s="11" t="inlineStr">
-        <is>
-          <t>Gaceta del SJF — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N118" s="11" t="inlineStr"/>
+      <c r="O118" s="11" t="inlineStr"/>
       <c r="P118" s="11" t="inlineStr"/>
       <c r="Q118" s="11" t="inlineStr">
         <is>
-          <t>El aviso de terminación de arrendamiento por tiempo indeterminado se computa en días HÁBILES por defecto. Solo si las partes pactaron expresamente días naturales, aplica esa modalidad.</t>
+          <t>Vencido el contrato, si el arrendatario continúa en la posesión del bien con consentimiento del arrendador (recibos de renta o silencio) por más de 10 días, el contrato se considera renovado por tiempo indeterminado.</t>
         </is>
       </c>
       <c r="R118" s="11" t="inlineStr">
         <is>
-          <t>Define plazo real para desocupación en CDMX.</t>
+          <t>Trampa frecuente: el arrendador pierde plazo fijo por no actuar.</t>
         </is>
       </c>
       <c r="S118" s="11" t="inlineStr">
         <is>
-          <t>Confusión frecuente: muchos contratos asumen días naturales sin pactarlo. El plazo es hábil. Hay que dar el aviso anticipándose.</t>
+          <t>Al vencer el contrato, el arrendador debe requerir formalmente desocupación si no quiere renovación tácita. Recibir un solo pago posterior al vencimiento es indicio fuerte de reconducción.</t>
         </is>
       </c>
       <c r="T118" s="11" t="inlineStr"/>
       <c r="U118" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2017872</t>
         </is>
       </c>
       <c r="V118" s="11" t="inlineStr">
         <is>
-          <t>arrendamiento CDMX · aviso terminación · días hábiles</t>
+          <t>tácita reconducción · vencimiento · renovación</t>
         </is>
       </c>
     </row>
     <row r="119" ht="80" customHeight="1">
       <c r="A119" s="13" t="inlineStr">
         <is>
-          <t>fam-div-001</t>
+          <t>civ-arr-004</t>
         </is>
       </c>
       <c r="B119" s="13" t="n">
@@ -16782,12 +16880,12 @@
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>Divorcio sin expresión de causa</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F119" s="13" t="inlineStr">
         <is>
-          <t>Procedencia del recurso de revocación</t>
+          <t>Consignación de llaves no libera de pago</t>
         </is>
       </c>
       <c r="G119" s="13" t="inlineStr">
@@ -16807,17 +16905,17 @@
       </c>
       <c r="J119" s="13" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K119" s="14" t="inlineStr">
         <is>
-          <t>DIVORCIO SIN EXPRESIÓN DE CAUSA. PROCEDENCIA DEL RECURSO DE REVOCACIÓN CONTRA LAS RESOLUCIONES DICTADAS DURANTE SU SUSTANCIACIÓN.</t>
+          <t>ARRENDAMIENTO. LA CONSIGNACIÓN DE LLAVES DEL INMUEBLE ARRENDADO EXHIBIDAS MEDIANTE ESCRITO ANTE EL ÓRGANO JURISDICCIONAL NO LIBERA AL DEMANDADO DEL PAGO DE RENTAS, MANTENIMIENTO, SERVICIOS DE GAS Y AGUA, SI NO ACREDITA HABER IMPULSADO EL PROCEDIMIENTO.</t>
         </is>
       </c>
       <c r="L119" s="13" t="inlineStr">
         <is>
-          <t>2031170</t>
+          <t>2031626</t>
         </is>
       </c>
       <c r="M119" s="13" t="inlineStr"/>
@@ -16828,41 +16926,41 @@
       </c>
       <c r="O119" s="13" t="inlineStr">
         <is>
-          <t>SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — VERIFICADO</t>
         </is>
       </c>
       <c r="P119" s="13" t="inlineStr"/>
       <c r="Q119" s="13" t="inlineStr">
         <is>
-          <t>Las resoluciones dictadas durante la sustanciación del divorcio sin causa admiten recurso de revocación conforme a los arts. 685, 685 bis y 691 del CPC para CDMX.</t>
+          <t>El arrendatario que pretende terminar el contrato consignando las llaves debe impulsar la notificación al arrendador. Sin ese impulso procesal, sigue obligado al pago de rentas y servicios.</t>
         </is>
       </c>
       <c r="R119" s="13" t="inlineStr">
         <is>
-          <t>Vía expedita contra resoluciones intermedias en divorcio incausado CDMX.</t>
+          <t>Defensa del arrendador contra inquilinos que abandonan sin notificar.</t>
         </is>
       </c>
       <c r="S119" s="13" t="inlineStr">
         <is>
-          <t>Antes era confusa la vía. Ahora con esta tesis se aplica revocación. Permite revisar rápidamente medidas provisionales sobre alimentos o convivencia.</t>
+          <t>Inquilino que entrega llaves debe pedir actuario para notificar, no basta exhibirlas. Arrendador puede seguir cobrando hasta que el procedimiento esté impulsado.</t>
         </is>
       </c>
       <c r="T119" s="13" t="inlineStr"/>
       <c r="U119" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031170</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031626</t>
         </is>
       </c>
       <c r="V119" s="13" t="inlineStr">
         <is>
-          <t>divorcio incausado · revocación · CDMX · 12a Época</t>
+          <t>arrendamiento · consignación llaves · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="120" ht="80" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>fam-div-002</t>
+          <t>civ-arr-005</t>
         </is>
       </c>
       <c r="B120" s="11" t="n">
@@ -16880,12 +16978,12 @@
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>Divorcio sin expresión de causa</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>Amparo directo contra sentencia</t>
+          <t>Aviso de terminación — cómputo de plazo</t>
         </is>
       </c>
       <c r="G120" s="11" t="inlineStr">
@@ -16905,62 +17003,62 @@
       </c>
       <c r="J120" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K120" s="12" t="inlineStr">
         <is>
-          <t>AMPARO DIRECTO. PROCEDE CONTRA LA SENTENCIA QUE DECLARA LA DISOLUCIÓN DEL VÍNCULO MATRIMONIAL EN UN JUICIO DE DIVORCIO SIN EXPRESIÓN DE CAUSA Y RESUELVE PROVISIONALMENTE SOBRE LOS ALIMENTOS U OTRAS CUESTIONES INHERENTES.</t>
+          <t>CONTRATO DE ARRENDAMIENTO POR TIEMPO INDETERMINADO PARA PREDIOS URBANOS. LA OPORTUNIDAD DEL AVISO PARA DARLO POR CONCLUIDO DEBE COMPUTARSE EN DÍAS HÁBILES, A MENOS QUE LAS PARTES RENUNCIEN A ESE DERECHO.</t>
         </is>
       </c>
       <c r="L120" s="11" t="inlineStr">
         <is>
-          <t>2029853</t>
+          <t>2024563</t>
         </is>
       </c>
       <c r="M120" s="11" t="inlineStr"/>
       <c r="N120" s="11" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O120" s="11" t="inlineStr">
         <is>
-          <t>SJF — VERIFICADO</t>
+          <t>Gaceta del SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P120" s="11" t="inlineStr"/>
       <c r="Q120" s="11" t="inlineStr">
         <is>
-          <t>La sentencia de divorcio sin expresión de causa que resuelve sobre alimentos provisionales o cuestiones inherentes es definitiva para efectos del amparo directo.</t>
+          <t>El aviso de terminación de arrendamiento por tiempo indeterminado se computa en días HÁBILES por defecto. Solo si las partes pactaron expresamente días naturales, aplica esa modalidad.</t>
         </is>
       </c>
       <c r="R120" s="11" t="inlineStr">
         <is>
-          <t>Define vía de impugnación: amparo directo, no indirecto.</t>
+          <t>Define plazo real para desocupación en CDMX.</t>
         </is>
       </c>
       <c r="S120" s="11" t="inlineStr">
         <is>
-          <t>Importante para no equivocarse de vía. Si tu sentencia incluye medidas sobre alimentos: amparo directo. Si solo es disolución limpia: dependerá del caso.</t>
+          <t>Confusión frecuente: muchos contratos asumen días naturales sin pactarlo. El plazo es hábil. Hay que dar el aviso anticipándose.</t>
         </is>
       </c>
       <c r="T120" s="11" t="inlineStr"/>
       <c r="U120" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029853</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
         </is>
       </c>
       <c r="V120" s="11" t="inlineStr">
         <is>
-          <t>divorcio incausado · amparo directo · alimentos</t>
+          <t>arrendamiento CDMX · aviso terminación · días hábiles</t>
         </is>
       </c>
     </row>
     <row r="121" ht="80" customHeight="1">
       <c r="A121" s="13" t="inlineStr">
         <is>
-          <t>civ-ext-003</t>
+          <t>fam-div-001</t>
         </is>
       </c>
       <c r="B121" s="13" t="n">
@@ -16978,12 +17076,12 @@
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>Extinción de dominio</t>
+          <t>Divorcio sin expresión de causa</t>
         </is>
       </c>
       <c r="F121" s="13" t="inlineStr">
         <is>
-          <t>Comportarse como dueño — concepto</t>
+          <t>Procedencia del recurso de revocación</t>
         </is>
       </c>
       <c r="G121" s="13" t="inlineStr">
@@ -16993,7 +17091,7 @@
       </c>
       <c r="H121" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I121" s="13" t="inlineStr">
@@ -17003,62 +17101,62 @@
       </c>
       <c r="J121" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K121" s="14" t="inlineStr">
         <is>
-          <t>ACCIÓN DE EXTINCIÓN DE DOMINIO. CONCEPTO DE "COMPORTARSE U OSTENTARSE COMO DUEÑO", PARA LOS EFECTOS DE LA LEY FEDERAL DE EXTINCIÓN DE DOMINIO (ABROGADA).</t>
+          <t>DIVORCIO SIN EXPRESIÓN DE CAUSA. PROCEDENCIA DEL RECURSO DE REVOCACIÓN CONTRA LAS RESOLUCIONES DICTADAS DURANTE SU SUSTANCIACIÓN.</t>
         </is>
       </c>
       <c r="L121" s="13" t="inlineStr">
         <is>
-          <t>2024407</t>
+          <t>2031170</t>
         </is>
       </c>
       <c r="M121" s="13" t="inlineStr"/>
       <c r="N121" s="13" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O121" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P121" s="13" t="inlineStr"/>
       <c r="Q121" s="13" t="inlineStr">
         <is>
-          <t>El "comportarse u ostentarse como dueño" requiere acreditar actos materiales objetivos: posesión, administración, disposición, sin que baste la mera titularidad registral.</t>
+          <t>Las resoluciones dictadas durante la sustanciación del divorcio sin causa admiten recurso de revocación conforme a los arts. 685, 685 bis y 691 del CPC para CDMX.</t>
         </is>
       </c>
       <c r="R121" s="13" t="inlineStr">
         <is>
-          <t>Estándar para acreditar legitimación pasiva en extinción.</t>
+          <t>Vía expedita contra resoluciones intermedias en divorcio incausado CDMX.</t>
         </is>
       </c>
       <c r="S121" s="13" t="inlineStr">
         <is>
-          <t>Defensa: probar que tu cliente solo era titular registral, no se ostentaba como dueño.</t>
+          <t>Antes era confusa la vía. Ahora con esta tesis se aplica revocación. Permite revisar rápidamente medidas provisionales sobre alimentos o convivencia.</t>
         </is>
       </c>
       <c r="T121" s="13" t="inlineStr"/>
       <c r="U121" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024407</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031170</t>
         </is>
       </c>
       <c r="V121" s="13" t="inlineStr">
         <is>
-          <t>extinción dominio · ostentación · comportamiento · LFED</t>
+          <t>divorcio incausado · revocación · CDMX · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="122" ht="80" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>civ-fid-003</t>
+          <t>fam-div-002</t>
         </is>
       </c>
       <c r="B122" s="11" t="n">
@@ -17076,12 +17174,12 @@
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>Fideicomisos</t>
+          <t>Divorcio sin expresión de causa</t>
         </is>
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
-          <t>Fideicomiso de garantía y mediación — avalúo</t>
+          <t>Amparo directo contra sentencia</t>
         </is>
       </c>
       <c r="G122" s="11" t="inlineStr">
@@ -17106,57 +17204,57 @@
       </c>
       <c r="K122" s="12" t="inlineStr">
         <is>
-          <t>FIDEICOMISO EN GARANTÍA DERIVADO DE UN CONVENIO DE MEDIACIÓN. CUANDO SE PRETENDA SU EJECUCIÓN JUDICIAL DEBE EXHIBIRSE EL AVALÚO DEL BIEN INMUEBLE DADO EN GARANTÍA, AL SER UN ELEMENTO DE LA ACCIÓN CONFORME AL ARTÍCULO 1414 BIS DEL CÓDIGO DE COMERCIO.</t>
+          <t>AMPARO DIRECTO. PROCEDE CONTRA LA SENTENCIA QUE DECLARA LA DISOLUCIÓN DEL VÍNCULO MATRIMONIAL EN UN JUICIO DE DIVORCIO SIN EXPRESIÓN DE CAUSA Y RESUELVE PROVISIONALMENTE SOBRE LOS ALIMENTOS U OTRAS CUESTIONES INHERENTES.</t>
         </is>
       </c>
       <c r="L122" s="11" t="inlineStr">
         <is>
-          <t>2027244</t>
+          <t>2029853</t>
         </is>
       </c>
       <c r="M122" s="11" t="inlineStr"/>
       <c r="N122" s="11" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O122" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P122" s="11" t="inlineStr"/>
       <c r="Q122" s="11" t="inlineStr">
         <is>
-          <t>Para ejecutar judicialmente fideicomiso de garantía constituido por convenio de mediación, el actor DEBE exhibir avalúo del bien al promover. Sin avalúo, la acción es improcedente.</t>
+          <t>La sentencia de divorcio sin expresión de causa que resuelve sobre alimentos provisionales o cuestiones inherentes es definitiva para efectos del amparo directo.</t>
         </is>
       </c>
       <c r="R122" s="11" t="inlineStr">
         <is>
-          <t>Requisito formal estricto para ejecutar fideicomiso de garantía vía mediación.</t>
+          <t>Define vía de impugnación: amparo directo, no indirecto.</t>
         </is>
       </c>
       <c r="S122" s="11" t="inlineStr">
         <is>
-          <t>Antes de demandar ejecución hay que conseguir avalúo de perito autorizado.</t>
+          <t>Importante para no equivocarse de vía. Si tu sentencia incluye medidas sobre alimentos: amparo directo. Si solo es disolución limpia: dependerá del caso.</t>
         </is>
       </c>
       <c r="T122" s="11" t="inlineStr"/>
       <c r="U122" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029853</t>
         </is>
       </c>
       <c r="V122" s="11" t="inlineStr">
         <is>
-          <t>fideicomiso garantía · mediación · art. 1414 bis Cco · avalúo</t>
+          <t>divorcio incausado · amparo directo · alimentos</t>
         </is>
       </c>
     </row>
     <row r="123" ht="80" customHeight="1">
       <c r="A123" s="13" t="inlineStr">
         <is>
-          <t>auto-2032124</t>
+          <t>civ-ext-003</t>
         </is>
       </c>
       <c r="B123" s="13" t="n">
@@ -17174,12 +17272,12 @@
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Extinción de dominio</t>
         </is>
       </c>
       <c r="F123" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Comportarse como dueño — concepto</t>
         </is>
       </c>
       <c r="G123" s="13" t="inlineStr">
@@ -17189,7 +17287,7 @@
       </c>
       <c r="H123" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I123" s="13" t="inlineStr">
@@ -17204,57 +17302,57 @@
       </c>
       <c r="K123" s="14" t="inlineStr">
         <is>
-          <t>CRÉDITOS HIPOTECARIOS OTORGADOS POR LAS INSTITUCIONES FINANCIERAS A SUS PERSONAS TRABAJADORAS. EL ESTUDIO SOBRE LA MODIFICACIÓN DE LAS CLÁUSULAS QUE CONTENGAN UN BENEFICIO OTORGADO DERIVADO DE LA RELACIÓN LABORAL PROCEDE EN ESTA VÍA.</t>
+          <t>ACCIÓN DE EXTINCIÓN DE DOMINIO. CONCEPTO DE "COMPORTARSE U OSTENTARSE COMO DUEÑO", PARA LOS EFECTOS DE LA LEY FEDERAL DE EXTINCIÓN DE DOMINIO (ABROGADA).</t>
         </is>
       </c>
       <c r="L123" s="13" t="inlineStr">
         <is>
-          <t>2032124</t>
+          <t>2024407</t>
         </is>
       </c>
       <c r="M123" s="13" t="inlineStr"/>
       <c r="N123" s="13" t="inlineStr">
         <is>
-          <t>viernes 15 de mayo de 2026 10:20 h</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O123" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P123" s="13" t="inlineStr"/>
       <c r="Q123" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>El "comportarse u ostentarse como dueño" requiere acreditar actos materiales objetivos: posesión, administración, disposición, sin que baste la mera titularidad registral.</t>
         </is>
       </c>
       <c r="R123" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Estándar para acreditar legitimación pasiva en extinción.</t>
         </is>
       </c>
       <c r="S123" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Defensa: probar que tu cliente solo era titular registral, no se ostentaba como dueño.</t>
         </is>
       </c>
       <c r="T123" s="13" t="inlineStr"/>
       <c r="U123" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032124</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024407</t>
         </is>
       </c>
       <c r="V123" s="13" t="inlineStr">
         <is>
-          <t>Juicio hipotecario · actualización automática</t>
+          <t>extinción dominio · ostentación · comportamiento · LFED</t>
         </is>
       </c>
     </row>
     <row r="124" ht="80" customHeight="1">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>auto-2032537</t>
+          <t>civ-fid-003</t>
         </is>
       </c>
       <c r="B124" s="11" t="n">
@@ -17272,12 +17370,12 @@
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Fideicomisos</t>
         </is>
       </c>
       <c r="F124" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Fideicomiso de garantía y mediación — avalúo</t>
         </is>
       </c>
       <c r="G124" s="11" t="inlineStr">
@@ -17287,7 +17385,7 @@
       </c>
       <c r="H124" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
@@ -17302,57 +17400,57 @@
       </c>
       <c r="K124" s="12" t="inlineStr">
         <is>
-          <t>SEGURO DE VIDA VINCULADO A UN CRÉDITO HIPOTECARIO. CUANDO EL ACREEDOR ES BENEFICIARIO PREFERENTE, DEBE AGOTAR LA ACCIÓN DERIVADA DEL CONTRATO DE SEGURO ANTES DE EJERCER LA ACCIÓN HIPOTECARIA CONTRA LA SUCESIÓN DEL DEUDOR.</t>
+          <t>FIDEICOMISO EN GARANTÍA DERIVADO DE UN CONVENIO DE MEDIACIÓN. CUANDO SE PRETENDA SU EJECUCIÓN JUDICIAL DEBE EXHIBIRSE EL AVALÚO DEL BIEN INMUEBLE DADO EN GARANTÍA, AL SER UN ELEMENTO DE LA ACCIÓN CONFORME AL ARTÍCULO 1414 BIS DEL CÓDIGO DE COMERCIO.</t>
         </is>
       </c>
       <c r="L124" s="11" t="inlineStr">
         <is>
-          <t>2032537</t>
+          <t>2027244</t>
         </is>
       </c>
       <c r="M124" s="11" t="inlineStr"/>
       <c r="N124" s="11" t="inlineStr">
         <is>
-          <t>viernes 21 de agosto de 2026 10:29 h</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="O124" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P124" s="11" t="inlineStr"/>
       <c r="Q124" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Para ejecutar judicialmente fideicomiso de garantía constituido por convenio de mediación, el actor DEBE exhibir avalúo del bien al promover. Sin avalúo, la acción es improcedente.</t>
         </is>
       </c>
       <c r="R124" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Requisito formal estricto para ejecutar fideicomiso de garantía vía mediación.</t>
         </is>
       </c>
       <c r="S124" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Antes de demandar ejecución hay que conseguir avalúo de perito autorizado.</t>
         </is>
       </c>
       <c r="T124" s="11" t="inlineStr"/>
       <c r="U124" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032537</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
         </is>
       </c>
       <c r="V124" s="11" t="inlineStr">
         <is>
-          <t>Juicio hipotecario · actualización automática</t>
+          <t>fideicomiso garantía · mediación · art. 1414 bis Cco · avalúo</t>
         </is>
       </c>
     </row>
     <row r="125" ht="80" customHeight="1">
       <c r="A125" s="13" t="inlineStr">
         <is>
-          <t>civ-hip-003</t>
+          <t>auto-2032124</t>
         </is>
       </c>
       <c r="B125" s="13" t="n">
@@ -17375,7 +17473,7 @@
       </c>
       <c r="F125" s="13" t="inlineStr">
         <is>
-          <t>Intereses y anatocismo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G125" s="13" t="inlineStr">
@@ -17385,7 +17483,7 @@
       </c>
       <c r="H125" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I125" s="13" t="inlineStr">
@@ -17395,54 +17493,62 @@
       </c>
       <c r="J125" s="13" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K125" s="14" t="inlineStr">
         <is>
-          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
+          <t>CRÉDITOS HIPOTECARIOS OTORGADOS POR LAS INSTITUCIONES FINANCIERAS A SUS PERSONAS TRABAJADORAS. EL ESTUDIO SOBRE LA MODIFICACIÓN DE LAS CLÁUSULAS QUE CONTENGAN UN BENEFICIO OTORGADO DERIVADO DE LA RELACIÓN LABORAL PROCEDE EN ESTA VÍA.</t>
         </is>
       </c>
       <c r="L125" s="13" t="inlineStr">
         <is>
-          <t>200721</t>
+          <t>2032124</t>
         </is>
       </c>
       <c r="M125" s="13" t="inlineStr"/>
-      <c r="N125" s="13" t="inlineStr"/>
-      <c r="O125" s="13" t="inlineStr"/>
+      <c r="N125" s="13" t="inlineStr">
+        <is>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
+        </is>
+      </c>
+      <c r="O125" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P125" s="13" t="inlineStr"/>
       <c r="Q125" s="13" t="inlineStr">
         <is>
-          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R125" s="13" t="inlineStr">
         <is>
-          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S125" s="13" t="inlineStr">
         <is>
-          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T125" s="13" t="inlineStr"/>
       <c r="U125" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032124</t>
         </is>
       </c>
       <c r="V125" s="13" t="inlineStr">
         <is>
-          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
+          <t>Juicio hipotecario · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="126" ht="80" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>civ-hip-004</t>
+          <t>auto-2032537</t>
         </is>
       </c>
       <c r="B126" s="11" t="n">
@@ -17465,7 +17571,7 @@
       </c>
       <c r="F126" s="11" t="inlineStr">
         <is>
-          <t>Apelación en efecto devolutivo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G126" s="11" t="inlineStr">
@@ -17475,7 +17581,7 @@
       </c>
       <c r="H126" s="11" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I126" s="11" t="inlineStr">
@@ -17485,62 +17591,62 @@
       </c>
       <c r="J126" s="11" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K126" s="12" t="inlineStr">
         <is>
-          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
+          <t>SEGURO DE VIDA VINCULADO A UN CRÉDITO HIPOTECARIO. CUANDO EL ACREEDOR ES BENEFICIARIO PREFERENTE, DEBE AGOTAR LA ACCIÓN DERIVADA DEL CONTRATO DE SEGURO ANTES DE EJERCER LA ACCIÓN HIPOTECARIA CONTRA LA SUCESIÓN DEL DEUDOR.</t>
         </is>
       </c>
       <c r="L126" s="11" t="inlineStr">
         <is>
-          <t>162554</t>
+          <t>2032537</t>
         </is>
       </c>
       <c r="M126" s="11" t="inlineStr"/>
       <c r="N126" s="11" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>viernes 21 de agosto de 2026 10:29 h</t>
         </is>
       </c>
       <c r="O126" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P126" s="11" t="inlineStr"/>
       <c r="Q126" s="11" t="inlineStr">
         <is>
-          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R126" s="11" t="inlineStr">
         <is>
-          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S126" s="11" t="inlineStr">
         <is>
-          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T126" s="11" t="inlineStr"/>
       <c r="U126" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032537</t>
         </is>
       </c>
       <c r="V126" s="11" t="inlineStr">
         <is>
-          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
+          <t>Juicio hipotecario · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="127" ht="80" customHeight="1">
       <c r="A127" s="13" t="inlineStr">
         <is>
-          <t>civ-hip-005</t>
+          <t>civ-hip-003</t>
         </is>
       </c>
       <c r="B127" s="13" t="n">
@@ -17563,7 +17669,7 @@
       </c>
       <c r="F127" s="13" t="inlineStr">
         <is>
-          <t>Ejecución limitada al bien hipotecado</t>
+          <t>Intereses y anatocismo</t>
         </is>
       </c>
       <c r="G127" s="13" t="inlineStr">
@@ -17573,7 +17679,7 @@
       </c>
       <c r="H127" s="13" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I127" s="13" t="inlineStr">
@@ -17583,62 +17689,54 @@
       </c>
       <c r="J127" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K127" s="14" t="inlineStr">
         <is>
-          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
+          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
         </is>
       </c>
       <c r="L127" s="13" t="inlineStr">
         <is>
-          <t>180865</t>
+          <t>200721</t>
         </is>
       </c>
       <c r="M127" s="13" t="inlineStr"/>
-      <c r="N127" s="13" t="inlineStr">
-        <is>
-          <t>Novena Época</t>
-        </is>
-      </c>
-      <c r="O127" s="13" t="inlineStr">
-        <is>
-          <t>SJF — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N127" s="13" t="inlineStr"/>
+      <c r="O127" s="13" t="inlineStr"/>
       <c r="P127" s="13" t="inlineStr"/>
       <c r="Q127" s="13" t="inlineStr">
         <is>
-          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
+          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
         </is>
       </c>
       <c r="R127" s="13" t="inlineStr">
         <is>
-          <t>Límite de garantía real del juicio hipotecario.</t>
+          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
         </is>
       </c>
       <c r="S127" s="13" t="inlineStr">
         <is>
-          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
+          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
         </is>
       </c>
       <c r="T127" s="13" t="inlineStr"/>
       <c r="U127" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
         </is>
       </c>
       <c r="V127" s="13" t="inlineStr">
         <is>
-          <t>hipotecario · acción real · ejecución limitada</t>
+          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
         </is>
       </c>
     </row>
     <row r="128" ht="80" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>sen-019</t>
+          <t>civ-hip-004</t>
         </is>
       </c>
       <c r="B128" s="11" t="n">
@@ -17656,22 +17754,22 @@
       </c>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>Notificaciones — domicilio convencional vs. real</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr">
         <is>
-          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
+          <t>Apelación en efecto devolutivo</t>
         </is>
       </c>
       <c r="G128" s="11" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H128" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I128" s="11" t="inlineStr">
@@ -17681,58 +17779,62 @@
       </c>
       <c r="J128" s="11" t="inlineStr">
         <is>
-          <t>Primer Circuito — CDMX</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K128" s="12" t="inlineStr">
         <is>
-          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
+          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
         </is>
       </c>
       <c r="L128" s="11" t="inlineStr">
         <is>
-          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
+          <t>162554</t>
         </is>
       </c>
       <c r="M128" s="11" t="inlineStr"/>
       <c r="N128" s="11" t="inlineStr">
         <is>
-          <t>Línea consolidada</t>
-        </is>
-      </c>
-      <c r="O128" s="11" t="inlineStr"/>
+          <t>Novena Época</t>
+        </is>
+      </c>
+      <c r="O128" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P128" s="11" t="inlineStr"/>
       <c r="Q128" s="11" t="inlineStr">
         <is>
-          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
+          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
         </is>
       </c>
       <c r="R128" s="11" t="inlineStr">
         <is>
-          <t>Defensa nuclear contra emplazamientos ficticios.</t>
+          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
         </is>
       </c>
       <c r="S128" s="11" t="inlineStr">
         <is>
-          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
+          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
         </is>
       </c>
       <c r="T128" s="11" t="inlineStr"/>
       <c r="U128" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
         </is>
       </c>
       <c r="V128" s="11" t="inlineStr">
         <is>
-          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
+          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
         </is>
       </c>
     </row>
     <row r="129" ht="80" customHeight="1">
       <c r="A129" s="13" t="inlineStr">
         <is>
-          <t>fam-com-001</t>
+          <t>civ-hip-005</t>
         </is>
       </c>
       <c r="B129" s="13" t="n">
@@ -17750,12 +17852,12 @@
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>Pensión compensatoria</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F129" s="13" t="inlineStr">
         <is>
-          <t>Inversión de carga probatoria</t>
+          <t>Ejecución limitada al bien hipotecado</t>
         </is>
       </c>
       <c r="G129" s="13" t="inlineStr">
@@ -17765,7 +17867,7 @@
       </c>
       <c r="H129" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I129" s="13" t="inlineStr">
@@ -17780,18 +17882,18 @@
       </c>
       <c r="K129" s="14" t="inlineStr">
         <is>
-          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
+          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
         </is>
       </c>
       <c r="L129" s="13" t="inlineStr">
         <is>
-          <t>2031387</t>
+          <t>180865</t>
         </is>
       </c>
       <c r="M129" s="13" t="inlineStr"/>
       <c r="N129" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="O129" s="13" t="inlineStr">
@@ -17802,35 +17904,35 @@
       <c r="P129" s="13" t="inlineStr"/>
       <c r="Q129" s="13" t="inlineStr">
         <is>
-          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
+          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
         </is>
       </c>
       <c r="R129" s="13" t="inlineStr">
         <is>
-          <t>Garantía procesal en juicios de compensación / pensión.</t>
+          <t>Límite de garantía real del juicio hipotecario.</t>
         </is>
       </c>
       <c r="S129" s="13" t="inlineStr">
         <is>
-          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
+          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
         </is>
       </c>
       <c r="T129" s="13" t="inlineStr"/>
       <c r="U129" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
         </is>
       </c>
       <c r="V129" s="13" t="inlineStr">
         <is>
-          <t>pensión compensatoria · carga probatoria · 12a Época</t>
+          <t>hipotecario · acción real · ejecución limitada</t>
         </is>
       </c>
     </row>
     <row r="130" ht="80" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>auto-2032319</t>
+          <t>sen-019</t>
         </is>
       </c>
       <c r="B130" s="11" t="n">
@@ -17848,22 +17950,22 @@
       </c>
       <c r="E130" s="11" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva</t>
+          <t>Notificaciones — domicilio convencional vs. real</t>
         </is>
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
         </is>
       </c>
       <c r="G130" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H130" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I130" s="11" t="inlineStr">
@@ -17873,62 +17975,58 @@
       </c>
       <c r="J130" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Primer Circuito — CDMX</t>
         </is>
       </c>
       <c r="K130" s="12" t="inlineStr">
         <is>
-          <t>CONTRATO DE ENAJENACIÓN DE DERECHOS AGRARIOS. CUANDO SE DECLARA SU NULIDAD POR VIOLACIÓN AL DERECHO DEL TANTO, DEBEN DEJARSE A SALVO LOS DERECHOS DE LA PERSONA DEMANDADA PARA EJERCER, EN SU CASO, LA ACCIÓN DE USUCAPIÓN.</t>
+          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
         </is>
       </c>
       <c r="L130" s="11" t="inlineStr">
         <is>
-          <t>2032319</t>
+          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
         </is>
       </c>
       <c r="M130" s="11" t="inlineStr"/>
       <c r="N130" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
-        </is>
-      </c>
-      <c r="O130" s="11" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
-        </is>
-      </c>
+          <t>Línea consolidada</t>
+        </is>
+      </c>
+      <c r="O130" s="11" t="inlineStr"/>
       <c r="P130" s="11" t="inlineStr"/>
       <c r="Q130" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
         </is>
       </c>
       <c r="R130" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Defensa nuclear contra emplazamientos ficticios.</t>
         </is>
       </c>
       <c r="S130" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
         </is>
       </c>
       <c r="T130" s="11" t="inlineStr"/>
       <c r="U130" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032319</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
         </is>
       </c>
       <c r="V130" s="11" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva · actualización automática</t>
+          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
         </is>
       </c>
     </row>
     <row r="131" ht="80" customHeight="1">
       <c r="A131" s="13" t="inlineStr">
         <is>
-          <t>civ-usu-003</t>
+          <t>fam-com-001</t>
         </is>
       </c>
       <c r="B131" s="13" t="n">
@@ -17946,22 +18044,22 @@
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva</t>
+          <t>Pensión compensatoria</t>
         </is>
       </c>
       <c r="F131" s="13" t="inlineStr">
         <is>
-          <t>Pericial topográfica / agrimensura</t>
+          <t>Inversión de carga probatoria</t>
         </is>
       </c>
       <c r="G131" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H131" s="13" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I131" s="13" t="inlineStr">
@@ -17971,58 +18069,62 @@
       </c>
       <c r="J131" s="13" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K131" s="14" t="inlineStr">
         <is>
-          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
+          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
         </is>
       </c>
       <c r="L131" s="13" t="inlineStr">
         <is>
-          <t>190377</t>
+          <t>2031387</t>
         </is>
       </c>
       <c r="M131" s="13" t="inlineStr"/>
-      <c r="N131" s="13" t="inlineStr"/>
+      <c r="N131" s="13" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
       <c r="O131" s="13" t="inlineStr">
         <is>
-          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P131" s="13" t="inlineStr"/>
       <c r="Q131" s="13" t="inlineStr">
         <is>
-          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
+          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
         </is>
       </c>
       <c r="R131" s="13" t="inlineStr">
         <is>
-          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
+          <t>Garantía procesal en juicios de compensación / pensión.</t>
         </is>
       </c>
       <c r="S131" s="13" t="inlineStr">
         <is>
-          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
+          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
         </is>
       </c>
       <c r="T131" s="13" t="inlineStr"/>
       <c r="U131" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
         </is>
       </c>
       <c r="V131" s="13" t="inlineStr">
         <is>
-          <t>pericial · topografía · identidad del bien</t>
+          <t>pensión compensatoria · carga probatoria · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="132" ht="80" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>civ-usu-005</t>
+          <t>auto-2032319</t>
         </is>
       </c>
       <c r="B132" s="11" t="n">
@@ -18045,17 +18147,17 @@
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>Posesión derivada vs. originaria</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G132" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H132" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I132" s="11" t="inlineStr">
@@ -18070,49 +18172,57 @@
       </c>
       <c r="K132" s="12" t="inlineStr">
         <is>
-          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
+          <t>CONTRATO DE ENAJENACIÓN DE DERECHOS AGRARIOS. CUANDO SE DECLARA SU NULIDAD POR VIOLACIÓN AL DERECHO DEL TANTO, DEBEN DEJARSE A SALVO LOS DERECHOS DE LA PERSONA DEMANDADA PARA EJERCER, EN SU CASO, LA ACCIÓN DE USUCAPIÓN.</t>
         </is>
       </c>
       <c r="L132" s="11" t="inlineStr">
         <is>
-          <t>2030499</t>
+          <t>2032319</t>
         </is>
       </c>
       <c r="M132" s="11" t="inlineStr"/>
-      <c r="N132" s="11" t="inlineStr"/>
-      <c r="O132" s="11" t="inlineStr"/>
+      <c r="N132" s="11" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
+      <c r="O132" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P132" s="11" t="inlineStr"/>
       <c r="Q132" s="11" t="inlineStr">
         <is>
-          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R132" s="11" t="inlineStr">
         <is>
-          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S132" s="11" t="inlineStr">
         <is>
-          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T132" s="11" t="inlineStr"/>
       <c r="U132" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030499</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032319</t>
         </is>
       </c>
       <c r="V132" s="11" t="inlineStr">
         <is>
-          <t>posesión derivada · concepto de propietario · interversión</t>
+          <t>Usucapión / Prescripción positiva · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="133" ht="80" customHeight="1">
       <c r="A133" s="13" t="inlineStr">
         <is>
-          <t>con-asa-001</t>
+          <t>civ-usu-003</t>
         </is>
       </c>
       <c r="B133" s="13" t="n">
@@ -18125,27 +18235,27 @@
       </c>
       <c r="D133" s="13" t="inlineStr">
         <is>
-          <t>Civil — Condominio</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>Régimen de propiedad en condominio</t>
+          <t>Usucapión / Prescripción positiva</t>
         </is>
       </c>
       <c r="F133" s="13" t="inlineStr">
         <is>
-          <t>Asambleas — convocatoria y validez</t>
+          <t>Pericial topográfica / agrimensura</t>
         </is>
       </c>
       <c r="G133" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H133" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I133" s="13" t="inlineStr">
@@ -18155,54 +18265,58 @@
       </c>
       <c r="J133" s="13" t="inlineStr">
         <is>
-          <t>Federal — interpreta LPCI CDMX</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K133" s="14" t="inlineStr">
         <is>
-          <t>ASAMBLEAS CONDOMINALES. LA INDEBIDA CONVOCATORIA AFECTA LA VALIDEZ DE LOS ACUERDOS Y PERMITE SU IMPUGNACIÓN.</t>
+          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
         </is>
       </c>
       <c r="L133" s="13" t="inlineStr">
         <is>
-          <t>Art. 32 LPCI CDMX</t>
+          <t>190377</t>
         </is>
       </c>
       <c r="M133" s="13" t="inlineStr"/>
       <c r="N133" s="13" t="inlineStr"/>
-      <c r="O133" s="13" t="inlineStr"/>
+      <c r="O133" s="13" t="inlineStr">
+        <is>
+          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
+        </is>
+      </c>
       <c r="P133" s="13" t="inlineStr"/>
       <c r="Q133" s="13" t="inlineStr">
         <is>
-          <t>La convocatoria debe respetar plazo, forma y orden del día (art. 32 LPCI CDMX). Su incumplimiento es causal de nulidad de los acuerdos adoptados, salvo ratificación expresa en asamblea posterior debidamente convocada.</t>
+          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
         </is>
       </c>
       <c r="R133" s="13" t="inlineStr">
         <is>
-          <t>Defensa frecuente de minorías condominales.</t>
+          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
         </is>
       </c>
       <c r="S133" s="13" t="inlineStr">
         <is>
-          <t>Conserva pruebas de cómo se realizó la convocatoria (carteles, mensajes, fotos). Plazo de impugnación es corto (60 días naturales en CDMX desde celebración o conocimiento).</t>
+          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
         </is>
       </c>
       <c r="T133" s="13" t="inlineStr"/>
       <c r="U133" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028919</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
         </is>
       </c>
       <c r="V133" s="13" t="inlineStr">
         <is>
-          <t>asamblea · convocatoria · nulidad · LPCI CDMX</t>
+          <t>pericial · topografía · identidad del bien</t>
         </is>
       </c>
     </row>
     <row r="134" ht="80" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>amp-cui-001</t>
+          <t>civ-usu-005</t>
         </is>
       </c>
       <c r="B134" s="11" t="n">
@@ -18215,27 +18329,27 @@
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>Derecho humano al cuidado</t>
+          <t>Usucapión / Prescripción positiva</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
-          <t>Reconocimiento e interés legítimo</t>
+          <t>Posesión derivada vs. originaria</t>
         </is>
       </c>
       <c r="G134" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H134" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I134" s="11" t="inlineStr">
@@ -18250,57 +18364,49 @@
       </c>
       <c r="K134" s="12" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO AL CUIDADO. IMPONE OBLIGACIONES DE CUYO CUMPLIMIENTO DEPENDE DIRECTAMENTE EL BIENESTAR DE LAS PERSONAS E INDIRECTAMENTE, POR INTERDEPENDENCIA, EL EJERCICIO EFECTIVO DE OTROS DERECHOS HUMANOS.</t>
+          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
         </is>
       </c>
       <c r="L134" s="11" t="inlineStr">
         <is>
-          <t>2032085</t>
+          <t>2030499</t>
         </is>
       </c>
       <c r="M134" s="11" t="inlineStr"/>
-      <c r="N134" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O134" s="11" t="inlineStr">
-        <is>
-          <t>SJF 12a Época — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N134" s="11" t="inlineStr"/>
+      <c r="O134" s="11" t="inlineStr"/>
       <c r="P134" s="11" t="inlineStr"/>
       <c r="Q134" s="11" t="inlineStr">
         <is>
-          <t>El cuidado se reconoce como derecho humano autónomo. El Estado tiene obligación de garantizarlo mediante políticas públicas, infraestructura social y reconocimiento del trabajo de cuidado no remunerado.</t>
+          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
         </is>
       </c>
       <c r="R134" s="11" t="inlineStr">
         <is>
-          <t>Pieza inaugural de un nuevo derecho humano en México.</t>
+          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
         </is>
       </c>
       <c r="S134" s="11" t="inlineStr">
         <is>
-          <t>Marco para litigios sobre obligaciones del Estado en guarderías, cuidado de personas mayores, discapacidad y omisiones legislativas absolutas.</t>
+          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
         </is>
       </c>
       <c r="T134" s="11" t="inlineStr"/>
       <c r="U134" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032085</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030499</t>
         </is>
       </c>
       <c r="V134" s="11" t="inlineStr">
         <is>
-          <t>derecho al cuidado · 12a Época · DDHH · cuidadoras</t>
+          <t>posesión derivada · concepto de propietario · interversión</t>
         </is>
       </c>
     </row>
     <row r="135" ht="80" customHeight="1">
       <c r="A135" s="13" t="inlineStr">
         <is>
-          <t>amp-cui-002</t>
+          <t>con-asa-001</t>
         </is>
       </c>
       <c r="B135" s="13" t="n">
@@ -18313,17 +18419,17 @@
       </c>
       <c r="D135" s="13" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil — Condominio</t>
         </is>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>Derecho humano al cuidado</t>
+          <t>Régimen de propiedad en condominio</t>
         </is>
       </c>
       <c r="F135" s="13" t="inlineStr">
         <is>
-          <t>Interés legítimo para combatir omisiones legislativas</t>
+          <t>Asambleas — convocatoria y validez</t>
         </is>
       </c>
       <c r="G135" s="13" t="inlineStr">
@@ -18333,7 +18439,7 @@
       </c>
       <c r="H135" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I135" s="13" t="inlineStr">
@@ -18343,62 +18449,54 @@
       </c>
       <c r="J135" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — interpreta LPCI CDMX</t>
         </is>
       </c>
       <c r="K135" s="14" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO AL CUIDADO. LAS MUJERES QUE REALIZAN CUIDADOS SIMPLES O COTIDIANOS NO REMUNERADOS TIENEN INTERÉS LEGÍTIMO PARA RECLAMAR OMISIONES LEGISLATIVAS ABSOLUTAS QUE IMPIDAN SU PLENO EJERCICIO.</t>
+          <t>ASAMBLEAS CONDOMINALES. LA INDEBIDA CONVOCATORIA AFECTA LA VALIDEZ DE LOS ACUERDOS Y PERMITE SU IMPUGNACIÓN.</t>
         </is>
       </c>
       <c r="L135" s="13" t="inlineStr">
         <is>
-          <t>2032086</t>
+          <t>Art. 32 LPCI CDMX</t>
         </is>
       </c>
       <c r="M135" s="13" t="inlineStr"/>
-      <c r="N135" s="13" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="O135" s="13" t="inlineStr">
-        <is>
-          <t>SJF 12a Época — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N135" s="13" t="inlineStr"/>
+      <c r="O135" s="13" t="inlineStr"/>
       <c r="P135" s="13" t="inlineStr"/>
       <c r="Q135" s="13" t="inlineStr">
         <is>
-          <t>Las mujeres que realizan trabajo de cuidados no remunerados tienen interés legítimo, sin necesidad de afectación individualizada estricta, para promover amparo contra omisiones legislativas absolutas en la materia.</t>
+          <t>La convocatoria debe respetar plazo, forma y orden del día (art. 32 LPCI CDMX). Su incumplimiento es causal de nulidad de los acuerdos adoptados, salvo ratificación expresa en asamblea posterior debidamente convocada.</t>
         </is>
       </c>
       <c r="R135" s="13" t="inlineStr">
         <is>
-          <t>Abre vía de amparo colectivo a millones de cuidadoras.</t>
+          <t>Defensa frecuente de minorías condominales.</t>
         </is>
       </c>
       <c r="S135" s="13" t="inlineStr">
         <is>
-          <t>Estrategia colectiva: amparos contra ausencia de legislación de cuidados. Beneficia particularmente a mujeres de bajos ingresos que sostienen familia.</t>
+          <t>Conserva pruebas de cómo se realizó la convocatoria (carteles, mensajes, fotos). Plazo de impugnación es corto (60 días naturales en CDMX desde celebración o conocimiento).</t>
         </is>
       </c>
       <c r="T135" s="13" t="inlineStr"/>
       <c r="U135" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032086</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028919</t>
         </is>
       </c>
       <c r="V135" s="13" t="inlineStr">
         <is>
-          <t>cuidado · interés legítimo · omisión legislativa · perspectiva género</t>
+          <t>asamblea · convocatoria · nulidad · LPCI CDMX</t>
         </is>
       </c>
     </row>
     <row r="136" ht="80" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>auto-2032312</t>
+          <t>amp-cui-001</t>
         </is>
       </c>
       <c r="B136" s="11" t="n">
@@ -18416,12 +18514,12 @@
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>Medio ambiente sano</t>
+          <t>Derecho humano al cuidado</t>
         </is>
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Reconocimiento e interés legítimo</t>
         </is>
       </c>
       <c r="G136" s="11" t="inlineStr">
@@ -18446,57 +18544,57 @@
       </c>
       <c r="K136" s="12" t="inlineStr">
         <is>
-          <t>ÁREAS VERDES EN LA CIUDAD DE MÉXICO. EL ARTÍCULO 105 DE LA LEY AMBIENTAL LOCAL EN LA PORCIÓN NORMATIVA QUE DISPONE SU FORMA DE COMPENSACIÓN DE LAS AFECTADAS POR LA EJECUCIÓN DE ALGUNA OBRA PÚBLICA, VIOLA EL DERECHO HUMANO A UN MEDIO AMBIENTE SANO, EN SU VERTIENTE DE PROGRESIVIDAD.</t>
+          <t>DERECHO HUMANO AL CUIDADO. IMPONE OBLIGACIONES DE CUYO CUMPLIMIENTO DEPENDE DIRECTAMENTE EL BIENESTAR DE LAS PERSONAS E INDIRECTAMENTE, POR INTERDEPENDENCIA, EL EJERCICIO EFECTIVO DE OTROS DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L136" s="11" t="inlineStr">
         <is>
-          <t>2032312</t>
+          <t>2032085</t>
         </is>
       </c>
       <c r="M136" s="11" t="inlineStr"/>
       <c r="N136" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O136" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P136" s="11" t="inlineStr"/>
       <c r="Q136" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>El cuidado se reconoce como derecho humano autónomo. El Estado tiene obligación de garantizarlo mediante políticas públicas, infraestructura social y reconocimiento del trabajo de cuidado no remunerado.</t>
         </is>
       </c>
       <c r="R136" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Pieza inaugural de un nuevo derecho humano en México.</t>
         </is>
       </c>
       <c r="S136" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Marco para litigios sobre obligaciones del Estado en guarderías, cuidado de personas mayores, discapacidad y omisiones legislativas absolutas.</t>
         </is>
       </c>
       <c r="T136" s="11" t="inlineStr"/>
       <c r="U136" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032312</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032085</t>
         </is>
       </c>
       <c r="V136" s="11" t="inlineStr">
         <is>
-          <t>Medio ambiente sano · actualización automática</t>
+          <t>derecho al cuidado · 12a Época · DDHH · cuidadoras</t>
         </is>
       </c>
     </row>
     <row r="137" ht="80" customHeight="1">
       <c r="A137" s="13" t="inlineStr">
         <is>
-          <t>auto-2032313</t>
+          <t>amp-cui-002</t>
         </is>
       </c>
       <c r="B137" s="13" t="n">
@@ -18514,12 +18612,12 @@
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>Medio ambiente sano</t>
+          <t>Derecho humano al cuidado</t>
         </is>
       </c>
       <c r="F137" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Interés legítimo para combatir omisiones legislativas</t>
         </is>
       </c>
       <c r="G137" s="13" t="inlineStr">
@@ -18544,57 +18642,57 @@
       </c>
       <c r="K137" s="14" t="inlineStr">
         <is>
-          <t>ÁREAS VERDES EN LA CIUDAD DE MÉXICO. EL ARTÍCULO 105 DE LA LEY AMBIENTAL LOCAL EN LA PORCIÓN NORMATIVA QUE ESTABLECE QUE LAS ÁREAS VERDES DEBERÁN INCREMENTAR O CONSERVAR SU EXTENSIÓN, NO VIOLA EL DERECHO HUMANO A UN MEDIO AMBIENTE SANO, EN SU VERTIENTE DE PROGRESIVIDAD.</t>
+          <t>DERECHO HUMANO AL CUIDADO. LAS MUJERES QUE REALIZAN CUIDADOS SIMPLES O COTIDIANOS NO REMUNERADOS TIENEN INTERÉS LEGÍTIMO PARA RECLAMAR OMISIONES LEGISLATIVAS ABSOLUTAS QUE IMPIDAN SU PLENO EJERCICIO.</t>
         </is>
       </c>
       <c r="L137" s="13" t="inlineStr">
         <is>
-          <t>2032313</t>
+          <t>2032086</t>
         </is>
       </c>
       <c r="M137" s="13" t="inlineStr"/>
       <c r="N137" s="13" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O137" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P137" s="13" t="inlineStr"/>
       <c r="Q137" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Las mujeres que realizan trabajo de cuidados no remunerados tienen interés legítimo, sin necesidad de afectación individualizada estricta, para promover amparo contra omisiones legislativas absolutas en la materia.</t>
         </is>
       </c>
       <c r="R137" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Abre vía de amparo colectivo a millones de cuidadoras.</t>
         </is>
       </c>
       <c r="S137" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Estrategia colectiva: amparos contra ausencia de legislación de cuidados. Beneficia particularmente a mujeres de bajos ingresos que sostienen familia.</t>
         </is>
       </c>
       <c r="T137" s="13" t="inlineStr"/>
       <c r="U137" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032313</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032086</t>
         </is>
       </c>
       <c r="V137" s="13" t="inlineStr">
         <is>
-          <t>Medio ambiente sano · actualización automática</t>
+          <t>cuidado · interés legítimo · omisión legislativa · perspectiva género</t>
         </is>
       </c>
     </row>
     <row r="138" ht="80" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>auto-2032154</t>
+          <t>auto-2032312</t>
         </is>
       </c>
       <c r="B138" s="11" t="n">
@@ -18612,7 +18710,7 @@
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género</t>
+          <t>Medio ambiente sano</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr">
@@ -18642,18 +18740,18 @@
       </c>
       <c r="K138" s="12" t="inlineStr">
         <is>
-          <t>COMPENSACIÓN ECONÓMICA. ELEMENTOS MÍNIMOS QUE LA PERSONA JUZGADORA DEBE CONSIDERAR PARA MOTIVAR LA RESOLUCIÓN QUE LA CUANTIFICA, CON PERSPECTIVA DE GÉNERO.</t>
+          <t>ÁREAS VERDES EN LA CIUDAD DE MÉXICO. EL ARTÍCULO 105 DE LA LEY AMBIENTAL LOCAL EN LA PORCIÓN NORMATIVA QUE DISPONE SU FORMA DE COMPENSACIÓN DE LAS AFECTADAS POR LA EJECUCIÓN DE ALGUNA OBRA PÚBLICA, VIOLA EL DERECHO HUMANO A UN MEDIO AMBIENTE SANO, EN SU VERTIENTE DE PROGRESIVIDAD.</t>
         </is>
       </c>
       <c r="L138" s="11" t="inlineStr">
         <is>
-          <t>2032154</t>
+          <t>2032312</t>
         </is>
       </c>
       <c r="M138" s="11" t="inlineStr"/>
       <c r="N138" s="11" t="inlineStr">
         <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
+          <t>viernes 26 de junio de 2026 10:</t>
         </is>
       </c>
       <c r="O138" s="11" t="inlineStr">
@@ -18680,19 +18778,19 @@
       <c r="T138" s="11" t="inlineStr"/>
       <c r="U138" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032154</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032312</t>
         </is>
       </c>
       <c r="V138" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género · actualización automática</t>
+          <t>Medio ambiente sano · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="139" ht="80" customHeight="1">
       <c r="A139" s="13" t="inlineStr">
         <is>
-          <t>auto-2032184</t>
+          <t>auto-2032313</t>
         </is>
       </c>
       <c r="B139" s="13" t="n">
@@ -18710,7 +18808,7 @@
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>Perspectiva de género</t>
+          <t>Medio ambiente sano</t>
         </is>
       </c>
       <c r="F139" s="13" t="inlineStr">
@@ -18740,18 +18838,18 @@
       </c>
       <c r="K139" s="14" t="inlineStr">
         <is>
-          <t>VIOLENCIA FAMILIAR. CUANDO LA VÍCTIMA SEA UNA PERSONA MENOR DE EDAD Y SE ALEGUE ALIENACIÓN O MANIPULACIÓN PARENTAL, EL ÓRGANO JURISDICCIONAL DEBE ORDENAR LA PRÁCTICA DE PRUEBAS PERICIALES PARA VERIFICAR SI SE ACTUALIZA DICHA CONDICIÓN.</t>
+          <t>ÁREAS VERDES EN LA CIUDAD DE MÉXICO. EL ARTÍCULO 105 DE LA LEY AMBIENTAL LOCAL EN LA PORCIÓN NORMATIVA QUE ESTABLECE QUE LAS ÁREAS VERDES DEBERÁN INCREMENTAR O CONSERVAR SU EXTENSIÓN, NO VIOLA EL DERECHO HUMANO A UN MEDIO AMBIENTE SANO, EN SU VERTIENTE DE PROGRESIVIDAD.</t>
         </is>
       </c>
       <c r="L139" s="13" t="inlineStr">
         <is>
-          <t>2032184</t>
+          <t>2032313</t>
         </is>
       </c>
       <c r="M139" s="13" t="inlineStr"/>
       <c r="N139" s="13" t="inlineStr">
         <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O139" s="13" t="inlineStr">
@@ -18778,19 +18876,19 @@
       <c r="T139" s="13" t="inlineStr"/>
       <c r="U139" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032184</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032313</t>
         </is>
       </c>
       <c r="V139" s="13" t="inlineStr">
         <is>
-          <t>Perspectiva de género · actualización automática</t>
+          <t>Medio ambiente sano · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="140" ht="80" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>auto-2032279</t>
+          <t>auto-2032575</t>
         </is>
       </c>
       <c r="B140" s="11" t="n">
@@ -18808,7 +18906,7 @@
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género</t>
+          <t>Medio ambiente sano</t>
         </is>
       </c>
       <c r="F140" s="11" t="inlineStr">
@@ -18838,18 +18936,18 @@
       </c>
       <c r="K140" s="12" t="inlineStr">
         <is>
-          <t>ACTA ADMINISTRATIVA DE INVESTIGACIÓN EN EL JUICIO LABORAL. TIENE VALOR PROBATORIO AUNQUE NO SE RATIFIQUE ANTE LA AUTORIDAD JURISDICCIONAL, CUANDO CONSIGNE EL TESTIMONIO DE NIÑAS, NIÑOS Y ADOLECENTES POR ACTOS DE CONNOTACIÓN SEXUAL REALIZADOS EN SU CONTRA.</t>
+          <t>SUSPENSIÓN DEFINITIVA EN AMPARO INDIRECTO. PARA CONCEDERLA CONTRA LA AFECTACIÓN A ÁREAS NATURALES PROTEGIDAS, EL JUZGADO DE DISTRITO DEBE ATENDER A UN ESTÁNDAR DE PROTECCIÓN REFORZADA APLICANDO LOS PRINCIPIOS AMBIENTALES DE PREVENCIÓN Y DE PRECAUCIÓN.</t>
         </is>
       </c>
       <c r="L140" s="11" t="inlineStr">
         <is>
-          <t>2032279</t>
+          <t>2032575</t>
         </is>
       </c>
       <c r="M140" s="11" t="inlineStr"/>
       <c r="N140" s="11" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>viernes 28 de agosto de 2026 10:36 h</t>
         </is>
       </c>
       <c r="O140" s="11" t="inlineStr">
@@ -18876,19 +18974,19 @@
       <c r="T140" s="11" t="inlineStr"/>
       <c r="U140" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032279</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032575</t>
         </is>
       </c>
       <c r="V140" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género · actualización automática</t>
+          <t>Medio ambiente sano · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="141" ht="80" customHeight="1">
       <c r="A141" s="13" t="inlineStr">
         <is>
-          <t>auto-2032302</t>
+          <t>auto-2032154</t>
         </is>
       </c>
       <c r="B141" s="13" t="n">
@@ -18936,18 +19034,18 @@
       </c>
       <c r="K141" s="14" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LAS AUTORIDADES INVOLUCRADAS EN DETERMINAR EL MONTO INDEMNIZATORIO POR ACTIVIDAD ADMINISTRATIVA IRREGULAR DEBEN ANALIZAR CÓMO LA PERSPECTIVA DE GÉNERO PUEDE CAMBIAR LA MANERA DE PERCIBIR Y VALORAR LAS CIRCUNSTANCIAS DEL CASO.</t>
+          <t>COMPENSACIÓN ECONÓMICA. ELEMENTOS MÍNIMOS QUE LA PERSONA JUZGADORA DEBE CONSIDERAR PARA MOTIVAR LA RESOLUCIÓN QUE LA CUANTIFICA, CON PERSPECTIVA DE GÉNERO.</t>
         </is>
       </c>
       <c r="L141" s="13" t="inlineStr">
         <is>
-          <t>2032302</t>
+          <t>2032154</t>
         </is>
       </c>
       <c r="M141" s="13" t="inlineStr"/>
       <c r="N141" s="13" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O141" s="13" t="inlineStr">
@@ -18974,7 +19072,7 @@
       <c r="T141" s="13" t="inlineStr"/>
       <c r="U141" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032302</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032154</t>
         </is>
       </c>
       <c r="V141" s="13" t="inlineStr">
@@ -18986,7 +19084,7 @@
     <row r="142" ht="80" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>auto-2032309</t>
+          <t>auto-2032184</t>
         </is>
       </c>
       <c r="B142" s="11" t="n">
@@ -19034,18 +19132,18 @@
       </c>
       <c r="K142" s="12" t="inlineStr">
         <is>
-          <t>ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA INSTITUCIÓN EDUCATIVA SE ENCUENTRA VINCULADA A CUMPLIR CON LA GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN.</t>
+          <t>VIOLENCIA FAMILIAR. CUANDO LA VÍCTIMA SEA UNA PERSONA MENOR DE EDAD Y SE ALEGUE ALIENACIÓN O MANIPULACIÓN PARENTAL, EL ÓRGANO JURISDICCIONAL DEBE ORDENAR LA PRÁCTICA DE PRUEBAS PERICIALES PARA VERIFICAR SI SE ACTUALIZA DICHA CONDICIÓN.</t>
         </is>
       </c>
       <c r="L142" s="11" t="inlineStr">
         <is>
-          <t>2032309</t>
+          <t>2032184</t>
         </is>
       </c>
       <c r="M142" s="11" t="inlineStr"/>
       <c r="N142" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O142" s="11" t="inlineStr">
@@ -19072,7 +19170,7 @@
       <c r="T142" s="11" t="inlineStr"/>
       <c r="U142" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032309</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032184</t>
         </is>
       </c>
       <c r="V142" s="11" t="inlineStr">
@@ -19084,7 +19182,7 @@
     <row r="143" ht="80" customHeight="1">
       <c r="A143" s="13" t="inlineStr">
         <is>
-          <t>auto-2032325</t>
+          <t>auto-2032279</t>
         </is>
       </c>
       <c r="B143" s="13" t="n">
@@ -19132,18 +19230,18 @@
       </c>
       <c r="K143" s="14" t="inlineStr">
         <is>
-          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. ESTÁNDAR PROBATORIO PARA DETERMINAR LA LEGALIDAD DE LA RESCISIÓN DE LA RELACIÓN LABORAL.</t>
+          <t>ACTA ADMINISTRATIVA DE INVESTIGACIÓN EN EL JUICIO LABORAL. TIENE VALOR PROBATORIO AUNQUE NO SE RATIFIQUE ANTE LA AUTORIDAD JURISDICCIONAL, CUANDO CONSIGNE EL TESTIMONIO DE NIÑAS, NIÑOS Y ADOLECENTES POR ACTOS DE CONNOTACIÓN SEXUAL REALIZADOS EN SU CONTRA.</t>
         </is>
       </c>
       <c r="L143" s="13" t="inlineStr">
         <is>
-          <t>2032325</t>
+          <t>2032279</t>
         </is>
       </c>
       <c r="M143" s="13" t="inlineStr"/>
       <c r="N143" s="13" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O143" s="13" t="inlineStr">
@@ -19170,7 +19268,7 @@
       <c r="T143" s="13" t="inlineStr"/>
       <c r="U143" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032325</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032279</t>
         </is>
       </c>
       <c r="V143" s="13" t="inlineStr">
@@ -19182,7 +19280,7 @@
     <row r="144" ht="80" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>auto-2032326</t>
+          <t>auto-2032302</t>
         </is>
       </c>
       <c r="B144" s="11" t="n">
@@ -19230,18 +19328,18 @@
       </c>
       <c r="K144" s="12" t="inlineStr">
         <is>
-          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA AUTORIDAD JURISDICCIONAL DEBE ARMONIZAR EL PRINCIPIO DE PRESUNCIÓN DE INOCENCIA CON LA PERSPECTIVA DE GÉNERO.</t>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LAS AUTORIDADES INVOLUCRADAS EN DETERMINAR EL MONTO INDEMNIZATORIO POR ACTIVIDAD ADMINISTRATIVA IRREGULAR DEBEN ANALIZAR CÓMO LA PERSPECTIVA DE GÉNERO PUEDE CAMBIAR LA MANERA DE PERCIBIR Y VALORAR LAS CIRCUNSTANCIAS DEL CASO.</t>
         </is>
       </c>
       <c r="L144" s="11" t="inlineStr">
         <is>
-          <t>2032326</t>
+          <t>2032302</t>
         </is>
       </c>
       <c r="M144" s="11" t="inlineStr"/>
       <c r="N144" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O144" s="11" t="inlineStr">
@@ -19268,7 +19366,7 @@
       <c r="T144" s="11" t="inlineStr"/>
       <c r="U144" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032326</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032302</t>
         </is>
       </c>
       <c r="V144" s="11" t="inlineStr">
@@ -19280,7 +19378,7 @@
     <row r="145" ht="80" customHeight="1">
       <c r="A145" s="13" t="inlineStr">
         <is>
-          <t>auto-2032327</t>
+          <t>auto-2032309</t>
         </is>
       </c>
       <c r="B145" s="13" t="n">
@@ -19328,12 +19426,12 @@
       </c>
       <c r="K145" s="14" t="inlineStr">
         <is>
-          <t>ESTÁNDAR DE LA PERSONA OBSERVADORA RAZONABLE. ASPECTOS QUE DEBE PONDERAR LA AUTORIDAD LABORAL PARA DETERMINAR LA EVENTUAL GRAVEDAD DE LA FALTA DE PROBIDAD ATRIBUIDA A LA PERSONA TRABAJADORA EN CASOS DE ACOSO U HOSTIGAMIENTO SEXUAL EN INSTITUCIONES EDUCATIVAS.</t>
+          <t>ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA INSTITUCIÓN EDUCATIVA SE ENCUENTRA VINCULADA A CUMPLIR CON LA GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN.</t>
         </is>
       </c>
       <c r="L145" s="13" t="inlineStr">
         <is>
-          <t>2032327</t>
+          <t>2032309</t>
         </is>
       </c>
       <c r="M145" s="13" t="inlineStr"/>
@@ -19366,7 +19464,7 @@
       <c r="T145" s="13" t="inlineStr"/>
       <c r="U145" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032327</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032309</t>
         </is>
       </c>
       <c r="V145" s="13" t="inlineStr">
@@ -19378,7 +19476,7 @@
     <row r="146" ht="80" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>auto-2032338</t>
+          <t>auto-2032325</t>
         </is>
       </c>
       <c r="B146" s="11" t="n">
@@ -19426,12 +19524,12 @@
       </c>
       <c r="K146" s="12" t="inlineStr">
         <is>
-          <t>PERSPECTIVA DE GÉNERO. DEBE OBSERVARSE EN EL TRÁMITE Y RESOLUCIÓN DEL JUICIO LABORAL COMO GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN DE ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES.</t>
+          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. ESTÁNDAR PROBATORIO PARA DETERMINAR LA LEGALIDAD DE LA RESCISIÓN DE LA RELACIÓN LABORAL.</t>
         </is>
       </c>
       <c r="L146" s="11" t="inlineStr">
         <is>
-          <t>2032338</t>
+          <t>2032325</t>
         </is>
       </c>
       <c r="M146" s="11" t="inlineStr"/>
@@ -19464,7 +19562,7 @@
       <c r="T146" s="11" t="inlineStr"/>
       <c r="U146" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032338</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032325</t>
         </is>
       </c>
       <c r="V146" s="11" t="inlineStr">
@@ -19476,7 +19574,7 @@
     <row r="147" ht="80" customHeight="1">
       <c r="A147" s="13" t="inlineStr">
         <is>
-          <t>auto-2032340</t>
+          <t>auto-2032326</t>
         </is>
       </c>
       <c r="B147" s="13" t="n">
@@ -19524,12 +19622,12 @@
       </c>
       <c r="K147" s="14" t="inlineStr">
         <is>
-          <t>PERSPECTIVA DE PERSONA ADULTA MAYOR. SU APLICACIÓN EXIGE IDENTIFICAR LAS CONDICIONES CONCRETAS DE VULNERABILIDAD QUE PUEDAN GENERAR UNA DESVENTAJA EN EL EJERCICIO DE SUS DERECHOS.</t>
+          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA AUTORIDAD JURISDICCIONAL DEBE ARMONIZAR EL PRINCIPIO DE PRESUNCIÓN DE INOCENCIA CON LA PERSPECTIVA DE GÉNERO.</t>
         </is>
       </c>
       <c r="L147" s="13" t="inlineStr">
         <is>
-          <t>2032340</t>
+          <t>2032326</t>
         </is>
       </c>
       <c r="M147" s="13" t="inlineStr"/>
@@ -19562,7 +19660,7 @@
       <c r="T147" s="13" t="inlineStr"/>
       <c r="U147" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032340</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032326</t>
         </is>
       </c>
       <c r="V147" s="13" t="inlineStr">
@@ -19574,7 +19672,7 @@
     <row r="148" ht="80" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>auto-2032347</t>
+          <t>auto-2032327</t>
         </is>
       </c>
       <c r="B148" s="11" t="n">
@@ -19622,12 +19720,12 @@
       </c>
       <c r="K148" s="12" t="inlineStr">
         <is>
-          <t>PRUEBA TESTIMONIAL EN EL PROCEDIMIENTO LABORAL. LA DECLARACIÓN RENDIDA POR PERSONAS DOCENTES GOZA DE RELEVANCIA PROBATORIA EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS.</t>
+          <t>ESTÁNDAR DE LA PERSONA OBSERVADORA RAZONABLE. ASPECTOS QUE DEBE PONDERAR LA AUTORIDAD LABORAL PARA DETERMINAR LA EVENTUAL GRAVEDAD DE LA FALTA DE PROBIDAD ATRIBUIDA A LA PERSONA TRABAJADORA EN CASOS DE ACOSO U HOSTIGAMIENTO SEXUAL EN INSTITUCIONES EDUCATIVAS.</t>
         </is>
       </c>
       <c r="L148" s="11" t="inlineStr">
         <is>
-          <t>2032347</t>
+          <t>2032327</t>
         </is>
       </c>
       <c r="M148" s="11" t="inlineStr"/>
@@ -19660,7 +19758,7 @@
       <c r="T148" s="11" t="inlineStr"/>
       <c r="U148" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032347</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032327</t>
         </is>
       </c>
       <c r="V148" s="11" t="inlineStr">
@@ -19672,7 +19770,7 @@
     <row r="149" ht="80" customHeight="1">
       <c r="A149" s="13" t="inlineStr">
         <is>
-          <t>auto-2032376</t>
+          <t>auto-2032338</t>
         </is>
       </c>
       <c r="B149" s="13" t="n">
@@ -19720,18 +19818,18 @@
       </c>
       <c r="K149" s="14" t="inlineStr">
         <is>
-          <t>DAÑO MORAL RECLAMADO A LAS COMPAÑÍAS ASEGURADORAS. PUEDE GENERARSE ANTE ACTOS DISCRIMINATORIOS OCASIONADOS POR EL USO DE LENGUAJE BASADO EN ESTEREOTIPOS O PREJUICIOS POR RAZÓN DE GÉNERO.</t>
+          <t>PERSPECTIVA DE GÉNERO. DEBE OBSERVARSE EN EL TRÁMITE Y RESOLUCIÓN DEL JUICIO LABORAL COMO GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN DE ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES.</t>
         </is>
       </c>
       <c r="L149" s="13" t="inlineStr">
         <is>
-          <t>2032376</t>
+          <t>2032338</t>
         </is>
       </c>
       <c r="M149" s="13" t="inlineStr"/>
       <c r="N149" s="13" t="inlineStr">
         <is>
-          <t>viernes 03 de julio de 2026 10:10 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O149" s="13" t="inlineStr">
@@ -19758,7 +19856,7 @@
       <c r="T149" s="13" t="inlineStr"/>
       <c r="U149" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032376</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032338</t>
         </is>
       </c>
       <c r="V149" s="13" t="inlineStr">
@@ -19770,7 +19868,7 @@
     <row r="150" ht="80" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>amp-gen-001</t>
+          <t>auto-2032340</t>
         </is>
       </c>
       <c r="B150" s="11" t="n">
@@ -19788,12 +19886,12 @@
       </c>
       <c r="E150" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género interseccional</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F150" s="11" t="inlineStr">
         <is>
-          <t>Acceso a la justicia para mujeres cuidadoras</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr">
@@ -19818,57 +19916,57 @@
       </c>
       <c r="K150" s="12" t="inlineStr">
         <is>
-          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
+          <t>PERSPECTIVA DE PERSONA ADULTA MAYOR. SU APLICACIÓN EXIGE IDENTIFICAR LAS CONDICIONES CONCRETAS DE VULNERABILIDAD QUE PUEDAN GENERAR UNA DESVENTAJA EN EL EJERCICIO DE SUS DERECHOS.</t>
         </is>
       </c>
       <c r="L150" s="11" t="inlineStr">
         <is>
-          <t>2032067</t>
+          <t>2032340</t>
         </is>
       </c>
       <c r="M150" s="11" t="inlineStr"/>
       <c r="N150" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O150" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P150" s="11" t="inlineStr"/>
       <c r="Q150" s="11" t="inlineStr">
         <is>
-          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R150" s="11" t="inlineStr">
         <is>
-          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S150" s="11" t="inlineStr">
         <is>
-          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T150" s="11" t="inlineStr"/>
       <c r="U150" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032340</t>
         </is>
       </c>
       <c r="V150" s="11" t="inlineStr">
         <is>
-          <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="151" ht="80" customHeight="1">
       <c r="A151" s="13" t="inlineStr">
         <is>
-          <t>fis-cfd-002</t>
+          <t>auto-2032347</t>
         </is>
       </c>
       <c r="B151" s="13" t="n">
@@ -19881,22 +19979,22 @@
       </c>
       <c r="D151" s="13" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E151" s="13" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F151" s="13" t="inlineStr">
         <is>
-          <t>69-B — recurso de revocación y buzón tributario</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G151" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H151" s="13" t="inlineStr">
@@ -19916,57 +20014,57 @@
       </c>
       <c r="K151" s="14" t="inlineStr">
         <is>
-          <t>RECURSO DE REVOCACIÓN CONTRA LA RESOLUCIÓN FINAL PREVISTA EN EL ARTÍCULO 69-B, PÁRRAFO CUARTO, DEL CFF. EL PLAZO PARA INTERPONERLO COMIENZA A PARTIR DE SU NOTIFICACIÓN A TRAVÉS DEL BUZÓN TRIBUTARIO.</t>
+          <t>PRUEBA TESTIMONIAL EN EL PROCEDIMIENTO LABORAL. LA DECLARACIÓN RENDIDA POR PERSONAS DOCENTES GOZA DE RELEVANCIA PROBATORIA EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS.</t>
         </is>
       </c>
       <c r="L151" s="13" t="inlineStr">
         <is>
-          <t>2031931</t>
+          <t>2032347</t>
         </is>
       </c>
       <c r="M151" s="13" t="inlineStr"/>
       <c r="N151" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O151" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P151" s="13" t="inlineStr"/>
       <c r="Q151" s="13" t="inlineStr">
         <is>
-          <t>El plazo de 30 días para interponer recurso de revocación contra resolución definitiva del 69-B se computa desde notificación por buzón tributario, no desde publicación en DOF.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R151" s="13" t="inlineStr">
         <is>
-          <t>Define cómputo de plazo para defensa contra inclusión definitiva en EFOS.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S151" s="13" t="inlineStr">
         <is>
-          <t>Hay que monitorear el buzón tributario. Cuenta el plazo desde recepción ahí, no desde publicación DOF. Crítico para no perder defensa.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T151" s="13" t="inlineStr"/>
       <c r="U151" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031931</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032347</t>
         </is>
       </c>
       <c r="V151" s="13" t="inlineStr">
         <is>
-          <t>69-B CFF · recurso revocación · buzón tributario · EFOS</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="152" ht="80" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>fis-cfd-003</t>
+          <t>auto-2032376</t>
         </is>
       </c>
       <c r="B152" s="11" t="n">
@@ -19979,17 +20077,17 @@
       </c>
       <c r="D152" s="11" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F152" s="11" t="inlineStr">
         <is>
-          <t>Materialidad — fundar y motivar</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G152" s="11" t="inlineStr">
@@ -20014,57 +20112,57 @@
       </c>
       <c r="K152" s="12" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES. DEBER DE FUNDAR Y MOTIVAR LA DECISIÓN DE REVERTIR LA CARGA PROBATORIA PARA ACREDITAR SU MATERIALIDAD.</t>
+          <t>DAÑO MORAL RECLAMADO A LAS COMPAÑÍAS ASEGURADORAS. PUEDE GENERARSE ANTE ACTOS DISCRIMINATORIOS OCASIONADOS POR EL USO DE LENGUAJE BASADO EN ESTEREOTIPOS O PREJUICIOS POR RAZÓN DE GÉNERO.</t>
         </is>
       </c>
       <c r="L152" s="11" t="inlineStr">
         <is>
-          <t>2031350</t>
+          <t>2032376</t>
         </is>
       </c>
       <c r="M152" s="11" t="inlineStr"/>
       <c r="N152" s="11" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 03 de julio de 2026 10:10 h</t>
         </is>
       </c>
       <c r="O152" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P152" s="11" t="inlineStr"/>
       <c r="Q152" s="11" t="inlineStr">
         <is>
-          <t>El SAT no puede simplemente requerir materialidad; debe fundar y motivar específicamente las razones por las que presume inexistencia. Sin esa fundamentación, la inversión de carga es inválida.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R152" s="11" t="inlineStr">
         <is>
-          <t>Defensa fuerte para contribuyentes auditados.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S152" s="11" t="inlineStr">
         <is>
-          <t>Si el SAT no detalla por qué presume inexistencia (red flag específico), su requerimiento es nulo. Cuestionar fundamentación es el primer paso del litigio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T152" s="11" t="inlineStr"/>
       <c r="U152" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031350</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032376</t>
         </is>
       </c>
       <c r="V152" s="11" t="inlineStr">
         <is>
-          <t>69-B · materialidad · fundamentación · 12a Época</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="153" ht="80" customHeight="1">
       <c r="A153" s="13" t="inlineStr">
         <is>
-          <t>fis-cfd-004</t>
+          <t>amp-gen-001</t>
         </is>
       </c>
       <c r="B153" s="13" t="n">
@@ -20077,17 +20175,17 @@
       </c>
       <c r="D153" s="13" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Perspectiva de género interseccional</t>
         </is>
       </c>
       <c r="F153" s="13" t="inlineStr">
         <is>
-          <t>Nulidad EFOS — efectos sobre proveedor</t>
+          <t>Acceso a la justicia para mujeres cuidadoras</t>
         </is>
       </c>
       <c r="G153" s="13" t="inlineStr">
@@ -20112,57 +20210,57 @@
       </c>
       <c r="K153" s="14" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES. CONSECUENCIA DE LA NULIDAD DE LA RESOLUCIÓN QUE INCLUYE A UN PROVEEDOR EN EL LISTADO DE EMPRESAS QUE FACTURAN OPERACIONES SIMULADAS (EFOS).</t>
+          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
         </is>
       </c>
       <c r="L153" s="13" t="inlineStr">
         <is>
-          <t>2031349</t>
+          <t>2032067</t>
         </is>
       </c>
       <c r="M153" s="13" t="inlineStr"/>
       <c r="N153" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O153" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P153" s="13" t="inlineStr"/>
       <c r="Q153" s="13" t="inlineStr">
         <is>
-          <t>Cuando se obtiene la nulidad de la resolución que incluyó al proveedor en EFOS definitivas, esa nulidad debe surtir efectos respecto del contribuyente que deducción afectada.</t>
+          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
         </is>
       </c>
       <c r="R153" s="13" t="inlineStr">
         <is>
-          <t>Cadena de protección para contribuyentes que dedujeron con proveedores listados.</t>
+          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
         </is>
       </c>
       <c r="S153" s="13" t="inlineStr">
         <is>
-          <t>Si tu proveedor logra que le quiten de EFOS por sentencia firme, tú puedes invocarlo para recuperar deducciones rechazadas. Defensa colectiva.</t>
+          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
         </is>
       </c>
       <c r="T153" s="13" t="inlineStr"/>
       <c r="U153" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031349</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
         </is>
       </c>
       <c r="V153" s="13" t="inlineStr">
         <is>
-          <t>EFOS · nulidad · deducciones · 12a Época</t>
+          <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="154" ht="80" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>auto-2032254</t>
+          <t>fis-cfd-002</t>
         </is>
       </c>
       <c r="B154" s="11" t="n">
@@ -20175,22 +20273,22 @@
       </c>
       <c r="D154" s="11" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>Despido injustificado</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F154" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>69-B — recurso de revocación y buzón tributario</t>
         </is>
       </c>
       <c r="G154" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H154" s="11" t="inlineStr">
@@ -20210,57 +20308,57 @@
       </c>
       <c r="K154" s="12" t="inlineStr">
         <is>
-          <t>CARGA PROBATORIA EN EL JUICIO LABORAL. CORRESPONDE A LA PATRONAL ACREDITAR EL MONTO Y PAGO DEL SALARIO, AUN CUANDO LA PERSONA TRABAJADORA ALEGUE QUE RECIBE UNA PARTE "FUERA DE NÓMINA".</t>
+          <t>RECURSO DE REVOCACIÓN CONTRA LA RESOLUCIÓN FINAL PREVISTA EN EL ARTÍCULO 69-B, PÁRRAFO CUARTO, DEL CFF. EL PLAZO PARA INTERPONERLO COMIENZA A PARTIR DE SU NOTIFICACIÓN A TRAVÉS DEL BUZÓN TRIBUTARIO.</t>
         </is>
       </c>
       <c r="L154" s="11" t="inlineStr">
         <is>
-          <t>2032254</t>
+          <t>2031931</t>
         </is>
       </c>
       <c r="M154" s="11" t="inlineStr"/>
       <c r="N154" s="11" t="inlineStr">
         <is>
-          <t>viernes 12 de junio de 2026 10:18 h</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O154" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P154" s="11" t="inlineStr"/>
       <c r="Q154" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>El plazo de 30 días para interponer recurso de revocación contra resolución definitiva del 69-B se computa desde notificación por buzón tributario, no desde publicación en DOF.</t>
         </is>
       </c>
       <c r="R154" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Define cómputo de plazo para defensa contra inclusión definitiva en EFOS.</t>
         </is>
       </c>
       <c r="S154" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Hay que monitorear el buzón tributario. Cuenta el plazo desde recepción ahí, no desde publicación DOF. Crítico para no perder defensa.</t>
         </is>
       </c>
       <c r="T154" s="11" t="inlineStr"/>
       <c r="U154" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032254</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031931</t>
         </is>
       </c>
       <c r="V154" s="11" t="inlineStr">
         <is>
-          <t>Despido injustificado · actualización automática</t>
+          <t>69-B CFF · recurso revocación · buzón tributario · EFOS</t>
         </is>
       </c>
     </row>
     <row r="155" ht="80" customHeight="1">
       <c r="A155" s="13" t="inlineStr">
         <is>
-          <t>lab-des-002</t>
+          <t>fis-cfd-003</t>
         </is>
       </c>
       <c r="B155" s="13" t="n">
@@ -20273,17 +20371,17 @@
       </c>
       <c r="D155" s="13" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E155" s="13" t="inlineStr">
         <is>
-          <t>Despido injustificado</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F155" s="13" t="inlineStr">
         <is>
-          <t>Carga patrón cuando alega rescisión justificada posterior</t>
+          <t>Materialidad — fundar y motivar</t>
         </is>
       </c>
       <c r="G155" s="13" t="inlineStr">
@@ -20293,7 +20391,7 @@
       </c>
       <c r="H155" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I155" s="13" t="inlineStr">
@@ -20308,18 +20406,18 @@
       </c>
       <c r="K155" s="14" t="inlineStr">
         <is>
-          <t>RELACIÓN LABORAL. CUANDO LA PERSONA TRABAJADORA MANIFIESTA QUE FUE DESPEDIDA INJUSTIFICADAMENTE EN CIERTA FECHA Y EL PATRÓN ARGUMENTA QUE AQUÉLLA SUBSISTIÓ Y QUE POSTERIORMENTE LA RESCINDIÓ DE FORMA JUSTIFICADA, LE CORRESPONDE PROBAR AMBOS HECHOS.</t>
+          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES. DEBER DE FUNDAR Y MOTIVAR LA DECISIÓN DE REVERTIR LA CARGA PROBATORIA PARA ACREDITAR SU MATERIALIDAD.</t>
         </is>
       </c>
       <c r="L155" s="13" t="inlineStr">
         <is>
-          <t>2029731</t>
+          <t>2031350</t>
         </is>
       </c>
       <c r="M155" s="13" t="inlineStr"/>
       <c r="N155" s="13" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O155" s="13" t="inlineStr">
@@ -20330,35 +20428,35 @@
       <c r="P155" s="13" t="inlineStr"/>
       <c r="Q155" s="13" t="inlineStr">
         <is>
-          <t>Si el patrón niega el despido alegado y agrega rescisión justificada posterior, tiene carga de probar AMBOS: que la relación subsistió tras la fecha del supuesto despido y que la rescisión posterior fue justificada.</t>
+          <t>El SAT no puede simplemente requerir materialidad; debe fundar y motivar específicamente las razones por las que presume inexistencia. Sin esa fundamentación, la inversión de carga es inválida.</t>
         </is>
       </c>
       <c r="R155" s="13" t="inlineStr">
         <is>
-          <t>Carga doble para patrón que cambia versión durante el juicio.</t>
+          <t>Defensa fuerte para contribuyentes auditados.</t>
         </is>
       </c>
       <c r="S155" s="13" t="inlineStr">
         <is>
-          <t>Estrategia trabajadora: forzar al patrón a esa narrativa, queda con carga reforzada.</t>
+          <t>Si el SAT no detalla por qué presume inexistencia (red flag específico), su requerimiento es nulo. Cuestionar fundamentación es el primer paso del litigio.</t>
         </is>
       </c>
       <c r="T155" s="13" t="inlineStr"/>
       <c r="U155" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029731</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031350</t>
         </is>
       </c>
       <c r="V155" s="13" t="inlineStr">
         <is>
-          <t>despido · rescisión · carga probatoria patrón</t>
+          <t>69-B · materialidad · fundamentación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="156" ht="80" customHeight="1">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>lab-ren-001</t>
+          <t>fis-cfd-004</t>
         </is>
       </c>
       <c r="B156" s="11" t="n">
@@ -20371,17 +20469,17 @@
       </c>
       <c r="D156" s="11" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
         <is>
-          <t>Renuncia laboral</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F156" s="11" t="inlineStr">
         <is>
-          <t>Hora de terminación — carga del patrón</t>
+          <t>Nulidad EFOS — efectos sobre proveedor</t>
         </is>
       </c>
       <c r="G156" s="11" t="inlineStr">
@@ -20391,7 +20489,7 @@
       </c>
       <c r="H156" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I156" s="11" t="inlineStr">
@@ -20406,18 +20504,18 @@
       </c>
       <c r="K156" s="12" t="inlineStr">
         <is>
-          <t>RENUNCIA. CORRESPONDE A LA PARTE DEMANDADA PERFECCIONARLA CON ALGÚN MEDIO DE PRUEBA, CUANDO EXISTA CONTROVERSIA RESPECTO DE LA HORA DE TERMINACIÓN DEL VÍNCULO LABORAL Y ÉSTA NO CONSTE EN EL ESCRITO RELATIVO.</t>
+          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES. CONSECUENCIA DE LA NULIDAD DE LA RESOLUCIÓN QUE INCLUYE A UN PROVEEDOR EN EL LISTADO DE EMPRESAS QUE FACTURAN OPERACIONES SIMULADAS (EFOS).</t>
         </is>
       </c>
       <c r="L156" s="11" t="inlineStr">
         <is>
-          <t>2028640</t>
+          <t>2031349</t>
         </is>
       </c>
       <c r="M156" s="11" t="inlineStr"/>
       <c r="N156" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O156" s="11" t="inlineStr">
@@ -20428,35 +20526,35 @@
       <c r="P156" s="11" t="inlineStr"/>
       <c r="Q156" s="11" t="inlineStr">
         <is>
-          <t>Si el patrón ofrece renuncia sin hora exacta y el trabajador alega despido a cierta hora, el patrón debe acreditar con prueba adicional la hora de la renuncia.</t>
+          <t>Cuando se obtiene la nulidad de la resolución que incluyó al proveedor en EFOS definitivas, esa nulidad debe surtir efectos respecto del contribuyente que deducción afectada.</t>
         </is>
       </c>
       <c r="R156" s="11" t="inlineStr">
         <is>
-          <t>Cuestionamiento a renuncias forzadas con fechas/horas imprecisas.</t>
+          <t>Cadena de protección para contribuyentes que dedujeron con proveedores listados.</t>
         </is>
       </c>
       <c r="S156" s="11" t="inlineStr">
         <is>
-          <t>Trabajador debe declarar hora exacta del despido; patrón tendrá que probar hora distinta.</t>
+          <t>Si tu proveedor logra que le quiten de EFOS por sentencia firme, tú puedes invocarlo para recuperar deducciones rechazadas. Defensa colectiva.</t>
         </is>
       </c>
       <c r="T156" s="11" t="inlineStr"/>
       <c r="U156" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028640</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031349</t>
         </is>
       </c>
       <c r="V156" s="11" t="inlineStr">
         <is>
-          <t>renuncia · hora despido · carga probatoria</t>
+          <t>EFOS · nulidad · deducciones · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="157" ht="80" customHeight="1">
       <c r="A157" s="13" t="inlineStr">
         <is>
-          <t>lab-ren-002</t>
+          <t>auto-2032254</t>
         </is>
       </c>
       <c r="B157" s="13" t="n">
@@ -20474,12 +20572,12 @@
       </c>
       <c r="E157" s="13" t="inlineStr">
         <is>
-          <t>Renuncia laboral</t>
+          <t>Despido injustificado</t>
         </is>
       </c>
       <c r="F157" s="13" t="inlineStr">
         <is>
-          <t>Veracidad — carga reforzada si trabajador iba a jubilarse</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G157" s="13" t="inlineStr">
@@ -20489,7 +20587,7 @@
       </c>
       <c r="H157" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I157" s="13" t="inlineStr">
@@ -20504,57 +20602,57 @@
       </c>
       <c r="K157" s="14" t="inlineStr">
         <is>
-          <t>RENUNCIA. PARA QUE SEA VEROSÍMIL Y, POR ENDE, TENGA EFICACIA DEMOSTRATIVA PLENA, CORRESPONDE AL PATRÓN PROBAR QUE REÚNE LAS CONDICIONES DE CERTEZA Y LOS ELEMENTOS MÍNIMOS QUE REFLEJEN LA VOLUNTAD, AUTONOMÍA Y ESPONTANEIDAD DEL TRABAJADOR, SI ESTÁ PRÓXIMO A JUBILARSE.</t>
+          <t>CARGA PROBATORIA EN EL JUICIO LABORAL. CORRESPONDE A LA PATRONAL ACREDITAR EL MONTO Y PAGO DEL SALARIO, AUN CUANDO LA PERSONA TRABAJADORA ALEGUE QUE RECIBE UNA PARTE "FUERA DE NÓMINA".</t>
         </is>
       </c>
       <c r="L157" s="13" t="inlineStr">
         <is>
-          <t>2027058</t>
+          <t>2032254</t>
         </is>
       </c>
       <c r="M157" s="13" t="inlineStr"/>
       <c r="N157" s="13" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>viernes 12 de junio de 2026 10:18 h</t>
         </is>
       </c>
       <c r="O157" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P157" s="13" t="inlineStr"/>
       <c r="Q157" s="13" t="inlineStr">
         <is>
-          <t>Cuando el trabajador estaba próximo a adquirir derechos jubilatorios, la renuncia exigida pasa por estándar reforzado de veracidad: voluntad, autonomía y espontaneidad demostradas con prueba sólida.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R157" s="13" t="inlineStr">
         <is>
-          <t>Protección antes de jubilación: renuncias sospechosas no pasan.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S157" s="13" t="inlineStr">
         <is>
-          <t>Defensa trabajadora: si estaba a meses/años de jubilarse, atacar renuncia por falta de espontaneidad.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T157" s="13" t="inlineStr"/>
       <c r="U157" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027058</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032254</t>
         </is>
       </c>
       <c r="V157" s="13" t="inlineStr">
         <is>
-          <t>renuncia · jubilación · veracidad · carga reforzada</t>
+          <t>Despido injustificado · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="158" ht="80" customHeight="1">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>sen-020</t>
+          <t>lab-des-002</t>
         </is>
       </c>
       <c r="B158" s="11" t="n">
@@ -20567,27 +20665,27 @@
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
         <is>
-          <t>Costas en juicio mercantil — tasación</t>
+          <t>Despido injustificado</t>
         </is>
       </c>
       <c r="F158" s="11" t="inlineStr">
         <is>
-          <t>Línea del Primer y Segundo Circuito (CDMX y Edomex)</t>
+          <t>Carga patrón cuando alega rescisión justificada posterior</t>
         </is>
       </c>
       <c r="G158" s="11" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H158" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I158" s="11" t="inlineStr">
@@ -20597,58 +20695,62 @@
       </c>
       <c r="J158" s="11" t="inlineStr">
         <is>
-          <t>Primer y Segundo Circuito</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K158" s="12" t="inlineStr">
         <is>
-          <t>Costas mercantiles — base de cuantificación y arancel aplicable</t>
+          <t>RELACIÓN LABORAL. CUANDO LA PERSONA TRABAJADORA MANIFIESTA QUE FUE DESPEDIDA INJUSTIFICADAMENTE EN CIERTA FECHA Y EL PATRÓN ARGUMENTA QUE AQUÉLLA SUBSISTIÓ Y QUE POSTERIORMENTE LA RESCINDIÓ DE FORMA JUSTIFICADA, LE CORRESPONDE PROBAR AMBOS HECHOS.</t>
         </is>
       </c>
       <c r="L158" s="11" t="inlineStr">
         <is>
-          <t>Línea de Colegiados — múltiples</t>
+          <t>2029731</t>
         </is>
       </c>
       <c r="M158" s="11" t="inlineStr"/>
       <c r="N158" s="11" t="inlineStr">
         <is>
-          <t>Línea consolidada</t>
-        </is>
-      </c>
-      <c r="O158" s="11" t="inlineStr"/>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="O158" s="11" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P158" s="11" t="inlineStr"/>
       <c r="Q158" s="11" t="inlineStr">
         <is>
-          <t>Las costas en juicio mercantil se cuantifican con base en el monto efectivamente condenado y conforme al arancel local vigente al momento de cuantificarlas. La condena en costas presupone temeridad o vencimiento total.</t>
+          <t>Si el patrón niega el despido alegado y agrega rescisión justificada posterior, tiene carga de probar AMBOS: que la relación subsistió tras la fecha del supuesto despido y que la rescisión posterior fue justificada.</t>
         </is>
       </c>
       <c r="R158" s="11" t="inlineStr">
         <is>
-          <t>Marco práctico para pretensión y oposición a costas.</t>
+          <t>Carga doble para patrón que cambia versión durante el juicio.</t>
         </is>
       </c>
       <c r="S158" s="11" t="inlineStr">
         <is>
-          <t>El acreedor que gana en ejecutivo debe solicitar tasación con arancel actualizado. El deudor debe oponerse cuando la cuantificación excede el monto del juicio o aplica arancel inadecuado.</t>
+          <t>Estrategia trabajadora: forzar al patrón a esa narrativa, queda con carga reforzada.</t>
         </is>
       </c>
       <c r="T158" s="11" t="inlineStr"/>
       <c r="U158" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031803</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029731</t>
         </is>
       </c>
       <c r="V158" s="11" t="inlineStr">
         <is>
-          <t>costas · tasación · arancel · mercantil</t>
+          <t>despido · rescisión · carga probatoria patrón</t>
         </is>
       </c>
     </row>
     <row r="159" ht="80" customHeight="1">
       <c r="A159" s="13" t="inlineStr">
         <is>
-          <t>auto-2032198</t>
+          <t>lab-ren-001</t>
         </is>
       </c>
       <c r="B159" s="13" t="n">
@@ -20661,17 +20763,17 @@
       </c>
       <c r="D159" s="13" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E159" s="13" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Renuncia laboral</t>
         </is>
       </c>
       <c r="F159" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Hora de terminación — carga del patrón</t>
         </is>
       </c>
       <c r="G159" s="13" t="inlineStr">
@@ -20681,7 +20783,7 @@
       </c>
       <c r="H159" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I159" s="13" t="inlineStr">
@@ -20696,57 +20798,57 @@
       </c>
       <c r="K159" s="14" t="inlineStr">
         <is>
-          <t>GARANTÍA PARA QUE SIGA SURTIENDO EFECTOS LA SUSPENSIÓN EN AMPARO INDIRECTO. ES EXIGIBLE A LA PERSONA MORAL PRIVADA DECLARADA EN QUIEBRA, AL NO ACTUALIZARSE ALGÚN SUPUESTO LEGAL PARA EXENTAR SU EXHIBICIÓN.</t>
+          <t>RENUNCIA. CORRESPONDE A LA PARTE DEMANDADA PERFECCIONARLA CON ALGÚN MEDIO DE PRUEBA, CUANDO EXISTA CONTROVERSIA RESPECTO DE LA HORA DE TERMINACIÓN DEL VÍNCULO LABORAL Y ÉSTA NO CONSTE EN EL ESCRITO RELATIVO.</t>
         </is>
       </c>
       <c r="L159" s="13" t="inlineStr">
         <is>
-          <t>2032198</t>
+          <t>2028640</t>
         </is>
       </c>
       <c r="M159" s="13" t="inlineStr"/>
       <c r="N159" s="13" t="inlineStr">
         <is>
-          <t>viernes 29 de mayo de 2026 10:34 h</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="O159" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P159" s="13" t="inlineStr"/>
       <c r="Q159" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Si el patrón ofrece renuncia sin hora exacta y el trabajador alega despido a cierta hora, el patrón debe acreditar con prueba adicional la hora de la renuncia.</t>
         </is>
       </c>
       <c r="R159" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Cuestionamiento a renuncias forzadas con fechas/horas imprecisas.</t>
         </is>
       </c>
       <c r="S159" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Trabajador debe declarar hora exacta del despido; patrón tendrá que probar hora distinta.</t>
         </is>
       </c>
       <c r="T159" s="13" t="inlineStr"/>
       <c r="U159" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032198</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028640</t>
         </is>
       </c>
       <c r="V159" s="13" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil · actualización automática</t>
+          <t>renuncia · hora despido · carga probatoria</t>
         </is>
       </c>
     </row>
     <row r="160" ht="80" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>auto-2032274</t>
+          <t>lab-ren-002</t>
         </is>
       </c>
       <c r="B160" s="11" t="n">
@@ -20759,17 +20861,17 @@
       </c>
       <c r="D160" s="11" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Renuncia laboral</t>
         </is>
       </c>
       <c r="F160" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Veracidad — carga reforzada si trabajador iba a jubilarse</t>
         </is>
       </c>
       <c r="G160" s="11" t="inlineStr">
@@ -20779,7 +20881,7 @@
       </c>
       <c r="H160" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I160" s="11" t="inlineStr">
@@ -20794,57 +20896,57 @@
       </c>
       <c r="K160" s="12" t="inlineStr">
         <is>
-          <t>PRUEBA TESTIMONIAL FORÁNEA EN EL JUICIO EJECUTIVO MERCANTIL ORAL. PROCEDE DESECHARLA CUANDO NO SE OFRECE EN TÉRMINOS DEL ARTÍCULO 1269 DEL CÓDIGO DE COMERCIO.</t>
+          <t>RENUNCIA. PARA QUE SEA VEROSÍMIL Y, POR ENDE, TENGA EFICACIA DEMOSTRATIVA PLENA, CORRESPONDE AL PATRÓN PROBAR QUE REÚNE LAS CONDICIONES DE CERTEZA Y LOS ELEMENTOS MÍNIMOS QUE REFLEJEN LA VOLUNTAD, AUTONOMÍA Y ESPONTANEIDAD DEL TRABAJADOR, SI ESTÁ PRÓXIMO A JUBILARSE.</t>
         </is>
       </c>
       <c r="L160" s="11" t="inlineStr">
         <is>
-          <t>2032274</t>
+          <t>2027058</t>
         </is>
       </c>
       <c r="M160" s="11" t="inlineStr"/>
       <c r="N160" s="11" t="inlineStr">
         <is>
-          <t>viernes 12 de junio de 2026 10:18 h</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="O160" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P160" s="11" t="inlineStr"/>
       <c r="Q160" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Cuando el trabajador estaba próximo a adquirir derechos jubilatorios, la renuncia exigida pasa por estándar reforzado de veracidad: voluntad, autonomía y espontaneidad demostradas con prueba sólida.</t>
         </is>
       </c>
       <c r="R160" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Protección antes de jubilación: renuncias sospechosas no pasan.</t>
         </is>
       </c>
       <c r="S160" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Defensa trabajadora: si estaba a meses/años de jubilarse, atacar renuncia por falta de espontaneidad.</t>
         </is>
       </c>
       <c r="T160" s="11" t="inlineStr"/>
       <c r="U160" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032274</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027058</t>
         </is>
       </c>
       <c r="V160" s="11" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil · actualización automática</t>
+          <t>renuncia · jubilación · veracidad · carga reforzada</t>
         </is>
       </c>
     </row>
     <row r="161" ht="80" customHeight="1">
       <c r="A161" s="13" t="inlineStr">
         <is>
-          <t>auto-2032414</t>
+          <t>sen-020</t>
         </is>
       </c>
       <c r="B161" s="13" t="n">
@@ -20862,22 +20964,22 @@
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Costas en juicio mercantil — tasación</t>
         </is>
       </c>
       <c r="F161" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Línea del Primer y Segundo Circuito (CDMX y Edomex)</t>
         </is>
       </c>
       <c r="G161" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H161" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I161" s="13" t="inlineStr">
@@ -20887,62 +20989,58 @@
       </c>
       <c r="J161" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Primer y Segundo Circuito</t>
         </is>
       </c>
       <c r="K161" s="14" t="inlineStr">
         <is>
-          <t>INCIDENTE DE LIQUIDACIÓN DE GASTOS Y COSTAS EN EL JUICIO EJECUTIVO MERCANTIL ORAL. SU ADMISIÓN DEBE NOTIFICARSE DE MANERA PERSONAL, AL CONSTITUIR UN PROCEDIMIENTO CONTENCIOSO AUTÓNOMO E INDEPENDIENTE, Y EQUIPARARSE CON EL EMPLAZAMIENTO A JUICIO.</t>
+          <t>Costas mercantiles — base de cuantificación y arancel aplicable</t>
         </is>
       </c>
       <c r="L161" s="13" t="inlineStr">
         <is>
-          <t>2032414</t>
+          <t>Línea de Colegiados — múltiples</t>
         </is>
       </c>
       <c r="M161" s="13" t="inlineStr"/>
       <c r="N161" s="13" t="inlineStr">
         <is>
-          <t>viernes 10 de julio de 2026 10:17 h</t>
-        </is>
-      </c>
-      <c r="O161" s="13" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
-        </is>
-      </c>
+          <t>Línea consolidada</t>
+        </is>
+      </c>
+      <c r="O161" s="13" t="inlineStr"/>
       <c r="P161" s="13" t="inlineStr"/>
       <c r="Q161" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Las costas en juicio mercantil se cuantifican con base en el monto efectivamente condenado y conforme al arancel local vigente al momento de cuantificarlas. La condena en costas presupone temeridad o vencimiento total.</t>
         </is>
       </c>
       <c r="R161" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Marco práctico para pretensión y oposición a costas.</t>
         </is>
       </c>
       <c r="S161" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>El acreedor que gana en ejecutivo debe solicitar tasación con arancel actualizado. El deudor debe oponerse cuando la cuantificación excede el monto del juicio o aplica arancel inadecuado.</t>
         </is>
       </c>
       <c r="T161" s="13" t="inlineStr"/>
       <c r="U161" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032414</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031803</t>
         </is>
       </c>
       <c r="V161" s="13" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil · actualización automática</t>
+          <t>costas · tasación · arancel · mercantil</t>
         </is>
       </c>
     </row>
     <row r="162" ht="80" customHeight="1">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>auto-2032458</t>
+          <t>auto-2032198</t>
         </is>
       </c>
       <c r="B162" s="11" t="n">
@@ -20990,18 +21088,18 @@
       </c>
       <c r="K162" s="12" t="inlineStr">
         <is>
-          <t>MUTUO SUBROGATORIO. PARA QUE OPERE POR MINISTERIO DE LEY EN LOS DERECHOS DEL ACREEDOR, DEBEN CUMPLIRSE LOS REQUISITOS DEL ARTÍCULO 2059 DEL CÓDIGO CIVIL FEDERAL.</t>
+          <t>GARANTÍA PARA QUE SIGA SURTIENDO EFECTOS LA SUSPENSIÓN EN AMPARO INDIRECTO. ES EXIGIBLE A LA PERSONA MORAL PRIVADA DECLARADA EN QUIEBRA, AL NO ACTUALIZARSE ALGÚN SUPUESTO LEGAL PARA EXENTAR SU EXHIBICIÓN.</t>
         </is>
       </c>
       <c r="L162" s="11" t="inlineStr">
         <is>
-          <t>2032458</t>
+          <t>2032198</t>
         </is>
       </c>
       <c r="M162" s="11" t="inlineStr"/>
       <c r="N162" s="11" t="inlineStr">
         <is>
-          <t>viernes 07 de agosto de 2026 10:15 h</t>
+          <t>viernes 29 de mayo de 2026 10:34 h</t>
         </is>
       </c>
       <c r="O162" s="11" t="inlineStr">
@@ -21028,7 +21126,7 @@
       <c r="T162" s="11" t="inlineStr"/>
       <c r="U162" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032458</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032198</t>
         </is>
       </c>
       <c r="V162" s="11" t="inlineStr">
@@ -21040,7 +21138,7 @@
     <row r="163" ht="80" customHeight="1">
       <c r="A163" s="13" t="inlineStr">
         <is>
-          <t>mer-eje-002</t>
+          <t>auto-2032274</t>
         </is>
       </c>
       <c r="B163" s="13" t="n">
@@ -21063,17 +21161,17 @@
       </c>
       <c r="F163" s="13" t="inlineStr">
         <is>
-          <t>Improcedencia — análisis oficioso en amparo directo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G163" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H163" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I163" s="13" t="inlineStr">
@@ -21088,57 +21186,57 @@
       </c>
       <c r="K163" s="14" t="inlineStr">
         <is>
-          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
+          <t>PRUEBA TESTIMONIAL FORÁNEA EN EL JUICIO EJECUTIVO MERCANTIL ORAL. PROCEDE DESECHARLA CUANDO NO SE OFRECE EN TÉRMINOS DEL ARTÍCULO 1269 DEL CÓDIGO DE COMERCIO.</t>
         </is>
       </c>
       <c r="L163" s="13" t="inlineStr">
         <is>
-          <t>2025924</t>
+          <t>2032274</t>
         </is>
       </c>
       <c r="M163" s="13" t="inlineStr"/>
       <c r="N163" s="13" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>viernes 12 de junio de 2026 10:18 h</t>
         </is>
       </c>
       <c r="O163" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P163" s="13" t="inlineStr"/>
       <c r="Q163" s="13" t="inlineStr">
         <is>
-          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R163" s="13" t="inlineStr">
         <is>
-          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S163" s="13" t="inlineStr">
         <is>
-          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T163" s="13" t="inlineStr"/>
       <c r="U163" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032274</t>
         </is>
       </c>
       <c r="V163" s="13" t="inlineStr">
         <is>
-          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="164" ht="80" customHeight="1">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>mer-eje-003</t>
+          <t>auto-2032414</t>
         </is>
       </c>
       <c r="B164" s="11" t="n">
@@ -21161,7 +21259,7 @@
       </c>
       <c r="F164" s="11" t="inlineStr">
         <is>
-          <t>Mora — fecha de actualización</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G164" s="11" t="inlineStr">
@@ -21186,57 +21284,57 @@
       </c>
       <c r="K164" s="12" t="inlineStr">
         <is>
-          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
+          <t>INCIDENTE DE LIQUIDACIÓN DE GASTOS Y COSTAS EN EL JUICIO EJECUTIVO MERCANTIL ORAL. SU ADMISIÓN DEBE NOTIFICARSE DE MANERA PERSONAL, AL CONSTITUIR UN PROCEDIMIENTO CONTENCIOSO AUTÓNOMO E INDEPENDIENTE, Y EQUIPARARSE CON EL EMPLAZAMIENTO A JUICIO.</t>
         </is>
       </c>
       <c r="L164" s="11" t="inlineStr">
         <is>
-          <t>2031591</t>
+          <t>2032414</t>
         </is>
       </c>
       <c r="M164" s="11" t="inlineStr"/>
       <c r="N164" s="11" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 10 de julio de 2026 10:17 h</t>
         </is>
       </c>
       <c r="O164" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P164" s="11" t="inlineStr"/>
       <c r="Q164" s="11" t="inlineStr">
         <is>
-          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R164" s="11" t="inlineStr">
         <is>
-          <t>Define desde cuándo corren intereses moratorios.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S164" s="11" t="inlineStr">
         <is>
-          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T164" s="11" t="inlineStr"/>
       <c r="U164" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032414</t>
         </is>
       </c>
       <c r="V164" s="11" t="inlineStr">
         <is>
-          <t>mora · intereses moratorios · interpelación · 12a Época</t>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="165" ht="80" customHeight="1">
       <c r="A165" s="13" t="inlineStr">
         <is>
-          <t>mer-pag-002</t>
+          <t>auto-2032458</t>
         </is>
       </c>
       <c r="B165" s="13" t="n">
@@ -21254,12 +21352,12 @@
       </c>
       <c r="E165" s="13" t="inlineStr">
         <is>
-          <t>Títulos de crédito — pagaré</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F165" s="13" t="inlineStr">
         <is>
-          <t>Acción causal — pagaré como prueba del contrato</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G165" s="13" t="inlineStr">
@@ -21269,7 +21367,7 @@
       </c>
       <c r="H165" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I165" s="13" t="inlineStr">
@@ -21284,57 +21382,57 @@
       </c>
       <c r="K165" s="14" t="inlineStr">
         <is>
-          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
+          <t>MUTUO SUBROGATORIO. PARA QUE OPERE POR MINISTERIO DE LEY EN LOS DERECHOS DEL ACREEDOR, DEBEN CUMPLIRSE LOS REQUISITOS DEL ARTÍCULO 2059 DEL CÓDIGO CIVIL FEDERAL.</t>
         </is>
       </c>
       <c r="L165" s="13" t="inlineStr">
         <is>
-          <t>2024056</t>
+          <t>2032458</t>
         </is>
       </c>
       <c r="M165" s="13" t="inlineStr"/>
       <c r="N165" s="13" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>viernes 07 de agosto de 2026 10:15 h</t>
         </is>
       </c>
       <c r="O165" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P165" s="13" t="inlineStr"/>
       <c r="Q165" s="13" t="inlineStr">
         <is>
-          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R165" s="13" t="inlineStr">
         <is>
-          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S165" s="13" t="inlineStr">
         <is>
-          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T165" s="13" t="inlineStr"/>
       <c r="U165" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032458</t>
         </is>
       </c>
       <c r="V165" s="13" t="inlineStr">
         <is>
-          <t>pagaré · acción causal · ordinario mercantil</t>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="166" ht="80" customHeight="1">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>mer-pag-003</t>
+          <t>auto-2032557</t>
         </is>
       </c>
       <c r="B166" s="11" t="n">
@@ -21352,12 +21450,12 @@
       </c>
       <c r="E166" s="11" t="inlineStr">
         <is>
-          <t>Títulos de crédito — pagaré</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F166" s="11" t="inlineStr">
         <is>
-          <t>Pagarés seriados — lugar de pago</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G166" s="11" t="inlineStr">
@@ -21367,7 +21465,7 @@
       </c>
       <c r="H166" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I166" s="11" t="inlineStr">
@@ -21382,57 +21480,57 @@
       </c>
       <c r="K166" s="12" t="inlineStr">
         <is>
-          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
+          <t>COSTAS EN EL JUICIO EJECUTIVO MERCANTIL. LA EXCLUSIÓN DE CONCEPTOS DERIVADOS DEL TÍTULO DE CRÉDITO QUE NO FUERON RECLAMADOS COMO PRESTACIONES, NO CONFIGURA UN VENCIMIENTO PARCIAL.</t>
         </is>
       </c>
       <c r="L166" s="11" t="inlineStr">
         <is>
-          <t>2019464</t>
+          <t>2032557</t>
         </is>
       </c>
       <c r="M166" s="11" t="inlineStr"/>
       <c r="N166" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>viernes 28 de agosto de 2026 10:36 h</t>
         </is>
       </c>
       <c r="O166" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P166" s="11" t="inlineStr"/>
       <c r="Q166" s="11" t="inlineStr">
         <is>
-          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R166" s="11" t="inlineStr">
         <is>
-          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S166" s="11" t="inlineStr">
         <is>
-          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T166" s="11" t="inlineStr"/>
       <c r="U166" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032557</t>
         </is>
       </c>
       <c r="V166" s="11" t="inlineStr">
         <is>
-          <t>pagaré · pagarés seriados · lugar de pago</t>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="167" ht="80" customHeight="1">
       <c r="A167" s="13" t="inlineStr">
         <is>
-          <t>auto-2032371</t>
+          <t>mer-eje-002</t>
         </is>
       </c>
       <c r="B167" s="13" t="n">
@@ -21445,27 +21543,27 @@
       </c>
       <c r="D167" s="13" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E167" s="13" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F167" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Improcedencia — análisis oficioso en amparo directo</t>
         </is>
       </c>
       <c r="G167" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H167" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I167" s="13" t="inlineStr">
@@ -21480,57 +21578,57 @@
       </c>
       <c r="K167" s="14" t="inlineStr">
         <is>
-          <t>COSA JUZGADA EN EL JUICIO DE AMPARO. CUANDO SE INVOLUCRAN DERECHOS DE NIÑAS, NIÑOS Y ADOLESCENTES, SU ACTUALIZACIÓN REQUIERE UN ANÁLISIS REFORZADO Y UNA CORRESPONDENCIA MATERIAL ENTRE LO PREVIAMENTE RESUELTO Y EL ACTO RECLAMADO.</t>
+          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
         </is>
       </c>
       <c r="L167" s="13" t="inlineStr">
         <is>
-          <t>2032371</t>
+          <t>2025924</t>
         </is>
       </c>
       <c r="M167" s="13" t="inlineStr"/>
       <c r="N167" s="13" t="inlineStr">
         <is>
-          <t>viernes 03 de julio de 2026 10:10 h</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="O167" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P167" s="13" t="inlineStr"/>
       <c r="Q167" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
         </is>
       </c>
       <c r="R167" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
         </is>
       </c>
       <c r="S167" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
         </is>
       </c>
       <c r="T167" s="13" t="inlineStr"/>
       <c r="U167" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032371</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
         </is>
       </c>
       <c r="V167" s="13" t="inlineStr">
         <is>
-          <t>Cadena de custodia · actualización automática</t>
+          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
         </is>
       </c>
     </row>
     <row r="168" ht="80" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>pen-cad-002</t>
+          <t>mer-eje-003</t>
         </is>
       </c>
       <c r="B168" s="11" t="n">
@@ -21543,27 +21641,27 @@
       </c>
       <c r="D168" s="11" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E168" s="11" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F168" s="11" t="inlineStr">
         <is>
-          <t>Responsabilidad de la Fiscalía aun con datos del inculpado</t>
+          <t>Mora — fecha de actualización</t>
         </is>
       </c>
       <c r="G168" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H168" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I168" s="11" t="inlineStr">
@@ -21578,57 +21676,57 @@
       </c>
       <c r="K168" s="12" t="inlineStr">
         <is>
-          <t>CADENA DE CUSTODIA. ES RESPONSABILIDAD EXCLUSIVA DE LOS SERVIDORES PÚBLICOS DE LA FISCALÍA, INCLUSO RESPECTO DE DATOS O MEDIOS DE PRUEBA APORTADOS POR EL INCULPADO O SU DEFENSA.</t>
+          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
         </is>
       </c>
       <c r="L168" s="11" t="inlineStr">
         <is>
-          <t>2027962</t>
+          <t>2031591</t>
         </is>
       </c>
       <c r="M168" s="11" t="inlineStr"/>
       <c r="N168" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O168" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P168" s="11" t="inlineStr"/>
       <c r="Q168" s="11" t="inlineStr">
         <is>
-          <t>Conforme al CNPP, la cadena de custodia recae siempre en la Fiscalía, incluso respecto de evidencia aportada por la defensa. La defensa NO carga con su preservación; el MP debe registrarla y custodiarla.</t>
+          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
         </is>
       </c>
       <c r="R168" s="11" t="inlineStr">
         <is>
-          <t>Reforma carga: la defensa puede aportar evidencia sin temor a romper cadena.</t>
+          <t>Define desde cuándo corren intereses moratorios.</t>
         </is>
       </c>
       <c r="S168" s="11" t="inlineStr">
         <is>
-          <t>Defensa puede aportar peritajes, fotos, audios sin asumir custodia formal.</t>
+          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
         </is>
       </c>
       <c r="T168" s="11" t="inlineStr"/>
       <c r="U168" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027962</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
         </is>
       </c>
       <c r="V168" s="11" t="inlineStr">
         <is>
-          <t>cadena custodia · CNPP · Fiscalía · evidencia defensa</t>
+          <t>mora · intereses moratorios · interpelación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="169" ht="80" customHeight="1">
       <c r="A169" s="13" t="inlineStr">
         <is>
-          <t>pen-cad-003</t>
+          <t>mer-pag-002</t>
         </is>
       </c>
       <c r="B169" s="13" t="n">
@@ -21641,17 +21739,17 @@
       </c>
       <c r="D169" s="13" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E169" s="13" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Títulos de crédito — pagaré</t>
         </is>
       </c>
       <c r="F169" s="13" t="inlineStr">
         <is>
-          <t>Transgresión no torna ilícita la prueba</t>
+          <t>Acción causal — pagaré como prueba del contrato</t>
         </is>
       </c>
       <c r="G169" s="13" t="inlineStr">
@@ -21661,7 +21759,7 @@
       </c>
       <c r="H169" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I169" s="13" t="inlineStr">
@@ -21676,18 +21774,18 @@
       </c>
       <c r="K169" s="14" t="inlineStr">
         <is>
-          <t>CADENA DE CUSTODIA. SU TRANSGRESIÓN NO TORNA ILÍCITOS LOS DATOS DE PRUEBA.</t>
+          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
         </is>
       </c>
       <c r="L169" s="13" t="inlineStr">
         <is>
-          <t>2021845</t>
+          <t>2024056</t>
         </is>
       </c>
       <c r="M169" s="13" t="inlineStr"/>
       <c r="N169" s="13" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O169" s="13" t="inlineStr">
@@ -21698,35 +21796,35 @@
       <c r="P169" s="13" t="inlineStr"/>
       <c r="Q169" s="13" t="inlineStr">
         <is>
-          <t>La ruptura de cadena de custodia NO convierte automáticamente en ilícita la prueba; solo afecta su valor probatorio. El juez debe ponderar la magnitud de la ruptura.</t>
+          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
         </is>
       </c>
       <c r="R169" s="13" t="inlineStr">
         <is>
-          <t>Matiza la regla de exclusión: cadena rota = valor probatorio reducido, no exclusión.</t>
+          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
         </is>
       </c>
       <c r="S169" s="13" t="inlineStr">
         <is>
-          <t>Defensa: argumentar valor cero por ruptura. Acusación: defender la prueba a pesar de la ruptura.</t>
+          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
         </is>
       </c>
       <c r="T169" s="13" t="inlineStr"/>
       <c r="U169" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
         </is>
       </c>
       <c r="V169" s="13" t="inlineStr">
         <is>
-          <t>cadena custodia · valor probatorio · exclusión</t>
+          <t>pagaré · acción causal · ordinario mercantil</t>
         </is>
       </c>
     </row>
     <row r="170" ht="80" customHeight="1">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>pen-ppo-001</t>
+          <t>mer-pag-003</t>
         </is>
       </c>
       <c r="B170" s="11" t="n">
@@ -21739,17 +21837,17 @@
       </c>
       <c r="D170" s="11" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E170" s="11" t="inlineStr">
         <is>
-          <t>Prisión preventiva oficiosa</t>
+          <t>Títulos de crédito — pagaré</t>
         </is>
       </c>
       <c r="F170" s="11" t="inlineStr">
         <is>
-          <t>Víctima — falta de legitimación para impugnar cese</t>
+          <t>Pagarés seriados — lugar de pago</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr">
@@ -21759,7 +21857,7 @@
       </c>
       <c r="H170" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I170" s="11" t="inlineStr">
@@ -21774,57 +21872,57 @@
       </c>
       <c r="K170" s="12" t="inlineStr">
         <is>
-          <t>PRISIÓN PREVENTIVA OFICIOSA. LA VÍCTIMA U OFENDIDO DEL DELITO CARECE DE LEGITIMACIÓN PARA IMPUGNAR EN SEDE CONSTITUCIONAL SU CESE, AL NO TENER INCORPORADA A SU ESFERA JURÍDICA ALGÚN DERECHO QUE LA FACULTE.</t>
+          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
         </is>
       </c>
       <c r="L170" s="11" t="inlineStr">
         <is>
-          <t>2032107</t>
+          <t>2019464</t>
         </is>
       </c>
       <c r="M170" s="11" t="inlineStr"/>
       <c r="N170" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="O170" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P170" s="11" t="inlineStr"/>
       <c r="Q170" s="11" t="inlineStr">
         <is>
-          <t>La víctima no puede impugnar por amparo la liberación del imputado cuando se cesa la PPO. No hay derecho subjetivo a que el imputado permanezca en prisión preventiva.</t>
+          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
         </is>
       </c>
       <c r="R170" s="11" t="inlineStr">
         <is>
-          <t>Restringe vía de víctima contra liberaciones por exceso de plazo.</t>
+          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
         </is>
       </c>
       <c r="S170" s="11" t="inlineStr">
         <is>
-          <t>Tras PPO cesada (más de 2 años sin sentencia, por ejemplo), la víctima no puede ampararse. Su vía es civil/coadyuvancia para impulsar el proceso, no constitucional.</t>
+          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
         </is>
       </c>
       <c r="T170" s="11" t="inlineStr"/>
       <c r="U170" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032107</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
         </is>
       </c>
       <c r="V170" s="11" t="inlineStr">
         <is>
-          <t>PPO · víctima · legitimación · 12a Época</t>
+          <t>pagaré · pagarés seriados · lugar de pago</t>
         </is>
       </c>
     </row>
     <row r="171" ht="80" customHeight="1">
       <c r="A171" s="13" t="inlineStr">
         <is>
-          <t>pen-ppo-002</t>
+          <t>auto-2032371</t>
         </is>
       </c>
       <c r="B171" s="13" t="n">
@@ -21842,12 +21940,12 @@
       </c>
       <c r="E171" s="13" t="inlineStr">
         <is>
-          <t>Prisión preventiva oficiosa</t>
+          <t>Cadena de custodia</t>
         </is>
       </c>
       <c r="F171" s="13" t="inlineStr">
         <is>
-          <t>Cese cuando MP no prueba prolongación</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G171" s="13" t="inlineStr">
@@ -21872,57 +21970,57 @@
       </c>
       <c r="K171" s="14" t="inlineStr">
         <is>
-          <t>PRISIÓN PREVENTIVA OFICIOSA. SU CESE ORDENADO CUANDO EL MINISTERIO PÚBLICO NO PRUEBA NI JUSTIFICA SU PROLONGACIÓN, PARA EFECTOS DE QUE SE DEBATA LA IMPOSICIÓN DE OTRAS MEDIDAS CAUTELARES MENOS RESTRICTIVAS.</t>
+          <t>COSA JUZGADA EN EL JUICIO DE AMPARO. CUANDO SE INVOLUCRAN DERECHOS DE NIÑAS, NIÑOS Y ADOLESCENTES, SU ACTUALIZACIÓN REQUIERE UN ANÁLISIS REFORZADO Y UNA CORRESPONDENCIA MATERIAL ENTRE LO PREVIAMENTE RESUELTO Y EL ACTO RECLAMADO.</t>
         </is>
       </c>
       <c r="L171" s="13" t="inlineStr">
         <is>
-          <t>2032108</t>
+          <t>2032371</t>
         </is>
       </c>
       <c r="M171" s="13" t="inlineStr"/>
       <c r="N171" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 03 de julio de 2026 10:10 h</t>
         </is>
       </c>
       <c r="O171" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P171" s="13" t="inlineStr"/>
       <c r="Q171" s="13" t="inlineStr">
         <is>
-          <t>Al solicitar prolongación de PPO, el MP tiene carga probatoria. Si no la cumple, el juez debe cesar la PPO y reabrir debate sobre medidas cautelares alternativas.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R171" s="13" t="inlineStr">
         <is>
-          <t>Defensa decisiva contra prolongación automática de PPO.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S171" s="13" t="inlineStr">
         <is>
-          <t>Cuando MP solicita prolongación sin justificar, la defensa debe exigir prueba concreta. Sin ella, opera el cese y se debate medida alterna (caución, brazalete, presentación periódica).</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T171" s="13" t="inlineStr"/>
       <c r="U171" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032108</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032371</t>
         </is>
       </c>
       <c r="V171" s="13" t="inlineStr">
         <is>
-          <t>PPO · prolongación · carga probatoria MP · 12a Época</t>
+          <t>Cadena de custodia · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="172" ht="80" customHeight="1">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>auto-2032300</t>
+          <t>pen-cad-002</t>
         </is>
       </c>
       <c r="B172" s="11" t="n">
@@ -21940,22 +22038,22 @@
       </c>
       <c r="E172" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Cadena de custodia</t>
         </is>
       </c>
       <c r="F172" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Responsabilidad de la Fiscalía aun con datos del inculpado</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H172" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I172" s="11" t="inlineStr">
@@ -21970,57 +22068,57 @@
       </c>
       <c r="K172" s="12" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. OBLIGAR A UNA ADOLESCENTE VÍCTIMA DE MALA PRÁXIS MÉDICA A RECIBIR ATENCIÓN MÉDICA POSTERIOR PARA EJERCER SUS DERECHOS REPRODUCTIVOS EN LA MISMA INSTITUCIÓN DE SALUD QUE ACTUÓ EN FORMA IRREGULAR, CONSTITUYE UNA ACTIVIDAD REVICTIMIZANTE.</t>
+          <t>CADENA DE CUSTODIA. ES RESPONSABILIDAD EXCLUSIVA DE LOS SERVIDORES PÚBLICOS DE LA FISCALÍA, INCLUSO RESPECTO DE DATOS O MEDIOS DE PRUEBA APORTADOS POR EL INCULPADO O SU DEFENSA.</t>
         </is>
       </c>
       <c r="L172" s="11" t="inlineStr">
         <is>
-          <t>2032300</t>
+          <t>2027962</t>
         </is>
       </c>
       <c r="M172" s="11" t="inlineStr"/>
       <c r="N172" s="11" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="O172" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P172" s="11" t="inlineStr"/>
       <c r="Q172" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Conforme al CNPP, la cadena de custodia recae siempre en la Fiscalía, incluso respecto de evidencia aportada por la defensa. La defensa NO carga con su preservación; el MP debe registrarla y custodiarla.</t>
         </is>
       </c>
       <c r="R172" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Reforma carga: la defensa puede aportar evidencia sin temor a romper cadena.</t>
         </is>
       </c>
       <c r="S172" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Defensa puede aportar peritajes, fotos, audios sin asumir custodia formal.</t>
         </is>
       </c>
       <c r="T172" s="11" t="inlineStr"/>
       <c r="U172" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032300</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027962</t>
         </is>
       </c>
       <c r="V172" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño · actualización automática</t>
+          <t>cadena custodia · CNPP · Fiscalía · evidencia defensa</t>
         </is>
       </c>
     </row>
     <row r="173" ht="80" customHeight="1">
       <c r="A173" s="13" t="inlineStr">
         <is>
-          <t>auto-2032301</t>
+          <t>pen-cad-003</t>
         </is>
       </c>
       <c r="B173" s="13" t="n">
@@ -22038,12 +22136,12 @@
       </c>
       <c r="E173" s="13" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Cadena de custodia</t>
         </is>
       </c>
       <c r="F173" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Transgresión no torna ilícita la prueba</t>
         </is>
       </c>
       <c r="G173" s="13" t="inlineStr">
@@ -22053,7 +22151,7 @@
       </c>
       <c r="H173" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I173" s="13" t="inlineStr">
@@ -22068,57 +22166,57 @@
       </c>
       <c r="K173" s="14" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LA REPARACIÓN INTEGRAL DEL DAÑO NO SE LIMITA AL RESARCIMIENTO ECONÓMICO, SINO QUE INCLUYE LA REHABILITACIÓN PARA FACILITAR A LA VÍCTIMA HACER FRENTE A LOS EFECTOS DEL DAÑO SUFRIDO (LEY GENERAL DE VÍCTIMAS).</t>
+          <t>CADENA DE CUSTODIA. SU TRANSGRESIÓN NO TORNA ILÍCITOS LOS DATOS DE PRUEBA.</t>
         </is>
       </c>
       <c r="L173" s="13" t="inlineStr">
         <is>
-          <t>2032301</t>
+          <t>2021845</t>
         </is>
       </c>
       <c r="M173" s="13" t="inlineStr"/>
       <c r="N173" s="13" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="O173" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P173" s="13" t="inlineStr"/>
       <c r="Q173" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La ruptura de cadena de custodia NO convierte automáticamente en ilícita la prueba; solo afecta su valor probatorio. El juez debe ponderar la magnitud de la ruptura.</t>
         </is>
       </c>
       <c r="R173" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Matiza la regla de exclusión: cadena rota = valor probatorio reducido, no exclusión.</t>
         </is>
       </c>
       <c r="S173" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Defensa: argumentar valor cero por ruptura. Acusación: defender la prueba a pesar de la ruptura.</t>
         </is>
       </c>
       <c r="T173" s="13" t="inlineStr"/>
       <c r="U173" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032301</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
         </is>
       </c>
       <c r="V173" s="13" t="inlineStr">
         <is>
-          <t>Reparación del daño · actualización automática</t>
+          <t>cadena custodia · valor probatorio · exclusión</t>
         </is>
       </c>
     </row>
     <row r="174" ht="80" customHeight="1">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>auto-2032304</t>
+          <t>pen-ppo-001</t>
         </is>
       </c>
       <c r="B174" s="11" t="n">
@@ -22136,12 +22234,12 @@
       </c>
       <c r="E174" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Prisión preventiva oficiosa</t>
         </is>
       </c>
       <c r="F174" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Víctima — falta de legitimación para impugnar cese</t>
         </is>
       </c>
       <c r="G174" s="11" t="inlineStr">
@@ -22166,57 +22264,57 @@
       </c>
       <c r="K174" s="12" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. PARA DETERMINAR LA REPARACIÓN INTEGRAL DEL DAÑO SE DEBE CONSIDERAR TANTO EL HECHO VICTIMIZANTE COMO SUS EFECTOS, PARA QUE SU FIJACIÓN PERMITA A LAS VÍCTIMAS DIRECTAS E INDIRECTAS REHACER SU PROYECTO DE VIDA.</t>
+          <t>PRISIÓN PREVENTIVA OFICIOSA. LA VÍCTIMA U OFENDIDO DEL DELITO CARECE DE LEGITIMACIÓN PARA IMPUGNAR EN SEDE CONSTITUCIONAL SU CESE, AL NO TENER INCORPORADA A SU ESFERA JURÍDICA ALGÚN DERECHO QUE LA FACULTE.</t>
         </is>
       </c>
       <c r="L174" s="11" t="inlineStr">
         <is>
-          <t>2032304</t>
+          <t>2032107</t>
         </is>
       </c>
       <c r="M174" s="11" t="inlineStr"/>
       <c r="N174" s="11" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O174" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P174" s="11" t="inlineStr"/>
       <c r="Q174" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La víctima no puede impugnar por amparo la liberación del imputado cuando se cesa la PPO. No hay derecho subjetivo a que el imputado permanezca en prisión preventiva.</t>
         </is>
       </c>
       <c r="R174" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Restringe vía de víctima contra liberaciones por exceso de plazo.</t>
         </is>
       </c>
       <c r="S174" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Tras PPO cesada (más de 2 años sin sentencia, por ejemplo), la víctima no puede ampararse. Su vía es civil/coadyuvancia para impulsar el proceso, no constitucional.</t>
         </is>
       </c>
       <c r="T174" s="11" t="inlineStr"/>
       <c r="U174" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032304</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032107</t>
         </is>
       </c>
       <c r="V174" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño · actualización automática</t>
+          <t>PPO · víctima · legitimación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="175" ht="80" customHeight="1">
       <c r="A175" s="13" t="inlineStr">
         <is>
-          <t>auto-2032335</t>
+          <t>pen-ppo-002</t>
         </is>
       </c>
       <c r="B175" s="13" t="n">
@@ -22234,12 +22332,12 @@
       </c>
       <c r="E175" s="13" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Prisión preventiva oficiosa</t>
         </is>
       </c>
       <c r="F175" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Cese cuando MP no prueba prolongación</t>
         </is>
       </c>
       <c r="G175" s="13" t="inlineStr">
@@ -22264,57 +22362,57 @@
       </c>
       <c r="K175" s="14" t="inlineStr">
         <is>
-          <t>PERSONA INIMPUTABLE POR TRANSTORNO MENTAL. LA MEDIDA DE SEGURIDAD DE INTERNAMIENTO DEBE IMPONERSE CONFORME AL MODELO SOCIAL DE DISCAPACIDAD Y NO CON BASE EN LA PUNIBILIDAD DEL TIPO PENAL ATRIBUIDO.</t>
+          <t>PRISIÓN PREVENTIVA OFICIOSA. SU CESE ORDENADO CUANDO EL MINISTERIO PÚBLICO NO PRUEBA NI JUSTIFICA SU PROLONGACIÓN, PARA EFECTOS DE QUE SE DEBATA LA IMPOSICIÓN DE OTRAS MEDIDAS CAUTELARES MENOS RESTRICTIVAS.</t>
         </is>
       </c>
       <c r="L175" s="13" t="inlineStr">
         <is>
-          <t>2032335</t>
+          <t>2032108</t>
         </is>
       </c>
       <c r="M175" s="13" t="inlineStr"/>
       <c r="N175" s="13" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O175" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P175" s="13" t="inlineStr"/>
       <c r="Q175" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Al solicitar prolongación de PPO, el MP tiene carga probatoria. Si no la cumple, el juez debe cesar la PPO y reabrir debate sobre medidas cautelares alternativas.</t>
         </is>
       </c>
       <c r="R175" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Defensa decisiva contra prolongación automática de PPO.</t>
         </is>
       </c>
       <c r="S175" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Cuando MP solicita prolongación sin justificar, la defensa debe exigir prueba concreta. Sin ella, opera el cese y se debate medida alterna (caución, brazalete, presentación periódica).</t>
         </is>
       </c>
       <c r="T175" s="13" t="inlineStr"/>
       <c r="U175" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032335</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032108</t>
         </is>
       </c>
       <c r="V175" s="13" t="inlineStr">
         <is>
-          <t>Reparación del daño · actualización automática</t>
+          <t>PPO · prolongación · carga probatoria MP · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="176" ht="80" customHeight="1">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>auto-2032337</t>
+          <t>auto-2032300</t>
         </is>
       </c>
       <c r="B176" s="11" t="n">
@@ -22362,18 +22460,18 @@
       </c>
       <c r="K176" s="12" t="inlineStr">
         <is>
-          <t>PERSONAS INIMPUTABLES. ES IMPROCEDENTE CONDENARLAS AL PAGO DE LA REPARACIÓN DEL DAÑO, POR LO QUE EL ESTADO DEBE ASUMIRLO DE MANERA SUBSIDIARIA.</t>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. OBLIGAR A UNA ADOLESCENTE VÍCTIMA DE MALA PRÁXIS MÉDICA A RECIBIR ATENCIÓN MÉDICA POSTERIOR PARA EJERCER SUS DERECHOS REPRODUCTIVOS EN LA MISMA INSTITUCIÓN DE SALUD QUE ACTUÓ EN FORMA IRREGULAR, CONSTITUYE UNA ACTIVIDAD REVICTIMIZANTE.</t>
         </is>
       </c>
       <c r="L176" s="11" t="inlineStr">
         <is>
-          <t>2032337</t>
+          <t>2032300</t>
         </is>
       </c>
       <c r="M176" s="11" t="inlineStr"/>
       <c r="N176" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O176" s="11" t="inlineStr">
@@ -22400,7 +22498,7 @@
       <c r="T176" s="11" t="inlineStr"/>
       <c r="U176" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032337</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032300</t>
         </is>
       </c>
       <c r="V176" s="11" t="inlineStr">
@@ -22412,7 +22510,7 @@
     <row r="177" ht="80" customHeight="1">
       <c r="A177" s="13" t="inlineStr">
         <is>
-          <t>auto-2032390</t>
+          <t>auto-2032301</t>
         </is>
       </c>
       <c r="B177" s="13" t="n">
@@ -22460,18 +22558,18 @@
       </c>
       <c r="K177" s="14" t="inlineStr">
         <is>
-          <t>PAGO DE INDEMNIZACIÓN POR DAÑOS PUNITIVOS. PROCEDE ANTE ACTOS DISCRIMINATORIOS OCASIONADOS POR EL USO DEL LENGUAJE BASADO EN ESTEREOTIPOS O PREJUICIOS POR RAZÓN DE GÉNERO, Y CONDUCTAS IRREGULARES E INJUSTIFICADAS DERIVADAS DE UN CONTRATO DE SEGURO.</t>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LA REPARACIÓN INTEGRAL DEL DAÑO NO SE LIMITA AL RESARCIMIENTO ECONÓMICO, SINO QUE INCLUYE LA REHABILITACIÓN PARA FACILITAR A LA VÍCTIMA HACER FRENTE A LOS EFECTOS DEL DAÑO SUFRIDO (LEY GENERAL DE VÍCTIMAS).</t>
         </is>
       </c>
       <c r="L177" s="13" t="inlineStr">
         <is>
-          <t>2032390</t>
+          <t>2032301</t>
         </is>
       </c>
       <c r="M177" s="13" t="inlineStr"/>
       <c r="N177" s="13" t="inlineStr">
         <is>
-          <t>viernes 03 de julio de 2026 10:10 h</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O177" s="13" t="inlineStr">
@@ -22498,7 +22596,7 @@
       <c r="T177" s="13" t="inlineStr"/>
       <c r="U177" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032390</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032301</t>
         </is>
       </c>
       <c r="V177" s="13" t="inlineStr">
@@ -22510,7 +22608,7 @@
     <row r="178" ht="80" customHeight="1">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>auto-2032469</t>
+          <t>auto-2032304</t>
         </is>
       </c>
       <c r="B178" s="11" t="n">
@@ -22558,18 +22656,18 @@
       </c>
       <c r="K178" s="12" t="inlineStr">
         <is>
-          <t>RECURSO DE REVOCACIÓN PREVISTO EN EL ARTÍCULO 170 DE LA LEY NACIONAL DEL SISTEMA INTEGRAL DE JUSTICIA PENAL PARA ADOLESCENTES. PROCEDE CONTRA EL AUTO QUE INADMITE LA APELACIÓN, Y EN OBSERVANCIA AL PRINCIPIO DE DEFINITIVIDAD, DEBE AGOTARSE PREVIO A PROMOVER EL AMPARO.</t>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. PARA DETERMINAR LA REPARACIÓN INTEGRAL DEL DAÑO SE DEBE CONSIDERAR TANTO EL HECHO VICTIMIZANTE COMO SUS EFECTOS, PARA QUE SU FIJACIÓN PERMITA A LAS VÍCTIMAS DIRECTAS E INDIRECTAS REHACER SU PROYECTO DE VIDA.</t>
         </is>
       </c>
       <c r="L178" s="11" t="inlineStr">
         <is>
-          <t>2032469</t>
+          <t>2032304</t>
         </is>
       </c>
       <c r="M178" s="11" t="inlineStr"/>
       <c r="N178" s="11" t="inlineStr">
         <is>
-          <t>viernes 07 de agosto de 2026 10:15 h</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O178" s="11" t="inlineStr">
@@ -22596,17 +22694,409 @@
       <c r="T178" s="11" t="inlineStr"/>
       <c r="U178" s="11" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032304</t>
+        </is>
+      </c>
+      <c r="V178" s="11" t="inlineStr">
+        <is>
+          <t>Reparación del daño · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="80" customHeight="1">
+      <c r="A179" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032335</t>
+        </is>
+      </c>
+      <c r="B179" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C179" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D179" s="13" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E179" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño</t>
+        </is>
+      </c>
+      <c r="F179" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G179" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H179" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J179" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K179" s="14" t="inlineStr">
+        <is>
+          <t>PERSONA INIMPUTABLE POR TRANSTORNO MENTAL. LA MEDIDA DE SEGURIDAD DE INTERNAMIENTO DEBE IMPONERSE CONFORME AL MODELO SOCIAL DE DISCAPACIDAD Y NO CON BASE EN LA PUNIBILIDAD DEL TIPO PENAL ATRIBUIDO.</t>
+        </is>
+      </c>
+      <c r="L179" s="13" t="inlineStr">
+        <is>
+          <t>2032335</t>
+        </is>
+      </c>
+      <c r="M179" s="13" t="inlineStr"/>
+      <c r="N179" s="13" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
+      <c r="O179" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P179" s="13" t="inlineStr"/>
+      <c r="Q179" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R179" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S179" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T179" s="13" t="inlineStr"/>
+      <c r="U179" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032335</t>
+        </is>
+      </c>
+      <c r="V179" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="80" customHeight="1">
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032337</t>
+        </is>
+      </c>
+      <c r="B180" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C180" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D180" s="11" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E180" s="11" t="inlineStr">
+        <is>
+          <t>Reparación del daño</t>
+        </is>
+      </c>
+      <c r="F180" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G180" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H180" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I180" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J180" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K180" s="12" t="inlineStr">
+        <is>
+          <t>PERSONAS INIMPUTABLES. ES IMPROCEDENTE CONDENARLAS AL PAGO DE LA REPARACIÓN DEL DAÑO, POR LO QUE EL ESTADO DEBE ASUMIRLO DE MANERA SUBSIDIARIA.</t>
+        </is>
+      </c>
+      <c r="L180" s="11" t="inlineStr">
+        <is>
+          <t>2032337</t>
+        </is>
+      </c>
+      <c r="M180" s="11" t="inlineStr"/>
+      <c r="N180" s="11" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
+      <c r="O180" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P180" s="11" t="inlineStr"/>
+      <c r="Q180" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R180" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S180" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T180" s="11" t="inlineStr"/>
+      <c r="U180" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032337</t>
+        </is>
+      </c>
+      <c r="V180" s="11" t="inlineStr">
+        <is>
+          <t>Reparación del daño · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="80" customHeight="1">
+      <c r="A181" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032390</t>
+        </is>
+      </c>
+      <c r="B181" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C181" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D181" s="13" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E181" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño</t>
+        </is>
+      </c>
+      <c r="F181" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G181" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H181" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I181" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J181" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K181" s="14" t="inlineStr">
+        <is>
+          <t>PAGO DE INDEMNIZACIÓN POR DAÑOS PUNITIVOS. PROCEDE ANTE ACTOS DISCRIMINATORIOS OCASIONADOS POR EL USO DEL LENGUAJE BASADO EN ESTEREOTIPOS O PREJUICIOS POR RAZÓN DE GÉNERO, Y CONDUCTAS IRREGULARES E INJUSTIFICADAS DERIVADAS DE UN CONTRATO DE SEGURO.</t>
+        </is>
+      </c>
+      <c r="L181" s="13" t="inlineStr">
+        <is>
+          <t>2032390</t>
+        </is>
+      </c>
+      <c r="M181" s="13" t="inlineStr"/>
+      <c r="N181" s="13" t="inlineStr">
+        <is>
+          <t>viernes 03 de julio de 2026 10:10 h</t>
+        </is>
+      </c>
+      <c r="O181" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P181" s="13" t="inlineStr"/>
+      <c r="Q181" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R181" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S181" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T181" s="13" t="inlineStr"/>
+      <c r="U181" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032390</t>
+        </is>
+      </c>
+      <c r="V181" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="80" customHeight="1">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032469</t>
+        </is>
+      </c>
+      <c r="B182" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C182" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D182" s="11" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E182" s="11" t="inlineStr">
+        <is>
+          <t>Reparación del daño</t>
+        </is>
+      </c>
+      <c r="F182" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G182" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H182" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I182" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J182" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K182" s="12" t="inlineStr">
+        <is>
+          <t>RECURSO DE REVOCACIÓN PREVISTO EN EL ARTÍCULO 170 DE LA LEY NACIONAL DEL SISTEMA INTEGRAL DE JUSTICIA PENAL PARA ADOLESCENTES. PROCEDE CONTRA EL AUTO QUE INADMITE LA APELACIÓN, Y EN OBSERVANCIA AL PRINCIPIO DE DEFINITIVIDAD, DEBE AGOTARSE PREVIO A PROMOVER EL AMPARO.</t>
+        </is>
+      </c>
+      <c r="L182" s="11" t="inlineStr">
+        <is>
+          <t>2032469</t>
+        </is>
+      </c>
+      <c r="M182" s="11" t="inlineStr"/>
+      <c r="N182" s="11" t="inlineStr">
+        <is>
+          <t>viernes 07 de agosto de 2026 10:15 h</t>
+        </is>
+      </c>
+      <c r="O182" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P182" s="11" t="inlineStr"/>
+      <c r="Q182" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R182" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S182" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T182" s="11" t="inlineStr"/>
+      <c r="U182" s="11" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032469</t>
         </is>
       </c>
-      <c r="V178" s="11" t="inlineStr">
+      <c r="V182" s="11" t="inlineStr">
         <is>
           <t>Reparación del daño · actualización automática</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V178"/>
+  <autoFilter ref="A1:V182"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22617,7 +23107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25652,8 +26142,106 @@
         </is>
       </c>
     </row>
+    <row r="32" ht="80" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032562</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Administrativo</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Responsabilidad administrativa de servidores públicos</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K32" s="12" t="inlineStr">
+        <is>
+          <t>IMPUESTO SOBRE LA RENTA. NO PROCEDE SU DEDUCCIÓN POR EL PAGO DE PENAS CONVENCIONALES EN TÉRMINOS DEL ARTÍCULO 32, FRACCIÓN VI, DE LA LEY RELATIVA, CUANDO EXISTE UN MECANISMO CONTRACTUAL PARA EVITAR SU PAGO Y NO SE EJERCE (LEGISLACIÓN VIGENTE EN 2013).</t>
+        </is>
+      </c>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
+          <t>2032562</t>
+        </is>
+      </c>
+      <c r="M32" s="11" t="inlineStr"/>
+      <c r="N32" s="11" t="inlineStr">
+        <is>
+          <t>viernes 28 de agosto de 2026 10:36 h</t>
+        </is>
+      </c>
+      <c r="O32" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P32" s="11" t="inlineStr"/>
+      <c r="Q32" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R32" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S32" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T32" s="11" t="inlineStr"/>
+      <c r="U32" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032562</t>
+        </is>
+      </c>
+      <c r="V32" s="11" t="inlineStr">
+        <is>
+          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V31"/>
+  <autoFilter ref="A1:V32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -25664,7 +26252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27347,8 +27935,106 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032576</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Amparo</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Suspensión</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA LA EXPULSIÓN DE UNA PERSONA ADOLESCENTE DE LA ESCUELA EN LA QUE CURSA LA EDUCACIÓN BÁSICA (SECUNDARIA) POR ACUMULAR FALTAS A SU REGLAMENTO.</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>2032576</t>
+        </is>
+      </c>
+      <c r="M18" s="11" t="inlineStr"/>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>viernes 28 de agosto de 2026 10:36 h</t>
+        </is>
+      </c>
+      <c r="O18" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P18" s="11" t="inlineStr"/>
+      <c r="Q18" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R18" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S18" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T18" s="11" t="inlineStr"/>
+      <c r="U18" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032576</t>
+        </is>
+      </c>
+      <c r="V18" s="11" t="inlineStr">
+        <is>
+          <t>Suspensión · actualización automática</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V17"/>
+  <autoFilter ref="A1:V18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -31723,7 +32409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -33381,7 +34067,7 @@
     <row r="18" ht="80" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>auto-2032154</t>
+          <t>auto-2032575</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
@@ -33399,7 +34085,7 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género</t>
+          <t>Medio ambiente sano</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -33429,18 +34115,18 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>COMPENSACIÓN ECONÓMICA. ELEMENTOS MÍNIMOS QUE LA PERSONA JUZGADORA DEBE CONSIDERAR PARA MOTIVAR LA RESOLUCIÓN QUE LA CUANTIFICA, CON PERSPECTIVA DE GÉNERO.</t>
+          <t>SUSPENSIÓN DEFINITIVA EN AMPARO INDIRECTO. PARA CONCEDERLA CONTRA LA AFECTACIÓN A ÁREAS NATURALES PROTEGIDAS, EL JUZGADO DE DISTRITO DEBE ATENDER A UN ESTÁNDAR DE PROTECCIÓN REFORZADA APLICANDO LOS PRINCIPIOS AMBIENTALES DE PREVENCIÓN Y DE PRECAUCIÓN.</t>
         </is>
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>2032154</t>
+          <t>2032575</t>
         </is>
       </c>
       <c r="M18" s="11" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
+          <t>viernes 28 de agosto de 2026 10:36 h</t>
         </is>
       </c>
       <c r="O18" s="11" t="inlineStr">
@@ -33467,19 +34153,19 @@
       <c r="T18" s="11" t="inlineStr"/>
       <c r="U18" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032154</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032575</t>
         </is>
       </c>
       <c r="V18" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género · actualización automática</t>
+          <t>Medio ambiente sano · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="19" ht="80" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>auto-2032184</t>
+          <t>auto-2032154</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
@@ -33527,12 +34213,12 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>VIOLENCIA FAMILIAR. CUANDO LA VÍCTIMA SEA UNA PERSONA MENOR DE EDAD Y SE ALEGUE ALIENACIÓN O MANIPULACIÓN PARENTAL, EL ÓRGANO JURISDICCIONAL DEBE ORDENAR LA PRÁCTICA DE PRUEBAS PERICIALES PARA VERIFICAR SI SE ACTUALIZA DICHA CONDICIÓN.</t>
+          <t>COMPENSACIÓN ECONÓMICA. ELEMENTOS MÍNIMOS QUE LA PERSONA JUZGADORA DEBE CONSIDERAR PARA MOTIVAR LA RESOLUCIÓN QUE LA CUANTIFICA, CON PERSPECTIVA DE GÉNERO.</t>
         </is>
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t>2032184</t>
+          <t>2032154</t>
         </is>
       </c>
       <c r="M19" s="13" t="inlineStr"/>
@@ -33565,7 +34251,7 @@
       <c r="T19" s="13" t="inlineStr"/>
       <c r="U19" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032184</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032154</t>
         </is>
       </c>
       <c r="V19" s="13" t="inlineStr">
@@ -33577,7 +34263,7 @@
     <row r="20" ht="80" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>auto-2032279</t>
+          <t>auto-2032184</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
@@ -33625,18 +34311,18 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>ACTA ADMINISTRATIVA DE INVESTIGACIÓN EN EL JUICIO LABORAL. TIENE VALOR PROBATORIO AUNQUE NO SE RATIFIQUE ANTE LA AUTORIDAD JURISDICCIONAL, CUANDO CONSIGNE EL TESTIMONIO DE NIÑAS, NIÑOS Y ADOLECENTES POR ACTOS DE CONNOTACIÓN SEXUAL REALIZADOS EN SU CONTRA.</t>
+          <t>VIOLENCIA FAMILIAR. CUANDO LA VÍCTIMA SEA UNA PERSONA MENOR DE EDAD Y SE ALEGUE ALIENACIÓN O MANIPULACIÓN PARENTAL, EL ÓRGANO JURISDICCIONAL DEBE ORDENAR LA PRÁCTICA DE PRUEBAS PERICIALES PARA VERIFICAR SI SE ACTUALIZA DICHA CONDICIÓN.</t>
         </is>
       </c>
       <c r="L20" s="11" t="inlineStr">
         <is>
-          <t>2032279</t>
+          <t>2032184</t>
         </is>
       </c>
       <c r="M20" s="11" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O20" s="11" t="inlineStr">
@@ -33663,7 +34349,7 @@
       <c r="T20" s="11" t="inlineStr"/>
       <c r="U20" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032279</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032184</t>
         </is>
       </c>
       <c r="V20" s="11" t="inlineStr">
@@ -33675,7 +34361,7 @@
     <row r="21" ht="80" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>auto-2032302</t>
+          <t>auto-2032279</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
@@ -33723,12 +34409,12 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LAS AUTORIDADES INVOLUCRADAS EN DETERMINAR EL MONTO INDEMNIZATORIO POR ACTIVIDAD ADMINISTRATIVA IRREGULAR DEBEN ANALIZAR CÓMO LA PERSPECTIVA DE GÉNERO PUEDE CAMBIAR LA MANERA DE PERCIBIR Y VALORAR LAS CIRCUNSTANCIAS DEL CASO.</t>
+          <t>ACTA ADMINISTRATIVA DE INVESTIGACIÓN EN EL JUICIO LABORAL. TIENE VALOR PROBATORIO AUNQUE NO SE RATIFIQUE ANTE LA AUTORIDAD JURISDICCIONAL, CUANDO CONSIGNE EL TESTIMONIO DE NIÑAS, NIÑOS Y ADOLECENTES POR ACTOS DE CONNOTACIÓN SEXUAL REALIZADOS EN SU CONTRA.</t>
         </is>
       </c>
       <c r="L21" s="13" t="inlineStr">
         <is>
-          <t>2032302</t>
+          <t>2032279</t>
         </is>
       </c>
       <c r="M21" s="13" t="inlineStr"/>
@@ -33761,7 +34447,7 @@
       <c r="T21" s="13" t="inlineStr"/>
       <c r="U21" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032302</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032279</t>
         </is>
       </c>
       <c r="V21" s="13" t="inlineStr">
@@ -33773,7 +34459,7 @@
     <row r="22" ht="80" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>auto-2032309</t>
+          <t>auto-2032302</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
@@ -33821,18 +34507,18 @@
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA INSTITUCIÓN EDUCATIVA SE ENCUENTRA VINCULADA A CUMPLIR CON LA GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN.</t>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LAS AUTORIDADES INVOLUCRADAS EN DETERMINAR EL MONTO INDEMNIZATORIO POR ACTIVIDAD ADMINISTRATIVA IRREGULAR DEBEN ANALIZAR CÓMO LA PERSPECTIVA DE GÉNERO PUEDE CAMBIAR LA MANERA DE PERCIBIR Y VALORAR LAS CIRCUNSTANCIAS DEL CASO.</t>
         </is>
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>2032309</t>
+          <t>2032302</t>
         </is>
       </c>
       <c r="M22" s="11" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O22" s="11" t="inlineStr">
@@ -33859,7 +34545,7 @@
       <c r="T22" s="11" t="inlineStr"/>
       <c r="U22" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032309</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032302</t>
         </is>
       </c>
       <c r="V22" s="11" t="inlineStr">
@@ -33871,7 +34557,7 @@
     <row r="23" ht="80" customHeight="1">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>auto-2032325</t>
+          <t>auto-2032309</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
@@ -33919,12 +34605,12 @@
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. ESTÁNDAR PROBATORIO PARA DETERMINAR LA LEGALIDAD DE LA RESCISIÓN DE LA RELACIÓN LABORAL.</t>
+          <t>ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA INSTITUCIÓN EDUCATIVA SE ENCUENTRA VINCULADA A CUMPLIR CON LA GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN.</t>
         </is>
       </c>
       <c r="L23" s="13" t="inlineStr">
         <is>
-          <t>2032325</t>
+          <t>2032309</t>
         </is>
       </c>
       <c r="M23" s="13" t="inlineStr"/>
@@ -33957,7 +34643,7 @@
       <c r="T23" s="13" t="inlineStr"/>
       <c r="U23" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032325</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032309</t>
         </is>
       </c>
       <c r="V23" s="13" t="inlineStr">
@@ -33969,7 +34655,7 @@
     <row r="24" ht="80" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>auto-2032326</t>
+          <t>auto-2032325</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
@@ -34017,12 +34703,12 @@
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA AUTORIDAD JURISDICCIONAL DEBE ARMONIZAR EL PRINCIPIO DE PRESUNCIÓN DE INOCENCIA CON LA PERSPECTIVA DE GÉNERO.</t>
+          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. ESTÁNDAR PROBATORIO PARA DETERMINAR LA LEGALIDAD DE LA RESCISIÓN DE LA RELACIÓN LABORAL.</t>
         </is>
       </c>
       <c r="L24" s="11" t="inlineStr">
         <is>
-          <t>2032326</t>
+          <t>2032325</t>
         </is>
       </c>
       <c r="M24" s="11" t="inlineStr"/>
@@ -34055,7 +34741,7 @@
       <c r="T24" s="11" t="inlineStr"/>
       <c r="U24" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032326</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032325</t>
         </is>
       </c>
       <c r="V24" s="11" t="inlineStr">
@@ -34067,7 +34753,7 @@
     <row r="25" ht="80" customHeight="1">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>auto-2032327</t>
+          <t>auto-2032326</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
@@ -34115,12 +34801,12 @@
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>ESTÁNDAR DE LA PERSONA OBSERVADORA RAZONABLE. ASPECTOS QUE DEBE PONDERAR LA AUTORIDAD LABORAL PARA DETERMINAR LA EVENTUAL GRAVEDAD DE LA FALTA DE PROBIDAD ATRIBUIDA A LA PERSONA TRABAJADORA EN CASOS DE ACOSO U HOSTIGAMIENTO SEXUAL EN INSTITUCIONES EDUCATIVAS.</t>
+          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA AUTORIDAD JURISDICCIONAL DEBE ARMONIZAR EL PRINCIPIO DE PRESUNCIÓN DE INOCENCIA CON LA PERSPECTIVA DE GÉNERO.</t>
         </is>
       </c>
       <c r="L25" s="13" t="inlineStr">
         <is>
-          <t>2032327</t>
+          <t>2032326</t>
         </is>
       </c>
       <c r="M25" s="13" t="inlineStr"/>
@@ -34153,7 +34839,7 @@
       <c r="T25" s="13" t="inlineStr"/>
       <c r="U25" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032327</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032326</t>
         </is>
       </c>
       <c r="V25" s="13" t="inlineStr">
@@ -34165,7 +34851,7 @@
     <row r="26" ht="80" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>auto-2032338</t>
+          <t>auto-2032327</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
@@ -34213,12 +34899,12 @@
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>PERSPECTIVA DE GÉNERO. DEBE OBSERVARSE EN EL TRÁMITE Y RESOLUCIÓN DEL JUICIO LABORAL COMO GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN DE ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES.</t>
+          <t>ESTÁNDAR DE LA PERSONA OBSERVADORA RAZONABLE. ASPECTOS QUE DEBE PONDERAR LA AUTORIDAD LABORAL PARA DETERMINAR LA EVENTUAL GRAVEDAD DE LA FALTA DE PROBIDAD ATRIBUIDA A LA PERSONA TRABAJADORA EN CASOS DE ACOSO U HOSTIGAMIENTO SEXUAL EN INSTITUCIONES EDUCATIVAS.</t>
         </is>
       </c>
       <c r="L26" s="11" t="inlineStr">
         <is>
-          <t>2032338</t>
+          <t>2032327</t>
         </is>
       </c>
       <c r="M26" s="11" t="inlineStr"/>
@@ -34251,7 +34937,7 @@
       <c r="T26" s="11" t="inlineStr"/>
       <c r="U26" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032338</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032327</t>
         </is>
       </c>
       <c r="V26" s="11" t="inlineStr">
@@ -34263,7 +34949,7 @@
     <row r="27" ht="80" customHeight="1">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>auto-2032340</t>
+          <t>auto-2032338</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
@@ -34311,12 +34997,12 @@
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>PERSPECTIVA DE PERSONA ADULTA MAYOR. SU APLICACIÓN EXIGE IDENTIFICAR LAS CONDICIONES CONCRETAS DE VULNERABILIDAD QUE PUEDAN GENERAR UNA DESVENTAJA EN EL EJERCICIO DE SUS DERECHOS.</t>
+          <t>PERSPECTIVA DE GÉNERO. DEBE OBSERVARSE EN EL TRÁMITE Y RESOLUCIÓN DEL JUICIO LABORAL COMO GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN DE ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES.</t>
         </is>
       </c>
       <c r="L27" s="13" t="inlineStr">
         <is>
-          <t>2032340</t>
+          <t>2032338</t>
         </is>
       </c>
       <c r="M27" s="13" t="inlineStr"/>
@@ -34349,7 +35035,7 @@
       <c r="T27" s="13" t="inlineStr"/>
       <c r="U27" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032340</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032338</t>
         </is>
       </c>
       <c r="V27" s="13" t="inlineStr">
@@ -34361,7 +35047,7 @@
     <row r="28" ht="80" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>auto-2032347</t>
+          <t>auto-2032340</t>
         </is>
       </c>
       <c r="B28" s="11" t="n">
@@ -34409,12 +35095,12 @@
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>PRUEBA TESTIMONIAL EN EL PROCEDIMIENTO LABORAL. LA DECLARACIÓN RENDIDA POR PERSONAS DOCENTES GOZA DE RELEVANCIA PROBATORIA EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS.</t>
+          <t>PERSPECTIVA DE PERSONA ADULTA MAYOR. SU APLICACIÓN EXIGE IDENTIFICAR LAS CONDICIONES CONCRETAS DE VULNERABILIDAD QUE PUEDAN GENERAR UNA DESVENTAJA EN EL EJERCICIO DE SUS DERECHOS.</t>
         </is>
       </c>
       <c r="L28" s="11" t="inlineStr">
         <is>
-          <t>2032347</t>
+          <t>2032340</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr"/>
@@ -34447,7 +35133,7 @@
       <c r="T28" s="11" t="inlineStr"/>
       <c r="U28" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032347</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032340</t>
         </is>
       </c>
       <c r="V28" s="11" t="inlineStr">
@@ -34459,7 +35145,7 @@
     <row r="29" ht="80" customHeight="1">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>auto-2032376</t>
+          <t>auto-2032347</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
@@ -34507,18 +35193,18 @@
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>DAÑO MORAL RECLAMADO A LAS COMPAÑÍAS ASEGURADORAS. PUEDE GENERARSE ANTE ACTOS DISCRIMINATORIOS OCASIONADOS POR EL USO DE LENGUAJE BASADO EN ESTEREOTIPOS O PREJUICIOS POR RAZÓN DE GÉNERO.</t>
+          <t>PRUEBA TESTIMONIAL EN EL PROCEDIMIENTO LABORAL. LA DECLARACIÓN RENDIDA POR PERSONAS DOCENTES GOZA DE RELEVANCIA PROBATORIA EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS.</t>
         </is>
       </c>
       <c r="L29" s="13" t="inlineStr">
         <is>
-          <t>2032376</t>
+          <t>2032347</t>
         </is>
       </c>
       <c r="M29" s="13" t="inlineStr"/>
       <c r="N29" s="13" t="inlineStr">
         <is>
-          <t>viernes 03 de julio de 2026 10:10 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O29" s="13" t="inlineStr">
@@ -34545,7 +35231,7 @@
       <c r="T29" s="13" t="inlineStr"/>
       <c r="U29" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032376</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032347</t>
         </is>
       </c>
       <c r="V29" s="13" t="inlineStr">
@@ -34557,7 +35243,7 @@
     <row r="30" ht="80" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>amp-gen-001</t>
+          <t>auto-2032376</t>
         </is>
       </c>
       <c r="B30" s="11" t="n">
@@ -34575,12 +35261,12 @@
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género interseccional</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>Acceso a la justicia para mujeres cuidadoras</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G30" s="11" t="inlineStr">
@@ -34605,55 +35291,153 @@
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
+          <t>DAÑO MORAL RECLAMADO A LAS COMPAÑÍAS ASEGURADORAS. PUEDE GENERARSE ANTE ACTOS DISCRIMINATORIOS OCASIONADOS POR EL USO DE LENGUAJE BASADO EN ESTEREOTIPOS O PREJUICIOS POR RAZÓN DE GÉNERO.</t>
         </is>
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>2032067</t>
+          <t>2032376</t>
         </is>
       </c>
       <c r="M30" s="11" t="inlineStr"/>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 03 de julio de 2026 10:10 h</t>
         </is>
       </c>
       <c r="O30" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P30" s="11" t="inlineStr"/>
       <c r="Q30" s="11" t="inlineStr">
         <is>
-          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R30" s="11" t="inlineStr">
         <is>
-          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S30" s="11" t="inlineStr">
         <is>
-          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T30" s="11" t="inlineStr"/>
       <c r="U30" s="11" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032376</t>
+        </is>
+      </c>
+      <c r="V30" s="11" t="inlineStr">
+        <is>
+          <t>Perspectiva de género · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="80" customHeight="1">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>amp-gen-001</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Constitucional / DDHH</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Perspectiva de género interseccional</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>Acceso a la justicia para mujeres cuidadoras</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K31" s="14" t="inlineStr">
+        <is>
+          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
+        </is>
+      </c>
+      <c r="L31" s="13" t="inlineStr">
+        <is>
+          <t>2032067</t>
+        </is>
+      </c>
+      <c r="M31" s="13" t="inlineStr"/>
+      <c r="N31" s="13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O31" s="13" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P31" s="13" t="inlineStr"/>
+      <c r="Q31" s="13" t="inlineStr">
+        <is>
+          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
+        </is>
+      </c>
+      <c r="R31" s="13" t="inlineStr">
+        <is>
+          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
+        </is>
+      </c>
+      <c r="S31" s="13" t="inlineStr">
+        <is>
+          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
+        </is>
+      </c>
+      <c r="T31" s="13" t="inlineStr"/>
+      <c r="U31" s="13" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
         </is>
       </c>
-      <c r="V30" s="11" t="inlineStr">
+      <c r="V31" s="13" t="inlineStr">
         <is>
           <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V30"/>
+  <autoFilter ref="A1:V31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Acervo_Jurisprudencial.xlsx
+++ b/Acervo_Jurisprudencial.xlsx
@@ -20,12 +20,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Penal" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Acervo (maestra)'!$A$1:$V$208</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Administrativo'!$A$1:$V$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Amparo'!$A$1:$V$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Acervo (maestra)'!$A$1:$V$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Administrativo'!$A$1:$V$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Amparo'!$A$1:$V$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Civil'!$A$1:$V$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Civil — Condominio'!$A$1:$V$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Constitucional - DDHH'!$A$1:$V$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Constitucional - DDHH'!$A$1:$V$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Fiscal'!$A$1:$V$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Laboral'!$A$1:$V$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Mercantil'!$A$1:$V$20</definedName>
@@ -635,7 +635,7 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
@@ -645,11 +645,11 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>Penal</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -6398,7 +6398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V208"/>
+  <dimension ref="A1:V213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16380,7 +16380,7 @@
     <row r="106" ht="80" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>auto-2032177</t>
+          <t>auto-2032790</t>
         </is>
       </c>
       <c r="B106" s="11" t="n">
@@ -16398,7 +16398,7 @@
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos</t>
+          <t>Derecho humano a la salud</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
@@ -16428,18 +16428,18 @@
       </c>
       <c r="K106" s="12" t="inlineStr">
         <is>
-          <t>PRUEBAS EN EL JUICIO CONTENCIOSO ADMINISTRATIVO FEDERAL. EL ARTÍCULO 40, PÁRRAFO SEGUNDO, DE LA LEY FEDERAL DE PROCEDIMIENTO CONTENCIOSO ADMINISTRATIVO NO VIOLA EL DERECHO DE ACCESO A LA JUSTICIA.</t>
+          <t>TRABAJADORA EMBARAZADA. LA AUTORIDAD JURISDICCIONAL LABORAL DEBE OTORGAR DE OFICIO LAS MEDIDAS CAUTELARES NECESARIAS PARA GARANTIZAR EL ACCESO A LOS SERVICIOS DE SALUD Y ATENCIÓN MÉDICA DURANTE EL EMBARAZO O EL EJERCICIO DEL DERECHO A LA MATERNIDAD PROTEGIDA.</t>
         </is>
       </c>
       <c r="L106" s="11" t="inlineStr">
         <is>
-          <t>2032177</t>
+          <t>2032790</t>
         </is>
       </c>
       <c r="M106" s="11" t="inlineStr"/>
       <c r="N106" s="11" t="inlineStr">
         <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
+          <t>viernes 16 de octubre de 2026 10:26 h</t>
         </is>
       </c>
       <c r="O106" s="11" t="inlineStr">
@@ -16466,19 +16466,19 @@
       <c r="T106" s="11" t="inlineStr"/>
       <c r="U106" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032177</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032790</t>
         </is>
       </c>
       <c r="V106" s="11" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
+          <t>Derecho humano a la salud · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="107" ht="80" customHeight="1">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>auto-2032233</t>
+          <t>auto-2032177</t>
         </is>
       </c>
       <c r="B107" s="13" t="n">
@@ -16526,18 +16526,18 @@
       </c>
       <c r="K107" s="14" t="inlineStr">
         <is>
-          <t>PROCEDIMIENTO DE SEPARACIÓN DEL CARGO PREVISTO EN LOS ARTÍCULOS 209 Y 210 DE LA LEY ORGÁNICA DEL PODER JUDICIAL DEL ESTADO DE PUEBLA (ABROGADA). AL NO PREVER LA FORMA COMO DEBE INICIARSE NI LOS TÉRMINOS DE SU SUSTANCIACIÓN, LE ES APLICABLE EL DE RESPONSABILIDAD ADMINISTRATIVA.</t>
+          <t>PRUEBAS EN EL JUICIO CONTENCIOSO ADMINISTRATIVO FEDERAL. EL ARTÍCULO 40, PÁRRAFO SEGUNDO, DE LA LEY FEDERAL DE PROCEDIMIENTO CONTENCIOSO ADMINISTRATIVO NO VIOLA EL DERECHO DE ACCESO A LA JUSTICIA.</t>
         </is>
       </c>
       <c r="L107" s="13" t="inlineStr">
         <is>
-          <t>2032233</t>
+          <t>2032177</t>
         </is>
       </c>
       <c r="M107" s="13" t="inlineStr"/>
       <c r="N107" s="13" t="inlineStr">
         <is>
-          <t>viernes 05 de junio de 2026 10:11</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O107" s="13" t="inlineStr">
@@ -16564,7 +16564,7 @@
       <c r="T107" s="13" t="inlineStr"/>
       <c r="U107" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032233</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032177</t>
         </is>
       </c>
       <c r="V107" s="13" t="inlineStr">
@@ -16576,7 +16576,7 @@
     <row r="108" ht="80" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>auto-2032330</t>
+          <t>auto-2032233</t>
         </is>
       </c>
       <c r="B108" s="11" t="n">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="G108" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H108" s="11" t="inlineStr">
@@ -16624,18 +16624,18 @@
       </c>
       <c r="K108" s="12" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SALUD PARA EL BIENESTAR (INSABI). LE CORRESPONDE LA ADQUISICIÓN Y SUMINISTRO DE MEDICAMENTOS E INSUMOS O, EN SU CASO, EL FINANCIAMIENTO PARA SU ADQUISICIÓN, RELACIONADOS CON EL TRATAMIENTO DE ENFERMEDADES QUE PROVOCAN GASTOS CATASTRÓFICOS.</t>
+          <t>PROCEDIMIENTO DE SEPARACIÓN DEL CARGO PREVISTO EN LOS ARTÍCULOS 209 Y 210 DE LA LEY ORGÁNICA DEL PODER JUDICIAL DEL ESTADO DE PUEBLA (ABROGADA). AL NO PREVER LA FORMA COMO DEBE INICIARSE NI LOS TÉRMINOS DE SU SUSTANCIACIÓN, LE ES APLICABLE EL DE RESPONSABILIDAD ADMINISTRATIVA.</t>
         </is>
       </c>
       <c r="L108" s="11" t="inlineStr">
         <is>
-          <t>2032330</t>
+          <t>2032233</t>
         </is>
       </c>
       <c r="M108" s="11" t="inlineStr"/>
       <c r="N108" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 05 de junio de 2026 10:11</t>
         </is>
       </c>
       <c r="O108" s="11" t="inlineStr">
@@ -16662,7 +16662,7 @@
       <c r="T108" s="11" t="inlineStr"/>
       <c r="U108" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032330</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032233</t>
         </is>
       </c>
       <c r="V108" s="11" t="inlineStr">
@@ -16674,7 +16674,7 @@
     <row r="109" ht="80" customHeight="1">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>auto-2032462</t>
+          <t>auto-2032330</t>
         </is>
       </c>
       <c r="B109" s="13" t="n">
@@ -16702,7 +16702,7 @@
       </c>
       <c r="G109" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H109" s="13" t="inlineStr">
@@ -16722,18 +16722,18 @@
       </c>
       <c r="K109" s="14" t="inlineStr">
         <is>
-          <t>PROCEDIMIENTO DE RESPONSABILIDADES ADMINISTRATIVAS CONTRA UNA PERSONA JUEZA DEL SISTEMA PENAL ACUSATORIO EN EL ESTADO DE CHIHUAHUA. CORRESPONDE AL ÓRGANO DE ADMINISTRACIÓN JUDICIAL DETERMINAR LA ACTUALIZACIÓN DE LAS FALTAS ADMINISTRATIVAS QUE SE LE ATRIBUYEN.</t>
+          <t>INSTITUTO DE SALUD PARA EL BIENESTAR (INSABI). LE CORRESPONDE LA ADQUISICIÓN Y SUMINISTRO DE MEDICAMENTOS E INSUMOS O, EN SU CASO, EL FINANCIAMIENTO PARA SU ADQUISICIÓN, RELACIONADOS CON EL TRATAMIENTO DE ENFERMEDADES QUE PROVOCAN GASTOS CATASTRÓFICOS.</t>
         </is>
       </c>
       <c r="L109" s="13" t="inlineStr">
         <is>
-          <t>2032462</t>
+          <t>2032330</t>
         </is>
       </c>
       <c r="M109" s="13" t="inlineStr"/>
       <c r="N109" s="13" t="inlineStr">
         <is>
-          <t>viernes 07 de agosto de 2026 10:15 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O109" s="13" t="inlineStr">
@@ -16760,7 +16760,7 @@
       <c r="T109" s="13" t="inlineStr"/>
       <c r="U109" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032462</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032330</t>
         </is>
       </c>
       <c r="V109" s="13" t="inlineStr">
@@ -16772,7 +16772,7 @@
     <row r="110" ht="80" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>auto-2032502</t>
+          <t>auto-2032462</t>
         </is>
       </c>
       <c r="B110" s="11" t="n">
@@ -16820,18 +16820,18 @@
       </c>
       <c r="K110" s="12" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. PARA DETERMINAR SI SE ACTUALIZA POR SU ACTIVIDAD ADMINISTRATIVA IRREGULAR SE DEBE DEFINIR SI LOS DAÑOS RECLAMADOS SON DE CARÁCTER CONTRACTUAL O EXTRACONTRACTUAL.</t>
+          <t>PROCEDIMIENTO DE RESPONSABILIDADES ADMINISTRATIVAS CONTRA UNA PERSONA JUEZA DEL SISTEMA PENAL ACUSATORIO EN EL ESTADO DE CHIHUAHUA. CORRESPONDE AL ÓRGANO DE ADMINISTRACIÓN JUDICIAL DETERMINAR LA ACTUALIZACIÓN DE LAS FALTAS ADMINISTRATIVAS QUE SE LE ATRIBUYEN.</t>
         </is>
       </c>
       <c r="L110" s="11" t="inlineStr">
         <is>
-          <t>2032502</t>
+          <t>2032462</t>
         </is>
       </c>
       <c r="M110" s="11" t="inlineStr"/>
       <c r="N110" s="11" t="inlineStr">
         <is>
-          <t>viernes 14 de agosto de 2026 10:22 h</t>
+          <t>viernes 07 de agosto de 2026 10:15 h</t>
         </is>
       </c>
       <c r="O110" s="11" t="inlineStr">
@@ -16858,7 +16858,7 @@
       <c r="T110" s="11" t="inlineStr"/>
       <c r="U110" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032502</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032462</t>
         </is>
       </c>
       <c r="V110" s="11" t="inlineStr">
@@ -16870,7 +16870,7 @@
     <row r="111" ht="80" customHeight="1">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>auto-2032562</t>
+          <t>auto-2032502</t>
         </is>
       </c>
       <c r="B111" s="13" t="n">
@@ -16918,18 +16918,18 @@
       </c>
       <c r="K111" s="14" t="inlineStr">
         <is>
-          <t>IMPUESTO SOBRE LA RENTA. NO PROCEDE SU DEDUCCIÓN POR EL PAGO DE PENAS CONVENCIONALES EN TÉRMINOS DEL ARTÍCULO 32, FRACCIÓN VI, DE LA LEY RELATIVA, CUANDO EXISTE UN MECANISMO CONTRACTUAL PARA EVITAR SU PAGO Y NO SE EJERCE (LEGISLACIÓN VIGENTE EN 2013).</t>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. PARA DETERMINAR SI SE ACTUALIZA POR SU ACTIVIDAD ADMINISTRATIVA IRREGULAR SE DEBE DEFINIR SI LOS DAÑOS RECLAMADOS SON DE CARÁCTER CONTRACTUAL O EXTRACONTRACTUAL.</t>
         </is>
       </c>
       <c r="L111" s="13" t="inlineStr">
         <is>
-          <t>2032562</t>
+          <t>2032502</t>
         </is>
       </c>
       <c r="M111" s="13" t="inlineStr"/>
       <c r="N111" s="13" t="inlineStr">
         <is>
-          <t>viernes 28 de agosto de 2026 10:36 h</t>
+          <t>viernes 14 de agosto de 2026 10:22 h</t>
         </is>
       </c>
       <c r="O111" s="13" t="inlineStr">
@@ -16956,7 +16956,7 @@
       <c r="T111" s="13" t="inlineStr"/>
       <c r="U111" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032562</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032502</t>
         </is>
       </c>
       <c r="V111" s="13" t="inlineStr">
@@ -16968,7 +16968,7 @@
     <row r="112" ht="80" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>auto-2032717</t>
+          <t>auto-2032562</t>
         </is>
       </c>
       <c r="B112" s="11" t="n">
@@ -17016,18 +17016,18 @@
       </c>
       <c r="K112" s="12" t="inlineStr">
         <is>
-          <t>RECURSO DE REVISIÓN ADMINISTRATIVA. ES IMPROCEDENTE CONTRA LA SENTENCIA EMITIDA POR LA SALA SUPERIOR DEL TRIBUNAL DE JUSTICIA ADMINISTRATIVA DEL ESTADO DE JALISCO, QUE RESUELVE UN RECURSO DE APELACIÓN EN UN ASUNTO DE RESPONSABILIDAD ADMINISTRATIVA.</t>
+          <t>IMPUESTO SOBRE LA RENTA. NO PROCEDE SU DEDUCCIÓN POR EL PAGO DE PENAS CONVENCIONALES EN TÉRMINOS DEL ARTÍCULO 32, FRACCIÓN VI, DE LA LEY RELATIVA, CUANDO EXISTE UN MECANISMO CONTRACTUAL PARA EVITAR SU PAGO Y NO SE EJERCE (LEGISLACIÓN VIGENTE EN 2013).</t>
         </is>
       </c>
       <c r="L112" s="11" t="inlineStr">
         <is>
-          <t>2032717</t>
+          <t>2032562</t>
         </is>
       </c>
       <c r="M112" s="11" t="inlineStr"/>
       <c r="N112" s="11" t="inlineStr">
         <is>
-          <t>viernes 02 de octubre de 2026 10:12 h</t>
+          <t>viernes 28 de agosto de 2026 10:36 h</t>
         </is>
       </c>
       <c r="O112" s="11" t="inlineStr">
@@ -17054,7 +17054,7 @@
       <c r="T112" s="11" t="inlineStr"/>
       <c r="U112" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032717</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032562</t>
         </is>
       </c>
       <c r="V112" s="11" t="inlineStr">
@@ -17066,7 +17066,7 @@
     <row r="113" ht="80" customHeight="1">
       <c r="A113" s="13" t="inlineStr">
         <is>
-          <t>amp-eje-001</t>
+          <t>auto-2032717</t>
         </is>
       </c>
       <c r="B113" s="13" t="n">
@@ -17079,17 +17079,17 @@
       </c>
       <c r="D113" s="13" t="inlineStr">
         <is>
-          <t>Amparo</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>Amparo contra normas generales</t>
+          <t>Responsabilidad administrativa de servidores públicos</t>
         </is>
       </c>
       <c r="F113" s="13" t="inlineStr">
         <is>
-          <t>Efectos reflejos del fallo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G113" s="13" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="H113" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I113" s="13" t="inlineStr">
@@ -17114,57 +17114,57 @@
       </c>
       <c r="K113" s="14" t="inlineStr">
         <is>
-          <t>AMPARO CONTRA NORMAS GENERALES. SU NEGATIVA VINCULA Y TIENE EFECTOS REFLEJOS EN OTROS LITIGIOS DONDE LA MISMA PERSONA SOLICITE, EN EJERCICIO DEL CONTROL DIFUSO O DE CONSTITUCIONALIDAD Y CONVENCIONALIDAD EX OFFICIO, LA INAPLICACIÓN DE AQUÉLLAS.</t>
+          <t>RECURSO DE REVISIÓN ADMINISTRATIVA. ES IMPROCEDENTE CONTRA LA SENTENCIA EMITIDA POR LA SALA SUPERIOR DEL TRIBUNAL DE JUSTICIA ADMINISTRATIVA DEL ESTADO DE JALISCO, QUE RESUELVE UN RECURSO DE APELACIÓN EN UN ASUNTO DE RESPONSABILIDAD ADMINISTRATIVA.</t>
         </is>
       </c>
       <c r="L113" s="13" t="inlineStr">
         <is>
-          <t>2029745</t>
+          <t>2032717</t>
         </is>
       </c>
       <c r="M113" s="13" t="inlineStr"/>
       <c r="N113" s="13" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>viernes 02 de octubre de 2026 10:12 h</t>
         </is>
       </c>
       <c r="O113" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P113" s="13" t="inlineStr"/>
       <c r="Q113" s="13" t="inlineStr">
         <is>
-          <t>Si una persona pierde amparo contra norma general, esa cosa juzgada le aplica también en otros litigios donde pretenda inaplicación de la misma norma por control difuso.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R113" s="13" t="inlineStr">
         <is>
-          <t>Cierra puerta a relitigar inconstitucionalidad por vías paralelas.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S113" s="13" t="inlineStr">
         <is>
-          <t>Si ya perdiste amparo contra norma, no insistas vía control difuso en otro juicio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T113" s="13" t="inlineStr"/>
       <c r="U113" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029745</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032717</t>
         </is>
       </c>
       <c r="V113" s="13" t="inlineStr">
         <is>
-          <t>amparo normas · control difuso · efectos reflejos</t>
+          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="114" ht="80" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>auto-2032478</t>
+          <t>amp-eje-001</t>
         </is>
       </c>
       <c r="B114" s="11" t="n">
@@ -17182,12 +17182,12 @@
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>Procedencia del amparo</t>
+          <t>Amparo contra normas generales</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Efectos reflejos del fallo</t>
         </is>
       </c>
       <c r="G114" s="11" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="H114" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I114" s="11" t="inlineStr">
@@ -17212,57 +17212,57 @@
       </c>
       <c r="K114" s="12" t="inlineStr">
         <is>
-          <t>ACCIÓN PERSONAL PARA RECUPERAR LA POSESIÓN DE UN BIEN INMUEBLE ENTRE EXCONCUBINOS. ES IMPROCEDENTE CUANDO ÉSTE FORMA PARTE DEL DERECHO DE HABITACIÓN DE LAS PERSONAS ACREEDORAS ALIMENTARIAS.</t>
+          <t>AMPARO CONTRA NORMAS GENERALES. SU NEGATIVA VINCULA Y TIENE EFECTOS REFLEJOS EN OTROS LITIGIOS DONDE LA MISMA PERSONA SOLICITE, EN EJERCICIO DEL CONTROL DIFUSO O DE CONSTITUCIONALIDAD Y CONVENCIONALIDAD EX OFFICIO, LA INAPLICACIÓN DE AQUÉLLAS.</t>
         </is>
       </c>
       <c r="L114" s="11" t="inlineStr">
         <is>
-          <t>2032478</t>
+          <t>2029745</t>
         </is>
       </c>
       <c r="M114" s="11" t="inlineStr"/>
       <c r="N114" s="11" t="inlineStr">
         <is>
-          <t>viernes 14 de agosto de 2026 10:22 h</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O114" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P114" s="11" t="inlineStr"/>
       <c r="Q114" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Si una persona pierde amparo contra norma general, esa cosa juzgada le aplica también en otros litigios donde pretenda inaplicación de la misma norma por control difuso.</t>
         </is>
       </c>
       <c r="R114" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Cierra puerta a relitigar inconstitucionalidad por vías paralelas.</t>
         </is>
       </c>
       <c r="S114" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Si ya perdiste amparo contra norma, no insistas vía control difuso en otro juicio.</t>
         </is>
       </c>
       <c r="T114" s="11" t="inlineStr"/>
       <c r="U114" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032478</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029745</t>
         </is>
       </c>
       <c r="V114" s="11" t="inlineStr">
         <is>
-          <t>Procedencia del amparo · actualización automática</t>
+          <t>amparo normas · control difuso · efectos reflejos</t>
         </is>
       </c>
     </row>
     <row r="115" ht="80" customHeight="1">
       <c r="A115" s="13" t="inlineStr">
         <is>
-          <t>auto-2032523</t>
+          <t>auto-2032478</t>
         </is>
       </c>
       <c r="B115" s="13" t="n">
@@ -17310,18 +17310,18 @@
       </c>
       <c r="K115" s="14" t="inlineStr">
         <is>
-          <t>INTERÉS LEGÍTIMO EN AMPARO INDIRECTO. CONSTITUYE UN CONCEPTO ÍNTIMAMENTE VINCULADO CON LOS DERECHOS DE ACCESO A LA JUSTICIA Y DE PARTICIPACIÓN DEMOCRÁTICA PARA LA PROTECCIÓN EFECTIVA DE LOS DERECHOS HUMANOS.</t>
+          <t>ACCIÓN PERSONAL PARA RECUPERAR LA POSESIÓN DE UN BIEN INMUEBLE ENTRE EXCONCUBINOS. ES IMPROCEDENTE CUANDO ÉSTE FORMA PARTE DEL DERECHO DE HABITACIÓN DE LAS PERSONAS ACREEDORAS ALIMENTARIAS.</t>
         </is>
       </c>
       <c r="L115" s="13" t="inlineStr">
         <is>
-          <t>2032523</t>
+          <t>2032478</t>
         </is>
       </c>
       <c r="M115" s="13" t="inlineStr"/>
       <c r="N115" s="13" t="inlineStr">
         <is>
-          <t>viernes 21 de agosto de 2026 10:29 h</t>
+          <t>viernes 14 de agosto de 2026 10:22 h</t>
         </is>
       </c>
       <c r="O115" s="13" t="inlineStr">
@@ -17348,7 +17348,7 @@
       <c r="T115" s="13" t="inlineStr"/>
       <c r="U115" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032523</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032478</t>
         </is>
       </c>
       <c r="V115" s="13" t="inlineStr">
@@ -17360,7 +17360,7 @@
     <row r="116" ht="80" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>auto-2032525</t>
+          <t>auto-2032523</t>
         </is>
       </c>
       <c r="B116" s="11" t="n">
@@ -17408,12 +17408,12 @@
       </c>
       <c r="K116" s="12" t="inlineStr">
         <is>
-          <t>LEYES AUTOAPLICATIVAS. SU CONCEPCIÓN ACTUAL DEBE INTERPRETARSE A LA LUZ DEL INTERÉS LEGÍTIMO Y DEL DERECHO DE ACCESO A LA JUSTICIA.</t>
+          <t>INTERÉS LEGÍTIMO EN AMPARO INDIRECTO. CONSTITUYE UN CONCEPTO ÍNTIMAMENTE VINCULADO CON LOS DERECHOS DE ACCESO A LA JUSTICIA Y DE PARTICIPACIÓN DEMOCRÁTICA PARA LA PROTECCIÓN EFECTIVA DE LOS DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L116" s="11" t="inlineStr">
         <is>
-          <t>2032525</t>
+          <t>2032523</t>
         </is>
       </c>
       <c r="M116" s="11" t="inlineStr"/>
@@ -17446,7 +17446,7 @@
       <c r="T116" s="11" t="inlineStr"/>
       <c r="U116" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032525</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032523</t>
         </is>
       </c>
       <c r="V116" s="11" t="inlineStr">
@@ -17458,7 +17458,7 @@
     <row r="117" ht="80" customHeight="1">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>auto-2032701</t>
+          <t>auto-2032525</t>
         </is>
       </c>
       <c r="B117" s="13" t="n">
@@ -17486,7 +17486,7 @@
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H117" s="13" t="inlineStr">
@@ -17506,18 +17506,18 @@
       </c>
       <c r="K117" s="14" t="inlineStr">
         <is>
-          <t>INTERÉS JURÍDICO EN AMPARO INDIRECTO. LO TIENE LA PERSONA APODERADA LEGAL DE LA PARTE TRABAJADORA REVOCADA POR EL TRIBUNAL LABORAL EN TÉRMINOS DEL ARTÍCULO 685 BIS DE LA LEY FEDERAL DEL TRABAJO.</t>
+          <t>LEYES AUTOAPLICATIVAS. SU CONCEPCIÓN ACTUAL DEBE INTERPRETARSE A LA LUZ DEL INTERÉS LEGÍTIMO Y DEL DERECHO DE ACCESO A LA JUSTICIA.</t>
         </is>
       </c>
       <c r="L117" s="13" t="inlineStr">
         <is>
-          <t>2032701</t>
+          <t>2032525</t>
         </is>
       </c>
       <c r="M117" s="13" t="inlineStr"/>
       <c r="N117" s="13" t="inlineStr">
         <is>
-          <t>viernes 02 de octubre de 2026 10:12 h</t>
+          <t>viernes 21 de agosto de 2026 10:29 h</t>
         </is>
       </c>
       <c r="O117" s="13" t="inlineStr">
@@ -17544,7 +17544,7 @@
       <c r="T117" s="13" t="inlineStr"/>
       <c r="U117" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032701</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032525</t>
         </is>
       </c>
       <c r="V117" s="13" t="inlineStr">
@@ -17556,7 +17556,7 @@
     <row r="118" ht="80" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>amp-sus-002</t>
+          <t>auto-2032701</t>
         </is>
       </c>
       <c r="B118" s="11" t="n">
@@ -17574,17 +17574,17 @@
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>Suspensión</t>
+          <t>Procedencia del amparo</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
-          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G118" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H118" s="11" t="inlineStr">
@@ -17604,57 +17604,57 @@
       </c>
       <c r="K118" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
+          <t>INTERÉS JURÍDICO EN AMPARO INDIRECTO. LO TIENE LA PERSONA APODERADA LEGAL DE LA PARTE TRABAJADORA REVOCADA POR EL TRIBUNAL LABORAL EN TÉRMINOS DEL ARTÍCULO 685 BIS DE LA LEY FEDERAL DEL TRABAJO.</t>
         </is>
       </c>
       <c r="L118" s="11" t="inlineStr">
         <is>
-          <t>2032118</t>
+          <t>2032701</t>
         </is>
       </c>
       <c r="M118" s="11" t="inlineStr"/>
       <c r="N118" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 02 de octubre de 2026 10:12 h</t>
         </is>
       </c>
       <c r="O118" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P118" s="11" t="inlineStr"/>
       <c r="Q118" s="11" t="inlineStr">
         <is>
-          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R118" s="11" t="inlineStr">
         <is>
-          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S118" s="11" t="inlineStr">
         <is>
-          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T118" s="11" t="inlineStr"/>
       <c r="U118" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032701</t>
         </is>
       </c>
       <c r="V118" s="11" t="inlineStr">
         <is>
-          <t>suspensión amparo · medida cautelar · 12a Época</t>
+          <t>Procedencia del amparo · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="119" ht="80" customHeight="1">
       <c r="A119" s="13" t="inlineStr">
         <is>
-          <t>amp-sus-003</t>
+          <t>auto-2032784</t>
         </is>
       </c>
       <c r="B119" s="13" t="n">
@@ -17672,12 +17672,12 @@
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>Suspensión</t>
+          <t>Procedencia del amparo</t>
         </is>
       </c>
       <c r="F119" s="13" t="inlineStr">
         <is>
-          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G119" s="13" t="inlineStr">
@@ -17702,57 +17702,57 @@
       </c>
       <c r="K119" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
+          <t>REPRESENTANTE ESPECIAL DE UNA PERSONA MENOR DE EDAD EN EL JUICIO DE AMPARO. DEBE NOMBRARSE CUANDO UN PROGENITOR PROMUEVE EL JUICIO, PERO NO EJERCE CORRECTAMENTE LA REPRESENTACIÓN PARA PROTEGER LOS INTERESES DE AQUÉLLA (INTERPRETACIÓN EXTENSIVA DEL ARTÍCULO 8o. DE LA LEY DE AMPARO).</t>
         </is>
       </c>
       <c r="L119" s="13" t="inlineStr">
         <is>
-          <t>2032066</t>
+          <t>2032784</t>
         </is>
       </c>
       <c r="M119" s="13" t="inlineStr"/>
       <c r="N119" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 16 de octubre de 2026</t>
         </is>
       </c>
       <c r="O119" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P119" s="13" t="inlineStr"/>
       <c r="Q119" s="13" t="inlineStr">
         <is>
-          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R119" s="13" t="inlineStr">
         <is>
-          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S119" s="13" t="inlineStr">
         <is>
-          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T119" s="13" t="inlineStr"/>
       <c r="U119" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032066</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032784</t>
         </is>
       </c>
       <c r="V119" s="13" t="inlineStr">
         <is>
-          <t>suspensión restitutoria · incapacidad médica · IMSS · 12a Época</t>
+          <t>Procedencia del amparo · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="120" ht="80" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>auto-2032354</t>
+          <t>amp-sus-002</t>
         </is>
       </c>
       <c r="B120" s="11" t="n">
@@ -17775,7 +17775,7 @@
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
         </is>
       </c>
       <c r="G120" s="11" t="inlineStr">
@@ -17800,57 +17800,57 @@
       </c>
       <c r="K120" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. AL PROVEER SOBRE SU CONCESIÓN CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN, SE DEBE CONSIDERAR QUE LAS REPERCUSIONES NEGATIVAS DE LA BIOMETRÍA EMPEORAN GRAVEMENTE EN EL MODELO ECONÓMICO ACTUAL DEL CAPITALISMO DE VIGILANCIA.</t>
+          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L120" s="11" t="inlineStr">
         <is>
-          <t>2032354</t>
+          <t>2032118</t>
         </is>
       </c>
       <c r="M120" s="11" t="inlineStr"/>
       <c r="N120" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O120" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P120" s="11" t="inlineStr"/>
       <c r="Q120" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
         </is>
       </c>
       <c r="R120" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
         </is>
       </c>
       <c r="S120" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
         </is>
       </c>
       <c r="T120" s="11" t="inlineStr"/>
       <c r="U120" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032354</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
         </is>
       </c>
       <c r="V120" s="11" t="inlineStr">
         <is>
-          <t>Suspensión · actualización automática</t>
+          <t>suspensión amparo · medida cautelar · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="121" ht="80" customHeight="1">
       <c r="A121" s="13" t="inlineStr">
         <is>
-          <t>auto-2032355</t>
+          <t>amp-sus-003</t>
         </is>
       </c>
       <c r="B121" s="13" t="n">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="F121" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
         </is>
       </c>
       <c r="G121" s="13" t="inlineStr">
@@ -17898,57 +17898,57 @@
       </c>
       <c r="K121" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN QUE PREVÉ LA CREACIÓN DE LA CLAVE ÚNICA DE REGISTRO DE POBLACIÓN (CURP) BIOMÉTRICA.</t>
+          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
         </is>
       </c>
       <c r="L121" s="13" t="inlineStr">
         <is>
-          <t>2032355</t>
+          <t>2032066</t>
         </is>
       </c>
       <c r="M121" s="13" t="inlineStr"/>
       <c r="N121" s="13" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O121" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P121" s="13" t="inlineStr"/>
       <c r="Q121" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
         </is>
       </c>
       <c r="R121" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
         </is>
       </c>
       <c r="S121" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
         </is>
       </c>
       <c r="T121" s="13" t="inlineStr"/>
       <c r="U121" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032355</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032066</t>
         </is>
       </c>
       <c r="V121" s="13" t="inlineStr">
         <is>
-          <t>Suspensión · actualización automática</t>
+          <t>suspensión restitutoria · incapacidad médica · IMSS · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="122" ht="80" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>auto-2032475</t>
+          <t>auto-2032354</t>
         </is>
       </c>
       <c r="B122" s="11" t="n">
@@ -17996,18 +17996,18 @@
       </c>
       <c r="K122" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CON EFECTOS RESTITUTORIOS ANTICIPADOS CONTRA LA OMISIÓN DE PAGO CORRESPONDIENTE AL PROGRAMA PENSIÓN PARA EL BIENESTAR DE LAS PERSONAS CON DISCAPACIDAD PERMANENTE.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. AL PROVEER SOBRE SU CONCESIÓN CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN, SE DEBE CONSIDERAR QUE LAS REPERCUSIONES NEGATIVAS DE LA BIOMETRÍA EMPEORAN GRAVEMENTE EN EL MODELO ECONÓMICO ACTUAL DEL CAPITALISMO DE VIGILANCIA.</t>
         </is>
       </c>
       <c r="L122" s="11" t="inlineStr">
         <is>
-          <t>2032475</t>
+          <t>2032354</t>
         </is>
       </c>
       <c r="M122" s="11" t="inlineStr"/>
       <c r="N122" s="11" t="inlineStr">
         <is>
-          <t>viernes 07 de agosto de 2026 10:15 h</t>
+          <t>viernes 26 de junio de 2026 10:</t>
         </is>
       </c>
       <c r="O122" s="11" t="inlineStr">
@@ -18034,7 +18034,7 @@
       <c r="T122" s="11" t="inlineStr"/>
       <c r="U122" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032475</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032354</t>
         </is>
       </c>
       <c r="V122" s="11" t="inlineStr">
@@ -18046,7 +18046,7 @@
     <row r="123" ht="80" customHeight="1">
       <c r="A123" s="13" t="inlineStr">
         <is>
-          <t>auto-2032542</t>
+          <t>auto-2032355</t>
         </is>
       </c>
       <c r="B123" s="13" t="n">
@@ -18094,18 +18094,18 @@
       </c>
       <c r="K123" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN AMPARO INDIRECTO. ES IMPROCEDENTE CONTRA NORMAS RECLAMADAS COMO AUTOAPLICATIVAS, CUANDO EL PLAZO DE VACATIO LEGIS NO ACTUALIZA EL REQUISITO DE PELIGRO EN LA DEMORA.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN QUE PREVÉ LA CREACIÓN DE LA CLAVE ÚNICA DE REGISTRO DE POBLACIÓN (CURP) BIOMÉTRICA.</t>
         </is>
       </c>
       <c r="L123" s="13" t="inlineStr">
         <is>
-          <t>2032542</t>
+          <t>2032355</t>
         </is>
       </c>
       <c r="M123" s="13" t="inlineStr"/>
       <c r="N123" s="13" t="inlineStr">
         <is>
-          <t>viernes 21 de agosto de 2026 10:29 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O123" s="13" t="inlineStr">
@@ -18132,7 +18132,7 @@
       <c r="T123" s="13" t="inlineStr"/>
       <c r="U123" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032542</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032355</t>
         </is>
       </c>
       <c r="V123" s="13" t="inlineStr">
@@ -18144,7 +18144,7 @@
     <row r="124" ht="80" customHeight="1">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>auto-2032544</t>
+          <t>auto-2032475</t>
         </is>
       </c>
       <c r="B124" s="11" t="n">
@@ -18192,18 +18192,18 @@
       </c>
       <c r="K124" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA LOS EFECTOS Y CONSECUENCIAS DEL ARTÍCULO 49 BIS DEL CÓDIGO FISCAL DE LA FEDERACIÓN.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CON EFECTOS RESTITUTORIOS ANTICIPADOS CONTRA LA OMISIÓN DE PAGO CORRESPONDIENTE AL PROGRAMA PENSIÓN PARA EL BIENESTAR DE LAS PERSONAS CON DISCAPACIDAD PERMANENTE.</t>
         </is>
       </c>
       <c r="L124" s="11" t="inlineStr">
         <is>
-          <t>2032544</t>
+          <t>2032475</t>
         </is>
       </c>
       <c r="M124" s="11" t="inlineStr"/>
       <c r="N124" s="11" t="inlineStr">
         <is>
-          <t>viernes 21 de agosto de 2026 10:29 h</t>
+          <t>viernes 07 de agosto de 2026 10:15 h</t>
         </is>
       </c>
       <c r="O124" s="11" t="inlineStr">
@@ -18230,7 +18230,7 @@
       <c r="T124" s="11" t="inlineStr"/>
       <c r="U124" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032544</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032475</t>
         </is>
       </c>
       <c r="V124" s="11" t="inlineStr">
@@ -18242,7 +18242,7 @@
     <row r="125" ht="80" customHeight="1">
       <c r="A125" s="13" t="inlineStr">
         <is>
-          <t>auto-2032576</t>
+          <t>auto-2032542</t>
         </is>
       </c>
       <c r="B125" s="13" t="n">
@@ -18290,18 +18290,18 @@
       </c>
       <c r="K125" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA LA EXPULSIÓN DE UNA PERSONA ADOLESCENTE DE LA ESCUELA EN LA QUE CURSA LA EDUCACIÓN BÁSICA (SECUNDARIA) POR ACUMULAR FALTAS A SU REGLAMENTO.</t>
+          <t>SUSPENSIÓN EN AMPARO INDIRECTO. ES IMPROCEDENTE CONTRA NORMAS RECLAMADAS COMO AUTOAPLICATIVAS, CUANDO EL PLAZO DE VACATIO LEGIS NO ACTUALIZA EL REQUISITO DE PELIGRO EN LA DEMORA.</t>
         </is>
       </c>
       <c r="L125" s="13" t="inlineStr">
         <is>
-          <t>2032576</t>
+          <t>2032542</t>
         </is>
       </c>
       <c r="M125" s="13" t="inlineStr"/>
       <c r="N125" s="13" t="inlineStr">
         <is>
-          <t>viernes 28 de agosto de 2026 10:36 h</t>
+          <t>viernes 21 de agosto de 2026 10:29 h</t>
         </is>
       </c>
       <c r="O125" s="13" t="inlineStr">
@@ -18328,7 +18328,7 @@
       <c r="T125" s="13" t="inlineStr"/>
       <c r="U125" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032576</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032542</t>
         </is>
       </c>
       <c r="V125" s="13" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="126" ht="80" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>auto-2032685</t>
+          <t>auto-2032544</t>
         </is>
       </c>
       <c r="B126" s="11" t="n">
@@ -18388,18 +18388,18 @@
       </c>
       <c r="K126" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL. PROCEDE CON EFECTOS RESTITUTORIOS (TUTELA ANTICIPADA) CONTRA LA OMISIÓN DE REALIZAR AJUSTES AL PROCEDIMIENTO PARA PERSONAS CON DISCAPACIDAD.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA LOS EFECTOS Y CONSECUENCIAS DEL ARTÍCULO 49 BIS DEL CÓDIGO FISCAL DE LA FEDERACIÓN.</t>
         </is>
       </c>
       <c r="L126" s="11" t="inlineStr">
         <is>
-          <t>2032685</t>
+          <t>2032544</t>
         </is>
       </c>
       <c r="M126" s="11" t="inlineStr"/>
       <c r="N126" s="11" t="inlineStr">
         <is>
-          <t>viernes 25 de septiembre de 2026 10:34 h</t>
+          <t>viernes 21 de agosto de 2026 10:29 h</t>
         </is>
       </c>
       <c r="O126" s="11" t="inlineStr">
@@ -18426,7 +18426,7 @@
       <c r="T126" s="11" t="inlineStr"/>
       <c r="U126" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032685</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032544</t>
         </is>
       </c>
       <c r="V126" s="11" t="inlineStr">
@@ -18438,7 +18438,7 @@
     <row r="127" ht="80" customHeight="1">
       <c r="A127" s="13" t="inlineStr">
         <is>
-          <t>auto-2032235</t>
+          <t>auto-2032576</t>
         </is>
       </c>
       <c r="B127" s="13" t="n">
@@ -18451,12 +18451,12 @@
       </c>
       <c r="D127" s="13" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>Arrendamiento</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F127" s="13" t="inlineStr">
@@ -18486,18 +18486,18 @@
       </c>
       <c r="K127" s="14" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE PAGO EN ARRENDAMIENTO DE BIENES INMUEBLES. NO SE ACTUALIZA CUANDO EN EL CONTRATO SE PACTAN MODALIDADES ESPECÍFICAS DE PAGO Y EL ARRENDATARIO LAS VARÍA DE MANERA UNILATERAL.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA LA EXPULSIÓN DE UNA PERSONA ADOLESCENTE DE LA ESCUELA EN LA QUE CURSA LA EDUCACIÓN BÁSICA (SECUNDARIA) POR ACUMULAR FALTAS A SU REGLAMENTO.</t>
         </is>
       </c>
       <c r="L127" s="13" t="inlineStr">
         <is>
-          <t>2032235</t>
+          <t>2032576</t>
         </is>
       </c>
       <c r="M127" s="13" t="inlineStr"/>
       <c r="N127" s="13" t="inlineStr">
         <is>
-          <t>viernes 05 de junio de 2026 10:11 h</t>
+          <t>viernes 28 de agosto de 2026 10:36 h</t>
         </is>
       </c>
       <c r="O127" s="13" t="inlineStr">
@@ -18524,19 +18524,19 @@
       <c r="T127" s="13" t="inlineStr"/>
       <c r="U127" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032235</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032576</t>
         </is>
       </c>
       <c r="V127" s="13" t="inlineStr">
         <is>
-          <t>Arrendamiento · actualización automática</t>
+          <t>Suspensión · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="128" ht="80" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>auto-2032255</t>
+          <t>auto-2032685</t>
         </is>
       </c>
       <c r="B128" s="11" t="n">
@@ -18549,12 +18549,12 @@
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>Arrendamiento</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr">
@@ -18584,18 +18584,18 @@
       </c>
       <c r="K128" s="12" t="inlineStr">
         <is>
-          <t>CRÉDITOS CONTRA LA MASA EN EL CONCURSO MERCANTIL. SON LOS CONTRAÍDOS CON POSTERIORIDAD AL INICIO DEL CONCURSO MERCANTIL Y AL DICTADO DE LA SENTENCIA DE DECLARACIÓN, CON EXCEPCIÓN DE LOS CRÉDITOS LABORALES, FISCALES Y AQUELLOS CON GARANTÍA REAL.</t>
+          <t>SUSPENSIÓN PROVISIONAL. PROCEDE CON EFECTOS RESTITUTORIOS (TUTELA ANTICIPADA) CONTRA LA OMISIÓN DE REALIZAR AJUSTES AL PROCEDIMIENTO PARA PERSONAS CON DISCAPACIDAD.</t>
         </is>
       </c>
       <c r="L128" s="11" t="inlineStr">
         <is>
-          <t>2032255</t>
+          <t>2032685</t>
         </is>
       </c>
       <c r="M128" s="11" t="inlineStr"/>
       <c r="N128" s="11" t="inlineStr">
         <is>
-          <t>viernes 12 de junio de 2026 10:18 h</t>
+          <t>viernes 25 de septiembre de 2026 10:34 h</t>
         </is>
       </c>
       <c r="O128" s="11" t="inlineStr">
@@ -18622,19 +18622,19 @@
       <c r="T128" s="11" t="inlineStr"/>
       <c r="U128" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032255</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032685</t>
         </is>
       </c>
       <c r="V128" s="11" t="inlineStr">
         <is>
-          <t>Arrendamiento · actualización automática</t>
+          <t>Suspensión · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="129" ht="80" customHeight="1">
       <c r="A129" s="13" t="inlineStr">
         <is>
-          <t>auto-2032412</t>
+          <t>auto-2032758</t>
         </is>
       </c>
       <c r="B129" s="13" t="n">
@@ -18647,12 +18647,12 @@
       </c>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>Arrendamiento</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F129" s="13" t="inlineStr">
@@ -18682,18 +18682,18 @@
       </c>
       <c r="K129" s="14" t="inlineStr">
         <is>
-          <t>DESECHAMIENTO DE LA DEMANDA EN EL JUICIO ORAL MERCANTIL. ES INVÁLIDO CUANDO SE BASA EN UNA APRECIACIÓN FORMAL DEL DESAHOGO DE LA PREVENCIÓN REALIZADA EN TÉRMINOS DEL ARTÍCULO 1390 BIS 12 DEL CÓDIGO DE COMERCIO.</t>
+          <t>SUSPENSIÓN PROVISIONAL. PROCEDE CON EFECTOS RESTITUTORIOS CONTRA LA OMISIÓN DE SEÑALAR FECHA Y CELEBRAR LA AUDIENCIA INICIAL O DE VERIFICACIÓN Y APROBACIÓN DE ACUERDO REPARATORIO, CUANDO EXISTA DILACIÓN ABIERTA E INJUSTIFICADA.</t>
         </is>
       </c>
       <c r="L129" s="13" t="inlineStr">
         <is>
-          <t>2032412</t>
+          <t>2032758</t>
         </is>
       </c>
       <c r="M129" s="13" t="inlineStr"/>
       <c r="N129" s="13" t="inlineStr">
         <is>
-          <t>viernes 10 de julio de 2026 10:17 h</t>
+          <t>viernes 09 de octubre de 2026 10:19 h</t>
         </is>
       </c>
       <c r="O129" s="13" t="inlineStr">
@@ -18720,19 +18720,19 @@
       <c r="T129" s="13" t="inlineStr"/>
       <c r="U129" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032412</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032758</t>
         </is>
       </c>
       <c r="V129" s="13" t="inlineStr">
         <is>
-          <t>Arrendamiento · actualización automática</t>
+          <t>Suspensión · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="130" ht="80" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>auto-2032524</t>
+          <t>auto-2032777</t>
         </is>
       </c>
       <c r="B130" s="11" t="n">
@@ -18745,12 +18745,12 @@
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>Amparo</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
         <is>
-          <t>Arrendamiento</t>
+          <t>Suspensión</t>
         </is>
       </c>
       <c r="F130" s="11" t="inlineStr">
@@ -18780,18 +18780,18 @@
       </c>
       <c r="K130" s="12" t="inlineStr">
         <is>
-          <t>INTERÉS LEGÍTIMO EN AMPARO INDIRECTO. LO TIENEN LAS PERSONAS QUE ACREDITEN LA PROPIEDAD O POSESIÓN LEGAL DE INMUEBLES DESTINADOS A ESTANCIAS TURÍSTICAS EVENTUALES PARA RECLAMAR LA LEY DE TURISMO DE LA CIUDAD DE MÉXICO.</t>
+          <t>PELIGRO EN LA DEMORA Y APARIENCIA DEL BUEN DERECHO. ES INNECESARIO SU ESTUDIO CUANDO LA NEGATIVA DE LA SUSPENSIÓN DERIVA DE LA PRESENCIA NOTORIA DE UN MOTIVO QUE LEGALMENTE IMPOSIBILITA SU OTORGAMIENTO.</t>
         </is>
       </c>
       <c r="L130" s="11" t="inlineStr">
         <is>
-          <t>2032524</t>
+          <t>2032777</t>
         </is>
       </c>
       <c r="M130" s="11" t="inlineStr"/>
       <c r="N130" s="11" t="inlineStr">
         <is>
-          <t>viernes 21 de agosto de 2026 10:29 h</t>
+          <t>viernes 16 de octubre de 2026 10:26 h</t>
         </is>
       </c>
       <c r="O130" s="11" t="inlineStr">
@@ -18818,19 +18818,19 @@
       <c r="T130" s="11" t="inlineStr"/>
       <c r="U130" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032524</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032777</t>
         </is>
       </c>
       <c r="V130" s="11" t="inlineStr">
         <is>
-          <t>Arrendamiento · actualización automática</t>
+          <t>Suspensión · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="131" ht="80" customHeight="1">
       <c r="A131" s="13" t="inlineStr">
         <is>
-          <t>auto-2032688</t>
+          <t>auto-2032235</t>
         </is>
       </c>
       <c r="B131" s="13" t="n">
@@ -18878,18 +18878,18 @@
       </c>
       <c r="K131" s="14" t="inlineStr">
         <is>
-          <t>ARRENDAMIENTO DE BIENES INMUEBLES. EL ARTÍCULO 2448 D, PÁRRAFO SEGUNDO, DEL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL, APLICABLE PARA LA CIUDAD DE MÉXICO, NO VIOLA EL PRINCIPIO DE AUTONOMÍA DE LA VOLUNTAD NI EL DERECHO A LA LIBERTAD CONTRACTUAL.</t>
+          <t>PRESUNCIÓN DE PAGO EN ARRENDAMIENTO DE BIENES INMUEBLES. NO SE ACTUALIZA CUANDO EN EL CONTRATO SE PACTAN MODALIDADES ESPECÍFICAS DE PAGO Y EL ARRENDATARIO LAS VARÍA DE MANERA UNILATERAL.</t>
         </is>
       </c>
       <c r="L131" s="13" t="inlineStr">
         <is>
-          <t>2032688</t>
+          <t>2032235</t>
         </is>
       </c>
       <c r="M131" s="13" t="inlineStr"/>
       <c r="N131" s="13" t="inlineStr">
         <is>
-          <t>viernes 02 de octubre de 2026 10:12 h</t>
+          <t>viernes 05 de junio de 2026 10:11 h</t>
         </is>
       </c>
       <c r="O131" s="13" t="inlineStr">
@@ -18916,7 +18916,7 @@
       <c r="T131" s="13" t="inlineStr"/>
       <c r="U131" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032688</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032235</t>
         </is>
       </c>
       <c r="V131" s="13" t="inlineStr">
@@ -18928,7 +18928,7 @@
     <row r="132" ht="80" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>auto-2032689</t>
+          <t>auto-2032255</t>
         </is>
       </c>
       <c r="B132" s="11" t="n">
@@ -18976,18 +18976,18 @@
       </c>
       <c r="K132" s="12" t="inlineStr">
         <is>
-          <t>ARRENDAMIENTO DE BIENES INMUEBLES. EL ARTÍCULO 2448 F, PÁRRAFOS TERCERO Y CUARTO, DEL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL, APLICABLE PARA LA CIUDAD DE MÉXICO, NO VIOLA EL DERECHO A LA PRIVACIDAD.</t>
+          <t>CRÉDITOS CONTRA LA MASA EN EL CONCURSO MERCANTIL. SON LOS CONTRAÍDOS CON POSTERIORIDAD AL INICIO DEL CONCURSO MERCANTIL Y AL DICTADO DE LA SENTENCIA DE DECLARACIÓN, CON EXCEPCIÓN DE LOS CRÉDITOS LABORALES, FISCALES Y AQUELLOS CON GARANTÍA REAL.</t>
         </is>
       </c>
       <c r="L132" s="11" t="inlineStr">
         <is>
-          <t>2032689</t>
+          <t>2032255</t>
         </is>
       </c>
       <c r="M132" s="11" t="inlineStr"/>
       <c r="N132" s="11" t="inlineStr">
         <is>
-          <t>viernes 02 de octubre de 2026 10:12 h</t>
+          <t>viernes 12 de junio de 2026 10:18 h</t>
         </is>
       </c>
       <c r="O132" s="11" t="inlineStr">
@@ -19014,7 +19014,7 @@
       <c r="T132" s="11" t="inlineStr"/>
       <c r="U132" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032689</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032255</t>
         </is>
       </c>
       <c r="V132" s="11" t="inlineStr">
@@ -19026,7 +19026,7 @@
     <row r="133" ht="80" customHeight="1">
       <c r="A133" s="13" t="inlineStr">
         <is>
-          <t>auto-2032748</t>
+          <t>auto-2032412</t>
         </is>
       </c>
       <c r="B133" s="13" t="n">
@@ -19074,18 +19074,18 @@
       </c>
       <c r="K133" s="14" t="inlineStr">
         <is>
-          <t>NOTIFICACIÓN DE LA SENTENCIA DICTADA EN LA APELACIÓN. DEBE REALIZARSE DE FORMA PERSONAL CUANDO LA TRAMITACIÓN IRREGULAR DEL RECURSO Y EL TRANSCURSO DE UN PERIODO PROLONGADO MÁS ALLÁ DE LOS PLAZOS LEGALES PUEDAN DEJAR EN ESTADO DE INDEFENSIÓN A LA PERSONA APELANTE.</t>
+          <t>DESECHAMIENTO DE LA DEMANDA EN EL JUICIO ORAL MERCANTIL. ES INVÁLIDO CUANDO SE BASA EN UNA APRECIACIÓN FORMAL DEL DESAHOGO DE LA PREVENCIÓN REALIZADA EN TÉRMINOS DEL ARTÍCULO 1390 BIS 12 DEL CÓDIGO DE COMERCIO.</t>
         </is>
       </c>
       <c r="L133" s="13" t="inlineStr">
         <is>
-          <t>2032748</t>
+          <t>2032412</t>
         </is>
       </c>
       <c r="M133" s="13" t="inlineStr"/>
       <c r="N133" s="13" t="inlineStr">
         <is>
-          <t>viernes 09 de octubre de 2026 10:19 h</t>
+          <t>viernes 10 de julio de 2026 10:17 h</t>
         </is>
       </c>
       <c r="O133" s="13" t="inlineStr">
@@ -19112,7 +19112,7 @@
       <c r="T133" s="13" t="inlineStr"/>
       <c r="U133" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032748</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032412</t>
         </is>
       </c>
       <c r="V133" s="13" t="inlineStr">
@@ -19124,7 +19124,7 @@
     <row r="134" ht="80" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>civ-arr-003</t>
+          <t>auto-2032524</t>
         </is>
       </c>
       <c r="B134" s="11" t="n">
@@ -19147,7 +19147,7 @@
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
-          <t>Tácita reconducción</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G134" s="11" t="inlineStr">
@@ -19157,7 +19157,7 @@
       </c>
       <c r="H134" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I134" s="11" t="inlineStr">
@@ -19167,54 +19167,62 @@
       </c>
       <c r="J134" s="11" t="inlineStr">
         <is>
-          <t>Federal — interpreta CCCDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K134" s="12" t="inlineStr">
         <is>
-          <t>TÁCITA RECONDUCCIÓN DEL ARRENDAMIENTO. SUS REQUISITOS Y EFECTOS CONFORME AL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL.</t>
+          <t>INTERÉS LEGÍTIMO EN AMPARO INDIRECTO. LO TIENEN LAS PERSONAS QUE ACREDITEN LA PROPIEDAD O POSESIÓN LEGAL DE INMUEBLES DESTINADOS A ESTANCIAS TURÍSTICAS EVENTUALES PARA RECLAMAR LA LEY DE TURISMO DE LA CIUDAD DE MÉXICO.</t>
         </is>
       </c>
       <c r="L134" s="11" t="inlineStr">
         <is>
-          <t>2017872</t>
+          <t>2032524</t>
         </is>
       </c>
       <c r="M134" s="11" t="inlineStr"/>
-      <c r="N134" s="11" t="inlineStr"/>
-      <c r="O134" s="11" t="inlineStr"/>
+      <c r="N134" s="11" t="inlineStr">
+        <is>
+          <t>viernes 21 de agosto de 2026 10:29 h</t>
+        </is>
+      </c>
+      <c r="O134" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P134" s="11" t="inlineStr"/>
       <c r="Q134" s="11" t="inlineStr">
         <is>
-          <t>Vencido el contrato, si el arrendatario continúa en la posesión del bien con consentimiento del arrendador (recibos de renta o silencio) por más de 10 días, el contrato se considera renovado por tiempo indeterminado.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R134" s="11" t="inlineStr">
         <is>
-          <t>Trampa frecuente: el arrendador pierde plazo fijo por no actuar.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S134" s="11" t="inlineStr">
         <is>
-          <t>Al vencer el contrato, el arrendador debe requerir formalmente desocupación si no quiere renovación tácita. Recibir un solo pago posterior al vencimiento es indicio fuerte de reconducción.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T134" s="11" t="inlineStr"/>
       <c r="U134" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2017872</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032524</t>
         </is>
       </c>
       <c r="V134" s="11" t="inlineStr">
         <is>
-          <t>tácita reconducción · vencimiento · renovación</t>
+          <t>Arrendamiento · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="135" ht="80" customHeight="1">
       <c r="A135" s="13" t="inlineStr">
         <is>
-          <t>civ-arr-004</t>
+          <t>auto-2032688</t>
         </is>
       </c>
       <c r="B135" s="13" t="n">
@@ -19237,7 +19245,7 @@
       </c>
       <c r="F135" s="13" t="inlineStr">
         <is>
-          <t>Consignación de llaves no libera de pago</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G135" s="13" t="inlineStr">
@@ -19262,57 +19270,57 @@
       </c>
       <c r="K135" s="14" t="inlineStr">
         <is>
-          <t>ARRENDAMIENTO. LA CONSIGNACIÓN DE LLAVES DEL INMUEBLE ARRENDADO EXHIBIDAS MEDIANTE ESCRITO ANTE EL ÓRGANO JURISDICCIONAL NO LIBERA AL DEMANDADO DEL PAGO DE RENTAS, MANTENIMIENTO, SERVICIOS DE GAS Y AGUA, SI NO ACREDITA HABER IMPULSADO EL PROCEDIMIENTO.</t>
+          <t>ARRENDAMIENTO DE BIENES INMUEBLES. EL ARTÍCULO 2448 D, PÁRRAFO SEGUNDO, DEL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL, APLICABLE PARA LA CIUDAD DE MÉXICO, NO VIOLA EL PRINCIPIO DE AUTONOMÍA DE LA VOLUNTAD NI EL DERECHO A LA LIBERTAD CONTRACTUAL.</t>
         </is>
       </c>
       <c r="L135" s="13" t="inlineStr">
         <is>
-          <t>2031626</t>
+          <t>2032688</t>
         </is>
       </c>
       <c r="M135" s="13" t="inlineStr"/>
       <c r="N135" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 02 de octubre de 2026 10:12 h</t>
         </is>
       </c>
       <c r="O135" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P135" s="13" t="inlineStr"/>
       <c r="Q135" s="13" t="inlineStr">
         <is>
-          <t>El arrendatario que pretende terminar el contrato consignando las llaves debe impulsar la notificación al arrendador. Sin ese impulso procesal, sigue obligado al pago de rentas y servicios.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R135" s="13" t="inlineStr">
         <is>
-          <t>Defensa del arrendador contra inquilinos que abandonan sin notificar.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S135" s="13" t="inlineStr">
         <is>
-          <t>Inquilino que entrega llaves debe pedir actuario para notificar, no basta exhibirlas. Arrendador puede seguir cobrando hasta que el procedimiento esté impulsado.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T135" s="13" t="inlineStr"/>
       <c r="U135" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031626</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032688</t>
         </is>
       </c>
       <c r="V135" s="13" t="inlineStr">
         <is>
-          <t>arrendamiento · consignación llaves · 12a Época</t>
+          <t>Arrendamiento · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="136" ht="80" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>civ-arr-005</t>
+          <t>auto-2032689</t>
         </is>
       </c>
       <c r="B136" s="11" t="n">
@@ -19335,7 +19343,7 @@
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>Aviso de terminación — cómputo de plazo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G136" s="11" t="inlineStr">
@@ -19345,7 +19353,7 @@
       </c>
       <c r="H136" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I136" s="11" t="inlineStr">
@@ -19355,62 +19363,62 @@
       </c>
       <c r="J136" s="11" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K136" s="12" t="inlineStr">
         <is>
-          <t>CONTRATO DE ARRENDAMIENTO POR TIEMPO INDETERMINADO PARA PREDIOS URBANOS. LA OPORTUNIDAD DEL AVISO PARA DARLO POR CONCLUIDO DEBE COMPUTARSE EN DÍAS HÁBILES, A MENOS QUE LAS PARTES RENUNCIEN A ESE DERECHO.</t>
+          <t>ARRENDAMIENTO DE BIENES INMUEBLES. EL ARTÍCULO 2448 F, PÁRRAFOS TERCERO Y CUARTO, DEL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL, APLICABLE PARA LA CIUDAD DE MÉXICO, NO VIOLA EL DERECHO A LA PRIVACIDAD.</t>
         </is>
       </c>
       <c r="L136" s="11" t="inlineStr">
         <is>
-          <t>2024563</t>
+          <t>2032689</t>
         </is>
       </c>
       <c r="M136" s="11" t="inlineStr"/>
       <c r="N136" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>viernes 02 de octubre de 2026 10:12 h</t>
         </is>
       </c>
       <c r="O136" s="11" t="inlineStr">
         <is>
-          <t>Gaceta del SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P136" s="11" t="inlineStr"/>
       <c r="Q136" s="11" t="inlineStr">
         <is>
-          <t>El aviso de terminación de arrendamiento por tiempo indeterminado se computa en días HÁBILES por defecto. Solo si las partes pactaron expresamente días naturales, aplica esa modalidad.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R136" s="11" t="inlineStr">
         <is>
-          <t>Define plazo real para desocupación en CDMX.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S136" s="11" t="inlineStr">
         <is>
-          <t>Confusión frecuente: muchos contratos asumen días naturales sin pactarlo. El plazo es hábil. Hay que dar el aviso anticipándose.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T136" s="11" t="inlineStr"/>
       <c r="U136" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032689</t>
         </is>
       </c>
       <c r="V136" s="11" t="inlineStr">
         <is>
-          <t>arrendamiento CDMX · aviso terminación · días hábiles</t>
+          <t>Arrendamiento · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="137" ht="80" customHeight="1">
       <c r="A137" s="13" t="inlineStr">
         <is>
-          <t>fam-div-001</t>
+          <t>auto-2032748</t>
         </is>
       </c>
       <c r="B137" s="13" t="n">
@@ -19428,12 +19436,12 @@
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>Divorcio sin expresión de causa</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F137" s="13" t="inlineStr">
         <is>
-          <t>Procedencia del recurso de revocación</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G137" s="13" t="inlineStr">
@@ -19453,62 +19461,62 @@
       </c>
       <c r="J137" s="13" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K137" s="14" t="inlineStr">
         <is>
-          <t>DIVORCIO SIN EXPRESIÓN DE CAUSA. PROCEDENCIA DEL RECURSO DE REVOCACIÓN CONTRA LAS RESOLUCIONES DICTADAS DURANTE SU SUSTANCIACIÓN.</t>
+          <t>NOTIFICACIÓN DE LA SENTENCIA DICTADA EN LA APELACIÓN. DEBE REALIZARSE DE FORMA PERSONAL CUANDO LA TRAMITACIÓN IRREGULAR DEL RECURSO Y EL TRANSCURSO DE UN PERIODO PROLONGADO MÁS ALLÁ DE LOS PLAZOS LEGALES PUEDAN DEJAR EN ESTADO DE INDEFENSIÓN A LA PERSONA APELANTE.</t>
         </is>
       </c>
       <c r="L137" s="13" t="inlineStr">
         <is>
-          <t>2031170</t>
+          <t>2032748</t>
         </is>
       </c>
       <c r="M137" s="13" t="inlineStr"/>
       <c r="N137" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 09 de octubre de 2026 10:19 h</t>
         </is>
       </c>
       <c r="O137" s="13" t="inlineStr">
         <is>
-          <t>SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P137" s="13" t="inlineStr"/>
       <c r="Q137" s="13" t="inlineStr">
         <is>
-          <t>Las resoluciones dictadas durante la sustanciación del divorcio sin causa admiten recurso de revocación conforme a los arts. 685, 685 bis y 691 del CPC para CDMX.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R137" s="13" t="inlineStr">
         <is>
-          <t>Vía expedita contra resoluciones intermedias en divorcio incausado CDMX.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S137" s="13" t="inlineStr">
         <is>
-          <t>Antes era confusa la vía. Ahora con esta tesis se aplica revocación. Permite revisar rápidamente medidas provisionales sobre alimentos o convivencia.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T137" s="13" t="inlineStr"/>
       <c r="U137" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031170</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032748</t>
         </is>
       </c>
       <c r="V137" s="13" t="inlineStr">
         <is>
-          <t>divorcio incausado · revocación · CDMX · 12a Época</t>
+          <t>Arrendamiento · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="138" ht="80" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>fam-div-002</t>
+          <t>civ-arr-003</t>
         </is>
       </c>
       <c r="B138" s="11" t="n">
@@ -19526,12 +19534,12 @@
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>Divorcio sin expresión de causa</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr">
         <is>
-          <t>Amparo directo contra sentencia</t>
+          <t>Tácita reconducción</t>
         </is>
       </c>
       <c r="G138" s="11" t="inlineStr">
@@ -19541,7 +19549,7 @@
       </c>
       <c r="H138" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I138" s="11" t="inlineStr">
@@ -19551,62 +19559,54 @@
       </c>
       <c r="J138" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — interpreta CCCDMX</t>
         </is>
       </c>
       <c r="K138" s="12" t="inlineStr">
         <is>
-          <t>AMPARO DIRECTO. PROCEDE CONTRA LA SENTENCIA QUE DECLARA LA DISOLUCIÓN DEL VÍNCULO MATRIMONIAL EN UN JUICIO DE DIVORCIO SIN EXPRESIÓN DE CAUSA Y RESUELVE PROVISIONALMENTE SOBRE LOS ALIMENTOS U OTRAS CUESTIONES INHERENTES.</t>
+          <t>TÁCITA RECONDUCCIÓN DEL ARRENDAMIENTO. SUS REQUISITOS Y EFECTOS CONFORME AL CÓDIGO CIVIL PARA EL DISTRITO FEDERAL.</t>
         </is>
       </c>
       <c r="L138" s="11" t="inlineStr">
         <is>
-          <t>2029853</t>
+          <t>2017872</t>
         </is>
       </c>
       <c r="M138" s="11" t="inlineStr"/>
-      <c r="N138" s="11" t="inlineStr">
-        <is>
-          <t>2024-2025</t>
-        </is>
-      </c>
-      <c r="O138" s="11" t="inlineStr">
-        <is>
-          <t>SJF — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N138" s="11" t="inlineStr"/>
+      <c r="O138" s="11" t="inlineStr"/>
       <c r="P138" s="11" t="inlineStr"/>
       <c r="Q138" s="11" t="inlineStr">
         <is>
-          <t>La sentencia de divorcio sin expresión de causa que resuelve sobre alimentos provisionales o cuestiones inherentes es definitiva para efectos del amparo directo.</t>
+          <t>Vencido el contrato, si el arrendatario continúa en la posesión del bien con consentimiento del arrendador (recibos de renta o silencio) por más de 10 días, el contrato se considera renovado por tiempo indeterminado.</t>
         </is>
       </c>
       <c r="R138" s="11" t="inlineStr">
         <is>
-          <t>Define vía de impugnación: amparo directo, no indirecto.</t>
+          <t>Trampa frecuente: el arrendador pierde plazo fijo por no actuar.</t>
         </is>
       </c>
       <c r="S138" s="11" t="inlineStr">
         <is>
-          <t>Importante para no equivocarse de vía. Si tu sentencia incluye medidas sobre alimentos: amparo directo. Si solo es disolución limpia: dependerá del caso.</t>
+          <t>Al vencer el contrato, el arrendador debe requerir formalmente desocupación si no quiere renovación tácita. Recibir un solo pago posterior al vencimiento es indicio fuerte de reconducción.</t>
         </is>
       </c>
       <c r="T138" s="11" t="inlineStr"/>
       <c r="U138" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029853</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2017872</t>
         </is>
       </c>
       <c r="V138" s="11" t="inlineStr">
         <is>
-          <t>divorcio incausado · amparo directo · alimentos</t>
+          <t>tácita reconducción · vencimiento · renovación</t>
         </is>
       </c>
     </row>
     <row r="139" ht="80" customHeight="1">
       <c r="A139" s="13" t="inlineStr">
         <is>
-          <t>civ-ext-003</t>
+          <t>civ-arr-004</t>
         </is>
       </c>
       <c r="B139" s="13" t="n">
@@ -19624,12 +19624,12 @@
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>Extinción de dominio</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F139" s="13" t="inlineStr">
         <is>
-          <t>Comportarse como dueño — concepto</t>
+          <t>Consignación de llaves no libera de pago</t>
         </is>
       </c>
       <c r="G139" s="13" t="inlineStr">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="H139" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I139" s="13" t="inlineStr">
@@ -19654,57 +19654,57 @@
       </c>
       <c r="K139" s="14" t="inlineStr">
         <is>
-          <t>ACCIÓN DE EXTINCIÓN DE DOMINIO. CONCEPTO DE "COMPORTARSE U OSTENTARSE COMO DUEÑO", PARA LOS EFECTOS DE LA LEY FEDERAL DE EXTINCIÓN DE DOMINIO (ABROGADA).</t>
+          <t>ARRENDAMIENTO. LA CONSIGNACIÓN DE LLAVES DEL INMUEBLE ARRENDADO EXHIBIDAS MEDIANTE ESCRITO ANTE EL ÓRGANO JURISDICCIONAL NO LIBERA AL DEMANDADO DEL PAGO DE RENTAS, MANTENIMIENTO, SERVICIOS DE GAS Y AGUA, SI NO ACREDITA HABER IMPULSADO EL PROCEDIMIENTO.</t>
         </is>
       </c>
       <c r="L139" s="13" t="inlineStr">
         <is>
-          <t>2024407</t>
+          <t>2031626</t>
         </is>
       </c>
       <c r="M139" s="13" t="inlineStr"/>
       <c r="N139" s="13" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O139" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — VERIFICADO</t>
         </is>
       </c>
       <c r="P139" s="13" t="inlineStr"/>
       <c r="Q139" s="13" t="inlineStr">
         <is>
-          <t>El "comportarse u ostentarse como dueño" requiere acreditar actos materiales objetivos: posesión, administración, disposición, sin que baste la mera titularidad registral.</t>
+          <t>El arrendatario que pretende terminar el contrato consignando las llaves debe impulsar la notificación al arrendador. Sin ese impulso procesal, sigue obligado al pago de rentas y servicios.</t>
         </is>
       </c>
       <c r="R139" s="13" t="inlineStr">
         <is>
-          <t>Estándar para acreditar legitimación pasiva en extinción.</t>
+          <t>Defensa del arrendador contra inquilinos que abandonan sin notificar.</t>
         </is>
       </c>
       <c r="S139" s="13" t="inlineStr">
         <is>
-          <t>Defensa: probar que tu cliente solo era titular registral, no se ostentaba como dueño.</t>
+          <t>Inquilino que entrega llaves debe pedir actuario para notificar, no basta exhibirlas. Arrendador puede seguir cobrando hasta que el procedimiento esté impulsado.</t>
         </is>
       </c>
       <c r="T139" s="13" t="inlineStr"/>
       <c r="U139" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024407</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031626</t>
         </is>
       </c>
       <c r="V139" s="13" t="inlineStr">
         <is>
-          <t>extinción dominio · ostentación · comportamiento · LFED</t>
+          <t>arrendamiento · consignación llaves · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="140" ht="80" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>civ-fid-003</t>
+          <t>civ-arr-005</t>
         </is>
       </c>
       <c r="B140" s="11" t="n">
@@ -19722,12 +19722,12 @@
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>Fideicomisos</t>
+          <t>Arrendamiento</t>
         </is>
       </c>
       <c r="F140" s="11" t="inlineStr">
         <is>
-          <t>Fideicomiso de garantía y mediación — avalúo</t>
+          <t>Aviso de terminación — cómputo de plazo</t>
         </is>
       </c>
       <c r="G140" s="11" t="inlineStr">
@@ -19747,62 +19747,62 @@
       </c>
       <c r="J140" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K140" s="12" t="inlineStr">
         <is>
-          <t>FIDEICOMISO EN GARANTÍA DERIVADO DE UN CONVENIO DE MEDIACIÓN. CUANDO SE PRETENDA SU EJECUCIÓN JUDICIAL DEBE EXHIBIRSE EL AVALÚO DEL BIEN INMUEBLE DADO EN GARANTÍA, AL SER UN ELEMENTO DE LA ACCIÓN CONFORME AL ARTÍCULO 1414 BIS DEL CÓDIGO DE COMERCIO.</t>
+          <t>CONTRATO DE ARRENDAMIENTO POR TIEMPO INDETERMINADO PARA PREDIOS URBANOS. LA OPORTUNIDAD DEL AVISO PARA DARLO POR CONCLUIDO DEBE COMPUTARSE EN DÍAS HÁBILES, A MENOS QUE LAS PARTES RENUNCIEN A ESE DERECHO.</t>
         </is>
       </c>
       <c r="L140" s="11" t="inlineStr">
         <is>
-          <t>2027244</t>
+          <t>2024563</t>
         </is>
       </c>
       <c r="M140" s="11" t="inlineStr"/>
       <c r="N140" s="11" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O140" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Gaceta del SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P140" s="11" t="inlineStr"/>
       <c r="Q140" s="11" t="inlineStr">
         <is>
-          <t>Para ejecutar judicialmente fideicomiso de garantía constituido por convenio de mediación, el actor DEBE exhibir avalúo del bien al promover. Sin avalúo, la acción es improcedente.</t>
+          <t>El aviso de terminación de arrendamiento por tiempo indeterminado se computa en días HÁBILES por defecto. Solo si las partes pactaron expresamente días naturales, aplica esa modalidad.</t>
         </is>
       </c>
       <c r="R140" s="11" t="inlineStr">
         <is>
-          <t>Requisito formal estricto para ejecutar fideicomiso de garantía vía mediación.</t>
+          <t>Define plazo real para desocupación en CDMX.</t>
         </is>
       </c>
       <c r="S140" s="11" t="inlineStr">
         <is>
-          <t>Antes de demandar ejecución hay que conseguir avalúo de perito autorizado.</t>
+          <t>Confusión frecuente: muchos contratos asumen días naturales sin pactarlo. El plazo es hábil. Hay que dar el aviso anticipándose.</t>
         </is>
       </c>
       <c r="T140" s="11" t="inlineStr"/>
       <c r="U140" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024563</t>
         </is>
       </c>
       <c r="V140" s="11" t="inlineStr">
         <is>
-          <t>fideicomiso garantía · mediación · art. 1414 bis Cco · avalúo</t>
+          <t>arrendamiento CDMX · aviso terminación · días hábiles</t>
         </is>
       </c>
     </row>
     <row r="141" ht="80" customHeight="1">
       <c r="A141" s="13" t="inlineStr">
         <is>
-          <t>auto-2032124</t>
+          <t>fam-div-001</t>
         </is>
       </c>
       <c r="B141" s="13" t="n">
@@ -19820,12 +19820,12 @@
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Divorcio sin expresión de causa</t>
         </is>
       </c>
       <c r="F141" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Procedencia del recurso de revocación</t>
         </is>
       </c>
       <c r="G141" s="13" t="inlineStr">
@@ -19845,62 +19845,62 @@
       </c>
       <c r="J141" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K141" s="14" t="inlineStr">
         <is>
-          <t>CRÉDITOS HIPOTECARIOS OTORGADOS POR LAS INSTITUCIONES FINANCIERAS A SUS PERSONAS TRABAJADORAS. EL ESTUDIO SOBRE LA MODIFICACIÓN DE LAS CLÁUSULAS QUE CONTENGAN UN BENEFICIO OTORGADO DERIVADO DE LA RELACIÓN LABORAL PROCEDE EN ESTA VÍA.</t>
+          <t>DIVORCIO SIN EXPRESIÓN DE CAUSA. PROCEDENCIA DEL RECURSO DE REVOCACIÓN CONTRA LAS RESOLUCIONES DICTADAS DURANTE SU SUSTANCIACIÓN.</t>
         </is>
       </c>
       <c r="L141" s="13" t="inlineStr">
         <is>
-          <t>2032124</t>
+          <t>2031170</t>
         </is>
       </c>
       <c r="M141" s="13" t="inlineStr"/>
       <c r="N141" s="13" t="inlineStr">
         <is>
-          <t>viernes 15 de mayo de 2026 10:20 h</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O141" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P141" s="13" t="inlineStr"/>
       <c r="Q141" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Las resoluciones dictadas durante la sustanciación del divorcio sin causa admiten recurso de revocación conforme a los arts. 685, 685 bis y 691 del CPC para CDMX.</t>
         </is>
       </c>
       <c r="R141" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Vía expedita contra resoluciones intermedias en divorcio incausado CDMX.</t>
         </is>
       </c>
       <c r="S141" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Antes era confusa la vía. Ahora con esta tesis se aplica revocación. Permite revisar rápidamente medidas provisionales sobre alimentos o convivencia.</t>
         </is>
       </c>
       <c r="T141" s="13" t="inlineStr"/>
       <c r="U141" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032124</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031170</t>
         </is>
       </c>
       <c r="V141" s="13" t="inlineStr">
         <is>
-          <t>Juicio hipotecario · actualización automática</t>
+          <t>divorcio incausado · revocación · CDMX · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="142" ht="80" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>auto-2032537</t>
+          <t>fam-div-002</t>
         </is>
       </c>
       <c r="B142" s="11" t="n">
@@ -19918,12 +19918,12 @@
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Divorcio sin expresión de causa</t>
         </is>
       </c>
       <c r="F142" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Amparo directo contra sentencia</t>
         </is>
       </c>
       <c r="G142" s="11" t="inlineStr">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="H142" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I142" s="11" t="inlineStr">
@@ -19948,57 +19948,57 @@
       </c>
       <c r="K142" s="12" t="inlineStr">
         <is>
-          <t>SEGURO DE VIDA VINCULADO A UN CRÉDITO HIPOTECARIO. CUANDO EL ACREEDOR ES BENEFICIARIO PREFERENTE, DEBE AGOTAR LA ACCIÓN DERIVADA DEL CONTRATO DE SEGURO ANTES DE EJERCER LA ACCIÓN HIPOTECARIA CONTRA LA SUCESIÓN DEL DEUDOR.</t>
+          <t>AMPARO DIRECTO. PROCEDE CONTRA LA SENTENCIA QUE DECLARA LA DISOLUCIÓN DEL VÍNCULO MATRIMONIAL EN UN JUICIO DE DIVORCIO SIN EXPRESIÓN DE CAUSA Y RESUELVE PROVISIONALMENTE SOBRE LOS ALIMENTOS U OTRAS CUESTIONES INHERENTES.</t>
         </is>
       </c>
       <c r="L142" s="11" t="inlineStr">
         <is>
-          <t>2032537</t>
+          <t>2029853</t>
         </is>
       </c>
       <c r="M142" s="11" t="inlineStr"/>
       <c r="N142" s="11" t="inlineStr">
         <is>
-          <t>viernes 21 de agosto de 2026 10:29 h</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O142" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P142" s="11" t="inlineStr"/>
       <c r="Q142" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La sentencia de divorcio sin expresión de causa que resuelve sobre alimentos provisionales o cuestiones inherentes es definitiva para efectos del amparo directo.</t>
         </is>
       </c>
       <c r="R142" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Define vía de impugnación: amparo directo, no indirecto.</t>
         </is>
       </c>
       <c r="S142" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Importante para no equivocarse de vía. Si tu sentencia incluye medidas sobre alimentos: amparo directo. Si solo es disolución limpia: dependerá del caso.</t>
         </is>
       </c>
       <c r="T142" s="11" t="inlineStr"/>
       <c r="U142" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032537</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029853</t>
         </is>
       </c>
       <c r="V142" s="11" t="inlineStr">
         <is>
-          <t>Juicio hipotecario · actualización automática</t>
+          <t>divorcio incausado · amparo directo · alimentos</t>
         </is>
       </c>
     </row>
     <row r="143" ht="80" customHeight="1">
       <c r="A143" s="13" t="inlineStr">
         <is>
-          <t>auto-2032745</t>
+          <t>civ-ext-003</t>
         </is>
       </c>
       <c r="B143" s="13" t="n">
@@ -20016,12 +20016,12 @@
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Extinción de dominio</t>
         </is>
       </c>
       <c r="F143" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Comportarse como dueño — concepto</t>
         </is>
       </c>
       <c r="G143" s="13" t="inlineStr">
@@ -20031,7 +20031,7 @@
       </c>
       <c r="H143" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I143" s="13" t="inlineStr">
@@ -20046,57 +20046,57 @@
       </c>
       <c r="K143" s="14" t="inlineStr">
         <is>
-          <t>LEGITIMACIÓN PASIVA EN EL JUICIO SUMARIO HIPOTECARIO. CARECE DE ELLA EL CÓNYUGE QUE SÓLO OTORGÓ SU CONSENTIMIENTO PARA GRAVAR EL BIEN INMUEBLE DESTINADO A CASA-HABITACIÓN FAMILIAR (INTERPRETACIÓN DEL ARTÍCULO 72, PÁRRAFO SEGUNDO, DEL CÓDIGO FAMILIAR DEL ESTADO DE SINALOA).</t>
+          <t>ACCIÓN DE EXTINCIÓN DE DOMINIO. CONCEPTO DE "COMPORTARSE U OSTENTARSE COMO DUEÑO", PARA LOS EFECTOS DE LA LEY FEDERAL DE EXTINCIÓN DE DOMINIO (ABROGADA).</t>
         </is>
       </c>
       <c r="L143" s="13" t="inlineStr">
         <is>
-          <t>2032745</t>
+          <t>2024407</t>
         </is>
       </c>
       <c r="M143" s="13" t="inlineStr"/>
       <c r="N143" s="13" t="inlineStr">
         <is>
-          <t>viernes 09 de octubre de 2026 10:19 h</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O143" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P143" s="13" t="inlineStr"/>
       <c r="Q143" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>El "comportarse u ostentarse como dueño" requiere acreditar actos materiales objetivos: posesión, administración, disposición, sin que baste la mera titularidad registral.</t>
         </is>
       </c>
       <c r="R143" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Estándar para acreditar legitimación pasiva en extinción.</t>
         </is>
       </c>
       <c r="S143" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Defensa: probar que tu cliente solo era titular registral, no se ostentaba como dueño.</t>
         </is>
       </c>
       <c r="T143" s="13" t="inlineStr"/>
       <c r="U143" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032745</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024407</t>
         </is>
       </c>
       <c r="V143" s="13" t="inlineStr">
         <is>
-          <t>Juicio hipotecario · actualización automática</t>
+          <t>extinción dominio · ostentación · comportamiento · LFED</t>
         </is>
       </c>
     </row>
     <row r="144" ht="80" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>civ-hip-003</t>
+          <t>civ-fid-003</t>
         </is>
       </c>
       <c r="B144" s="11" t="n">
@@ -20114,12 +20114,12 @@
       </c>
       <c r="E144" s="11" t="inlineStr">
         <is>
-          <t>Juicio hipotecario</t>
+          <t>Fideicomisos</t>
         </is>
       </c>
       <c r="F144" s="11" t="inlineStr">
         <is>
-          <t>Intereses y anatocismo</t>
+          <t>Fideicomiso de garantía y mediación — avalúo</t>
         </is>
       </c>
       <c r="G144" s="11" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="H144" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I144" s="11" t="inlineStr">
@@ -20139,54 +20139,62 @@
       </c>
       <c r="J144" s="11" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K144" s="12" t="inlineStr">
         <is>
-          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
+          <t>FIDEICOMISO EN GARANTÍA DERIVADO DE UN CONVENIO DE MEDIACIÓN. CUANDO SE PRETENDA SU EJECUCIÓN JUDICIAL DEBE EXHIBIRSE EL AVALÚO DEL BIEN INMUEBLE DADO EN GARANTÍA, AL SER UN ELEMENTO DE LA ACCIÓN CONFORME AL ARTÍCULO 1414 BIS DEL CÓDIGO DE COMERCIO.</t>
         </is>
       </c>
       <c r="L144" s="11" t="inlineStr">
         <is>
-          <t>200721</t>
+          <t>2027244</t>
         </is>
       </c>
       <c r="M144" s="11" t="inlineStr"/>
-      <c r="N144" s="11" t="inlineStr"/>
-      <c r="O144" s="11" t="inlineStr"/>
+      <c r="N144" s="11" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="O144" s="11" t="inlineStr">
+        <is>
+          <t>Gaceta SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P144" s="11" t="inlineStr"/>
       <c r="Q144" s="11" t="inlineStr">
         <is>
-          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
+          <t>Para ejecutar judicialmente fideicomiso de garantía constituido por convenio de mediación, el actor DEBE exhibir avalúo del bien al promover. Sin avalúo, la acción es improcedente.</t>
         </is>
       </c>
       <c r="R144" s="11" t="inlineStr">
         <is>
-          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
+          <t>Requisito formal estricto para ejecutar fideicomiso de garantía vía mediación.</t>
         </is>
       </c>
       <c r="S144" s="11" t="inlineStr">
         <is>
-          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
+          <t>Antes de demandar ejecución hay que conseguir avalúo de perito autorizado.</t>
         </is>
       </c>
       <c r="T144" s="11" t="inlineStr"/>
       <c r="U144" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027244</t>
         </is>
       </c>
       <c r="V144" s="11" t="inlineStr">
         <is>
-          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
+          <t>fideicomiso garantía · mediación · art. 1414 bis Cco · avalúo</t>
         </is>
       </c>
     </row>
     <row r="145" ht="80" customHeight="1">
       <c r="A145" s="13" t="inlineStr">
         <is>
-          <t>civ-hip-004</t>
+          <t>auto-2032124</t>
         </is>
       </c>
       <c r="B145" s="13" t="n">
@@ -20209,7 +20217,7 @@
       </c>
       <c r="F145" s="13" t="inlineStr">
         <is>
-          <t>Apelación en efecto devolutivo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G145" s="13" t="inlineStr">
@@ -20219,7 +20227,7 @@
       </c>
       <c r="H145" s="13" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I145" s="13" t="inlineStr">
@@ -20229,62 +20237,62 @@
       </c>
       <c r="J145" s="13" t="inlineStr">
         <is>
-          <t>CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K145" s="14" t="inlineStr">
         <is>
-          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
+          <t>CRÉDITOS HIPOTECARIOS OTORGADOS POR LAS INSTITUCIONES FINANCIERAS A SUS PERSONAS TRABAJADORAS. EL ESTUDIO SOBRE LA MODIFICACIÓN DE LAS CLÁUSULAS QUE CONTENGAN UN BENEFICIO OTORGADO DERIVADO DE LA RELACIÓN LABORAL PROCEDE EN ESTA VÍA.</t>
         </is>
       </c>
       <c r="L145" s="13" t="inlineStr">
         <is>
-          <t>162554</t>
+          <t>2032124</t>
         </is>
       </c>
       <c r="M145" s="13" t="inlineStr"/>
       <c r="N145" s="13" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>viernes 15 de mayo de 2026 10:20 h</t>
         </is>
       </c>
       <c r="O145" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P145" s="13" t="inlineStr"/>
       <c r="Q145" s="13" t="inlineStr">
         <is>
-          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R145" s="13" t="inlineStr">
         <is>
-          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S145" s="13" t="inlineStr">
         <is>
-          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T145" s="13" t="inlineStr"/>
       <c r="U145" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032124</t>
         </is>
       </c>
       <c r="V145" s="13" t="inlineStr">
         <is>
-          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
+          <t>Juicio hipotecario · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="146" ht="80" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>civ-hip-005</t>
+          <t>auto-2032537</t>
         </is>
       </c>
       <c r="B146" s="11" t="n">
@@ -20307,7 +20315,7 @@
       </c>
       <c r="F146" s="11" t="inlineStr">
         <is>
-          <t>Ejecución limitada al bien hipotecado</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G146" s="11" t="inlineStr">
@@ -20317,7 +20325,7 @@
       </c>
       <c r="H146" s="11" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I146" s="11" t="inlineStr">
@@ -20332,57 +20340,57 @@
       </c>
       <c r="K146" s="12" t="inlineStr">
         <is>
-          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
+          <t>SEGURO DE VIDA VINCULADO A UN CRÉDITO HIPOTECARIO. CUANDO EL ACREEDOR ES BENEFICIARIO PREFERENTE, DEBE AGOTAR LA ACCIÓN DERIVADA DEL CONTRATO DE SEGURO ANTES DE EJERCER LA ACCIÓN HIPOTECARIA CONTRA LA SUCESIÓN DEL DEUDOR.</t>
         </is>
       </c>
       <c r="L146" s="11" t="inlineStr">
         <is>
-          <t>180865</t>
+          <t>2032537</t>
         </is>
       </c>
       <c r="M146" s="11" t="inlineStr"/>
       <c r="N146" s="11" t="inlineStr">
         <is>
-          <t>Novena Época</t>
+          <t>viernes 21 de agosto de 2026 10:29 h</t>
         </is>
       </c>
       <c r="O146" s="11" t="inlineStr">
         <is>
-          <t>SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P146" s="11" t="inlineStr"/>
       <c r="Q146" s="11" t="inlineStr">
         <is>
-          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R146" s="11" t="inlineStr">
         <is>
-          <t>Límite de garantía real del juicio hipotecario.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S146" s="11" t="inlineStr">
         <is>
-          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T146" s="11" t="inlineStr"/>
       <c r="U146" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032537</t>
         </is>
       </c>
       <c r="V146" s="11" t="inlineStr">
         <is>
-          <t>hipotecario · acción real · ejecución limitada</t>
+          <t>Juicio hipotecario · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="147" ht="80" customHeight="1">
       <c r="A147" s="13" t="inlineStr">
         <is>
-          <t>sen-019</t>
+          <t>auto-2032745</t>
         </is>
       </c>
       <c r="B147" s="13" t="n">
@@ -20400,22 +20408,22 @@
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>Notificaciones — domicilio convencional vs. real</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F147" s="13" t="inlineStr">
         <is>
-          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G147" s="13" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H147" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I147" s="13" t="inlineStr">
@@ -20425,58 +20433,62 @@
       </c>
       <c r="J147" s="13" t="inlineStr">
         <is>
-          <t>Primer Circuito — CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K147" s="14" t="inlineStr">
         <is>
-          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
+          <t>LEGITIMACIÓN PASIVA EN EL JUICIO SUMARIO HIPOTECARIO. CARECE DE ELLA EL CÓNYUGE QUE SÓLO OTORGÓ SU CONSENTIMIENTO PARA GRAVAR EL BIEN INMUEBLE DESTINADO A CASA-HABITACIÓN FAMILIAR (INTERPRETACIÓN DEL ARTÍCULO 72, PÁRRAFO SEGUNDO, DEL CÓDIGO FAMILIAR DEL ESTADO DE SINALOA).</t>
         </is>
       </c>
       <c r="L147" s="13" t="inlineStr">
         <is>
-          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
+          <t>2032745</t>
         </is>
       </c>
       <c r="M147" s="13" t="inlineStr"/>
       <c r="N147" s="13" t="inlineStr">
         <is>
-          <t>Línea consolidada</t>
-        </is>
-      </c>
-      <c r="O147" s="13" t="inlineStr"/>
+          <t>viernes 09 de octubre de 2026 10:19 h</t>
+        </is>
+      </c>
+      <c r="O147" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P147" s="13" t="inlineStr"/>
       <c r="Q147" s="13" t="inlineStr">
         <is>
-          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R147" s="13" t="inlineStr">
         <is>
-          <t>Defensa nuclear contra emplazamientos ficticios.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S147" s="13" t="inlineStr">
         <is>
-          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T147" s="13" t="inlineStr"/>
       <c r="U147" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032745</t>
         </is>
       </c>
       <c r="V147" s="13" t="inlineStr">
         <is>
-          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
+          <t>Juicio hipotecario · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="148" ht="80" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>fam-com-001</t>
+          <t>civ-hip-003</t>
         </is>
       </c>
       <c r="B148" s="11" t="n">
@@ -20494,12 +20506,12 @@
       </c>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>Pensión compensatoria</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr">
         <is>
-          <t>Inversión de carga probatoria</t>
+          <t>Intereses y anatocismo</t>
         </is>
       </c>
       <c r="G148" s="11" t="inlineStr">
@@ -20509,7 +20521,7 @@
       </c>
       <c r="H148" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I148" s="11" t="inlineStr">
@@ -20519,62 +20531,54 @@
       </c>
       <c r="J148" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K148" s="12" t="inlineStr">
         <is>
-          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
+          <t>INTERESES MORATORIOS EN MUTUO HIPOTECARIO. SU CAPITALIZACIÓN REQUIERE PACTO EXPRESO Y POSTERIOR A SU CAUSACIÓN.</t>
         </is>
       </c>
       <c r="L148" s="11" t="inlineStr">
         <is>
-          <t>2031387</t>
+          <t>200721</t>
         </is>
       </c>
       <c r="M148" s="11" t="inlineStr"/>
-      <c r="N148" s="11" t="inlineStr">
-        <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-      <c r="O148" s="11" t="inlineStr">
-        <is>
-          <t>SJF — VERIFICADO</t>
-        </is>
-      </c>
+      <c r="N148" s="11" t="inlineStr"/>
+      <c r="O148" s="11" t="inlineStr"/>
       <c r="P148" s="11" t="inlineStr"/>
       <c r="Q148" s="11" t="inlineStr">
         <is>
-          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
+          <t>La capitalización de intereses (anatocismo) en mutuo hipotecario civil solo es válida cuando se pacta por escrito y POSTERIORMENTE a que los intereses se causaron. Pactos previos genéricos de capitalización son nulos.</t>
         </is>
       </c>
       <c r="R148" s="11" t="inlineStr">
         <is>
-          <t>Garantía procesal en juicios de compensación / pensión.</t>
+          <t>Defensa estándar del deudor en hipotecarios de banca.</t>
         </is>
       </c>
       <c r="S148" s="11" t="inlineStr">
         <is>
-          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
+          <t>El art. 2397 CCCDMX prohíbe el pacto anticipado de capitalización. En la práctica, las pólizas bancarias suelen incluir cláusula que se debe atacar como nula. Estudiar junto con criterios de Contradicción de Tesis 31/98 (anatocismo).</t>
         </is>
       </c>
       <c r="T148" s="11" t="inlineStr"/>
       <c r="U148" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/164463</t>
         </is>
       </c>
       <c r="V148" s="11" t="inlineStr">
         <is>
-          <t>pensión compensatoria · carga probatoria · 12a Época</t>
+          <t>intereses · anatocismo · art. 2397 CCCDMX</t>
         </is>
       </c>
     </row>
     <row r="149" ht="80" customHeight="1">
       <c r="A149" s="13" t="inlineStr">
         <is>
-          <t>auto-2032319</t>
+          <t>civ-hip-004</t>
         </is>
       </c>
       <c r="B149" s="13" t="n">
@@ -20592,12 +20596,12 @@
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F149" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Apelación en efecto devolutivo</t>
         </is>
       </c>
       <c r="G149" s="13" t="inlineStr">
@@ -20607,7 +20611,7 @@
       </c>
       <c r="H149" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I149" s="13" t="inlineStr">
@@ -20617,62 +20621,62 @@
       </c>
       <c r="J149" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>CDMX</t>
         </is>
       </c>
       <c r="K149" s="14" t="inlineStr">
         <is>
-          <t>CONTRATO DE ENAJENACIÓN DE DERECHOS AGRARIOS. CUANDO SE DECLARA SU NULIDAD POR VIOLACIÓN AL DERECHO DEL TANTO, DEBEN DEJARSE A SALVO LOS DERECHOS DE LA PERSONA DEMANDADA PARA EJERCER, EN SU CASO, LA ACCIÓN DE USUCAPIÓN.</t>
+          <t>JUICIO ESPECIAL HIPOTECARIO, APELACIÓN EN EL. DEBE ADMITIRSE EN EL EFECTO DEVOLUTIVO CONFORME AL ARTÍCULO 714 DEL CÓDIGO DE PROCEDIMIENTOS CIVILES PARA EL DISTRITO FEDERAL.</t>
         </is>
       </c>
       <c r="L149" s="13" t="inlineStr">
         <is>
-          <t>2032319</t>
+          <t>162554</t>
         </is>
       </c>
       <c r="M149" s="13" t="inlineStr"/>
       <c r="N149" s="13" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="O149" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Semanario Judicial de la Federación — VERIFICADO</t>
         </is>
       </c>
       <c r="P149" s="13" t="inlineStr"/>
       <c r="Q149" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Las apelaciones interlocutorias en el juicio especial hipotecario CDMX se admiten en efecto devolutivo, sin suspender la ejecución, conforme al art. 714 CPCDMX.</t>
         </is>
       </c>
       <c r="R149" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Acreedor mantiene ejecución pese a apelaciones del deudor.</t>
         </is>
       </c>
       <c r="S149" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Defensa del banco/acreedor: las apelaciones no detienen el remate. El deudor debe ir por amparo indirecto si quiere suspender.</t>
         </is>
       </c>
       <c r="T149" s="13" t="inlineStr"/>
       <c r="U149" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032319</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/162554</t>
         </is>
       </c>
       <c r="V149" s="13" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva · actualización automática</t>
+          <t>hipotecario · apelación · art. 714 CPCDMX · efecto devolutivo</t>
         </is>
       </c>
     </row>
     <row r="150" ht="80" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>civ-usu-003</t>
+          <t>civ-hip-005</t>
         </is>
       </c>
       <c r="B150" s="11" t="n">
@@ -20690,17 +20694,17 @@
       </c>
       <c r="E150" s="11" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva</t>
+          <t>Juicio hipotecario</t>
         </is>
       </c>
       <c r="F150" s="11" t="inlineStr">
         <is>
-          <t>Pericial topográfica / agrimensura</t>
+          <t>Ejecución limitada al bien hipotecado</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H150" s="11" t="inlineStr">
@@ -20715,58 +20719,62 @@
       </c>
       <c r="J150" s="11" t="inlineStr">
         <is>
-          <t>Federal — colegiados</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K150" s="12" t="inlineStr">
         <is>
-          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
+          <t>JUICIO HIPOTECARIO. ES JURÍDICAMENTE IMPOSIBLE DESPACHAR EJECUCIÓN EN UN INMUEBLE DISTINTO DEL BIEN MATERIA DE LA CONDENA.</t>
         </is>
       </c>
       <c r="L150" s="11" t="inlineStr">
         <is>
-          <t>190377</t>
+          <t>180865</t>
         </is>
       </c>
       <c r="M150" s="11" t="inlineStr"/>
-      <c r="N150" s="11" t="inlineStr"/>
+      <c r="N150" s="11" t="inlineStr">
+        <is>
+          <t>Novena Época</t>
+        </is>
+      </c>
       <c r="O150" s="11" t="inlineStr">
         <is>
-          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
+          <t>SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P150" s="11" t="inlineStr"/>
       <c r="Q150" s="11" t="inlineStr">
         <is>
-          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
+          <t>La acción real hipotecaria solo permite ejecutar sobre el bien hipotecado. No puede ampliarse a otros bienes del deudor mediante convenios anteriores a la sentencia.</t>
         </is>
       </c>
       <c r="R150" s="11" t="inlineStr">
         <is>
-          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
+          <t>Límite de garantía real del juicio hipotecario.</t>
         </is>
       </c>
       <c r="S150" s="11" t="inlineStr">
         <is>
-          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
+          <t>El acreedor que quiera ir contra otros bienes debe abrir vía ordinaria adicional. Defensa del deudor: oponer la limitación si el ejecutor intenta otros inmuebles.</t>
         </is>
       </c>
       <c r="T150" s="11" t="inlineStr"/>
       <c r="U150" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/180865</t>
         </is>
       </c>
       <c r="V150" s="11" t="inlineStr">
         <is>
-          <t>pericial · topografía · identidad del bien</t>
+          <t>hipotecario · acción real · ejecución limitada</t>
         </is>
       </c>
     </row>
     <row r="151" ht="80" customHeight="1">
       <c r="A151" s="13" t="inlineStr">
         <is>
-          <t>civ-usu-005</t>
+          <t>sen-019</t>
         </is>
       </c>
       <c r="B151" s="13" t="n">
@@ -20784,17 +20792,17 @@
       </c>
       <c r="E151" s="13" t="inlineStr">
         <is>
-          <t>Usucapión / Prescripción positiva</t>
+          <t>Notificaciones — domicilio convencional vs. real</t>
         </is>
       </c>
       <c r="F151" s="13" t="inlineStr">
         <is>
-          <t>Posesión derivada vs. originaria</t>
+          <t>Línea de Colegiados Primer Circuito (CDMX)</t>
         </is>
       </c>
       <c r="G151" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H151" s="13" t="inlineStr">
@@ -20809,54 +20817,58 @@
       </c>
       <c r="J151" s="13" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Primer Circuito — CDMX</t>
         </is>
       </c>
       <c r="K151" s="14" t="inlineStr">
         <is>
-          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
+          <t>Notificación personal — preeminencia del domicilio real cuando consta en autos</t>
         </is>
       </c>
       <c r="L151" s="13" t="inlineStr">
         <is>
-          <t>2030499</t>
+          <t>Tesis del Primer Circuito — múltiples colegiados civiles</t>
         </is>
       </c>
       <c r="M151" s="13" t="inlineStr"/>
-      <c r="N151" s="13" t="inlineStr"/>
+      <c r="N151" s="13" t="inlineStr">
+        <is>
+          <t>Línea consolidada</t>
+        </is>
+      </c>
       <c r="O151" s="13" t="inlineStr"/>
       <c r="P151" s="13" t="inlineStr"/>
       <c r="Q151" s="13" t="inlineStr">
         <is>
-          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
+          <t>Aunque exista domicilio convencional pactado, si en autos consta el domicilio real del demandado y el convencional resulta inhábil, el actuario debe notificar en el real para garantizar emplazamiento efectivo y derecho de audiencia.</t>
         </is>
       </c>
       <c r="R151" s="13" t="inlineStr">
         <is>
-          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
+          <t>Defensa nuclear contra emplazamientos ficticios.</t>
         </is>
       </c>
       <c r="S151" s="13" t="inlineStr">
         <is>
-          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
+          <t>En juicios ejecutivos y especiales hipotecarios, el demandado que no fue notificado personalmente y no tuvo oportunidad real de defensa puede pedir nulidad del emplazamiento. Ofrecer pruebas del domicilio real anteriores al juicio.</t>
         </is>
       </c>
       <c r="T151" s="13" t="inlineStr"/>
       <c r="U151" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030499</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030925</t>
         </is>
       </c>
       <c r="V151" s="13" t="inlineStr">
         <is>
-          <t>posesión derivada · concepto de propietario · interversión</t>
+          <t>notificación · emplazamiento · domicilio real · Primer Circuito</t>
         </is>
       </c>
     </row>
     <row r="152" ht="80" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>con-asa-001</t>
+          <t>fam-com-001</t>
         </is>
       </c>
       <c r="B152" s="11" t="n">
@@ -20869,17 +20881,17 @@
       </c>
       <c r="D152" s="11" t="inlineStr">
         <is>
-          <t>Civil — Condominio</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>Régimen de propiedad en condominio</t>
+          <t>Pensión compensatoria</t>
         </is>
       </c>
       <c r="F152" s="11" t="inlineStr">
         <is>
-          <t>Asambleas — convocatoria y validez</t>
+          <t>Inversión de carga probatoria</t>
         </is>
       </c>
       <c r="G152" s="11" t="inlineStr">
@@ -20889,7 +20901,7 @@
       </c>
       <c r="H152" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I152" s="11" t="inlineStr">
@@ -20899,54 +20911,62 @@
       </c>
       <c r="J152" s="11" t="inlineStr">
         <is>
-          <t>Federal — interpreta LPCI CDMX</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K152" s="12" t="inlineStr">
         <is>
-          <t>ASAMBLEAS CONDOMINALES. LA INDEBIDA CONVOCATORIA AFECTA LA VALIDEZ DE LOS ACUERDOS Y PERMITE SU IMPUGNACIÓN.</t>
+          <t>INVERSIÓN DE LA CARGA DE LA PRUEBA EN MATERIA FAMILIAR. CUANDO SE DEMANDA UNA PENSIÓN COMPENSATORIA Y SE PRODUCE AQUÉLLA, LA PERSONA JUZGADORA TIENE EL DEBER DE HACERLO SABER EXPRESA Y OPORTUNAMENTE A LA PARTE SOBRE LA QUE RECAE.</t>
         </is>
       </c>
       <c r="L152" s="11" t="inlineStr">
         <is>
-          <t>Art. 32 LPCI CDMX</t>
+          <t>2031387</t>
         </is>
       </c>
       <c r="M152" s="11" t="inlineStr"/>
-      <c r="N152" s="11" t="inlineStr"/>
-      <c r="O152" s="11" t="inlineStr"/>
+      <c r="N152" s="11" t="inlineStr">
+        <is>
+          <t>2025-2026</t>
+        </is>
+      </c>
+      <c r="O152" s="11" t="inlineStr">
+        <is>
+          <t>SJF — VERIFICADO</t>
+        </is>
+      </c>
       <c r="P152" s="11" t="inlineStr"/>
       <c r="Q152" s="11" t="inlineStr">
         <is>
-          <t>La convocatoria debe respetar plazo, forma y orden del día (art. 32 LPCI CDMX). Su incumplimiento es causal de nulidad de los acuerdos adoptados, salvo ratificación expresa en asamblea posterior debidamente convocada.</t>
+          <t>En juicios de pensión compensatoria, cuando opera la inversión de carga probatoria, el juez tiene deber DE OFICIO de notificar formalmente a la parte sobre la que recae para garantizar defensa adecuada.</t>
         </is>
       </c>
       <c r="R152" s="11" t="inlineStr">
         <is>
-          <t>Defensa frecuente de minorías condominales.</t>
+          <t>Garantía procesal en juicios de compensación / pensión.</t>
         </is>
       </c>
       <c r="S152" s="11" t="inlineStr">
         <is>
-          <t>Conserva pruebas de cómo se realizó la convocatoria (carteles, mensajes, fotos). Plazo de impugnación es corto (60 días naturales en CDMX desde celebración o conocimiento).</t>
+          <t>Defensa del deudor alimentario: si no le informaron expresamente la inversión, puede pedir nulidad de actuaciones. Defensa del acreedor: solicitar al juez que haga la notificación formal.</t>
         </is>
       </c>
       <c r="T152" s="11" t="inlineStr"/>
       <c r="U152" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028919</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031387</t>
         </is>
       </c>
       <c r="V152" s="11" t="inlineStr">
         <is>
-          <t>asamblea · convocatoria · nulidad · LPCI CDMX</t>
+          <t>pensión compensatoria · carga probatoria · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="153" ht="80" customHeight="1">
       <c r="A153" s="13" t="inlineStr">
         <is>
-          <t>amp-cui-001</t>
+          <t>auto-2032319</t>
         </is>
       </c>
       <c r="B153" s="13" t="n">
@@ -20959,17 +20979,17 @@
       </c>
       <c r="D153" s="13" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>Derecho humano al cuidado</t>
+          <t>Usucapión / Prescripción positiva</t>
         </is>
       </c>
       <c r="F153" s="13" t="inlineStr">
         <is>
-          <t>Reconocimiento e interés legítimo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G153" s="13" t="inlineStr">
@@ -20994,57 +21014,57 @@
       </c>
       <c r="K153" s="14" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO AL CUIDADO. IMPONE OBLIGACIONES DE CUYO CUMPLIMIENTO DEPENDE DIRECTAMENTE EL BIENESTAR DE LAS PERSONAS E INDIRECTAMENTE, POR INTERDEPENDENCIA, EL EJERCICIO EFECTIVO DE OTROS DERECHOS HUMANOS.</t>
+          <t>CONTRATO DE ENAJENACIÓN DE DERECHOS AGRARIOS. CUANDO SE DECLARA SU NULIDAD POR VIOLACIÓN AL DERECHO DEL TANTO, DEBEN DEJARSE A SALVO LOS DERECHOS DE LA PERSONA DEMANDADA PARA EJERCER, EN SU CASO, LA ACCIÓN DE USUCAPIÓN.</t>
         </is>
       </c>
       <c r="L153" s="13" t="inlineStr">
         <is>
-          <t>2032085</t>
+          <t>2032319</t>
         </is>
       </c>
       <c r="M153" s="13" t="inlineStr"/>
       <c r="N153" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O153" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P153" s="13" t="inlineStr"/>
       <c r="Q153" s="13" t="inlineStr">
         <is>
-          <t>El cuidado se reconoce como derecho humano autónomo. El Estado tiene obligación de garantizarlo mediante políticas públicas, infraestructura social y reconocimiento del trabajo de cuidado no remunerado.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R153" s="13" t="inlineStr">
         <is>
-          <t>Pieza inaugural de un nuevo derecho humano en México.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S153" s="13" t="inlineStr">
         <is>
-          <t>Marco para litigios sobre obligaciones del Estado en guarderías, cuidado de personas mayores, discapacidad y omisiones legislativas absolutas.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T153" s="13" t="inlineStr"/>
       <c r="U153" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032085</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032319</t>
         </is>
       </c>
       <c r="V153" s="13" t="inlineStr">
         <is>
-          <t>derecho al cuidado · 12a Época · DDHH · cuidadoras</t>
+          <t>Usucapión / Prescripción positiva · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="154" ht="80" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>amp-cui-002</t>
+          <t>civ-usu-003</t>
         </is>
       </c>
       <c r="B154" s="11" t="n">
@@ -21057,27 +21077,27 @@
       </c>
       <c r="D154" s="11" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>Derecho humano al cuidado</t>
+          <t>Usucapión / Prescripción positiva</t>
         </is>
       </c>
       <c r="F154" s="11" t="inlineStr">
         <is>
-          <t>Interés legítimo para combatir omisiones legislativas</t>
+          <t>Pericial topográfica / agrimensura</t>
         </is>
       </c>
       <c r="G154" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H154" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Novena Época</t>
         </is>
       </c>
       <c r="I154" s="11" t="inlineStr">
@@ -21087,62 +21107,58 @@
       </c>
       <c r="J154" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — colegiados</t>
         </is>
       </c>
       <c r="K154" s="12" t="inlineStr">
         <is>
-          <t>DERECHO HUMANO AL CUIDADO. LAS MUJERES QUE REALIZAN CUIDADOS SIMPLES O COTIDIANOS NO REMUNERADOS TIENEN INTERÉS LEGÍTIMO PARA RECLAMAR OMISIONES LEGISLATIVAS ABSOLUTAS QUE IMPIDAN SU PLENO EJERCICIO.</t>
+          <t>PERICIAL EN AGRIMENSURA. ES IDÓNEA PARA DEMOSTRAR LA IDENTIDAD DEL PREDIO MATERIA DE LA USUCAPIÓN, CUANDO ESTE NO APARECE INDIVIDUALIZADO EN EL REGISTRO PÚBLICO DE LA PROPIEDAD.</t>
         </is>
       </c>
       <c r="L154" s="11" t="inlineStr">
         <is>
-          <t>2032086</t>
+          <t>190377</t>
         </is>
       </c>
       <c r="M154" s="11" t="inlineStr"/>
-      <c r="N154" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="N154" s="11" t="inlineStr"/>
       <c r="O154" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>SJF y su Gaceta, Novena Época — VERIFICADO en SJF2</t>
         </is>
       </c>
       <c r="P154" s="11" t="inlineStr"/>
       <c r="Q154" s="11" t="inlineStr">
         <is>
-          <t>Las mujeres que realizan trabajo de cuidados no remunerados tienen interés legítimo, sin necesidad de afectación individualizada estricta, para promover amparo contra omisiones legislativas absolutas en la materia.</t>
+          <t>Cuando el inmueble se desprende de una superficie mayor o no aparece individualizado registralmente, la pericial topográfica es la prueba idónea para acreditar la identidad y localización exacta del predio que se pretende prescribir.</t>
         </is>
       </c>
       <c r="R154" s="11" t="inlineStr">
         <is>
-          <t>Abre vía de amparo colectivo a millones de cuidadoras.</t>
+          <t>Indispensable en cualquier predio desprendido de matriz mayor.</t>
         </is>
       </c>
       <c r="S154" s="11" t="inlineStr">
         <is>
-          <t>Estrategia colectiva: amparos contra ausencia de legislación de cuidados. Beneficia particularmente a mujeres de bajos ingresos que sostienen familia.</t>
+          <t>Sin pericial topográfica el juicio se expone a falta de identidad del bien. Hay que ofrecerla desde la demanda con cuestionario que incluya: medidas, colindancias, superficie y ubicación cartográfica.</t>
         </is>
       </c>
       <c r="T154" s="11" t="inlineStr"/>
       <c r="U154" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032086</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/190377</t>
         </is>
       </c>
       <c r="V154" s="11" t="inlineStr">
         <is>
-          <t>cuidado · interés legítimo · omisión legislativa · perspectiva género</t>
+          <t>pericial · topografía · identidad del bien</t>
         </is>
       </c>
     </row>
     <row r="155" ht="80" customHeight="1">
       <c r="A155" s="13" t="inlineStr">
         <is>
-          <t>auto-2032312</t>
+          <t>civ-usu-005</t>
         </is>
       </c>
       <c r="B155" s="13" t="n">
@@ -21155,27 +21171,27 @@
       </c>
       <c r="D155" s="13" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil</t>
         </is>
       </c>
       <c r="E155" s="13" t="inlineStr">
         <is>
-          <t>Medio ambiente sano</t>
+          <t>Usucapión / Prescripción positiva</t>
         </is>
       </c>
       <c r="F155" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Posesión derivada vs. originaria</t>
         </is>
       </c>
       <c r="G155" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H155" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I155" s="13" t="inlineStr">
@@ -21190,57 +21206,49 @@
       </c>
       <c r="K155" s="14" t="inlineStr">
         <is>
-          <t>ÁREAS VERDES EN LA CIUDAD DE MÉXICO. EL ARTÍCULO 105 DE LA LEY AMBIENTAL LOCAL EN LA PORCIÓN NORMATIVA QUE DISPONE SU FORMA DE COMPENSACIÓN DE LAS AFECTADAS POR LA EJECUCIÓN DE ALGUNA OBRA PÚBLICA, VIOLA EL DERECHO HUMANO A UN MEDIO AMBIENTE SANO, EN SU VERTIENTE DE PROGRESIVIDAD.</t>
+          <t>POSESIÓN DERIVADA. NO PRODUCE LOS EFECTOS DE LA POSESIÓN ORIGINARIA PARA EFECTOS DE LA PRESCRIPCIÓN ADQUISITIVA.</t>
         </is>
       </c>
       <c r="L155" s="13" t="inlineStr">
         <is>
-          <t>2032312</t>
+          <t>2030499</t>
         </is>
       </c>
       <c r="M155" s="13" t="inlineStr"/>
-      <c r="N155" s="13" t="inlineStr">
-        <is>
-          <t>viernes 26 de junio de 2026 10:</t>
-        </is>
-      </c>
-      <c r="O155" s="13" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
-        </is>
-      </c>
+      <c r="N155" s="13" t="inlineStr"/>
+      <c r="O155" s="13" t="inlineStr"/>
       <c r="P155" s="13" t="inlineStr"/>
       <c r="Q155" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Quien posee por virtud de un título que reconoce dominio ajeno (arrendatario, comodatario, usufructuario, depositario) no posee en concepto de propietario y no puede usucapir, salvo intervertio possessionis acreditada.</t>
         </is>
       </c>
       <c r="R155" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Filtra acciones de usucapión espurias por arrendatarios o detentadores.</t>
         </is>
       </c>
       <c r="S155" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>El demandado por arrendamiento puede oponer la usucapión solo si demuestra que cambió el concepto de su posesión a originaria — hecho que rara vez se prueba.</t>
         </is>
       </c>
       <c r="T155" s="13" t="inlineStr"/>
       <c r="U155" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032312</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2030499</t>
         </is>
       </c>
       <c r="V155" s="13" t="inlineStr">
         <is>
-          <t>Medio ambiente sano · actualización automática</t>
+          <t>posesión derivada · concepto de propietario · interversión</t>
         </is>
       </c>
     </row>
     <row r="156" ht="80" customHeight="1">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>auto-2032313</t>
+          <t>con-asa-001</t>
         </is>
       </c>
       <c r="B156" s="11" t="n">
@@ -21253,17 +21261,17 @@
       </c>
       <c r="D156" s="11" t="inlineStr">
         <is>
-          <t>Constitucional / DDHH</t>
+          <t>Civil — Condominio</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
         <is>
-          <t>Medio ambiente sano</t>
+          <t>Régimen de propiedad en condominio</t>
         </is>
       </c>
       <c r="F156" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Asambleas — convocatoria y validez</t>
         </is>
       </c>
       <c r="G156" s="11" t="inlineStr">
@@ -21273,7 +21281,7 @@
       </c>
       <c r="H156" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I156" s="11" t="inlineStr">
@@ -21283,62 +21291,54 @@
       </c>
       <c r="J156" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Federal — interpreta LPCI CDMX</t>
         </is>
       </c>
       <c r="K156" s="12" t="inlineStr">
         <is>
-          <t>ÁREAS VERDES EN LA CIUDAD DE MÉXICO. EL ARTÍCULO 105 DE LA LEY AMBIENTAL LOCAL EN LA PORCIÓN NORMATIVA QUE ESTABLECE QUE LAS ÁREAS VERDES DEBERÁN INCREMENTAR O CONSERVAR SU EXTENSIÓN, NO VIOLA EL DERECHO HUMANO A UN MEDIO AMBIENTE SANO, EN SU VERTIENTE DE PROGRESIVIDAD.</t>
+          <t>ASAMBLEAS CONDOMINALES. LA INDEBIDA CONVOCATORIA AFECTA LA VALIDEZ DE LOS ACUERDOS Y PERMITE SU IMPUGNACIÓN.</t>
         </is>
       </c>
       <c r="L156" s="11" t="inlineStr">
         <is>
-          <t>2032313</t>
+          <t>Art. 32 LPCI CDMX</t>
         </is>
       </c>
       <c r="M156" s="11" t="inlineStr"/>
-      <c r="N156" s="11" t="inlineStr">
-        <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
-        </is>
-      </c>
-      <c r="O156" s="11" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
-        </is>
-      </c>
+      <c r="N156" s="11" t="inlineStr"/>
+      <c r="O156" s="11" t="inlineStr"/>
       <c r="P156" s="11" t="inlineStr"/>
       <c r="Q156" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La convocatoria debe respetar plazo, forma y orden del día (art. 32 LPCI CDMX). Su incumplimiento es causal de nulidad de los acuerdos adoptados, salvo ratificación expresa en asamblea posterior debidamente convocada.</t>
         </is>
       </c>
       <c r="R156" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Defensa frecuente de minorías condominales.</t>
         </is>
       </c>
       <c r="S156" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Conserva pruebas de cómo se realizó la convocatoria (carteles, mensajes, fotos). Plazo de impugnación es corto (60 días naturales en CDMX desde celebración o conocimiento).</t>
         </is>
       </c>
       <c r="T156" s="11" t="inlineStr"/>
       <c r="U156" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032313</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028919</t>
         </is>
       </c>
       <c r="V156" s="11" t="inlineStr">
         <is>
-          <t>Medio ambiente sano · actualización automática</t>
+          <t>asamblea · convocatoria · nulidad · LPCI CDMX</t>
         </is>
       </c>
     </row>
     <row r="157" ht="80" customHeight="1">
       <c r="A157" s="13" t="inlineStr">
         <is>
-          <t>auto-2032575</t>
+          <t>amp-cui-001</t>
         </is>
       </c>
       <c r="B157" s="13" t="n">
@@ -21356,12 +21356,12 @@
       </c>
       <c r="E157" s="13" t="inlineStr">
         <is>
-          <t>Medio ambiente sano</t>
+          <t>Derecho humano al cuidado</t>
         </is>
       </c>
       <c r="F157" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Reconocimiento e interés legítimo</t>
         </is>
       </c>
       <c r="G157" s="13" t="inlineStr">
@@ -21386,57 +21386,57 @@
       </c>
       <c r="K157" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN DEFINITIVA EN AMPARO INDIRECTO. PARA CONCEDERLA CONTRA LA AFECTACIÓN A ÁREAS NATURALES PROTEGIDAS, EL JUZGADO DE DISTRITO DEBE ATENDER A UN ESTÁNDAR DE PROTECCIÓN REFORZADA APLICANDO LOS PRINCIPIOS AMBIENTALES DE PREVENCIÓN Y DE PRECAUCIÓN.</t>
+          <t>DERECHO HUMANO AL CUIDADO. IMPONE OBLIGACIONES DE CUYO CUMPLIMIENTO DEPENDE DIRECTAMENTE EL BIENESTAR DE LAS PERSONAS E INDIRECTAMENTE, POR INTERDEPENDENCIA, EL EJERCICIO EFECTIVO DE OTROS DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L157" s="13" t="inlineStr">
         <is>
-          <t>2032575</t>
+          <t>2032085</t>
         </is>
       </c>
       <c r="M157" s="13" t="inlineStr"/>
       <c r="N157" s="13" t="inlineStr">
         <is>
-          <t>viernes 28 de agosto de 2026 10:36 h</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O157" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P157" s="13" t="inlineStr"/>
       <c r="Q157" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>El cuidado se reconoce como derecho humano autónomo. El Estado tiene obligación de garantizarlo mediante políticas públicas, infraestructura social y reconocimiento del trabajo de cuidado no remunerado.</t>
         </is>
       </c>
       <c r="R157" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Pieza inaugural de un nuevo derecho humano en México.</t>
         </is>
       </c>
       <c r="S157" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Marco para litigios sobre obligaciones del Estado en guarderías, cuidado de personas mayores, discapacidad y omisiones legislativas absolutas.</t>
         </is>
       </c>
       <c r="T157" s="13" t="inlineStr"/>
       <c r="U157" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032575</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032085</t>
         </is>
       </c>
       <c r="V157" s="13" t="inlineStr">
         <is>
-          <t>Medio ambiente sano · actualización automática</t>
+          <t>derecho al cuidado · 12a Época · DDHH · cuidadoras</t>
         </is>
       </c>
     </row>
     <row r="158" ht="80" customHeight="1">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>auto-2032154</t>
+          <t>amp-cui-002</t>
         </is>
       </c>
       <c r="B158" s="11" t="n">
@@ -21454,12 +21454,12 @@
       </c>
       <c r="E158" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género</t>
+          <t>Derecho humano al cuidado</t>
         </is>
       </c>
       <c r="F158" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Interés legítimo para combatir omisiones legislativas</t>
         </is>
       </c>
       <c r="G158" s="11" t="inlineStr">
@@ -21484,57 +21484,57 @@
       </c>
       <c r="K158" s="12" t="inlineStr">
         <is>
-          <t>COMPENSACIÓN ECONÓMICA. ELEMENTOS MÍNIMOS QUE LA PERSONA JUZGADORA DEBE CONSIDERAR PARA MOTIVAR LA RESOLUCIÓN QUE LA CUANTIFICA, CON PERSPECTIVA DE GÉNERO.</t>
+          <t>DERECHO HUMANO AL CUIDADO. LAS MUJERES QUE REALIZAN CUIDADOS SIMPLES O COTIDIANOS NO REMUNERADOS TIENEN INTERÉS LEGÍTIMO PARA RECLAMAR OMISIONES LEGISLATIVAS ABSOLUTAS QUE IMPIDAN SU PLENO EJERCICIO.</t>
         </is>
       </c>
       <c r="L158" s="11" t="inlineStr">
         <is>
-          <t>2032154</t>
+          <t>2032086</t>
         </is>
       </c>
       <c r="M158" s="11" t="inlineStr"/>
       <c r="N158" s="11" t="inlineStr">
         <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O158" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P158" s="11" t="inlineStr"/>
       <c r="Q158" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Las mujeres que realizan trabajo de cuidados no remunerados tienen interés legítimo, sin necesidad de afectación individualizada estricta, para promover amparo contra omisiones legislativas absolutas en la materia.</t>
         </is>
       </c>
       <c r="R158" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Abre vía de amparo colectivo a millones de cuidadoras.</t>
         </is>
       </c>
       <c r="S158" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Estrategia colectiva: amparos contra ausencia de legislación de cuidados. Beneficia particularmente a mujeres de bajos ingresos que sostienen familia.</t>
         </is>
       </c>
       <c r="T158" s="11" t="inlineStr"/>
       <c r="U158" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032154</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032086</t>
         </is>
       </c>
       <c r="V158" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género · actualización automática</t>
+          <t>cuidado · interés legítimo · omisión legislativa · perspectiva género</t>
         </is>
       </c>
     </row>
     <row r="159" ht="80" customHeight="1">
       <c r="A159" s="13" t="inlineStr">
         <is>
-          <t>auto-2032184</t>
+          <t>auto-2032312</t>
         </is>
       </c>
       <c r="B159" s="13" t="n">
@@ -21552,7 +21552,7 @@
       </c>
       <c r="E159" s="13" t="inlineStr">
         <is>
-          <t>Perspectiva de género</t>
+          <t>Medio ambiente sano</t>
         </is>
       </c>
       <c r="F159" s="13" t="inlineStr">
@@ -21582,18 +21582,18 @@
       </c>
       <c r="K159" s="14" t="inlineStr">
         <is>
-          <t>VIOLENCIA FAMILIAR. CUANDO LA VÍCTIMA SEA UNA PERSONA MENOR DE EDAD Y SE ALEGUE ALIENACIÓN O MANIPULACIÓN PARENTAL, EL ÓRGANO JURISDICCIONAL DEBE ORDENAR LA PRÁCTICA DE PRUEBAS PERICIALES PARA VERIFICAR SI SE ACTUALIZA DICHA CONDICIÓN.</t>
+          <t>ÁREAS VERDES EN LA CIUDAD DE MÉXICO. EL ARTÍCULO 105 DE LA LEY AMBIENTAL LOCAL EN LA PORCIÓN NORMATIVA QUE DISPONE SU FORMA DE COMPENSACIÓN DE LAS AFECTADAS POR LA EJECUCIÓN DE ALGUNA OBRA PÚBLICA, VIOLA EL DERECHO HUMANO A UN MEDIO AMBIENTE SANO, EN SU VERTIENTE DE PROGRESIVIDAD.</t>
         </is>
       </c>
       <c r="L159" s="13" t="inlineStr">
         <is>
-          <t>2032184</t>
+          <t>2032312</t>
         </is>
       </c>
       <c r="M159" s="13" t="inlineStr"/>
       <c r="N159" s="13" t="inlineStr">
         <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
+          <t>viernes 26 de junio de 2026 10:</t>
         </is>
       </c>
       <c r="O159" s="13" t="inlineStr">
@@ -21620,19 +21620,19 @@
       <c r="T159" s="13" t="inlineStr"/>
       <c r="U159" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032184</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032312</t>
         </is>
       </c>
       <c r="V159" s="13" t="inlineStr">
         <is>
-          <t>Perspectiva de género · actualización automática</t>
+          <t>Medio ambiente sano · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="160" ht="80" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>auto-2032279</t>
+          <t>auto-2032313</t>
         </is>
       </c>
       <c r="B160" s="11" t="n">
@@ -21650,7 +21650,7 @@
       </c>
       <c r="E160" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género</t>
+          <t>Medio ambiente sano</t>
         </is>
       </c>
       <c r="F160" s="11" t="inlineStr">
@@ -21680,18 +21680,18 @@
       </c>
       <c r="K160" s="12" t="inlineStr">
         <is>
-          <t>ACTA ADMINISTRATIVA DE INVESTIGACIÓN EN EL JUICIO LABORAL. TIENE VALOR PROBATORIO AUNQUE NO SE RATIFIQUE ANTE LA AUTORIDAD JURISDICCIONAL, CUANDO CONSIGNE EL TESTIMONIO DE NIÑAS, NIÑOS Y ADOLECENTES POR ACTOS DE CONNOTACIÓN SEXUAL REALIZADOS EN SU CONTRA.</t>
+          <t>ÁREAS VERDES EN LA CIUDAD DE MÉXICO. EL ARTÍCULO 105 DE LA LEY AMBIENTAL LOCAL EN LA PORCIÓN NORMATIVA QUE ESTABLECE QUE LAS ÁREAS VERDES DEBERÁN INCREMENTAR O CONSERVAR SU EXTENSIÓN, NO VIOLA EL DERECHO HUMANO A UN MEDIO AMBIENTE SANO, EN SU VERTIENTE DE PROGRESIVIDAD.</t>
         </is>
       </c>
       <c r="L160" s="11" t="inlineStr">
         <is>
-          <t>2032279</t>
+          <t>2032313</t>
         </is>
       </c>
       <c r="M160" s="11" t="inlineStr"/>
       <c r="N160" s="11" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O160" s="11" t="inlineStr">
@@ -21718,19 +21718,19 @@
       <c r="T160" s="11" t="inlineStr"/>
       <c r="U160" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032279</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032313</t>
         </is>
       </c>
       <c r="V160" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género · actualización automática</t>
+          <t>Medio ambiente sano · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="161" ht="80" customHeight="1">
       <c r="A161" s="13" t="inlineStr">
         <is>
-          <t>auto-2032302</t>
+          <t>auto-2032575</t>
         </is>
       </c>
       <c r="B161" s="13" t="n">
@@ -21748,7 +21748,7 @@
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>Perspectiva de género</t>
+          <t>Medio ambiente sano</t>
         </is>
       </c>
       <c r="F161" s="13" t="inlineStr">
@@ -21778,18 +21778,18 @@
       </c>
       <c r="K161" s="14" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LAS AUTORIDADES INVOLUCRADAS EN DETERMINAR EL MONTO INDEMNIZATORIO POR ACTIVIDAD ADMINISTRATIVA IRREGULAR DEBEN ANALIZAR CÓMO LA PERSPECTIVA DE GÉNERO PUEDE CAMBIAR LA MANERA DE PERCIBIR Y VALORAR LAS CIRCUNSTANCIAS DEL CASO.</t>
+          <t>SUSPENSIÓN DEFINITIVA EN AMPARO INDIRECTO. PARA CONCEDERLA CONTRA LA AFECTACIÓN A ÁREAS NATURALES PROTEGIDAS, EL JUZGADO DE DISTRITO DEBE ATENDER A UN ESTÁNDAR DE PROTECCIÓN REFORZADA APLICANDO LOS PRINCIPIOS AMBIENTALES DE PREVENCIÓN Y DE PRECAUCIÓN.</t>
         </is>
       </c>
       <c r="L161" s="13" t="inlineStr">
         <is>
-          <t>2032302</t>
+          <t>2032575</t>
         </is>
       </c>
       <c r="M161" s="13" t="inlineStr"/>
       <c r="N161" s="13" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>viernes 28 de agosto de 2026 10:36 h</t>
         </is>
       </c>
       <c r="O161" s="13" t="inlineStr">
@@ -21816,19 +21816,19 @@
       <c r="T161" s="13" t="inlineStr"/>
       <c r="U161" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032302</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032575</t>
         </is>
       </c>
       <c r="V161" s="13" t="inlineStr">
         <is>
-          <t>Perspectiva de género · actualización automática</t>
+          <t>Medio ambiente sano · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="162" ht="80" customHeight="1">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>auto-2032309</t>
+          <t>auto-2032154</t>
         </is>
       </c>
       <c r="B162" s="11" t="n">
@@ -21876,18 +21876,18 @@
       </c>
       <c r="K162" s="12" t="inlineStr">
         <is>
-          <t>ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA INSTITUCIÓN EDUCATIVA SE ENCUENTRA VINCULADA A CUMPLIR CON LA GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN.</t>
+          <t>COMPENSACIÓN ECONÓMICA. ELEMENTOS MÍNIMOS QUE LA PERSONA JUZGADORA DEBE CONSIDERAR PARA MOTIVAR LA RESOLUCIÓN QUE LA CUANTIFICA, CON PERSPECTIVA DE GÉNERO.</t>
         </is>
       </c>
       <c r="L162" s="11" t="inlineStr">
         <is>
-          <t>2032309</t>
+          <t>2032154</t>
         </is>
       </c>
       <c r="M162" s="11" t="inlineStr"/>
       <c r="N162" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O162" s="11" t="inlineStr">
@@ -21914,7 +21914,7 @@
       <c r="T162" s="11" t="inlineStr"/>
       <c r="U162" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032309</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032154</t>
         </is>
       </c>
       <c r="V162" s="11" t="inlineStr">
@@ -21926,7 +21926,7 @@
     <row r="163" ht="80" customHeight="1">
       <c r="A163" s="13" t="inlineStr">
         <is>
-          <t>auto-2032325</t>
+          <t>auto-2032184</t>
         </is>
       </c>
       <c r="B163" s="13" t="n">
@@ -21974,18 +21974,18 @@
       </c>
       <c r="K163" s="14" t="inlineStr">
         <is>
-          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. ESTÁNDAR PROBATORIO PARA DETERMINAR LA LEGALIDAD DE LA RESCISIÓN DE LA RELACIÓN LABORAL.</t>
+          <t>VIOLENCIA FAMILIAR. CUANDO LA VÍCTIMA SEA UNA PERSONA MENOR DE EDAD Y SE ALEGUE ALIENACIÓN O MANIPULACIÓN PARENTAL, EL ÓRGANO JURISDICCIONAL DEBE ORDENAR LA PRÁCTICA DE PRUEBAS PERICIALES PARA VERIFICAR SI SE ACTUALIZA DICHA CONDICIÓN.</t>
         </is>
       </c>
       <c r="L163" s="13" t="inlineStr">
         <is>
-          <t>2032325</t>
+          <t>2032184</t>
         </is>
       </c>
       <c r="M163" s="13" t="inlineStr"/>
       <c r="N163" s="13" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O163" s="13" t="inlineStr">
@@ -22012,7 +22012,7 @@
       <c r="T163" s="13" t="inlineStr"/>
       <c r="U163" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032325</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032184</t>
         </is>
       </c>
       <c r="V163" s="13" t="inlineStr">
@@ -22024,7 +22024,7 @@
     <row r="164" ht="80" customHeight="1">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>auto-2032326</t>
+          <t>auto-2032279</t>
         </is>
       </c>
       <c r="B164" s="11" t="n">
@@ -22072,18 +22072,18 @@
       </c>
       <c r="K164" s="12" t="inlineStr">
         <is>
-          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA AUTORIDAD JURISDICCIONAL DEBE ARMONIZAR EL PRINCIPIO DE PRESUNCIÓN DE INOCENCIA CON LA PERSPECTIVA DE GÉNERO.</t>
+          <t>ACTA ADMINISTRATIVA DE INVESTIGACIÓN EN EL JUICIO LABORAL. TIENE VALOR PROBATORIO AUNQUE NO SE RATIFIQUE ANTE LA AUTORIDAD JURISDICCIONAL, CUANDO CONSIGNE EL TESTIMONIO DE NIÑAS, NIÑOS Y ADOLECENTES POR ACTOS DE CONNOTACIÓN SEXUAL REALIZADOS EN SU CONTRA.</t>
         </is>
       </c>
       <c r="L164" s="11" t="inlineStr">
         <is>
-          <t>2032326</t>
+          <t>2032279</t>
         </is>
       </c>
       <c r="M164" s="11" t="inlineStr"/>
       <c r="N164" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O164" s="11" t="inlineStr">
@@ -22110,7 +22110,7 @@
       <c r="T164" s="11" t="inlineStr"/>
       <c r="U164" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032326</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032279</t>
         </is>
       </c>
       <c r="V164" s="11" t="inlineStr">
@@ -22122,7 +22122,7 @@
     <row r="165" ht="80" customHeight="1">
       <c r="A165" s="13" t="inlineStr">
         <is>
-          <t>auto-2032327</t>
+          <t>auto-2032302</t>
         </is>
       </c>
       <c r="B165" s="13" t="n">
@@ -22170,18 +22170,18 @@
       </c>
       <c r="K165" s="14" t="inlineStr">
         <is>
-          <t>ESTÁNDAR DE LA PERSONA OBSERVADORA RAZONABLE. ASPECTOS QUE DEBE PONDERAR LA AUTORIDAD LABORAL PARA DETERMINAR LA EVENTUAL GRAVEDAD DE LA FALTA DE PROBIDAD ATRIBUIDA A LA PERSONA TRABAJADORA EN CASOS DE ACOSO U HOSTIGAMIENTO SEXUAL EN INSTITUCIONES EDUCATIVAS.</t>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LAS AUTORIDADES INVOLUCRADAS EN DETERMINAR EL MONTO INDEMNIZATORIO POR ACTIVIDAD ADMINISTRATIVA IRREGULAR DEBEN ANALIZAR CÓMO LA PERSPECTIVA DE GÉNERO PUEDE CAMBIAR LA MANERA DE PERCIBIR Y VALORAR LAS CIRCUNSTANCIAS DEL CASO.</t>
         </is>
       </c>
       <c r="L165" s="13" t="inlineStr">
         <is>
-          <t>2032327</t>
+          <t>2032302</t>
         </is>
       </c>
       <c r="M165" s="13" t="inlineStr"/>
       <c r="N165" s="13" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O165" s="13" t="inlineStr">
@@ -22208,7 +22208,7 @@
       <c r="T165" s="13" t="inlineStr"/>
       <c r="U165" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032327</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032302</t>
         </is>
       </c>
       <c r="V165" s="13" t="inlineStr">
@@ -22220,7 +22220,7 @@
     <row r="166" ht="80" customHeight="1">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>auto-2032338</t>
+          <t>auto-2032309</t>
         </is>
       </c>
       <c r="B166" s="11" t="n">
@@ -22268,12 +22268,12 @@
       </c>
       <c r="K166" s="12" t="inlineStr">
         <is>
-          <t>PERSPECTIVA DE GÉNERO. DEBE OBSERVARSE EN EL TRÁMITE Y RESOLUCIÓN DEL JUICIO LABORAL COMO GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN DE ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES.</t>
+          <t>ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA INSTITUCIÓN EDUCATIVA SE ENCUENTRA VINCULADA A CUMPLIR CON LA GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN.</t>
         </is>
       </c>
       <c r="L166" s="11" t="inlineStr">
         <is>
-          <t>2032338</t>
+          <t>2032309</t>
         </is>
       </c>
       <c r="M166" s="11" t="inlineStr"/>
@@ -22306,7 +22306,7 @@
       <c r="T166" s="11" t="inlineStr"/>
       <c r="U166" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032338</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032309</t>
         </is>
       </c>
       <c r="V166" s="11" t="inlineStr">
@@ -22318,7 +22318,7 @@
     <row r="167" ht="80" customHeight="1">
       <c r="A167" s="13" t="inlineStr">
         <is>
-          <t>auto-2032340</t>
+          <t>auto-2032325</t>
         </is>
       </c>
       <c r="B167" s="13" t="n">
@@ -22366,12 +22366,12 @@
       </c>
       <c r="K167" s="14" t="inlineStr">
         <is>
-          <t>PERSPECTIVA DE PERSONA ADULTA MAYOR. SU APLICACIÓN EXIGE IDENTIFICAR LAS CONDICIONES CONCRETAS DE VULNERABILIDAD QUE PUEDAN GENERAR UNA DESVENTAJA EN EL EJERCICIO DE SUS DERECHOS.</t>
+          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. ESTÁNDAR PROBATORIO PARA DETERMINAR LA LEGALIDAD DE LA RESCISIÓN DE LA RELACIÓN LABORAL.</t>
         </is>
       </c>
       <c r="L167" s="13" t="inlineStr">
         <is>
-          <t>2032340</t>
+          <t>2032325</t>
         </is>
       </c>
       <c r="M167" s="13" t="inlineStr"/>
@@ -22404,7 +22404,7 @@
       <c r="T167" s="13" t="inlineStr"/>
       <c r="U167" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032340</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032325</t>
         </is>
       </c>
       <c r="V167" s="13" t="inlineStr">
@@ -22416,7 +22416,7 @@
     <row r="168" ht="80" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>auto-2032347</t>
+          <t>auto-2032326</t>
         </is>
       </c>
       <c r="B168" s="11" t="n">
@@ -22464,12 +22464,12 @@
       </c>
       <c r="K168" s="12" t="inlineStr">
         <is>
-          <t>PRUEBA TESTIMONIAL EN EL PROCEDIMIENTO LABORAL. LA DECLARACIÓN RENDIDA POR PERSONAS DOCENTES GOZA DE RELEVANCIA PROBATORIA EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS.</t>
+          <t>DESPIDO DISCIPLINARIO EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS. LA AUTORIDAD JURISDICCIONAL DEBE ARMONIZAR EL PRINCIPIO DE PRESUNCIÓN DE INOCENCIA CON LA PERSPECTIVA DE GÉNERO.</t>
         </is>
       </c>
       <c r="L168" s="11" t="inlineStr">
         <is>
-          <t>2032347</t>
+          <t>2032326</t>
         </is>
       </c>
       <c r="M168" s="11" t="inlineStr"/>
@@ -22502,7 +22502,7 @@
       <c r="T168" s="11" t="inlineStr"/>
       <c r="U168" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032347</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032326</t>
         </is>
       </c>
       <c r="V168" s="11" t="inlineStr">
@@ -22514,7 +22514,7 @@
     <row r="169" ht="80" customHeight="1">
       <c r="A169" s="13" t="inlineStr">
         <is>
-          <t>auto-2032376</t>
+          <t>auto-2032327</t>
         </is>
       </c>
       <c r="B169" s="13" t="n">
@@ -22562,18 +22562,18 @@
       </c>
       <c r="K169" s="14" t="inlineStr">
         <is>
-          <t>DAÑO MORAL RECLAMADO A LAS COMPAÑÍAS ASEGURADORAS. PUEDE GENERARSE ANTE ACTOS DISCRIMINATORIOS OCASIONADOS POR EL USO DE LENGUAJE BASADO EN ESTEREOTIPOS O PREJUICIOS POR RAZÓN DE GÉNERO.</t>
+          <t>ESTÁNDAR DE LA PERSONA OBSERVADORA RAZONABLE. ASPECTOS QUE DEBE PONDERAR LA AUTORIDAD LABORAL PARA DETERMINAR LA EVENTUAL GRAVEDAD DE LA FALTA DE PROBIDAD ATRIBUIDA A LA PERSONA TRABAJADORA EN CASOS DE ACOSO U HOSTIGAMIENTO SEXUAL EN INSTITUCIONES EDUCATIVAS.</t>
         </is>
       </c>
       <c r="L169" s="13" t="inlineStr">
         <is>
-          <t>2032376</t>
+          <t>2032327</t>
         </is>
       </c>
       <c r="M169" s="13" t="inlineStr"/>
       <c r="N169" s="13" t="inlineStr">
         <is>
-          <t>viernes 03 de julio de 2026 10:10 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O169" s="13" t="inlineStr">
@@ -22600,7 +22600,7 @@
       <c r="T169" s="13" t="inlineStr"/>
       <c r="U169" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032376</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032327</t>
         </is>
       </c>
       <c r="V169" s="13" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="170" ht="80" customHeight="1">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t>auto-2032666</t>
+          <t>auto-2032338</t>
         </is>
       </c>
       <c r="B170" s="11" t="n">
@@ -22660,18 +22660,18 @@
       </c>
       <c r="K170" s="12" t="inlineStr">
         <is>
-          <t>NIÑAS Y NIÑOS CON DISCAPACIDAD. SU SITUACIÓN DE VULNERABILIDAD DEBE ANALIZARSE DESDE UNA PERSPECTIVA INTERSECCIONAL, QUE CONSIDERE TAMBIÉN LAS CONDICIONES DE LAS PERSONAS QUE EJERCEN SU CUIDADO PRIMARIO, A EFECTO DE GARANTIZARLES EL EJERCICIO DE SUS PROPIOS DERECHOS.</t>
+          <t>PERSPECTIVA DE GÉNERO. DEBE OBSERVARSE EN EL TRÁMITE Y RESOLUCIÓN DEL JUICIO LABORAL COMO GARANTÍA DE PREVENCIÓN, REPARACIÓN Y NO REPETICIÓN DE ACTOS DE VIOLENCIA O ACOSO SEXUAL DE UN TRABAJADOR DOCENTE CONTRA MUJERES ADOLESCENTES.</t>
         </is>
       </c>
       <c r="L170" s="11" t="inlineStr">
         <is>
-          <t>2032666</t>
+          <t>2032338</t>
         </is>
       </c>
       <c r="M170" s="11" t="inlineStr"/>
       <c r="N170" s="11" t="inlineStr">
         <is>
-          <t>viernes 25 de septiembre de 2026 10:34 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O170" s="11" t="inlineStr">
@@ -22698,7 +22698,7 @@
       <c r="T170" s="11" t="inlineStr"/>
       <c r="U170" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032666</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032338</t>
         </is>
       </c>
       <c r="V170" s="11" t="inlineStr">
@@ -22710,7 +22710,7 @@
     <row r="171" ht="80" customHeight="1">
       <c r="A171" s="13" t="inlineStr">
         <is>
-          <t>auto-2032687</t>
+          <t>auto-2032340</t>
         </is>
       </c>
       <c r="B171" s="13" t="n">
@@ -22758,18 +22758,18 @@
       </c>
       <c r="K171" s="14" t="inlineStr">
         <is>
-          <t>VÍA LABORAL. SU PROCEDENCIA DEBE ANALIZARSE CON PERSPECTIVA DE GÉNERO CUANDO UNA TRABAJADORA DEMANDA EL CESE DE HOSTIGAMIENTO LABORAL (MOBBING).</t>
+          <t>PERSPECTIVA DE PERSONA ADULTA MAYOR. SU APLICACIÓN EXIGE IDENTIFICAR LAS CONDICIONES CONCRETAS DE VULNERABILIDAD QUE PUEDAN GENERAR UNA DESVENTAJA EN EL EJERCICIO DE SUS DERECHOS.</t>
         </is>
       </c>
       <c r="L171" s="13" t="inlineStr">
         <is>
-          <t>2032687</t>
+          <t>2032340</t>
         </is>
       </c>
       <c r="M171" s="13" t="inlineStr"/>
       <c r="N171" s="13" t="inlineStr">
         <is>
-          <t>viernes 25 de septiembre de 2026 10:34 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O171" s="13" t="inlineStr">
@@ -22796,7 +22796,7 @@
       <c r="T171" s="13" t="inlineStr"/>
       <c r="U171" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032687</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032340</t>
         </is>
       </c>
       <c r="V171" s="13" t="inlineStr">
@@ -22808,7 +22808,7 @@
     <row r="172" ht="80" customHeight="1">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t>amp-gen-001</t>
+          <t>auto-2032347</t>
         </is>
       </c>
       <c r="B172" s="11" t="n">
@@ -22826,12 +22826,12 @@
       </c>
       <c r="E172" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género interseccional</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F172" s="11" t="inlineStr">
         <is>
-          <t>Acceso a la justicia para mujeres cuidadoras</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr">
@@ -22856,57 +22856,57 @@
       </c>
       <c r="K172" s="12" t="inlineStr">
         <is>
-          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
+          <t>PRUEBA TESTIMONIAL EN EL PROCEDIMIENTO LABORAL. LA DECLARACIÓN RENDIDA POR PERSONAS DOCENTES GOZA DE RELEVANCIA PROBATORIA EN CASOS DE ACOSO O VIOLENCIA SEXUAL CONTRA MUJERES ADOLESCENTES EN ESCUELAS.</t>
         </is>
       </c>
       <c r="L172" s="11" t="inlineStr">
         <is>
-          <t>2032067</t>
+          <t>2032347</t>
         </is>
       </c>
       <c r="M172" s="11" t="inlineStr"/>
       <c r="N172" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O172" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P172" s="11" t="inlineStr"/>
       <c r="Q172" s="11" t="inlineStr">
         <is>
-          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R172" s="11" t="inlineStr">
         <is>
-          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S172" s="11" t="inlineStr">
         <is>
-          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T172" s="11" t="inlineStr"/>
       <c r="U172" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032347</t>
         </is>
       </c>
       <c r="V172" s="11" t="inlineStr">
         <is>
-          <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="173" ht="80" customHeight="1">
       <c r="A173" s="13" t="inlineStr">
         <is>
-          <t>auto-2032750</t>
+          <t>auto-2032376</t>
         </is>
       </c>
       <c r="B173" s="13" t="n">
@@ -22919,12 +22919,12 @@
       </c>
       <c r="D173" s="13" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E173" s="13" t="inlineStr">
         <is>
-          <t>Caducidad de facultades del fisco</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F173" s="13" t="inlineStr">
@@ -22954,18 +22954,18 @@
       </c>
       <c r="K173" s="14" t="inlineStr">
         <is>
-          <t>PROCEDIMIENTO DE PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES DIGITALES POR INTERNET. LE ES INAPLICABLE EL PLAZO DE CADUCIDAD PREVISTO EN EL ARTÍCULO 67 DEL CÓDIGO FISCAL DE LA FEDERACIÓN.</t>
+          <t>DAÑO MORAL RECLAMADO A LAS COMPAÑÍAS ASEGURADORAS. PUEDE GENERARSE ANTE ACTOS DISCRIMINATORIOS OCASIONADOS POR EL USO DE LENGUAJE BASADO EN ESTEREOTIPOS O PREJUICIOS POR RAZÓN DE GÉNERO.</t>
         </is>
       </c>
       <c r="L173" s="13" t="inlineStr">
         <is>
-          <t>2032750</t>
+          <t>2032376</t>
         </is>
       </c>
       <c r="M173" s="13" t="inlineStr"/>
       <c r="N173" s="13" t="inlineStr">
         <is>
-          <t>viernes 09 de octubre de 2026 10:19 h</t>
+          <t>viernes 03 de julio de 2026 10:10 h</t>
         </is>
       </c>
       <c r="O173" s="13" t="inlineStr">
@@ -22992,19 +22992,19 @@
       <c r="T173" s="13" t="inlineStr"/>
       <c r="U173" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032750</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032376</t>
         </is>
       </c>
       <c r="V173" s="13" t="inlineStr">
         <is>
-          <t>Caducidad de facultades del fisco · actualización automática</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="174" ht="80" customHeight="1">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>auto-2032638</t>
+          <t>auto-2032666</t>
         </is>
       </c>
       <c r="B174" s="11" t="n">
@@ -23017,12 +23017,12 @@
       </c>
       <c r="D174" s="11" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F174" s="11" t="inlineStr">
@@ -23052,18 +23052,18 @@
       </c>
       <c r="K174" s="12" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES. DEBE NEGARSE VALOR PROBATORIO A LOS CONTRATOS DE COMODATO REDACTADOS DE FORMA GENÉRICA AL NO SER SUSCEPTIBLES DE EVIDENCIAR CAPACIDAD OPERATIVA REAL PARA ACREDITAR SU MATERIALIDAD.</t>
+          <t>NIÑAS Y NIÑOS CON DISCAPACIDAD. SU SITUACIÓN DE VULNERABILIDAD DEBE ANALIZARSE DESDE UNA PERSPECTIVA INTERSECCIONAL, QUE CONSIDERE TAMBIÉN LAS CONDICIONES DE LAS PERSONAS QUE EJERCEN SU CUIDADO PRIMARIO, A EFECTO DE GARANTIZARLES EL EJERCICIO DE SUS PROPIOS DERECHOS.</t>
         </is>
       </c>
       <c r="L174" s="11" t="inlineStr">
         <is>
-          <t>2032638</t>
+          <t>2032666</t>
         </is>
       </c>
       <c r="M174" s="11" t="inlineStr"/>
       <c r="N174" s="11" t="inlineStr">
         <is>
-          <t>viernes 18 de septiembre de 2026 10:27 h</t>
+          <t>viernes 25 de septiembre de 2026 10:34 h</t>
         </is>
       </c>
       <c r="O174" s="11" t="inlineStr">
@@ -23090,19 +23090,19 @@
       <c r="T174" s="11" t="inlineStr"/>
       <c r="U174" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032638</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032666</t>
         </is>
       </c>
       <c r="V174" s="11" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI) · actualización automática</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="175" ht="80" customHeight="1">
       <c r="A175" s="13" t="inlineStr">
         <is>
-          <t>fis-cfd-002</t>
+          <t>auto-2032687</t>
         </is>
       </c>
       <c r="B175" s="13" t="n">
@@ -23115,22 +23115,22 @@
       </c>
       <c r="D175" s="13" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E175" s="13" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F175" s="13" t="inlineStr">
         <is>
-          <t>69-B — recurso de revocación y buzón tributario</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G175" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H175" s="13" t="inlineStr">
@@ -23150,57 +23150,57 @@
       </c>
       <c r="K175" s="14" t="inlineStr">
         <is>
-          <t>RECURSO DE REVOCACIÓN CONTRA LA RESOLUCIÓN FINAL PREVISTA EN EL ARTÍCULO 69-B, PÁRRAFO CUARTO, DEL CFF. EL PLAZO PARA INTERPONERLO COMIENZA A PARTIR DE SU NOTIFICACIÓN A TRAVÉS DEL BUZÓN TRIBUTARIO.</t>
+          <t>VÍA LABORAL. SU PROCEDENCIA DEBE ANALIZARSE CON PERSPECTIVA DE GÉNERO CUANDO UNA TRABAJADORA DEMANDA EL CESE DE HOSTIGAMIENTO LABORAL (MOBBING).</t>
         </is>
       </c>
       <c r="L175" s="13" t="inlineStr">
         <is>
-          <t>2031931</t>
+          <t>2032687</t>
         </is>
       </c>
       <c r="M175" s="13" t="inlineStr"/>
       <c r="N175" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 25 de septiembre de 2026 10:34 h</t>
         </is>
       </c>
       <c r="O175" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P175" s="13" t="inlineStr"/>
       <c r="Q175" s="13" t="inlineStr">
         <is>
-          <t>El plazo de 30 días para interponer recurso de revocación contra resolución definitiva del 69-B se computa desde notificación por buzón tributario, no desde publicación en DOF.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R175" s="13" t="inlineStr">
         <is>
-          <t>Define cómputo de plazo para defensa contra inclusión definitiva en EFOS.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S175" s="13" t="inlineStr">
         <is>
-          <t>Hay que monitorear el buzón tributario. Cuenta el plazo desde recepción ahí, no desde publicación DOF. Crítico para no perder defensa.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T175" s="13" t="inlineStr"/>
       <c r="U175" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031931</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032687</t>
         </is>
       </c>
       <c r="V175" s="13" t="inlineStr">
         <is>
-          <t>69-B CFF · recurso revocación · buzón tributario · EFOS</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="176" ht="80" customHeight="1">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>fis-cfd-003</t>
+          <t>auto-2032779</t>
         </is>
       </c>
       <c r="B176" s="11" t="n">
@@ -23213,17 +23213,17 @@
       </c>
       <c r="D176" s="11" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E176" s="11" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F176" s="11" t="inlineStr">
         <is>
-          <t>Materialidad — fundar y motivar</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G176" s="11" t="inlineStr">
@@ -23248,57 +23248,57 @@
       </c>
       <c r="K176" s="12" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES. DEBER DE FUNDAR Y MOTIVAR LA DECISIÓN DE REVERTIR LA CARGA PROBATORIA PARA ACREDITAR SU MATERIALIDAD.</t>
+          <t>PERSPECTIVA DE GÉNERO EN MATERIA LABORAL. SU APLICACIÓN EXIGE A LA PERSONA JUZGADORA NO INCURRIR EN FORMALISMO MÁGICO DURANTE EL TRÁMITE Y RESOLUCIÓN DEL JUICIO.</t>
         </is>
       </c>
       <c r="L176" s="11" t="inlineStr">
         <is>
-          <t>2031350</t>
+          <t>2032779</t>
         </is>
       </c>
       <c r="M176" s="11" t="inlineStr"/>
       <c r="N176" s="11" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 16 de octubre de 2026 10:26 h</t>
         </is>
       </c>
       <c r="O176" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P176" s="11" t="inlineStr"/>
       <c r="Q176" s="11" t="inlineStr">
         <is>
-          <t>El SAT no puede simplemente requerir materialidad; debe fundar y motivar específicamente las razones por las que presume inexistencia. Sin esa fundamentación, la inversión de carga es inválida.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R176" s="11" t="inlineStr">
         <is>
-          <t>Defensa fuerte para contribuyentes auditados.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S176" s="11" t="inlineStr">
         <is>
-          <t>Si el SAT no detalla por qué presume inexistencia (red flag específico), su requerimiento es nulo. Cuestionar fundamentación es el primer paso del litigio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T176" s="11" t="inlineStr"/>
       <c r="U176" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031350</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032779</t>
         </is>
       </c>
       <c r="V176" s="11" t="inlineStr">
         <is>
-          <t>69-B · materialidad · fundamentación · 12a Época</t>
+          <t>Perspectiva de género · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="177" ht="80" customHeight="1">
       <c r="A177" s="13" t="inlineStr">
         <is>
-          <t>fis-cfd-004</t>
+          <t>amp-gen-001</t>
         </is>
       </c>
       <c r="B177" s="13" t="n">
@@ -23311,17 +23311,17 @@
       </c>
       <c r="D177" s="13" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Constitucional / DDHH</t>
         </is>
       </c>
       <c r="E177" s="13" t="inlineStr">
         <is>
-          <t>Comprobantes fiscales (CFDI)</t>
+          <t>Perspectiva de género interseccional</t>
         </is>
       </c>
       <c r="F177" s="13" t="inlineStr">
         <is>
-          <t>Nulidad EFOS — efectos sobre proveedor</t>
+          <t>Acceso a la justicia para mujeres cuidadoras</t>
         </is>
       </c>
       <c r="G177" s="13" t="inlineStr">
@@ -23346,57 +23346,57 @@
       </c>
       <c r="K177" s="14" t="inlineStr">
         <is>
-          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES. CONSECUENCIA DE LA NULIDAD DE LA RESOLUCIÓN QUE INCLUYE A UN PROVEEDOR EN EL LISTADO DE EMPRESAS QUE FACTURAN OPERACIONES SIMULADAS (EFOS).</t>
+          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
         </is>
       </c>
       <c r="L177" s="13" t="inlineStr">
         <is>
-          <t>2031349</t>
+          <t>2032067</t>
         </is>
       </c>
       <c r="M177" s="13" t="inlineStr"/>
       <c r="N177" s="13" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O177" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P177" s="13" t="inlineStr"/>
       <c r="Q177" s="13" t="inlineStr">
         <is>
-          <t>Cuando se obtiene la nulidad de la resolución que incluyó al proveedor en EFOS definitivas, esa nulidad debe surtir efectos respecto del contribuyente que deducción afectada.</t>
+          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
         </is>
       </c>
       <c r="R177" s="13" t="inlineStr">
         <is>
-          <t>Cadena de protección para contribuyentes que dedujeron con proveedores listados.</t>
+          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
         </is>
       </c>
       <c r="S177" s="13" t="inlineStr">
         <is>
-          <t>Si tu proveedor logra que le quiten de EFOS por sentencia firme, tú puedes invocarlo para recuperar deducciones rechazadas. Defensa colectiva.</t>
+          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
         </is>
       </c>
       <c r="T177" s="13" t="inlineStr"/>
       <c r="U177" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031349</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
         </is>
       </c>
       <c r="V177" s="13" t="inlineStr">
         <is>
-          <t>EFOS · nulidad · deducciones · 12a Época</t>
+          <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="178" ht="80" customHeight="1">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>auto-2032714</t>
+          <t>auto-2032750</t>
         </is>
       </c>
       <c r="B178" s="11" t="n">
@@ -23414,7 +23414,7 @@
       </c>
       <c r="E178" s="11" t="inlineStr">
         <is>
-          <t>Devolución de saldos a favor</t>
+          <t>Caducidad de facultades del fisco</t>
         </is>
       </c>
       <c r="F178" s="11" t="inlineStr">
@@ -23444,18 +23444,18 @@
       </c>
       <c r="K178" s="12" t="inlineStr">
         <is>
-          <t>PREMIO DE ANTIGÜEDAD. NO ES EQUIPARABLE A LA PRIMA DE ANTIGÜEDAD PARA EFECTOS DE LA EXENCIÓN PREVISTA EN EL ARTÍCULO 93, FRACCIÓN XIII, DE LA LEY DEL IMPUESTO SOBRE LA RENTA.</t>
+          <t>PROCEDIMIENTO DE PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES DIGITALES POR INTERNET. LE ES INAPLICABLE EL PLAZO DE CADUCIDAD PREVISTO EN EL ARTÍCULO 67 DEL CÓDIGO FISCAL DE LA FEDERACIÓN.</t>
         </is>
       </c>
       <c r="L178" s="11" t="inlineStr">
         <is>
-          <t>2032714</t>
+          <t>2032750</t>
         </is>
       </c>
       <c r="M178" s="11" t="inlineStr"/>
       <c r="N178" s="11" t="inlineStr">
         <is>
-          <t>viernes 02 de octubre de 2026 10:12 h</t>
+          <t>viernes 09 de octubre de 2026 10:19 h</t>
         </is>
       </c>
       <c r="O178" s="11" t="inlineStr">
@@ -23482,19 +23482,19 @@
       <c r="T178" s="11" t="inlineStr"/>
       <c r="U178" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032714</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032750</t>
         </is>
       </c>
       <c r="V178" s="11" t="inlineStr">
         <is>
-          <t>Devolución de saldos a favor · actualización automática</t>
+          <t>Caducidad de facultades del fisco · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="179" ht="80" customHeight="1">
       <c r="A179" s="13" t="inlineStr">
         <is>
-          <t>auto-2032254</t>
+          <t>auto-2032638</t>
         </is>
       </c>
       <c r="B179" s="13" t="n">
@@ -23507,12 +23507,12 @@
       </c>
       <c r="D179" s="13" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E179" s="13" t="inlineStr">
         <is>
-          <t>Despido injustificado</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F179" s="13" t="inlineStr">
@@ -23542,18 +23542,18 @@
       </c>
       <c r="K179" s="14" t="inlineStr">
         <is>
-          <t>CARGA PROBATORIA EN EL JUICIO LABORAL. CORRESPONDE A LA PATRONAL ACREDITAR EL MONTO Y PAGO DEL SALARIO, AUN CUANDO LA PERSONA TRABAJADORA ALEGUE QUE RECIBE UNA PARTE "FUERA DE NÓMINA".</t>
+          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES. DEBE NEGARSE VALOR PROBATORIO A LOS CONTRATOS DE COMODATO REDACTADOS DE FORMA GENÉRICA AL NO SER SUSCEPTIBLES DE EVIDENCIAR CAPACIDAD OPERATIVA REAL PARA ACREDITAR SU MATERIALIDAD.</t>
         </is>
       </c>
       <c r="L179" s="13" t="inlineStr">
         <is>
-          <t>2032254</t>
+          <t>2032638</t>
         </is>
       </c>
       <c r="M179" s="13" t="inlineStr"/>
       <c r="N179" s="13" t="inlineStr">
         <is>
-          <t>viernes 12 de junio de 2026 10:18 h</t>
+          <t>viernes 18 de septiembre de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O179" s="13" t="inlineStr">
@@ -23580,19 +23580,19 @@
       <c r="T179" s="13" t="inlineStr"/>
       <c r="U179" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032254</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032638</t>
         </is>
       </c>
       <c r="V179" s="13" t="inlineStr">
         <is>
-          <t>Despido injustificado · actualización automática</t>
+          <t>Comprobantes fiscales (CFDI) · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="180" ht="80" customHeight="1">
       <c r="A180" s="11" t="inlineStr">
         <is>
-          <t>lab-des-002</t>
+          <t>fis-cfd-002</t>
         </is>
       </c>
       <c r="B180" s="11" t="n">
@@ -23605,27 +23605,27 @@
       </c>
       <c r="D180" s="11" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E180" s="11" t="inlineStr">
         <is>
-          <t>Despido injustificado</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F180" s="11" t="inlineStr">
         <is>
-          <t>Carga patrón cuando alega rescisión justificada posterior</t>
+          <t>69-B — recurso de revocación y buzón tributario</t>
         </is>
       </c>
       <c r="G180" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H180" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I180" s="11" t="inlineStr">
@@ -23640,18 +23640,18 @@
       </c>
       <c r="K180" s="12" t="inlineStr">
         <is>
-          <t>RELACIÓN LABORAL. CUANDO LA PERSONA TRABAJADORA MANIFIESTA QUE FUE DESPEDIDA INJUSTIFICADAMENTE EN CIERTA FECHA Y EL PATRÓN ARGUMENTA QUE AQUÉLLA SUBSISTIÓ Y QUE POSTERIORMENTE LA RESCINDIÓ DE FORMA JUSTIFICADA, LE CORRESPONDE PROBAR AMBOS HECHOS.</t>
+          <t>RECURSO DE REVOCACIÓN CONTRA LA RESOLUCIÓN FINAL PREVISTA EN EL ARTÍCULO 69-B, PÁRRAFO CUARTO, DEL CFF. EL PLAZO PARA INTERPONERLO COMIENZA A PARTIR DE SU NOTIFICACIÓN A TRAVÉS DEL BUZÓN TRIBUTARIO.</t>
         </is>
       </c>
       <c r="L180" s="11" t="inlineStr">
         <is>
-          <t>2029731</t>
+          <t>2031931</t>
         </is>
       </c>
       <c r="M180" s="11" t="inlineStr"/>
       <c r="N180" s="11" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O180" s="11" t="inlineStr">
@@ -23662,35 +23662,35 @@
       <c r="P180" s="11" t="inlineStr"/>
       <c r="Q180" s="11" t="inlineStr">
         <is>
-          <t>Si el patrón niega el despido alegado y agrega rescisión justificada posterior, tiene carga de probar AMBOS: que la relación subsistió tras la fecha del supuesto despido y que la rescisión posterior fue justificada.</t>
+          <t>El plazo de 30 días para interponer recurso de revocación contra resolución definitiva del 69-B se computa desde notificación por buzón tributario, no desde publicación en DOF.</t>
         </is>
       </c>
       <c r="R180" s="11" t="inlineStr">
         <is>
-          <t>Carga doble para patrón que cambia versión durante el juicio.</t>
+          <t>Define cómputo de plazo para defensa contra inclusión definitiva en EFOS.</t>
         </is>
       </c>
       <c r="S180" s="11" t="inlineStr">
         <is>
-          <t>Estrategia trabajadora: forzar al patrón a esa narrativa, queda con carga reforzada.</t>
+          <t>Hay que monitorear el buzón tributario. Cuenta el plazo desde recepción ahí, no desde publicación DOF. Crítico para no perder defensa.</t>
         </is>
       </c>
       <c r="T180" s="11" t="inlineStr"/>
       <c r="U180" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029731</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031931</t>
         </is>
       </c>
       <c r="V180" s="11" t="inlineStr">
         <is>
-          <t>despido · rescisión · carga probatoria patrón</t>
+          <t>69-B CFF · recurso revocación · buzón tributario · EFOS</t>
         </is>
       </c>
     </row>
     <row r="181" ht="80" customHeight="1">
       <c r="A181" s="13" t="inlineStr">
         <is>
-          <t>lab-ren-001</t>
+          <t>fis-cfd-003</t>
         </is>
       </c>
       <c r="B181" s="13" t="n">
@@ -23703,17 +23703,17 @@
       </c>
       <c r="D181" s="13" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E181" s="13" t="inlineStr">
         <is>
-          <t>Renuncia laboral</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F181" s="13" t="inlineStr">
         <is>
-          <t>Hora de terminación — carga del patrón</t>
+          <t>Materialidad — fundar y motivar</t>
         </is>
       </c>
       <c r="G181" s="13" t="inlineStr">
@@ -23723,7 +23723,7 @@
       </c>
       <c r="H181" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I181" s="13" t="inlineStr">
@@ -23738,18 +23738,18 @@
       </c>
       <c r="K181" s="14" t="inlineStr">
         <is>
-          <t>RENUNCIA. CORRESPONDE A LA PARTE DEMANDADA PERFECCIONARLA CON ALGÚN MEDIO DE PRUEBA, CUANDO EXISTA CONTROVERSIA RESPECTO DE LA HORA DE TERMINACIÓN DEL VÍNCULO LABORAL Y ÉSTA NO CONSTE EN EL ESCRITO RELATIVO.</t>
+          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES AMPARADAS EN COMPROBANTES FISCALES. DEBER DE FUNDAR Y MOTIVAR LA DECISIÓN DE REVERTIR LA CARGA PROBATORIA PARA ACREDITAR SU MATERIALIDAD.</t>
         </is>
       </c>
       <c r="L181" s="13" t="inlineStr">
         <is>
-          <t>2028640</t>
+          <t>2031350</t>
         </is>
       </c>
       <c r="M181" s="13" t="inlineStr"/>
       <c r="N181" s="13" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O181" s="13" t="inlineStr">
@@ -23760,35 +23760,35 @@
       <c r="P181" s="13" t="inlineStr"/>
       <c r="Q181" s="13" t="inlineStr">
         <is>
-          <t>Si el patrón ofrece renuncia sin hora exacta y el trabajador alega despido a cierta hora, el patrón debe acreditar con prueba adicional la hora de la renuncia.</t>
+          <t>El SAT no puede simplemente requerir materialidad; debe fundar y motivar específicamente las razones por las que presume inexistencia. Sin esa fundamentación, la inversión de carga es inválida.</t>
         </is>
       </c>
       <c r="R181" s="13" t="inlineStr">
         <is>
-          <t>Cuestionamiento a renuncias forzadas con fechas/horas imprecisas.</t>
+          <t>Defensa fuerte para contribuyentes auditados.</t>
         </is>
       </c>
       <c r="S181" s="13" t="inlineStr">
         <is>
-          <t>Trabajador debe declarar hora exacta del despido; patrón tendrá que probar hora distinta.</t>
+          <t>Si el SAT no detalla por qué presume inexistencia (red flag específico), su requerimiento es nulo. Cuestionar fundamentación es el primer paso del litigio.</t>
         </is>
       </c>
       <c r="T181" s="13" t="inlineStr"/>
       <c r="U181" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028640</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031350</t>
         </is>
       </c>
       <c r="V181" s="13" t="inlineStr">
         <is>
-          <t>renuncia · hora despido · carga probatoria</t>
+          <t>69-B · materialidad · fundamentación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="182" ht="80" customHeight="1">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>lab-ren-002</t>
+          <t>fis-cfd-004</t>
         </is>
       </c>
       <c r="B182" s="11" t="n">
@@ -23801,17 +23801,17 @@
       </c>
       <c r="D182" s="11" t="inlineStr">
         <is>
-          <t>Laboral</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E182" s="11" t="inlineStr">
         <is>
-          <t>Renuncia laboral</t>
+          <t>Comprobantes fiscales (CFDI)</t>
         </is>
       </c>
       <c r="F182" s="11" t="inlineStr">
         <is>
-          <t>Veracidad — carga reforzada si trabajador iba a jubilarse</t>
+          <t>Nulidad EFOS — efectos sobre proveedor</t>
         </is>
       </c>
       <c r="G182" s="11" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="H182" s="11" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I182" s="11" t="inlineStr">
@@ -23836,18 +23836,18 @@
       </c>
       <c r="K182" s="12" t="inlineStr">
         <is>
-          <t>RENUNCIA. PARA QUE SEA VEROSÍMIL Y, POR ENDE, TENGA EFICACIA DEMOSTRATIVA PLENA, CORRESPONDE AL PATRÓN PROBAR QUE REÚNE LAS CONDICIONES DE CERTEZA Y LOS ELEMENTOS MÍNIMOS QUE REFLEJEN LA VOLUNTAD, AUTONOMÍA Y ESPONTANEIDAD DEL TRABAJADOR, SI ESTÁ PRÓXIMO A JUBILARSE.</t>
+          <t>PRESUNCIÓN DE INEXISTENCIA DE OPERACIONES. CONSECUENCIA DE LA NULIDAD DE LA RESOLUCIÓN QUE INCLUYE A UN PROVEEDOR EN EL LISTADO DE EMPRESAS QUE FACTURAN OPERACIONES SIMULADAS (EFOS).</t>
         </is>
       </c>
       <c r="L182" s="11" t="inlineStr">
         <is>
-          <t>2027058</t>
+          <t>2031349</t>
         </is>
       </c>
       <c r="M182" s="11" t="inlineStr"/>
       <c r="N182" s="11" t="inlineStr">
         <is>
-          <t>2023-2024</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O182" s="11" t="inlineStr">
@@ -23858,35 +23858,35 @@
       <c r="P182" s="11" t="inlineStr"/>
       <c r="Q182" s="11" t="inlineStr">
         <is>
-          <t>Cuando el trabajador estaba próximo a adquirir derechos jubilatorios, la renuncia exigida pasa por estándar reforzado de veracidad: voluntad, autonomía y espontaneidad demostradas con prueba sólida.</t>
+          <t>Cuando se obtiene la nulidad de la resolución que incluyó al proveedor en EFOS definitivas, esa nulidad debe surtir efectos respecto del contribuyente que deducción afectada.</t>
         </is>
       </c>
       <c r="R182" s="11" t="inlineStr">
         <is>
-          <t>Protección antes de jubilación: renuncias sospechosas no pasan.</t>
+          <t>Cadena de protección para contribuyentes que dedujeron con proveedores listados.</t>
         </is>
       </c>
       <c r="S182" s="11" t="inlineStr">
         <is>
-          <t>Defensa trabajadora: si estaba a meses/años de jubilarse, atacar renuncia por falta de espontaneidad.</t>
+          <t>Si tu proveedor logra que le quiten de EFOS por sentencia firme, tú puedes invocarlo para recuperar deducciones rechazadas. Defensa colectiva.</t>
         </is>
       </c>
       <c r="T182" s="11" t="inlineStr"/>
       <c r="U182" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027058</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031349</t>
         </is>
       </c>
       <c r="V182" s="11" t="inlineStr">
         <is>
-          <t>renuncia · jubilación · veracidad · carga reforzada</t>
+          <t>EFOS · nulidad · deducciones · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="183" ht="80" customHeight="1">
       <c r="A183" s="13" t="inlineStr">
         <is>
-          <t>sen-020</t>
+          <t>auto-2032714</t>
         </is>
       </c>
       <c r="B183" s="13" t="n">
@@ -23899,27 +23899,27 @@
       </c>
       <c r="D183" s="13" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E183" s="13" t="inlineStr">
         <is>
-          <t>Costas en juicio mercantil — tasación</t>
+          <t>Devolución de saldos a favor</t>
         </is>
       </c>
       <c r="F183" s="13" t="inlineStr">
         <is>
-          <t>Línea del Primer y Segundo Circuito (CDMX y Edomex)</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G183" s="13" t="inlineStr">
         <is>
-          <t>sentencia hito</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H183" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I183" s="13" t="inlineStr">
@@ -23929,58 +23929,62 @@
       </c>
       <c r="J183" s="13" t="inlineStr">
         <is>
-          <t>Primer y Segundo Circuito</t>
+          <t>Federal</t>
         </is>
       </c>
       <c r="K183" s="14" t="inlineStr">
         <is>
-          <t>Costas mercantiles — base de cuantificación y arancel aplicable</t>
+          <t>PREMIO DE ANTIGÜEDAD. NO ES EQUIPARABLE A LA PRIMA DE ANTIGÜEDAD PARA EFECTOS DE LA EXENCIÓN PREVISTA EN EL ARTÍCULO 93, FRACCIÓN XIII, DE LA LEY DEL IMPUESTO SOBRE LA RENTA.</t>
         </is>
       </c>
       <c r="L183" s="13" t="inlineStr">
         <is>
-          <t>Línea de Colegiados — múltiples</t>
+          <t>2032714</t>
         </is>
       </c>
       <c r="M183" s="13" t="inlineStr"/>
       <c r="N183" s="13" t="inlineStr">
         <is>
-          <t>Línea consolidada</t>
-        </is>
-      </c>
-      <c r="O183" s="13" t="inlineStr"/>
+          <t>viernes 02 de octubre de 2026 10:12 h</t>
+        </is>
+      </c>
+      <c r="O183" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
       <c r="P183" s="13" t="inlineStr"/>
       <c r="Q183" s="13" t="inlineStr">
         <is>
-          <t>Las costas en juicio mercantil se cuantifican con base en el monto efectivamente condenado y conforme al arancel local vigente al momento de cuantificarlas. La condena en costas presupone temeridad o vencimiento total.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R183" s="13" t="inlineStr">
         <is>
-          <t>Marco práctico para pretensión y oposición a costas.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S183" s="13" t="inlineStr">
         <is>
-          <t>El acreedor que gana en ejecutivo debe solicitar tasación con arancel actualizado. El deudor debe oponerse cuando la cuantificación excede el monto del juicio o aplica arancel inadecuado.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T183" s="13" t="inlineStr"/>
       <c r="U183" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031803</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032714</t>
         </is>
       </c>
       <c r="V183" s="13" t="inlineStr">
         <is>
-          <t>costas · tasación · arancel · mercantil</t>
+          <t>Devolución de saldos a favor · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="184" ht="80" customHeight="1">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>auto-2032198</t>
+          <t>auto-2032254</t>
         </is>
       </c>
       <c r="B184" s="11" t="n">
@@ -23993,12 +23997,12 @@
       </c>
       <c r="D184" s="11" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Despido injustificado</t>
         </is>
       </c>
       <c r="F184" s="11" t="inlineStr">
@@ -24028,18 +24032,18 @@
       </c>
       <c r="K184" s="12" t="inlineStr">
         <is>
-          <t>GARANTÍA PARA QUE SIGA SURTIENDO EFECTOS LA SUSPENSIÓN EN AMPARO INDIRECTO. ES EXIGIBLE A LA PERSONA MORAL PRIVADA DECLARADA EN QUIEBRA, AL NO ACTUALIZARSE ALGÚN SUPUESTO LEGAL PARA EXENTAR SU EXHIBICIÓN.</t>
+          <t>CARGA PROBATORIA EN EL JUICIO LABORAL. CORRESPONDE A LA PATRONAL ACREDITAR EL MONTO Y PAGO DEL SALARIO, AUN CUANDO LA PERSONA TRABAJADORA ALEGUE QUE RECIBE UNA PARTE "FUERA DE NÓMINA".</t>
         </is>
       </c>
       <c r="L184" s="11" t="inlineStr">
         <is>
-          <t>2032198</t>
+          <t>2032254</t>
         </is>
       </c>
       <c r="M184" s="11" t="inlineStr"/>
       <c r="N184" s="11" t="inlineStr">
         <is>
-          <t>viernes 29 de mayo de 2026 10:34 h</t>
+          <t>viernes 12 de junio de 2026 10:18 h</t>
         </is>
       </c>
       <c r="O184" s="11" t="inlineStr">
@@ -24066,19 +24070,19 @@
       <c r="T184" s="11" t="inlineStr"/>
       <c r="U184" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032198</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032254</t>
         </is>
       </c>
       <c r="V184" s="11" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil · actualización automática</t>
+          <t>Despido injustificado · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="185" ht="80" customHeight="1">
       <c r="A185" s="13" t="inlineStr">
         <is>
-          <t>auto-2032274</t>
+          <t>lab-des-002</t>
         </is>
       </c>
       <c r="B185" s="13" t="n">
@@ -24091,17 +24095,17 @@
       </c>
       <c r="D185" s="13" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E185" s="13" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Despido injustificado</t>
         </is>
       </c>
       <c r="F185" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Carga patrón cuando alega rescisión justificada posterior</t>
         </is>
       </c>
       <c r="G185" s="13" t="inlineStr">
@@ -24111,7 +24115,7 @@
       </c>
       <c r="H185" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I185" s="13" t="inlineStr">
@@ -24126,57 +24130,57 @@
       </c>
       <c r="K185" s="14" t="inlineStr">
         <is>
-          <t>PRUEBA TESTIMONIAL FORÁNEA EN EL JUICIO EJECUTIVO MERCANTIL ORAL. PROCEDE DESECHARLA CUANDO NO SE OFRECE EN TÉRMINOS DEL ARTÍCULO 1269 DEL CÓDIGO DE COMERCIO.</t>
+          <t>RELACIÓN LABORAL. CUANDO LA PERSONA TRABAJADORA MANIFIESTA QUE FUE DESPEDIDA INJUSTIFICADAMENTE EN CIERTA FECHA Y EL PATRÓN ARGUMENTA QUE AQUÉLLA SUBSISTIÓ Y QUE POSTERIORMENTE LA RESCINDIÓ DE FORMA JUSTIFICADA, LE CORRESPONDE PROBAR AMBOS HECHOS.</t>
         </is>
       </c>
       <c r="L185" s="13" t="inlineStr">
         <is>
-          <t>2032274</t>
+          <t>2029731</t>
         </is>
       </c>
       <c r="M185" s="13" t="inlineStr"/>
       <c r="N185" s="13" t="inlineStr">
         <is>
-          <t>viernes 12 de junio de 2026 10:18 h</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="O185" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P185" s="13" t="inlineStr"/>
       <c r="Q185" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Si el patrón niega el despido alegado y agrega rescisión justificada posterior, tiene carga de probar AMBOS: que la relación subsistió tras la fecha del supuesto despido y que la rescisión posterior fue justificada.</t>
         </is>
       </c>
       <c r="R185" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Carga doble para patrón que cambia versión durante el juicio.</t>
         </is>
       </c>
       <c r="S185" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Estrategia trabajadora: forzar al patrón a esa narrativa, queda con carga reforzada.</t>
         </is>
       </c>
       <c r="T185" s="13" t="inlineStr"/>
       <c r="U185" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032274</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2029731</t>
         </is>
       </c>
       <c r="V185" s="13" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil · actualización automática</t>
+          <t>despido · rescisión · carga probatoria patrón</t>
         </is>
       </c>
     </row>
     <row r="186" ht="80" customHeight="1">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t>auto-2032414</t>
+          <t>lab-ren-001</t>
         </is>
       </c>
       <c r="B186" s="11" t="n">
@@ -24189,17 +24193,17 @@
       </c>
       <c r="D186" s="11" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E186" s="11" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Renuncia laboral</t>
         </is>
       </c>
       <c r="F186" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Hora de terminación — carga del patrón</t>
         </is>
       </c>
       <c r="G186" s="11" t="inlineStr">
@@ -24209,7 +24213,7 @@
       </c>
       <c r="H186" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I186" s="11" t="inlineStr">
@@ -24224,57 +24228,57 @@
       </c>
       <c r="K186" s="12" t="inlineStr">
         <is>
-          <t>INCIDENTE DE LIQUIDACIÓN DE GASTOS Y COSTAS EN EL JUICIO EJECUTIVO MERCANTIL ORAL. SU ADMISIÓN DEBE NOTIFICARSE DE MANERA PERSONAL, AL CONSTITUIR UN PROCEDIMIENTO CONTENCIOSO AUTÓNOMO E INDEPENDIENTE, Y EQUIPARARSE CON EL EMPLAZAMIENTO A JUICIO.</t>
+          <t>RENUNCIA. CORRESPONDE A LA PARTE DEMANDADA PERFECCIONARLA CON ALGÚN MEDIO DE PRUEBA, CUANDO EXISTA CONTROVERSIA RESPECTO DE LA HORA DE TERMINACIÓN DEL VÍNCULO LABORAL Y ÉSTA NO CONSTE EN EL ESCRITO RELATIVO.</t>
         </is>
       </c>
       <c r="L186" s="11" t="inlineStr">
         <is>
-          <t>2032414</t>
+          <t>2028640</t>
         </is>
       </c>
       <c r="M186" s="11" t="inlineStr"/>
       <c r="N186" s="11" t="inlineStr">
         <is>
-          <t>viernes 10 de julio de 2026 10:17 h</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="O186" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P186" s="11" t="inlineStr"/>
       <c r="Q186" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Si el patrón ofrece renuncia sin hora exacta y el trabajador alega despido a cierta hora, el patrón debe acreditar con prueba adicional la hora de la renuncia.</t>
         </is>
       </c>
       <c r="R186" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Cuestionamiento a renuncias forzadas con fechas/horas imprecisas.</t>
         </is>
       </c>
       <c r="S186" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Trabajador debe declarar hora exacta del despido; patrón tendrá que probar hora distinta.</t>
         </is>
       </c>
       <c r="T186" s="11" t="inlineStr"/>
       <c r="U186" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032414</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2028640</t>
         </is>
       </c>
       <c r="V186" s="11" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil · actualización automática</t>
+          <t>renuncia · hora despido · carga probatoria</t>
         </is>
       </c>
     </row>
     <row r="187" ht="80" customHeight="1">
       <c r="A187" s="13" t="inlineStr">
         <is>
-          <t>auto-2032458</t>
+          <t>lab-ren-002</t>
         </is>
       </c>
       <c r="B187" s="13" t="n">
@@ -24287,17 +24291,17 @@
       </c>
       <c r="D187" s="13" t="inlineStr">
         <is>
-          <t>Mercantil</t>
+          <t>Laboral</t>
         </is>
       </c>
       <c r="E187" s="13" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Renuncia laboral</t>
         </is>
       </c>
       <c r="F187" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Veracidad — carga reforzada si trabajador iba a jubilarse</t>
         </is>
       </c>
       <c r="G187" s="13" t="inlineStr">
@@ -24307,7 +24311,7 @@
       </c>
       <c r="H187" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I187" s="13" t="inlineStr">
@@ -24322,57 +24326,57 @@
       </c>
       <c r="K187" s="14" t="inlineStr">
         <is>
-          <t>MUTUO SUBROGATORIO. PARA QUE OPERE POR MINISTERIO DE LEY EN LOS DERECHOS DEL ACREEDOR, DEBEN CUMPLIRSE LOS REQUISITOS DEL ARTÍCULO 2059 DEL CÓDIGO CIVIL FEDERAL.</t>
+          <t>RENUNCIA. PARA QUE SEA VEROSÍMIL Y, POR ENDE, TENGA EFICACIA DEMOSTRATIVA PLENA, CORRESPONDE AL PATRÓN PROBAR QUE REÚNE LAS CONDICIONES DE CERTEZA Y LOS ELEMENTOS MÍNIMOS QUE REFLEJEN LA VOLUNTAD, AUTONOMÍA Y ESPONTANEIDAD DEL TRABAJADOR, SI ESTÁ PRÓXIMO A JUBILARSE.</t>
         </is>
       </c>
       <c r="L187" s="13" t="inlineStr">
         <is>
-          <t>2032458</t>
+          <t>2027058</t>
         </is>
       </c>
       <c r="M187" s="13" t="inlineStr"/>
       <c r="N187" s="13" t="inlineStr">
         <is>
-          <t>viernes 07 de agosto de 2026 10:15 h</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="O187" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P187" s="13" t="inlineStr"/>
       <c r="Q187" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Cuando el trabajador estaba próximo a adquirir derechos jubilatorios, la renuncia exigida pasa por estándar reforzado de veracidad: voluntad, autonomía y espontaneidad demostradas con prueba sólida.</t>
         </is>
       </c>
       <c r="R187" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Protección antes de jubilación: renuncias sospechosas no pasan.</t>
         </is>
       </c>
       <c r="S187" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Defensa trabajadora: si estaba a meses/años de jubilarse, atacar renuncia por falta de espontaneidad.</t>
         </is>
       </c>
       <c r="T187" s="13" t="inlineStr"/>
       <c r="U187" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032458</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027058</t>
         </is>
       </c>
       <c r="V187" s="13" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil · actualización automática</t>
+          <t>renuncia · jubilación · veracidad · carga reforzada</t>
         </is>
       </c>
     </row>
     <row r="188" ht="80" customHeight="1">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>auto-2032557</t>
+          <t>sen-020</t>
         </is>
       </c>
       <c r="B188" s="11" t="n">
@@ -24390,22 +24394,22 @@
       </c>
       <c r="E188" s="11" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil</t>
+          <t>Costas en juicio mercantil — tasación</t>
         </is>
       </c>
       <c r="F188" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Línea del Primer y Segundo Circuito (CDMX y Edomex)</t>
         </is>
       </c>
       <c r="G188" s="11" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>sentencia hito</t>
         </is>
       </c>
       <c r="H188" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I188" s="11" t="inlineStr">
@@ -24415,62 +24419,58 @@
       </c>
       <c r="J188" s="11" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>Primer y Segundo Circuito</t>
         </is>
       </c>
       <c r="K188" s="12" t="inlineStr">
         <is>
-          <t>COSTAS EN EL JUICIO EJECUTIVO MERCANTIL. LA EXCLUSIÓN DE CONCEPTOS DERIVADOS DEL TÍTULO DE CRÉDITO QUE NO FUERON RECLAMADOS COMO PRESTACIONES, NO CONFIGURA UN VENCIMIENTO PARCIAL.</t>
+          <t>Costas mercantiles — base de cuantificación y arancel aplicable</t>
         </is>
       </c>
       <c r="L188" s="11" t="inlineStr">
         <is>
-          <t>2032557</t>
+          <t>Línea de Colegiados — múltiples</t>
         </is>
       </c>
       <c r="M188" s="11" t="inlineStr"/>
       <c r="N188" s="11" t="inlineStr">
         <is>
-          <t>viernes 28 de agosto de 2026 10:36 h</t>
-        </is>
-      </c>
-      <c r="O188" s="11" t="inlineStr">
-        <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
-        </is>
-      </c>
+          <t>Línea consolidada</t>
+        </is>
+      </c>
+      <c r="O188" s="11" t="inlineStr"/>
       <c r="P188" s="11" t="inlineStr"/>
       <c r="Q188" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Las costas en juicio mercantil se cuantifican con base en el monto efectivamente condenado y conforme al arancel local vigente al momento de cuantificarlas. La condena en costas presupone temeridad o vencimiento total.</t>
         </is>
       </c>
       <c r="R188" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Marco práctico para pretensión y oposición a costas.</t>
         </is>
       </c>
       <c r="S188" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>El acreedor que gana en ejecutivo debe solicitar tasación con arancel actualizado. El deudor debe oponerse cuando la cuantificación excede el monto del juicio o aplica arancel inadecuado.</t>
         </is>
       </c>
       <c r="T188" s="11" t="inlineStr"/>
       <c r="U188" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032557</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031803</t>
         </is>
       </c>
       <c r="V188" s="11" t="inlineStr">
         <is>
-          <t>Juicio ejecutivo mercantil · actualización automática</t>
+          <t>costas · tasación · arancel · mercantil</t>
         </is>
       </c>
     </row>
     <row r="189" ht="80" customHeight="1">
       <c r="A189" s="13" t="inlineStr">
         <is>
-          <t>auto-2032725</t>
+          <t>auto-2032198</t>
         </is>
       </c>
       <c r="B189" s="13" t="n">
@@ -24518,18 +24518,18 @@
       </c>
       <c r="K189" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL. ES IMPROCEDENTE CONTRA EL AUTO DE EXEQUENDO EMITIDO EN UN JUICIO EJECUTIVO MERCANTIL.</t>
+          <t>GARANTÍA PARA QUE SIGA SURTIENDO EFECTOS LA SUSPENSIÓN EN AMPARO INDIRECTO. ES EXIGIBLE A LA PERSONA MORAL PRIVADA DECLARADA EN QUIEBRA, AL NO ACTUALIZARSE ALGÚN SUPUESTO LEGAL PARA EXENTAR SU EXHIBICIÓN.</t>
         </is>
       </c>
       <c r="L189" s="13" t="inlineStr">
         <is>
-          <t>2032725</t>
+          <t>2032198</t>
         </is>
       </c>
       <c r="M189" s="13" t="inlineStr"/>
       <c r="N189" s="13" t="inlineStr">
         <is>
-          <t>viernes 02 de octubre de 2026 10:12 h</t>
+          <t>viernes 29 de mayo de 2026 10:34 h</t>
         </is>
       </c>
       <c r="O189" s="13" t="inlineStr">
@@ -24556,7 +24556,7 @@
       <c r="T189" s="13" t="inlineStr"/>
       <c r="U189" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032725</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032198</t>
         </is>
       </c>
       <c r="V189" s="13" t="inlineStr">
@@ -24568,7 +24568,7 @@
     <row r="190" ht="80" customHeight="1">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t>auto-2032730</t>
+          <t>auto-2032274</t>
         </is>
       </c>
       <c r="B190" s="11" t="n">
@@ -24616,18 +24616,18 @@
       </c>
       <c r="K190" s="12" t="inlineStr">
         <is>
-          <t>CONFESIÓN JUDICIAL. LA REALIZADA EN LA DILIGENCIA DE EXEQUENDO SOBRE EL ADEUDO ADMITE PRUEBA EN CONTRARIO Y, POR ELLO, DEBE ANALIZARSE EN CONJUNTO CON EL RESTANTE MATERIAL PROBATORIO CUANDO SE CUESTIONA LA FIRMA IMPRESA EN UN TÍTULO DE CRÉDITO.</t>
+          <t>PRUEBA TESTIMONIAL FORÁNEA EN EL JUICIO EJECUTIVO MERCANTIL ORAL. PROCEDE DESECHARLA CUANDO NO SE OFRECE EN TÉRMINOS DEL ARTÍCULO 1269 DEL CÓDIGO DE COMERCIO.</t>
         </is>
       </c>
       <c r="L190" s="11" t="inlineStr">
         <is>
-          <t>2032730</t>
+          <t>2032274</t>
         </is>
       </c>
       <c r="M190" s="11" t="inlineStr"/>
       <c r="N190" s="11" t="inlineStr">
         <is>
-          <t>viernes 09 de octubre de 2026 10:19 h</t>
+          <t>viernes 12 de junio de 2026 10:18 h</t>
         </is>
       </c>
       <c r="O190" s="11" t="inlineStr">
@@ -24654,7 +24654,7 @@
       <c r="T190" s="11" t="inlineStr"/>
       <c r="U190" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032730</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032274</t>
         </is>
       </c>
       <c r="V190" s="11" t="inlineStr">
@@ -24666,7 +24666,7 @@
     <row r="191" ht="80" customHeight="1">
       <c r="A191" s="13" t="inlineStr">
         <is>
-          <t>mer-eje-002</t>
+          <t>auto-2032414</t>
         </is>
       </c>
       <c r="B191" s="13" t="n">
@@ -24689,17 +24689,17 @@
       </c>
       <c r="F191" s="13" t="inlineStr">
         <is>
-          <t>Improcedencia — análisis oficioso en amparo directo</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G191" s="13" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H191" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I191" s="13" t="inlineStr">
@@ -24714,57 +24714,57 @@
       </c>
       <c r="K191" s="14" t="inlineStr">
         <is>
-          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
+          <t>INCIDENTE DE LIQUIDACIÓN DE GASTOS Y COSTAS EN EL JUICIO EJECUTIVO MERCANTIL ORAL. SU ADMISIÓN DEBE NOTIFICARSE DE MANERA PERSONAL, AL CONSTITUIR UN PROCEDIMIENTO CONTENCIOSO AUTÓNOMO E INDEPENDIENTE, Y EQUIPARARSE CON EL EMPLAZAMIENTO A JUICIO.</t>
         </is>
       </c>
       <c r="L191" s="13" t="inlineStr">
         <is>
-          <t>2025924</t>
+          <t>2032414</t>
         </is>
       </c>
       <c r="M191" s="13" t="inlineStr"/>
       <c r="N191" s="13" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>viernes 10 de julio de 2026 10:17 h</t>
         </is>
       </c>
       <c r="O191" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P191" s="13" t="inlineStr"/>
       <c r="Q191" s="13" t="inlineStr">
         <is>
-          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R191" s="13" t="inlineStr">
         <is>
-          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S191" s="13" t="inlineStr">
         <is>
-          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T191" s="13" t="inlineStr"/>
       <c r="U191" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032414</t>
         </is>
       </c>
       <c r="V191" s="13" t="inlineStr">
         <is>
-          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="192" ht="80" customHeight="1">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t>mer-eje-003</t>
+          <t>auto-2032458</t>
         </is>
       </c>
       <c r="B192" s="11" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="F192" s="11" t="inlineStr">
         <is>
-          <t>Mora — fecha de actualización</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G192" s="11" t="inlineStr">
@@ -24812,57 +24812,57 @@
       </c>
       <c r="K192" s="12" t="inlineStr">
         <is>
-          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
+          <t>MUTUO SUBROGATORIO. PARA QUE OPERE POR MINISTERIO DE LEY EN LOS DERECHOS DEL ACREEDOR, DEBEN CUMPLIRSE LOS REQUISITOS DEL ARTÍCULO 2059 DEL CÓDIGO CIVIL FEDERAL.</t>
         </is>
       </c>
       <c r="L192" s="11" t="inlineStr">
         <is>
-          <t>2031591</t>
+          <t>2032458</t>
         </is>
       </c>
       <c r="M192" s="11" t="inlineStr"/>
       <c r="N192" s="11" t="inlineStr">
         <is>
-          <t>2025-2026</t>
+          <t>viernes 07 de agosto de 2026 10:15 h</t>
         </is>
       </c>
       <c r="O192" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P192" s="11" t="inlineStr"/>
       <c r="Q192" s="11" t="inlineStr">
         <is>
-          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R192" s="11" t="inlineStr">
         <is>
-          <t>Define desde cuándo corren intereses moratorios.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S192" s="11" t="inlineStr">
         <is>
-          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T192" s="11" t="inlineStr"/>
       <c r="U192" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032458</t>
         </is>
       </c>
       <c r="V192" s="11" t="inlineStr">
         <is>
-          <t>mora · intereses moratorios · interpelación · 12a Época</t>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="193" ht="80" customHeight="1">
       <c r="A193" s="13" t="inlineStr">
         <is>
-          <t>mer-pag-002</t>
+          <t>auto-2032557</t>
         </is>
       </c>
       <c r="B193" s="13" t="n">
@@ -24880,12 +24880,12 @@
       </c>
       <c r="E193" s="13" t="inlineStr">
         <is>
-          <t>Títulos de crédito — pagaré</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F193" s="13" t="inlineStr">
         <is>
-          <t>Acción causal — pagaré como prueba del contrato</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G193" s="13" t="inlineStr">
@@ -24895,7 +24895,7 @@
       </c>
       <c r="H193" s="13" t="inlineStr">
         <is>
-          <t>Undécima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I193" s="13" t="inlineStr">
@@ -24910,57 +24910,57 @@
       </c>
       <c r="K193" s="14" t="inlineStr">
         <is>
-          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
+          <t>COSTAS EN EL JUICIO EJECUTIVO MERCANTIL. LA EXCLUSIÓN DE CONCEPTOS DERIVADOS DEL TÍTULO DE CRÉDITO QUE NO FUERON RECLAMADOS COMO PRESTACIONES, NO CONFIGURA UN VENCIMIENTO PARCIAL.</t>
         </is>
       </c>
       <c r="L193" s="13" t="inlineStr">
         <is>
-          <t>2024056</t>
+          <t>2032557</t>
         </is>
       </c>
       <c r="M193" s="13" t="inlineStr"/>
       <c r="N193" s="13" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>viernes 28 de agosto de 2026 10:36 h</t>
         </is>
       </c>
       <c r="O193" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P193" s="13" t="inlineStr"/>
       <c r="Q193" s="13" t="inlineStr">
         <is>
-          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R193" s="13" t="inlineStr">
         <is>
-          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S193" s="13" t="inlineStr">
         <is>
-          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T193" s="13" t="inlineStr"/>
       <c r="U193" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032557</t>
         </is>
       </c>
       <c r="V193" s="13" t="inlineStr">
         <is>
-          <t>pagaré · acción causal · ordinario mercantil</t>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="194" ht="80" customHeight="1">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t>mer-pag-003</t>
+          <t>auto-2032725</t>
         </is>
       </c>
       <c r="B194" s="11" t="n">
@@ -24978,12 +24978,12 @@
       </c>
       <c r="E194" s="11" t="inlineStr">
         <is>
-          <t>Títulos de crédito — pagaré</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F194" s="11" t="inlineStr">
         <is>
-          <t>Pagarés seriados — lugar de pago</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G194" s="11" t="inlineStr">
@@ -24993,7 +24993,7 @@
       </c>
       <c r="H194" s="11" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I194" s="11" t="inlineStr">
@@ -25008,57 +25008,57 @@
       </c>
       <c r="K194" s="12" t="inlineStr">
         <is>
-          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
+          <t>SUSPENSIÓN PROVISIONAL. ES IMPROCEDENTE CONTRA EL AUTO DE EXEQUENDO EMITIDO EN UN JUICIO EJECUTIVO MERCANTIL.</t>
         </is>
       </c>
       <c r="L194" s="11" t="inlineStr">
         <is>
-          <t>2019464</t>
+          <t>2032725</t>
         </is>
       </c>
       <c r="M194" s="11" t="inlineStr"/>
       <c r="N194" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>viernes 02 de octubre de 2026 10:12 h</t>
         </is>
       </c>
       <c r="O194" s="11" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P194" s="11" t="inlineStr"/>
       <c r="Q194" s="11" t="inlineStr">
         <is>
-          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R194" s="11" t="inlineStr">
         <is>
-          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S194" s="11" t="inlineStr">
         <is>
-          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T194" s="11" t="inlineStr"/>
       <c r="U194" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032725</t>
         </is>
       </c>
       <c r="V194" s="11" t="inlineStr">
         <is>
-          <t>pagaré · pagarés seriados · lugar de pago</t>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="195" ht="80" customHeight="1">
       <c r="A195" s="13" t="inlineStr">
         <is>
-          <t>auto-2032371</t>
+          <t>auto-2032730</t>
         </is>
       </c>
       <c r="B195" s="13" t="n">
@@ -25071,12 +25071,12 @@
       </c>
       <c r="D195" s="13" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E195" s="13" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F195" s="13" t="inlineStr">
@@ -25106,18 +25106,18 @@
       </c>
       <c r="K195" s="14" t="inlineStr">
         <is>
-          <t>COSA JUZGADA EN EL JUICIO DE AMPARO. CUANDO SE INVOLUCRAN DERECHOS DE NIÑAS, NIÑOS Y ADOLESCENTES, SU ACTUALIZACIÓN REQUIERE UN ANÁLISIS REFORZADO Y UNA CORRESPONDENCIA MATERIAL ENTRE LO PREVIAMENTE RESUELTO Y EL ACTO RECLAMADO.</t>
+          <t>CONFESIÓN JUDICIAL. LA REALIZADA EN LA DILIGENCIA DE EXEQUENDO SOBRE EL ADEUDO ADMITE PRUEBA EN CONTRARIO Y, POR ELLO, DEBE ANALIZARSE EN CONJUNTO CON EL RESTANTE MATERIAL PROBATORIO CUANDO SE CUESTIONA LA FIRMA IMPRESA EN UN TÍTULO DE CRÉDITO.</t>
         </is>
       </c>
       <c r="L195" s="13" t="inlineStr">
         <is>
-          <t>2032371</t>
+          <t>2032730</t>
         </is>
       </c>
       <c r="M195" s="13" t="inlineStr"/>
       <c r="N195" s="13" t="inlineStr">
         <is>
-          <t>viernes 03 de julio de 2026 10:10 h</t>
+          <t>viernes 09 de octubre de 2026 10:19 h</t>
         </is>
       </c>
       <c r="O195" s="13" t="inlineStr">
@@ -25144,19 +25144,19 @@
       <c r="T195" s="13" t="inlineStr"/>
       <c r="U195" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032371</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032730</t>
         </is>
       </c>
       <c r="V195" s="13" t="inlineStr">
         <is>
-          <t>Cadena de custodia · actualización automática</t>
+          <t>Juicio ejecutivo mercantil · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="196" ht="80" customHeight="1">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t>pen-cad-002</t>
+          <t>mer-eje-002</t>
         </is>
       </c>
       <c r="B196" s="11" t="n">
@@ -25169,17 +25169,17 @@
       </c>
       <c r="D196" s="11" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E196" s="11" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F196" s="11" t="inlineStr">
         <is>
-          <t>Responsabilidad de la Fiscalía aun con datos del inculpado</t>
+          <t>Improcedencia — análisis oficioso en amparo directo</t>
         </is>
       </c>
       <c r="G196" s="11" t="inlineStr">
@@ -25204,18 +25204,18 @@
       </c>
       <c r="K196" s="12" t="inlineStr">
         <is>
-          <t>CADENA DE CUSTODIA. ES RESPONSABILIDAD EXCLUSIVA DE LOS SERVIDORES PÚBLICOS DE LA FISCALÍA, INCLUSO RESPECTO DE DATOS O MEDIOS DE PRUEBA APORTADOS POR EL INCULPADO O SU DEFENSA.</t>
+          <t>IMPROCEDENCIA DE LA VÍA EJECUTIVA MERCANTIL. AL TRATARSE DE UN PRESUPUESTO PROCESAL, PUEDE ANALIZARSE DE OFICIO EN EL JUICIO DE AMPARO DIRECTO.</t>
         </is>
       </c>
       <c r="L196" s="11" t="inlineStr">
         <is>
-          <t>2027962</t>
+          <t>2025924</t>
         </is>
       </c>
       <c r="M196" s="11" t="inlineStr"/>
       <c r="N196" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="O196" s="11" t="inlineStr">
@@ -25226,35 +25226,35 @@
       <c r="P196" s="11" t="inlineStr"/>
       <c r="Q196" s="11" t="inlineStr">
         <is>
-          <t>Conforme al CNPP, la cadena de custodia recae siempre en la Fiscalía, incluso respecto de evidencia aportada por la defensa. La defensa NO carga con su preservación; el MP debe registrarla y custodiarla.</t>
+          <t>La improcedencia de la vía ejecutiva mercantil es presupuesto procesal y puede analizarse de oficio incluso en amparo directo, aunque las instancias previas no lo hayan abordado a fondo.</t>
         </is>
       </c>
       <c r="R196" s="11" t="inlineStr">
         <is>
-          <t>Reforma carga: la defensa puede aportar evidencia sin temor a romper cadena.</t>
+          <t>Defensa de última instancia para deudores ejecutados con documentos viciados.</t>
         </is>
       </c>
       <c r="S196" s="11" t="inlineStr">
         <is>
-          <t>Defensa puede aportar peritajes, fotos, audios sin asumir custodia formal.</t>
+          <t>Aun perdiendo en primera y segunda instancia, en amparo directo se puede plantear.</t>
         </is>
       </c>
       <c r="T196" s="11" t="inlineStr"/>
       <c r="U196" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027962</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2025924</t>
         </is>
       </c>
       <c r="V196" s="11" t="inlineStr">
         <is>
-          <t>cadena custodia · CNPP · Fiscalía · evidencia defensa</t>
+          <t>vía ejecutiva mercantil · amparo directo · oficio</t>
         </is>
       </c>
     </row>
     <row r="197" ht="80" customHeight="1">
       <c r="A197" s="13" t="inlineStr">
         <is>
-          <t>pen-cad-003</t>
+          <t>mer-eje-003</t>
         </is>
       </c>
       <c r="B197" s="13" t="n">
@@ -25267,17 +25267,17 @@
       </c>
       <c r="D197" s="13" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E197" s="13" t="inlineStr">
         <is>
-          <t>Cadena de custodia</t>
+          <t>Juicio ejecutivo mercantil</t>
         </is>
       </c>
       <c r="F197" s="13" t="inlineStr">
         <is>
-          <t>Transgresión no torna ilícita la prueba</t>
+          <t>Mora — fecha de actualización</t>
         </is>
       </c>
       <c r="G197" s="13" t="inlineStr">
@@ -25287,7 +25287,7 @@
       </c>
       <c r="H197" s="13" t="inlineStr">
         <is>
-          <t>Décima Época</t>
+          <t>Duodécima Época</t>
         </is>
       </c>
       <c r="I197" s="13" t="inlineStr">
@@ -25302,57 +25302,57 @@
       </c>
       <c r="K197" s="14" t="inlineStr">
         <is>
-          <t>CADENA DE CUSTODIA. SU TRANSGRESIÓN NO TORNA ILÍCITOS LOS DATOS DE PRUEBA.</t>
+          <t>MORA EN EL JUICIO EJECUTIVO MERCANTIL. SE ACTUALIZA CON MOTIVO DE LA INTERPELACIÓN FORMULADA EN EL EMPLAZAMIENTO Y NO EN LA FECHA DE VENCIMIENTO ESTABLECIDA EN EL PAGARÉ BASE DE LA ACCIÓN.</t>
         </is>
       </c>
       <c r="L197" s="13" t="inlineStr">
         <is>
-          <t>2021845</t>
+          <t>2031591</t>
         </is>
       </c>
       <c r="M197" s="13" t="inlineStr"/>
       <c r="N197" s="13" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025-2026</t>
         </is>
       </c>
       <c r="O197" s="13" t="inlineStr">
         <is>
-          <t>Gaceta SJF — VERIFICADO</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P197" s="13" t="inlineStr"/>
       <c r="Q197" s="13" t="inlineStr">
         <is>
-          <t>La ruptura de cadena de custodia NO convierte automáticamente en ilícita la prueba; solo afecta su valor probatorio. El juez debe ponderar la magnitud de la ruptura.</t>
+          <t>Cuando el pagaré señala genéricamente como lugar de pago una ciudad, la mora no se actualiza con el vencimiento sino con la interpelación en el emplazamiento judicial.</t>
         </is>
       </c>
       <c r="R197" s="13" t="inlineStr">
         <is>
-          <t>Matiza la regla de exclusión: cadena rota = valor probatorio reducido, no exclusión.</t>
+          <t>Define desde cuándo corren intereses moratorios.</t>
         </is>
       </c>
       <c r="S197" s="13" t="inlineStr">
         <is>
-          <t>Defensa: argumentar valor cero por ruptura. Acusación: defender la prueba a pesar de la ruptura.</t>
+          <t>Pagarés con lugar genérico: los intereses moratorios corren desde emplazamiento, no desde vencimiento.</t>
         </is>
       </c>
       <c r="T197" s="13" t="inlineStr"/>
       <c r="U197" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2031591</t>
         </is>
       </c>
       <c r="V197" s="13" t="inlineStr">
         <is>
-          <t>cadena custodia · valor probatorio · exclusión</t>
+          <t>mora · intereses moratorios · interpelación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="198" ht="80" customHeight="1">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t>pen-ppo-001</t>
+          <t>mer-pag-002</t>
         </is>
       </c>
       <c r="B198" s="11" t="n">
@@ -25365,17 +25365,17 @@
       </c>
       <c r="D198" s="11" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E198" s="11" t="inlineStr">
         <is>
-          <t>Prisión preventiva oficiosa</t>
+          <t>Títulos de crédito — pagaré</t>
         </is>
       </c>
       <c r="F198" s="11" t="inlineStr">
         <is>
-          <t>Víctima — falta de legitimación para impugnar cese</t>
+          <t>Acción causal — pagaré como prueba del contrato</t>
         </is>
       </c>
       <c r="G198" s="11" t="inlineStr">
@@ -25385,7 +25385,7 @@
       </c>
       <c r="H198" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I198" s="11" t="inlineStr">
@@ -25400,57 +25400,57 @@
       </c>
       <c r="K198" s="12" t="inlineStr">
         <is>
-          <t>PRISIÓN PREVENTIVA OFICIOSA. LA VÍCTIMA U OFENDIDO DEL DELITO CARECE DE LEGITIMACIÓN PARA IMPUGNAR EN SEDE CONSTITUCIONAL SU CESE, AL NO TENER INCORPORADA A SU ESFERA JURÍDICA ALGÚN DERECHO QUE LA FACULTE.</t>
+          <t>ACCIÓN CAUSAL. SU EJERCICIO PARA EL COBRO DE UN TÍTULO DE CRÉDITO PUEDE SUSTENTARSE EN EL CONTRATO CONTENIDO EN EL PAGARÉ, DERIVADO DEL OTORGAMIENTO DE UN PRÉSTAMO A CORTO PLAZO.</t>
         </is>
       </c>
       <c r="L198" s="11" t="inlineStr">
         <is>
-          <t>2032107</t>
+          <t>2024056</t>
         </is>
       </c>
       <c r="M198" s="11" t="inlineStr"/>
       <c r="N198" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="O198" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P198" s="11" t="inlineStr"/>
       <c r="Q198" s="11" t="inlineStr">
         <is>
-          <t>La víctima no puede impugnar por amparo la liberación del imputado cuando se cesa la PPO. No hay derecho subjetivo a que el imputado permanezca en prisión preventiva.</t>
+          <t>Si el pagaré pierde eficacia ejecutiva o el acreedor decide no usar la vía ejecutiva, puede ejercer acción causal con el pagaré como prueba documental del contrato subyacente.</t>
         </is>
       </c>
       <c r="R198" s="11" t="inlineStr">
         <is>
-          <t>Restringe vía de víctima contra liberaciones por exceso de plazo.</t>
+          <t>Salvavidas para acreedores cuando el pagaré tiene vicios formales.</t>
         </is>
       </c>
       <c r="S198" s="11" t="inlineStr">
         <is>
-          <t>Tras PPO cesada (más de 2 años sin sentencia, por ejemplo), la víctima no puede ampararse. Su vía es civil/coadyuvancia para impulsar el proceso, no constitucional.</t>
+          <t>Si no procede el ejecutivo, vía ordinaria con el pagaré como documental.</t>
         </is>
       </c>
       <c r="T198" s="11" t="inlineStr"/>
       <c r="U198" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032107</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2024056</t>
         </is>
       </c>
       <c r="V198" s="11" t="inlineStr">
         <is>
-          <t>PPO · víctima · legitimación · 12a Época</t>
+          <t>pagaré · acción causal · ordinario mercantil</t>
         </is>
       </c>
     </row>
     <row r="199" ht="80" customHeight="1">
       <c r="A199" s="13" t="inlineStr">
         <is>
-          <t>pen-ppo-002</t>
+          <t>mer-pag-003</t>
         </is>
       </c>
       <c r="B199" s="13" t="n">
@@ -25463,17 +25463,17 @@
       </c>
       <c r="D199" s="13" t="inlineStr">
         <is>
-          <t>Penal</t>
+          <t>Mercantil</t>
         </is>
       </c>
       <c r="E199" s="13" t="inlineStr">
         <is>
-          <t>Prisión preventiva oficiosa</t>
+          <t>Títulos de crédito — pagaré</t>
         </is>
       </c>
       <c r="F199" s="13" t="inlineStr">
         <is>
-          <t>Cese cuando MP no prueba prolongación</t>
+          <t>Pagarés seriados — lugar de pago</t>
         </is>
       </c>
       <c r="G199" s="13" t="inlineStr">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="H199" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I199" s="13" t="inlineStr">
@@ -25498,57 +25498,57 @@
       </c>
       <c r="K199" s="14" t="inlineStr">
         <is>
-          <t>PRISIÓN PREVENTIVA OFICIOSA. SU CESE ORDENADO CUANDO EL MINISTERIO PÚBLICO NO PRUEBA NI JUSTIFICA SU PROLONGACIÓN, PARA EFECTOS DE QUE SE DEBATA LA IMPOSICIÓN DE OTRAS MEDIDAS CAUTELARES MENOS RESTRICTIVAS.</t>
+          <t>PAGARÉS SERIADOS. ANTE LA AUSENCIA DE "LUGAR DE PAGO" EN UNO DE ÉSTOS, DEBE ATENDERSE A LO PACTADO EN OTRO DIVERSO DONDE SÍ SE SEÑALÓ.</t>
         </is>
       </c>
       <c r="L199" s="13" t="inlineStr">
         <is>
-          <t>2032108</t>
+          <t>2019464</t>
         </is>
       </c>
       <c r="M199" s="13" t="inlineStr"/>
       <c r="N199" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="O199" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P199" s="13" t="inlineStr"/>
       <c r="Q199" s="13" t="inlineStr">
         <is>
-          <t>Al solicitar prolongación de PPO, el MP tiene carga probatoria. Si no la cumple, el juez debe cesar la PPO y reabrir debate sobre medidas cautelares alternativas.</t>
+          <t>Cuando se emiten varios pagarés seriados y solo uno tiene lugar de pago expreso, ese lugar aplica a toda la serie por integración.</t>
         </is>
       </c>
       <c r="R199" s="13" t="inlineStr">
         <is>
-          <t>Defensa decisiva contra prolongación automática de PPO.</t>
+          <t>Importante en mutuos con tabla de pagos a 12, 24 o 36 meses.</t>
         </is>
       </c>
       <c r="S199" s="13" t="inlineStr">
         <is>
-          <t>Cuando MP solicita prolongación sin justificar, la defensa debe exigir prueba concreta. Sin ella, opera el cese y se debate medida alterna (caución, brazalete, presentación periódica).</t>
+          <t>Defensa contra excepción de pagaré sin lugar de pago en serie.</t>
         </is>
       </c>
       <c r="T199" s="13" t="inlineStr"/>
       <c r="U199" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032108</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2019464</t>
         </is>
       </c>
       <c r="V199" s="13" t="inlineStr">
         <is>
-          <t>PPO · prolongación · carga probatoria MP · 12a Época</t>
+          <t>pagaré · pagarés seriados · lugar de pago</t>
         </is>
       </c>
     </row>
     <row r="200" ht="80" customHeight="1">
       <c r="A200" s="11" t="inlineStr">
         <is>
-          <t>auto-2032300</t>
+          <t>auto-2032371</t>
         </is>
       </c>
       <c r="B200" s="11" t="n">
@@ -25566,7 +25566,7 @@
       </c>
       <c r="E200" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Cadena de custodia</t>
         </is>
       </c>
       <c r="F200" s="11" t="inlineStr">
@@ -25596,18 +25596,18 @@
       </c>
       <c r="K200" s="12" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. OBLIGAR A UNA ADOLESCENTE VÍCTIMA DE MALA PRÁXIS MÉDICA A RECIBIR ATENCIÓN MÉDICA POSTERIOR PARA EJERCER SUS DERECHOS REPRODUCTIVOS EN LA MISMA INSTITUCIÓN DE SALUD QUE ACTUÓ EN FORMA IRREGULAR, CONSTITUYE UNA ACTIVIDAD REVICTIMIZANTE.</t>
+          <t>COSA JUZGADA EN EL JUICIO DE AMPARO. CUANDO SE INVOLUCRAN DERECHOS DE NIÑAS, NIÑOS Y ADOLESCENTES, SU ACTUALIZACIÓN REQUIERE UN ANÁLISIS REFORZADO Y UNA CORRESPONDENCIA MATERIAL ENTRE LO PREVIAMENTE RESUELTO Y EL ACTO RECLAMADO.</t>
         </is>
       </c>
       <c r="L200" s="11" t="inlineStr">
         <is>
-          <t>2032300</t>
+          <t>2032371</t>
         </is>
       </c>
       <c r="M200" s="11" t="inlineStr"/>
       <c r="N200" s="11" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>viernes 03 de julio de 2026 10:10 h</t>
         </is>
       </c>
       <c r="O200" s="11" t="inlineStr">
@@ -25634,19 +25634,19 @@
       <c r="T200" s="11" t="inlineStr"/>
       <c r="U200" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032300</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032371</t>
         </is>
       </c>
       <c r="V200" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño · actualización automática</t>
+          <t>Cadena de custodia · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="201" ht="80" customHeight="1">
       <c r="A201" s="13" t="inlineStr">
         <is>
-          <t>auto-2032301</t>
+          <t>pen-cad-002</t>
         </is>
       </c>
       <c r="B201" s="13" t="n">
@@ -25664,22 +25664,22 @@
       </c>
       <c r="E201" s="13" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Cadena de custodia</t>
         </is>
       </c>
       <c r="F201" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Responsabilidad de la Fiscalía aun con datos del inculpado</t>
         </is>
       </c>
       <c r="G201" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H201" s="13" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Undécima Época</t>
         </is>
       </c>
       <c r="I201" s="13" t="inlineStr">
@@ -25694,57 +25694,57 @@
       </c>
       <c r="K201" s="14" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LA REPARACIÓN INTEGRAL DEL DAÑO NO SE LIMITA AL RESARCIMIENTO ECONÓMICO, SINO QUE INCLUYE LA REHABILITACIÓN PARA FACILITAR A LA VÍCTIMA HACER FRENTE A LOS EFECTOS DEL DAÑO SUFRIDO (LEY GENERAL DE VÍCTIMAS).</t>
+          <t>CADENA DE CUSTODIA. ES RESPONSABILIDAD EXCLUSIVA DE LOS SERVIDORES PÚBLICOS DE LA FISCALÍA, INCLUSO RESPECTO DE DATOS O MEDIOS DE PRUEBA APORTADOS POR EL INCULPADO O SU DEFENSA.</t>
         </is>
       </c>
       <c r="L201" s="13" t="inlineStr">
         <is>
-          <t>2032301</t>
+          <t>2027962</t>
         </is>
       </c>
       <c r="M201" s="13" t="inlineStr"/>
       <c r="N201" s="13" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="O201" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P201" s="13" t="inlineStr"/>
       <c r="Q201" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Conforme al CNPP, la cadena de custodia recae siempre en la Fiscalía, incluso respecto de evidencia aportada por la defensa. La defensa NO carga con su preservación; el MP debe registrarla y custodiarla.</t>
         </is>
       </c>
       <c r="R201" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Reforma carga: la defensa puede aportar evidencia sin temor a romper cadena.</t>
         </is>
       </c>
       <c r="S201" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Defensa puede aportar peritajes, fotos, audios sin asumir custodia formal.</t>
         </is>
       </c>
       <c r="T201" s="13" t="inlineStr"/>
       <c r="U201" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032301</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2027962</t>
         </is>
       </c>
       <c r="V201" s="13" t="inlineStr">
         <is>
-          <t>Reparación del daño · actualización automática</t>
+          <t>cadena custodia · CNPP · Fiscalía · evidencia defensa</t>
         </is>
       </c>
     </row>
     <row r="202" ht="80" customHeight="1">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t>auto-2032304</t>
+          <t>pen-cad-003</t>
         </is>
       </c>
       <c r="B202" s="11" t="n">
@@ -25762,12 +25762,12 @@
       </c>
       <c r="E202" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Cadena de custodia</t>
         </is>
       </c>
       <c r="F202" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Transgresión no torna ilícita la prueba</t>
         </is>
       </c>
       <c r="G202" s="11" t="inlineStr">
@@ -25777,7 +25777,7 @@
       </c>
       <c r="H202" s="11" t="inlineStr">
         <is>
-          <t>Duodécima Época</t>
+          <t>Décima Época</t>
         </is>
       </c>
       <c r="I202" s="11" t="inlineStr">
@@ -25792,57 +25792,57 @@
       </c>
       <c r="K202" s="12" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. PARA DETERMINAR LA REPARACIÓN INTEGRAL DEL DAÑO SE DEBE CONSIDERAR TANTO EL HECHO VICTIMIZANTE COMO SUS EFECTOS, PARA QUE SU FIJACIÓN PERMITA A LAS VÍCTIMAS DIRECTAS E INDIRECTAS REHACER SU PROYECTO DE VIDA.</t>
+          <t>CADENA DE CUSTODIA. SU TRANSGRESIÓN NO TORNA ILÍCITOS LOS DATOS DE PRUEBA.</t>
         </is>
       </c>
       <c r="L202" s="11" t="inlineStr">
         <is>
-          <t>2032304</t>
+          <t>2021845</t>
         </is>
       </c>
       <c r="M202" s="11" t="inlineStr"/>
       <c r="N202" s="11" t="inlineStr">
         <is>
-          <t>viernes 19 de junio de 2026 10:25 h</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="O202" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>Gaceta SJF — VERIFICADO</t>
         </is>
       </c>
       <c r="P202" s="11" t="inlineStr"/>
       <c r="Q202" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La ruptura de cadena de custodia NO convierte automáticamente en ilícita la prueba; solo afecta su valor probatorio. El juez debe ponderar la magnitud de la ruptura.</t>
         </is>
       </c>
       <c r="R202" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Matiza la regla de exclusión: cadena rota = valor probatorio reducido, no exclusión.</t>
         </is>
       </c>
       <c r="S202" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Defensa: argumentar valor cero por ruptura. Acusación: defender la prueba a pesar de la ruptura.</t>
         </is>
       </c>
       <c r="T202" s="11" t="inlineStr"/>
       <c r="U202" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032304</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2021845</t>
         </is>
       </c>
       <c r="V202" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño · actualización automática</t>
+          <t>cadena custodia · valor probatorio · exclusión</t>
         </is>
       </c>
     </row>
     <row r="203" ht="80" customHeight="1">
       <c r="A203" s="13" t="inlineStr">
         <is>
-          <t>auto-2032335</t>
+          <t>pen-ppo-001</t>
         </is>
       </c>
       <c r="B203" s="13" t="n">
@@ -25860,12 +25860,12 @@
       </c>
       <c r="E203" s="13" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Prisión preventiva oficiosa</t>
         </is>
       </c>
       <c r="F203" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Víctima — falta de legitimación para impugnar cese</t>
         </is>
       </c>
       <c r="G203" s="13" t="inlineStr">
@@ -25890,57 +25890,57 @@
       </c>
       <c r="K203" s="14" t="inlineStr">
         <is>
-          <t>PERSONA INIMPUTABLE POR TRANSTORNO MENTAL. LA MEDIDA DE SEGURIDAD DE INTERNAMIENTO DEBE IMPONERSE CONFORME AL MODELO SOCIAL DE DISCAPACIDAD Y NO CON BASE EN LA PUNIBILIDAD DEL TIPO PENAL ATRIBUIDO.</t>
+          <t>PRISIÓN PREVENTIVA OFICIOSA. LA VÍCTIMA U OFENDIDO DEL DELITO CARECE DE LEGITIMACIÓN PARA IMPUGNAR EN SEDE CONSTITUCIONAL SU CESE, AL NO TENER INCORPORADA A SU ESFERA JURÍDICA ALGÚN DERECHO QUE LA FACULTE.</t>
         </is>
       </c>
       <c r="L203" s="13" t="inlineStr">
         <is>
-          <t>2032335</t>
+          <t>2032107</t>
         </is>
       </c>
       <c r="M203" s="13" t="inlineStr"/>
       <c r="N203" s="13" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O203" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P203" s="13" t="inlineStr"/>
       <c r="Q203" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La víctima no puede impugnar por amparo la liberación del imputado cuando se cesa la PPO. No hay derecho subjetivo a que el imputado permanezca en prisión preventiva.</t>
         </is>
       </c>
       <c r="R203" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Restringe vía de víctima contra liberaciones por exceso de plazo.</t>
         </is>
       </c>
       <c r="S203" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Tras PPO cesada (más de 2 años sin sentencia, por ejemplo), la víctima no puede ampararse. Su vía es civil/coadyuvancia para impulsar el proceso, no constitucional.</t>
         </is>
       </c>
       <c r="T203" s="13" t="inlineStr"/>
       <c r="U203" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032335</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032107</t>
         </is>
       </c>
       <c r="V203" s="13" t="inlineStr">
         <is>
-          <t>Reparación del daño · actualización automática</t>
+          <t>PPO · víctima · legitimación · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="204" ht="80" customHeight="1">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t>auto-2032337</t>
+          <t>pen-ppo-002</t>
         </is>
       </c>
       <c r="B204" s="11" t="n">
@@ -25958,12 +25958,12 @@
       </c>
       <c r="E204" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño</t>
+          <t>Prisión preventiva oficiosa</t>
         </is>
       </c>
       <c r="F204" s="11" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Cese cuando MP no prueba prolongación</t>
         </is>
       </c>
       <c r="G204" s="11" t="inlineStr">
@@ -25988,57 +25988,57 @@
       </c>
       <c r="K204" s="12" t="inlineStr">
         <is>
-          <t>PERSONAS INIMPUTABLES. ES IMPROCEDENTE CONDENARLAS AL PAGO DE LA REPARACIÓN DEL DAÑO, POR LO QUE EL ESTADO DEBE ASUMIRLO DE MANERA SUBSIDIARIA.</t>
+          <t>PRISIÓN PREVENTIVA OFICIOSA. SU CESE ORDENADO CUANDO EL MINISTERIO PÚBLICO NO PRUEBA NI JUSTIFICA SU PROLONGACIÓN, PARA EFECTOS DE QUE SE DEBATA LA IMPOSICIÓN DE OTRAS MEDIDAS CAUTELARES MENOS RESTRICTIVAS.</t>
         </is>
       </c>
       <c r="L204" s="11" t="inlineStr">
         <is>
-          <t>2032337</t>
+          <t>2032108</t>
         </is>
       </c>
       <c r="M204" s="11" t="inlineStr"/>
       <c r="N204" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O204" s="11" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P204" s="11" t="inlineStr"/>
       <c r="Q204" s="11" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>Al solicitar prolongación de PPO, el MP tiene carga probatoria. Si no la cumple, el juez debe cesar la PPO y reabrir debate sobre medidas cautelares alternativas.</t>
         </is>
       </c>
       <c r="R204" s="11" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Defensa decisiva contra prolongación automática de PPO.</t>
         </is>
       </c>
       <c r="S204" s="11" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Cuando MP solicita prolongación sin justificar, la defensa debe exigir prueba concreta. Sin ella, opera el cese y se debate medida alterna (caución, brazalete, presentación periódica).</t>
         </is>
       </c>
       <c r="T204" s="11" t="inlineStr"/>
       <c r="U204" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032337</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032108</t>
         </is>
       </c>
       <c r="V204" s="11" t="inlineStr">
         <is>
-          <t>Reparación del daño · actualización automática</t>
+          <t>PPO · prolongación · carga probatoria MP · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="205" ht="80" customHeight="1">
       <c r="A205" s="13" t="inlineStr">
         <is>
-          <t>auto-2032390</t>
+          <t>auto-2032300</t>
         </is>
       </c>
       <c r="B205" s="13" t="n">
@@ -26086,18 +26086,18 @@
       </c>
       <c r="K205" s="14" t="inlineStr">
         <is>
-          <t>PAGO DE INDEMNIZACIÓN POR DAÑOS PUNITIVOS. PROCEDE ANTE ACTOS DISCRIMINATORIOS OCASIONADOS POR EL USO DEL LENGUAJE BASADO EN ESTEREOTIPOS O PREJUICIOS POR RAZÓN DE GÉNERO, Y CONDUCTAS IRREGULARES E INJUSTIFICADAS DERIVADAS DE UN CONTRATO DE SEGURO.</t>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. OBLIGAR A UNA ADOLESCENTE VÍCTIMA DE MALA PRÁXIS MÉDICA A RECIBIR ATENCIÓN MÉDICA POSTERIOR PARA EJERCER SUS DERECHOS REPRODUCTIVOS EN LA MISMA INSTITUCIÓN DE SALUD QUE ACTUÓ EN FORMA IRREGULAR, CONSTITUYE UNA ACTIVIDAD REVICTIMIZANTE.</t>
         </is>
       </c>
       <c r="L205" s="13" t="inlineStr">
         <is>
-          <t>2032390</t>
+          <t>2032300</t>
         </is>
       </c>
       <c r="M205" s="13" t="inlineStr"/>
       <c r="N205" s="13" t="inlineStr">
         <is>
-          <t>viernes 03 de julio de 2026 10:10 h</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O205" s="13" t="inlineStr">
@@ -26124,7 +26124,7 @@
       <c r="T205" s="13" t="inlineStr"/>
       <c r="U205" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032390</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032300</t>
         </is>
       </c>
       <c r="V205" s="13" t="inlineStr">
@@ -26136,7 +26136,7 @@
     <row r="206" ht="80" customHeight="1">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t>auto-2032469</t>
+          <t>auto-2032301</t>
         </is>
       </c>
       <c r="B206" s="11" t="n">
@@ -26184,18 +26184,18 @@
       </c>
       <c r="K206" s="12" t="inlineStr">
         <is>
-          <t>RECURSO DE REVOCACIÓN PREVISTO EN EL ARTÍCULO 170 DE LA LEY NACIONAL DEL SISTEMA INTEGRAL DE JUSTICIA PENAL PARA ADOLESCENTES. PROCEDE CONTRA EL AUTO QUE INADMITE LA APELACIÓN, Y EN OBSERVANCIA AL PRINCIPIO DE DEFINITIVIDAD, DEBE AGOTARSE PREVIO A PROMOVER EL AMPARO.</t>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. LA REPARACIÓN INTEGRAL DEL DAÑO NO SE LIMITA AL RESARCIMIENTO ECONÓMICO, SINO QUE INCLUYE LA REHABILITACIÓN PARA FACILITAR A LA VÍCTIMA HACER FRENTE A LOS EFECTOS DEL DAÑO SUFRIDO (LEY GENERAL DE VÍCTIMAS).</t>
         </is>
       </c>
       <c r="L206" s="11" t="inlineStr">
         <is>
-          <t>2032469</t>
+          <t>2032301</t>
         </is>
       </c>
       <c r="M206" s="11" t="inlineStr"/>
       <c r="N206" s="11" t="inlineStr">
         <is>
-          <t>viernes 07 de agosto de 2026 10:15 h</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O206" s="11" t="inlineStr">
@@ -26222,7 +26222,7 @@
       <c r="T206" s="11" t="inlineStr"/>
       <c r="U206" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032469</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032301</t>
         </is>
       </c>
       <c r="V206" s="11" t="inlineStr">
@@ -26234,7 +26234,7 @@
     <row r="207" ht="80" customHeight="1">
       <c r="A207" s="13" t="inlineStr">
         <is>
-          <t>auto-2032746</t>
+          <t>auto-2032304</t>
         </is>
       </c>
       <c r="B207" s="13" t="n">
@@ -26282,18 +26282,18 @@
       </c>
       <c r="K207" s="14" t="inlineStr">
         <is>
-          <t>LUCRO CESANTE COMO PARTE DE LA REPARACIÓN INTEGRAL DEL DAÑO EN EL PROCESO PENAL. SI SU PROCEDENCIA Y MONTO FUERON MATERIA DEL CONTRADICTORIO Y SE ABSOLVIÓ DE SU PAGO POR FALTA DE PRUEBA, NO PUEDEN DETERMINARSE EN LA ETAPA DE EJECUCIÓN.</t>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. PARA DETERMINAR LA REPARACIÓN INTEGRAL DEL DAÑO SE DEBE CONSIDERAR TANTO EL HECHO VICTIMIZANTE COMO SUS EFECTOS, PARA QUE SU FIJACIÓN PERMITA A LAS VÍCTIMAS DIRECTAS E INDIRECTAS REHACER SU PROYECTO DE VIDA.</t>
         </is>
       </c>
       <c r="L207" s="13" t="inlineStr">
         <is>
-          <t>2032746</t>
+          <t>2032304</t>
         </is>
       </c>
       <c r="M207" s="13" t="inlineStr"/>
       <c r="N207" s="13" t="inlineStr">
         <is>
-          <t>viernes 09 de octubre de 2026 10:19 h</t>
+          <t>viernes 19 de junio de 2026 10:25 h</t>
         </is>
       </c>
       <c r="O207" s="13" t="inlineStr">
@@ -26320,7 +26320,7 @@
       <c r="T207" s="13" t="inlineStr"/>
       <c r="U207" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032746</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032304</t>
         </is>
       </c>
       <c r="V207" s="13" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="208" ht="80" customHeight="1">
       <c r="A208" s="11" t="inlineStr">
         <is>
-          <t>auto-2032756</t>
+          <t>auto-2032335</t>
         </is>
       </c>
       <c r="B208" s="11" t="n">
@@ -26380,18 +26380,18 @@
       </c>
       <c r="K208" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN DEFINITIVA EN AMPARO INDIRECTO. PROCEDE RESPECTO DEL ORDEN DE PRELACIÓN OBLIGATORIO PARA GARANTIZAR EL INTERÉS FISCAL PREVISTO EN EL ARTÍCULO 141 DEL CÓDIGO FISCAL DE LA FEDERACIÓN (LEGISLACIÓN VIGENTE HASTA EL 9 DE ABRIL DE 2026).</t>
+          <t>PERSONA INIMPUTABLE POR TRANSTORNO MENTAL. LA MEDIDA DE SEGURIDAD DE INTERNAMIENTO DEBE IMPONERSE CONFORME AL MODELO SOCIAL DE DISCAPACIDAD Y NO CON BASE EN LA PUNIBILIDAD DEL TIPO PENAL ATRIBUIDO.</t>
         </is>
       </c>
       <c r="L208" s="11" t="inlineStr">
         <is>
-          <t>2032756</t>
+          <t>2032335</t>
         </is>
       </c>
       <c r="M208" s="11" t="inlineStr"/>
       <c r="N208" s="11" t="inlineStr">
         <is>
-          <t>viernes 09 de octubre de 2026 10:19 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O208" s="11" t="inlineStr">
@@ -26418,17 +26418,507 @@
       <c r="T208" s="11" t="inlineStr"/>
       <c r="U208" s="11" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032335</t>
+        </is>
+      </c>
+      <c r="V208" s="11" t="inlineStr">
+        <is>
+          <t>Reparación del daño · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="80" customHeight="1">
+      <c r="A209" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032337</t>
+        </is>
+      </c>
+      <c r="B209" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C209" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D209" s="13" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E209" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño</t>
+        </is>
+      </c>
+      <c r="F209" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G209" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H209" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I209" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J209" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K209" s="14" t="inlineStr">
+        <is>
+          <t>PERSONAS INIMPUTABLES. ES IMPROCEDENTE CONDENARLAS AL PAGO DE LA REPARACIÓN DEL DAÑO, POR LO QUE EL ESTADO DEBE ASUMIRLO DE MANERA SUBSIDIARIA.</t>
+        </is>
+      </c>
+      <c r="L209" s="13" t="inlineStr">
+        <is>
+          <t>2032337</t>
+        </is>
+      </c>
+      <c r="M209" s="13" t="inlineStr"/>
+      <c r="N209" s="13" t="inlineStr">
+        <is>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
+        </is>
+      </c>
+      <c r="O209" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P209" s="13" t="inlineStr"/>
+      <c r="Q209" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R209" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S209" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T209" s="13" t="inlineStr"/>
+      <c r="U209" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032337</t>
+        </is>
+      </c>
+      <c r="V209" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="80" customHeight="1">
+      <c r="A210" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032390</t>
+        </is>
+      </c>
+      <c r="B210" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C210" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D210" s="11" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E210" s="11" t="inlineStr">
+        <is>
+          <t>Reparación del daño</t>
+        </is>
+      </c>
+      <c r="F210" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G210" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H210" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I210" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J210" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K210" s="12" t="inlineStr">
+        <is>
+          <t>PAGO DE INDEMNIZACIÓN POR DAÑOS PUNITIVOS. PROCEDE ANTE ACTOS DISCRIMINATORIOS OCASIONADOS POR EL USO DEL LENGUAJE BASADO EN ESTEREOTIPOS O PREJUICIOS POR RAZÓN DE GÉNERO, Y CONDUCTAS IRREGULARES E INJUSTIFICADAS DERIVADAS DE UN CONTRATO DE SEGURO.</t>
+        </is>
+      </c>
+      <c r="L210" s="11" t="inlineStr">
+        <is>
+          <t>2032390</t>
+        </is>
+      </c>
+      <c r="M210" s="11" t="inlineStr"/>
+      <c r="N210" s="11" t="inlineStr">
+        <is>
+          <t>viernes 03 de julio de 2026 10:10 h</t>
+        </is>
+      </c>
+      <c r="O210" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P210" s="11" t="inlineStr"/>
+      <c r="Q210" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R210" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S210" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T210" s="11" t="inlineStr"/>
+      <c r="U210" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032390</t>
+        </is>
+      </c>
+      <c r="V210" s="11" t="inlineStr">
+        <is>
+          <t>Reparación del daño · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="80" customHeight="1">
+      <c r="A211" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032469</t>
+        </is>
+      </c>
+      <c r="B211" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C211" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D211" s="13" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E211" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño</t>
+        </is>
+      </c>
+      <c r="F211" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G211" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H211" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I211" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J211" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K211" s="14" t="inlineStr">
+        <is>
+          <t>RECURSO DE REVOCACIÓN PREVISTO EN EL ARTÍCULO 170 DE LA LEY NACIONAL DEL SISTEMA INTEGRAL DE JUSTICIA PENAL PARA ADOLESCENTES. PROCEDE CONTRA EL AUTO QUE INADMITE LA APELACIÓN, Y EN OBSERVANCIA AL PRINCIPIO DE DEFINITIVIDAD, DEBE AGOTARSE PREVIO A PROMOVER EL AMPARO.</t>
+        </is>
+      </c>
+      <c r="L211" s="13" t="inlineStr">
+        <is>
+          <t>2032469</t>
+        </is>
+      </c>
+      <c r="M211" s="13" t="inlineStr"/>
+      <c r="N211" s="13" t="inlineStr">
+        <is>
+          <t>viernes 07 de agosto de 2026 10:15 h</t>
+        </is>
+      </c>
+      <c r="O211" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P211" s="13" t="inlineStr"/>
+      <c r="Q211" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R211" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S211" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T211" s="13" t="inlineStr"/>
+      <c r="U211" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032469</t>
+        </is>
+      </c>
+      <c r="V211" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="80" customHeight="1">
+      <c r="A212" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032746</t>
+        </is>
+      </c>
+      <c r="B212" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C212" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D212" s="11" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E212" s="11" t="inlineStr">
+        <is>
+          <t>Reparación del daño</t>
+        </is>
+      </c>
+      <c r="F212" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G212" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H212" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I212" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J212" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K212" s="12" t="inlineStr">
+        <is>
+          <t>LUCRO CESANTE COMO PARTE DE LA REPARACIÓN INTEGRAL DEL DAÑO EN EL PROCESO PENAL. SI SU PROCEDENCIA Y MONTO FUERON MATERIA DEL CONTRADICTORIO Y SE ABSOLVIÓ DE SU PAGO POR FALTA DE PRUEBA, NO PUEDEN DETERMINARSE EN LA ETAPA DE EJECUCIÓN.</t>
+        </is>
+      </c>
+      <c r="L212" s="11" t="inlineStr">
+        <is>
+          <t>2032746</t>
+        </is>
+      </c>
+      <c r="M212" s="11" t="inlineStr"/>
+      <c r="N212" s="11" t="inlineStr">
+        <is>
+          <t>viernes 09 de octubre de 2026 10:19 h</t>
+        </is>
+      </c>
+      <c r="O212" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P212" s="11" t="inlineStr"/>
+      <c r="Q212" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R212" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S212" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T212" s="11" t="inlineStr"/>
+      <c r="U212" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032746</t>
+        </is>
+      </c>
+      <c r="V212" s="11" t="inlineStr">
+        <is>
+          <t>Reparación del daño · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="80" customHeight="1">
+      <c r="A213" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032756</t>
+        </is>
+      </c>
+      <c r="B213" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C213" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D213" s="13" t="inlineStr">
+        <is>
+          <t>Penal</t>
+        </is>
+      </c>
+      <c r="E213" s="13" t="inlineStr">
+        <is>
+          <t>Reparación del daño</t>
+        </is>
+      </c>
+      <c r="F213" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G213" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H213" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I213" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J213" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K213" s="14" t="inlineStr">
+        <is>
+          <t>SUSPENSIÓN DEFINITIVA EN AMPARO INDIRECTO. PROCEDE RESPECTO DEL ORDEN DE PRELACIÓN OBLIGATORIO PARA GARANTIZAR EL INTERÉS FISCAL PREVISTO EN EL ARTÍCULO 141 DEL CÓDIGO FISCAL DE LA FEDERACIÓN (LEGISLACIÓN VIGENTE HASTA EL 9 DE ABRIL DE 2026).</t>
+        </is>
+      </c>
+      <c r="L213" s="13" t="inlineStr">
+        <is>
+          <t>2032756</t>
+        </is>
+      </c>
+      <c r="M213" s="13" t="inlineStr"/>
+      <c r="N213" s="13" t="inlineStr">
+        <is>
+          <t>viernes 09 de octubre de 2026 10:19 h</t>
+        </is>
+      </c>
+      <c r="O213" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P213" s="13" t="inlineStr"/>
+      <c r="Q213" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R213" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S213" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T213" s="13" t="inlineStr"/>
+      <c r="U213" s="13" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032756</t>
         </is>
       </c>
-      <c r="V208" s="11" t="inlineStr">
+      <c r="V213" s="13" t="inlineStr">
         <is>
           <t>Reparación del daño · actualización automática</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V208"/>
+  <autoFilter ref="A1:V213"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26439,7 +26929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29281,7 +29771,7 @@
     <row r="30" ht="80" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>auto-2032177</t>
+          <t>auto-2032790</t>
         </is>
       </c>
       <c r="B30" s="11" t="n">
@@ -29299,7 +29789,7 @@
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos</t>
+          <t>Derecho humano a la salud</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -29329,18 +29819,18 @@
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>PRUEBAS EN EL JUICIO CONTENCIOSO ADMINISTRATIVO FEDERAL. EL ARTÍCULO 40, PÁRRAFO SEGUNDO, DE LA LEY FEDERAL DE PROCEDIMIENTO CONTENCIOSO ADMINISTRATIVO NO VIOLA EL DERECHO DE ACCESO A LA JUSTICIA.</t>
+          <t>TRABAJADORA EMBARAZADA. LA AUTORIDAD JURISDICCIONAL LABORAL DEBE OTORGAR DE OFICIO LAS MEDIDAS CAUTELARES NECESARIAS PARA GARANTIZAR EL ACCESO A LOS SERVICIOS DE SALUD Y ATENCIÓN MÉDICA DURANTE EL EMBARAZO O EL EJERCICIO DEL DERECHO A LA MATERNIDAD PROTEGIDA.</t>
         </is>
       </c>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>2032177</t>
+          <t>2032790</t>
         </is>
       </c>
       <c r="M30" s="11" t="inlineStr"/>
       <c r="N30" s="11" t="inlineStr">
         <is>
-          <t>viernes 22 de mayo de 2026 10:27 h</t>
+          <t>viernes 16 de octubre de 2026 10:26 h</t>
         </is>
       </c>
       <c r="O30" s="11" t="inlineStr">
@@ -29367,19 +29857,19 @@
       <c r="T30" s="11" t="inlineStr"/>
       <c r="U30" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032177</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032790</t>
         </is>
       </c>
       <c r="V30" s="11" t="inlineStr">
         <is>
-          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
+          <t>Derecho humano a la salud · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="31" ht="80" customHeight="1">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>auto-2032233</t>
+          <t>auto-2032177</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
@@ -29427,18 +29917,18 @@
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>PROCEDIMIENTO DE SEPARACIÓN DEL CARGO PREVISTO EN LOS ARTÍCULOS 209 Y 210 DE LA LEY ORGÁNICA DEL PODER JUDICIAL DEL ESTADO DE PUEBLA (ABROGADA). AL NO PREVER LA FORMA COMO DEBE INICIARSE NI LOS TÉRMINOS DE SU SUSTANCIACIÓN, LE ES APLICABLE EL DE RESPONSABILIDAD ADMINISTRATIVA.</t>
+          <t>PRUEBAS EN EL JUICIO CONTENCIOSO ADMINISTRATIVO FEDERAL. EL ARTÍCULO 40, PÁRRAFO SEGUNDO, DE LA LEY FEDERAL DE PROCEDIMIENTO CONTENCIOSO ADMINISTRATIVO NO VIOLA EL DERECHO DE ACCESO A LA JUSTICIA.</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr">
         <is>
-          <t>2032233</t>
+          <t>2032177</t>
         </is>
       </c>
       <c r="M31" s="13" t="inlineStr"/>
       <c r="N31" s="13" t="inlineStr">
         <is>
-          <t>viernes 05 de junio de 2026 10:11</t>
+          <t>viernes 22 de mayo de 2026 10:27 h</t>
         </is>
       </c>
       <c r="O31" s="13" t="inlineStr">
@@ -29465,7 +29955,7 @@
       <c r="T31" s="13" t="inlineStr"/>
       <c r="U31" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032233</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032177</t>
         </is>
       </c>
       <c r="V31" s="13" t="inlineStr">
@@ -29477,7 +29967,7 @@
     <row r="32" ht="80" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>auto-2032330</t>
+          <t>auto-2032233</t>
         </is>
       </c>
       <c r="B32" s="11" t="n">
@@ -29505,7 +29995,7 @@
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>jurisprudencia</t>
+          <t>tesis aislada</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
@@ -29525,18 +30015,18 @@
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SALUD PARA EL BIENESTAR (INSABI). LE CORRESPONDE LA ADQUISICIÓN Y SUMINISTRO DE MEDICAMENTOS E INSUMOS O, EN SU CASO, EL FINANCIAMIENTO PARA SU ADQUISICIÓN, RELACIONADOS CON EL TRATAMIENTO DE ENFERMEDADES QUE PROVOCAN GASTOS CATASTRÓFICOS.</t>
+          <t>PROCEDIMIENTO DE SEPARACIÓN DEL CARGO PREVISTO EN LOS ARTÍCULOS 209 Y 210 DE LA LEY ORGÁNICA DEL PODER JUDICIAL DEL ESTADO DE PUEBLA (ABROGADA). AL NO PREVER LA FORMA COMO DEBE INICIARSE NI LOS TÉRMINOS DE SU SUSTANCIACIÓN, LE ES APLICABLE EL DE RESPONSABILIDAD ADMINISTRATIVA.</t>
         </is>
       </c>
       <c r="L32" s="11" t="inlineStr">
         <is>
-          <t>2032330</t>
+          <t>2032233</t>
         </is>
       </c>
       <c r="M32" s="11" t="inlineStr"/>
       <c r="N32" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 05 de junio de 2026 10:11</t>
         </is>
       </c>
       <c r="O32" s="11" t="inlineStr">
@@ -29563,7 +30053,7 @@
       <c r="T32" s="11" t="inlineStr"/>
       <c r="U32" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032330</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032233</t>
         </is>
       </c>
       <c r="V32" s="11" t="inlineStr">
@@ -29575,7 +30065,7 @@
     <row r="33" ht="80" customHeight="1">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>auto-2032462</t>
+          <t>auto-2032330</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
@@ -29603,7 +30093,7 @@
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>tesis aislada</t>
+          <t>jurisprudencia</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
@@ -29623,18 +30113,18 @@
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>PROCEDIMIENTO DE RESPONSABILIDADES ADMINISTRATIVAS CONTRA UNA PERSONA JUEZA DEL SISTEMA PENAL ACUSATORIO EN EL ESTADO DE CHIHUAHUA. CORRESPONDE AL ÓRGANO DE ADMINISTRACIÓN JUDICIAL DETERMINAR LA ACTUALIZACIÓN DE LAS FALTAS ADMINISTRATIVAS QUE SE LE ATRIBUYEN.</t>
+          <t>INSTITUTO DE SALUD PARA EL BIENESTAR (INSABI). LE CORRESPONDE LA ADQUISICIÓN Y SUMINISTRO DE MEDICAMENTOS E INSUMOS O, EN SU CASO, EL FINANCIAMIENTO PARA SU ADQUISICIÓN, RELACIONADOS CON EL TRATAMIENTO DE ENFERMEDADES QUE PROVOCAN GASTOS CATASTRÓFICOS.</t>
         </is>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
-          <t>2032462</t>
+          <t>2032330</t>
         </is>
       </c>
       <c r="M33" s="13" t="inlineStr"/>
       <c r="N33" s="13" t="inlineStr">
         <is>
-          <t>viernes 07 de agosto de 2026 10:15 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O33" s="13" t="inlineStr">
@@ -29661,7 +30151,7 @@
       <c r="T33" s="13" t="inlineStr"/>
       <c r="U33" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032462</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032330</t>
         </is>
       </c>
       <c r="V33" s="13" t="inlineStr">
@@ -29673,7 +30163,7 @@
     <row r="34" ht="80" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>auto-2032502</t>
+          <t>auto-2032462</t>
         </is>
       </c>
       <c r="B34" s="11" t="n">
@@ -29721,18 +30211,18 @@
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. PARA DETERMINAR SI SE ACTUALIZA POR SU ACTIVIDAD ADMINISTRATIVA IRREGULAR SE DEBE DEFINIR SI LOS DAÑOS RECLAMADOS SON DE CARÁCTER CONTRACTUAL O EXTRACONTRACTUAL.</t>
+          <t>PROCEDIMIENTO DE RESPONSABILIDADES ADMINISTRATIVAS CONTRA UNA PERSONA JUEZA DEL SISTEMA PENAL ACUSATORIO EN EL ESTADO DE CHIHUAHUA. CORRESPONDE AL ÓRGANO DE ADMINISTRACIÓN JUDICIAL DETERMINAR LA ACTUALIZACIÓN DE LAS FALTAS ADMINISTRATIVAS QUE SE LE ATRIBUYEN.</t>
         </is>
       </c>
       <c r="L34" s="11" t="inlineStr">
         <is>
-          <t>2032502</t>
+          <t>2032462</t>
         </is>
       </c>
       <c r="M34" s="11" t="inlineStr"/>
       <c r="N34" s="11" t="inlineStr">
         <is>
-          <t>viernes 14 de agosto de 2026 10:22 h</t>
+          <t>viernes 07 de agosto de 2026 10:15 h</t>
         </is>
       </c>
       <c r="O34" s="11" t="inlineStr">
@@ -29759,7 +30249,7 @@
       <c r="T34" s="11" t="inlineStr"/>
       <c r="U34" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032502</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032462</t>
         </is>
       </c>
       <c r="V34" s="11" t="inlineStr">
@@ -29771,7 +30261,7 @@
     <row r="35" ht="80" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>auto-2032562</t>
+          <t>auto-2032502</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
@@ -29819,18 +30309,18 @@
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>IMPUESTO SOBRE LA RENTA. NO PROCEDE SU DEDUCCIÓN POR EL PAGO DE PENAS CONVENCIONALES EN TÉRMINOS DEL ARTÍCULO 32, FRACCIÓN VI, DE LA LEY RELATIVA, CUANDO EXISTE UN MECANISMO CONTRACTUAL PARA EVITAR SU PAGO Y NO SE EJERCE (LEGISLACIÓN VIGENTE EN 2013).</t>
+          <t>RESPONSABILIDAD PATRIMONIAL DEL ESTADO. PARA DETERMINAR SI SE ACTUALIZA POR SU ACTIVIDAD ADMINISTRATIVA IRREGULAR SE DEBE DEFINIR SI LOS DAÑOS RECLAMADOS SON DE CARÁCTER CONTRACTUAL O EXTRACONTRACTUAL.</t>
         </is>
       </c>
       <c r="L35" s="13" t="inlineStr">
         <is>
-          <t>2032562</t>
+          <t>2032502</t>
         </is>
       </c>
       <c r="M35" s="13" t="inlineStr"/>
       <c r="N35" s="13" t="inlineStr">
         <is>
-          <t>viernes 28 de agosto de 2026 10:36 h</t>
+          <t>viernes 14 de agosto de 2026 10:22 h</t>
         </is>
       </c>
       <c r="O35" s="13" t="inlineStr">
@@ -29857,7 +30347,7 @@
       <c r="T35" s="13" t="inlineStr"/>
       <c r="U35" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032562</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032502</t>
         </is>
       </c>
       <c r="V35" s="13" t="inlineStr">
@@ -29869,7 +30359,7 @@
     <row r="36" ht="80" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>auto-2032717</t>
+          <t>auto-2032562</t>
         </is>
       </c>
       <c r="B36" s="11" t="n">
@@ -29917,18 +30407,18 @@
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>RECURSO DE REVISIÓN ADMINISTRATIVA. ES IMPROCEDENTE CONTRA LA SENTENCIA EMITIDA POR LA SALA SUPERIOR DEL TRIBUNAL DE JUSTICIA ADMINISTRATIVA DEL ESTADO DE JALISCO, QUE RESUELVE UN RECURSO DE APELACIÓN EN UN ASUNTO DE RESPONSABILIDAD ADMINISTRATIVA.</t>
+          <t>IMPUESTO SOBRE LA RENTA. NO PROCEDE SU DEDUCCIÓN POR EL PAGO DE PENAS CONVENCIONALES EN TÉRMINOS DEL ARTÍCULO 32, FRACCIÓN VI, DE LA LEY RELATIVA, CUANDO EXISTE UN MECANISMO CONTRACTUAL PARA EVITAR SU PAGO Y NO SE EJERCE (LEGISLACIÓN VIGENTE EN 2013).</t>
         </is>
       </c>
       <c r="L36" s="11" t="inlineStr">
         <is>
-          <t>2032717</t>
+          <t>2032562</t>
         </is>
       </c>
       <c r="M36" s="11" t="inlineStr"/>
       <c r="N36" s="11" t="inlineStr">
         <is>
-          <t>viernes 02 de octubre de 2026 10:12 h</t>
+          <t>viernes 28 de agosto de 2026 10:36 h</t>
         </is>
       </c>
       <c r="O36" s="11" t="inlineStr">
@@ -29955,17 +30445,115 @@
       <c r="T36" s="11" t="inlineStr"/>
       <c r="U36" s="11" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032562</t>
+        </is>
+      </c>
+      <c r="V36" s="11" t="inlineStr">
+        <is>
+          <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="80" customHeight="1">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032717</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>Administrativo</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>Responsabilidad administrativa de servidores públicos</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K37" s="14" t="inlineStr">
+        <is>
+          <t>RECURSO DE REVISIÓN ADMINISTRATIVA. ES IMPROCEDENTE CONTRA LA SENTENCIA EMITIDA POR LA SALA SUPERIOR DEL TRIBUNAL DE JUSTICIA ADMINISTRATIVA DEL ESTADO DE JALISCO, QUE RESUELVE UN RECURSO DE APELACIÓN EN UN ASUNTO DE RESPONSABILIDAD ADMINISTRATIVA.</t>
+        </is>
+      </c>
+      <c r="L37" s="13" t="inlineStr">
+        <is>
+          <t>2032717</t>
+        </is>
+      </c>
+      <c r="M37" s="13" t="inlineStr"/>
+      <c r="N37" s="13" t="inlineStr">
+        <is>
+          <t>viernes 02 de octubre de 2026 10:12 h</t>
+        </is>
+      </c>
+      <c r="O37" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P37" s="13" t="inlineStr"/>
+      <c r="Q37" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R37" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S37" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T37" s="13" t="inlineStr"/>
+      <c r="U37" s="13" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032717</t>
         </is>
       </c>
-      <c r="V36" s="11" t="inlineStr">
+      <c r="V37" s="13" t="inlineStr">
         <is>
           <t>Responsabilidad administrativa de servidores públicos · actualización automática</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V36"/>
+  <autoFilter ref="A1:V37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -29976,7 +30564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -31172,7 +31760,7 @@
     <row r="13" ht="80" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>amp-sus-002</t>
+          <t>auto-2032784</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
@@ -31190,12 +31778,12 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>Suspensión</t>
+          <t>Procedencia del amparo</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
@@ -31220,57 +31808,57 @@
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
+          <t>REPRESENTANTE ESPECIAL DE UNA PERSONA MENOR DE EDAD EN EL JUICIO DE AMPARO. DEBE NOMBRARSE CUANDO UN PROGENITOR PROMUEVE EL JUICIO, PERO NO EJERCE CORRECTAMENTE LA REPRESENTACIÓN PARA PROTEGER LOS INTERESES DE AQUÉLLA (INTERPRETACIÓN EXTENSIVA DEL ARTÍCULO 8o. DE LA LEY DE AMPARO).</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>2032118</t>
+          <t>2032784</t>
         </is>
       </c>
       <c r="M13" s="13" t="inlineStr"/>
       <c r="N13" s="13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 16 de octubre de 2026</t>
         </is>
       </c>
       <c r="O13" s="13" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P13" s="13" t="inlineStr"/>
       <c r="Q13" s="13" t="inlineStr">
         <is>
-          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R13" s="13" t="inlineStr">
         <is>
-          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S13" s="13" t="inlineStr">
         <is>
-          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T13" s="13" t="inlineStr"/>
       <c r="U13" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032784</t>
         </is>
       </c>
       <c r="V13" s="13" t="inlineStr">
         <is>
-          <t>suspensión amparo · medida cautelar · 12a Época</t>
+          <t>Procedencia del amparo · actualización automática</t>
         </is>
       </c>
     </row>
     <row r="14" ht="80" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>amp-sus-003</t>
+          <t>amp-sus-002</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
@@ -31293,7 +31881,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
+          <t>Suspensión contra medidas cautelares civiles/mercantiles</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -31318,12 +31906,12 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
+          <t>SUSPENSIÓN EN EL JUICIO DE AMPARO. PUEDE CONCEDERSE CONTRA MEDIDAS CAUTELARES DICTADAS EN PROCESOS CIVILES O MERCANTILES CUANDO NO PRESERVAN LA MATERIA DEL JUICIO DE ORIGEN O IMPONEN RESTRICCIONES GENÉRICAS QUE AFECTAN INJUSTIFICADAMENTE DERECHOS HUMANOS.</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>2032066</t>
+          <t>2032118</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr"/>
@@ -31340,35 +31928,35 @@
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="11" t="inlineStr">
         <is>
-          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
+          <t>Las medidas cautelares civiles o mercantiles (embargos, restricciones, prohibiciones) pueden suspenderse vía amparo si exceden lo necesario para preservar la materia o son genéricas y afectan derechos humanos.</t>
         </is>
       </c>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
+          <t>Defensa contra embargos abusivos y medidas precautorias excesivas.</t>
         </is>
       </c>
       <c r="S14" s="11" t="inlineStr">
         <is>
-          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
+          <t>Embargado puede amparar si la medida es desproporcionada o no preserva materia del juicio.</t>
         </is>
       </c>
       <c r="T14" s="11" t="inlineStr"/>
       <c r="U14" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032066</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032118</t>
         </is>
       </c>
       <c r="V14" s="11" t="inlineStr">
         <is>
-          <t>suspensión restitutoria · incapacidad médica · IMSS · 12a Época</t>
+          <t>suspensión amparo · medida cautelar · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="15" ht="80" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>auto-2032354</t>
+          <t>amp-sus-003</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
@@ -31391,7 +31979,7 @@
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>Actualización automática semanal</t>
+          <t>Suspensión con efectos restitutorios — incapacidad médica</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
@@ -31416,57 +32004,57 @@
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. AL PROVEER SOBRE SU CONCESIÓN CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN, SE DEBE CONSIDERAR QUE LAS REPERCUSIONES NEGATIVAS DE LA BIOMETRÍA EMPEORAN GRAVEMENTE EN EL MODELO ECONÓMICO ACTUAL DEL CAPITALISMO DE VIGILANCIA.</t>
+          <t>SUSPENSIÓN EN AMPARO INDIRECTO CON EFECTOS RESTITUTORIOS. PROCEDE PARA LA EXPEDICIÓN DE UNA INCAPACIDAD MÉDICA CUANDO SU EFECTO ES TRANSITORIO Y EXISTE UN ESTADO CLÍNICO INCAPACITANTE PREVIAMENTE ACREDITADO.</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>2032354</t>
+          <t>2032066</t>
         </is>
       </c>
       <c r="M15" s="13" t="inlineStr"/>
       <c r="N15" s="13" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="O15" s="13" t="inlineStr">
         <is>
-          <t>Semanario Judicial de la Federación — captura automática</t>
+          <t>SJF 12a Época — VERIFICADO</t>
         </is>
       </c>
       <c r="P15" s="13" t="inlineStr"/>
       <c r="Q15" s="13" t="inlineStr">
         <is>
-          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+          <t>La suspensión puede tener efectos restitutorios (no solo conservativos): obligar al IMSS/ISSSTE a expedir incapacidad médica si hay estado clínico acreditado.</t>
         </is>
       </c>
       <c r="R15" s="13" t="inlineStr">
         <is>
-          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+          <t>Innovadora: suspensión que ORDENA actuar, no solo paraliza.</t>
         </is>
       </c>
       <c r="S15" s="13" t="inlineStr">
         <is>
-          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+          <t>Útil para trabajadores cuyas incapacidades son negadas pese a sustento médico.</t>
         </is>
       </c>
       <c r="T15" s="13" t="inlineStr"/>
       <c r="U15" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032354</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032066</t>
         </is>
       </c>
       <c r="V15" s="13" t="inlineStr">
         <is>
-          <t>Suspensión · actualización automática</t>
+          <t>suspensión restitutoria · incapacidad médica · IMSS · 12a Época</t>
         </is>
       </c>
     </row>
     <row r="16" ht="80" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>auto-2032355</t>
+          <t>auto-2032354</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
@@ -31514,18 +32102,18 @@
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN QUE PREVÉ LA CREACIÓN DE LA CLAVE ÚNICA DE REGISTRO DE POBLACIÓN (CURP) BIOMÉTRICA.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. AL PROVEER SOBRE SU CONCESIÓN CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN, SE DEBE CONSIDERAR QUE LAS REPERCUSIONES NEGATIVAS DE LA BIOMETRÍA EMPEORAN GRAVEMENTE EN EL MODELO ECONÓMICO ACTUAL DEL CAPITALISMO DE VIGILANCIA.</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>2032355</t>
+          <t>2032354</t>
         </is>
       </c>
       <c r="M16" s="11" t="inlineStr"/>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>viernes 26 de junio de 2026 10:32 h</t>
+          <t>viernes 26 de junio de 2026 10:</t>
         </is>
       </c>
       <c r="O16" s="11" t="inlineStr">
@@ -31552,7 +32140,7 @@
       <c r="T16" s="11" t="inlineStr"/>
       <c r="U16" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032355</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032354</t>
         </is>
       </c>
       <c r="V16" s="11" t="inlineStr">
@@ -31564,7 +32152,7 @@
     <row r="17" ht="80" customHeight="1">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>auto-2032475</t>
+          <t>auto-2032355</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
@@ -31612,18 +32200,18 @@
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CON EFECTOS RESTITUTORIOS ANTICIPADOS CONTRA LA OMISIÓN DE PAGO CORRESPONDIENTE AL PROGRAMA PENSIÓN PARA EL BIENESTAR DE LAS PERSONAS CON DISCAPACIDAD PERMANENTE.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA EL ARTÍCULO 91 BIS DE LA LEY GENERAL DE POBLACIÓN QUE PREVÉ LA CREACIÓN DE LA CLAVE ÚNICA DE REGISTRO DE POBLACIÓN (CURP) BIOMÉTRICA.</t>
         </is>
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>2032475</t>
+          <t>2032355</t>
         </is>
       </c>
       <c r="M17" s="13" t="inlineStr"/>
       <c r="N17" s="13" t="inlineStr">
         <is>
-          <t>viernes 07 de agosto de 2026 10:15 h</t>
+          <t>viernes 26 de junio de 2026 10:32 h</t>
         </is>
       </c>
       <c r="O17" s="13" t="inlineStr">
@@ -31650,7 +32238,7 @@
       <c r="T17" s="13" t="inlineStr"/>
       <c r="U17" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032475</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032355</t>
         </is>
       </c>
       <c r="V17" s="13" t="inlineStr">
@@ -31662,7 +32250,7 @@
     <row r="18" ht="80" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>auto-2032542</t>
+          <t>auto-2032475</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
@@ -31710,18 +32298,18 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN EN AMPARO INDIRECTO. ES IMPROCEDENTE CONTRA NORMAS RECLAMADAS COMO AUTOAPLICATIVAS, CUANDO EL PLAZO DE VACATIO LEGIS NO ACTUALIZA EL REQUISITO DE PELIGRO EN LA DEMORA.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CON EFECTOS RESTITUTORIOS ANTICIPADOS CONTRA LA OMISIÓN DE PAGO CORRESPONDIENTE AL PROGRAMA PENSIÓN PARA EL BIENESTAR DE LAS PERSONAS CON DISCAPACIDAD PERMANENTE.</t>
         </is>
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>2032542</t>
+          <t>2032475</t>
         </is>
       </c>
       <c r="M18" s="11" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>viernes 21 de agosto de 2026 10:29 h</t>
+          <t>viernes 07 de agosto de 2026 10:15 h</t>
         </is>
       </c>
       <c r="O18" s="11" t="inlineStr">
@@ -31748,7 +32336,7 @@
       <c r="T18" s="11" t="inlineStr"/>
       <c r="U18" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032542</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032475</t>
         </is>
       </c>
       <c r="V18" s="11" t="inlineStr">
@@ -31760,7 +32348,7 @@
     <row r="19" ht="80" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>auto-2032544</t>
+          <t>auto-2032542</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
@@ -31808,12 +32396,12 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA LOS EFECTOS Y CONSECUENCIAS DEL ARTÍCULO 49 BIS DEL CÓDIGO FISCAL DE LA FEDERACIÓN.</t>
+          <t>SUSPENSIÓN EN AMPARO INDIRECTO. ES IMPROCEDENTE CONTRA NORMAS RECLAMADAS COMO AUTOAPLICATIVAS, CUANDO EL PLAZO DE VACATIO LEGIS NO ACTUALIZA EL REQUISITO DE PELIGRO EN LA DEMORA.</t>
         </is>
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t>2032544</t>
+          <t>2032542</t>
         </is>
       </c>
       <c r="M19" s="13" t="inlineStr"/>
@@ -31846,7 +32434,7 @@
       <c r="T19" s="13" t="inlineStr"/>
       <c r="U19" s="13" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032544</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032542</t>
         </is>
       </c>
       <c r="V19" s="13" t="inlineStr">
@@ -31858,7 +32446,7 @@
     <row r="20" ht="80" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>auto-2032576</t>
+          <t>auto-2032544</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
@@ -31906,18 +32494,18 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA LA EXPULSIÓN DE UNA PERSONA ADOLESCENTE DE LA ESCUELA EN LA QUE CURSA LA EDUCACIÓN BÁSICA (SECUNDARIA) POR ACUMULAR FALTAS A SU REGLAMENTO.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA LOS EFECTOS Y CONSECUENCIAS DEL ARTÍCULO 49 BIS DEL CÓDIGO FISCAL DE LA FEDERACIÓN.</t>
         </is>
       </c>
       <c r="L20" s="11" t="inlineStr">
         <is>
-          <t>2032576</t>
+          <t>2032544</t>
         </is>
       </c>
       <c r="M20" s="11" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>viernes 28 de agosto de 2026 10:36 h</t>
+          <t>viernes 21 de agosto de 2026 10:29 h</t>
         </is>
       </c>
       <c r="O20" s="11" t="inlineStr">
@@ -31944,7 +32532,7 @@
       <c r="T20" s="11" t="inlineStr"/>
       <c r="U20" s="11" t="inlineStr">
         <is>
-          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032576</t>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032544</t>
         </is>
       </c>
       <c r="V20" s="11" t="inlineStr">
@@ -31956,7 +32544,7 @@
     <row r="21" ht="80" customHeight="1">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>auto-2032685</t>
+          <t>auto-2032576</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
@@ -32004,18 +32592,18 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>SUSPENSIÓN PROVISIONAL. PROCEDE CON EFECTOS RESTITUTORIOS (TUTELA ANTICIPADA) CONTRA LA OMISIÓN DE REALIZAR AJUSTES AL PROCEDIMIENTO PARA PERSONAS CON DISCAPACIDAD.</t>
+          <t>SUSPENSIÓN PROVISIONAL EN AMPARO INDIRECTO. PROCEDE CONTRA LA EXPULSIÓN DE UNA PERSONA ADOLESCENTE DE LA ESCUELA EN LA QUE CURSA LA EDUCACIÓN BÁSICA (SECUNDARIA) POR ACUMULAR FALTAS A SU REGLAMENTO.</t>
         </is>
       </c>
       <c r="L21" s="13" t="inlineStr">
         <is>
-          <t>2032685</t>
+          <t>2032576</t>
         </is>
       </c>
       <c r="M21" s="13" t="inlineStr"/>
       <c r="N21" s="13" t="inlineStr">
         <is>
-          <t>viernes 25 de septiembre de 2026 10:34 h</t>
+          <t>viernes 28 de agosto de 2026 10:36 h</t>
         </is>
       </c>
       <c r="O21" s="13" t="inlineStr">
@@ -32042,17 +32630,311 @@
       <c r="T21" s="13" t="inlineStr"/>
       <c r="U21" s="13" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032576</t>
+        </is>
+      </c>
+      <c r="V21" s="13" t="inlineStr">
+        <is>
+          <t>Suspensión · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032685</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Amparo</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Suspensión</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>SUSPENSIÓN PROVISIONAL. PROCEDE CON EFECTOS RESTITUTORIOS (TUTELA ANTICIPADA) CONTRA LA OMISIÓN DE REALIZAR AJUSTES AL PROCEDIMIENTO PARA PERSONAS CON DISCAPACIDAD.</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>2032685</t>
+        </is>
+      </c>
+      <c r="M22" s="11" t="inlineStr"/>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>viernes 25 de septiembre de 2026 10:34 h</t>
+        </is>
+      </c>
+      <c r="O22" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P22" s="11" t="inlineStr"/>
+      <c r="Q22" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R22" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S22" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T22" s="11" t="inlineStr"/>
+      <c r="U22" s="11" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032685</t>
         </is>
       </c>
-      <c r="V21" s="13" t="inlineStr">
+      <c r="V22" s="11" t="inlineStr">
         <is>
           <t>Suspensión · actualización automática</t>
         </is>
       </c>
     </row>
+    <row r="23" ht="80" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>auto-2032758</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Amparo</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Suspensión</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K23" s="14" t="inlineStr">
+        <is>
+          <t>SUSPENSIÓN PROVISIONAL. PROCEDE CON EFECTOS RESTITUTORIOS CONTRA LA OMISIÓN DE SEÑALAR FECHA Y CELEBRAR LA AUDIENCIA INICIAL O DE VERIFICACIÓN Y APROBACIÓN DE ACUERDO REPARATORIO, CUANDO EXISTA DILACIÓN ABIERTA E INJUSTIFICADA.</t>
+        </is>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>2032758</t>
+        </is>
+      </c>
+      <c r="M23" s="13" t="inlineStr"/>
+      <c r="N23" s="13" t="inlineStr">
+        <is>
+          <t>viernes 09 de octubre de 2026 10:19 h</t>
+        </is>
+      </c>
+      <c r="O23" s="13" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P23" s="13" t="inlineStr"/>
+      <c r="Q23" s="13" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R23" s="13" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S23" s="13" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T23" s="13" t="inlineStr"/>
+      <c r="U23" s="13" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032758</t>
+        </is>
+      </c>
+      <c r="V23" s="13" t="inlineStr">
+        <is>
+          <t>Suspensión · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>auto-2032777</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Amparo</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Suspensión</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Actualización automática semanal</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>PELIGRO EN LA DEMORA Y APARIENCIA DEL BUEN DERECHO. ES INNECESARIO SU ESTUDIO CUANDO LA NEGATIVA DE LA SUSPENSIÓN DERIVA DE LA PRESENCIA NOTORIA DE UN MOTIVO QUE LEGALMENTE IMPOSIBILITA SU OTORGAMIENTO.</t>
+        </is>
+      </c>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>2032777</t>
+        </is>
+      </c>
+      <c r="M24" s="11" t="inlineStr"/>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>viernes 16 de octubre de 2026 10:26 h</t>
+        </is>
+      </c>
+      <c r="O24" s="11" t="inlineStr">
+        <is>
+          <t>Semanario Judicial de la Federación — captura automática</t>
+        </is>
+      </c>
+      <c r="P24" s="11" t="inlineStr"/>
+      <c r="Q24" s="11" t="inlineStr">
+        <is>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
+        </is>
+      </c>
+      <c r="R24" s="11" t="inlineStr">
+        <is>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
+        </is>
+      </c>
+      <c r="S24" s="11" t="inlineStr">
+        <is>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
+        </is>
+      </c>
+      <c r="T24" s="11" t="inlineStr"/>
+      <c r="U24" s="11" t="inlineStr">
+        <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032777</t>
+        </is>
+      </c>
+      <c r="V24" s="11" t="inlineStr">
+        <is>
+          <t>Suspensión · actualización automática</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V21"/>
+  <autoFilter ref="A1:V24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36917,7 +37799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V34"/>
+  <dimension ref="A1:V35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40143,7 +41025,7 @@
     <row r="34" ht="80" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>amp-gen-001</t>
+          <t>auto-2032779</t>
         </is>
       </c>
       <c r="B34" s="11" t="n">
@@ -40161,12 +41043,12 @@
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Perspectiva de género interseccional</t>
+          <t>Perspectiva de género</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>Acceso a la justicia para mujeres cuidadoras</t>
+          <t>Actualización automática semanal</t>
         </is>
       </c>
       <c r="G34" s="11" t="inlineStr">
@@ -40191,55 +41073,153 @@
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
+          <t>PERSPECTIVA DE GÉNERO EN MATERIA LABORAL. SU APLICACIÓN EXIGE A LA PERSONA JUZGADORA NO INCURRIR EN FORMALISMO MÁGICO DURANTE EL TRÁMITE Y RESOLUCIÓN DEL JUICIO.</t>
         </is>
       </c>
       <c r="L34" s="11" t="inlineStr">
         <is>
-          <t>2032067</t>
+          <t>2032779</t>
         </is>
       </c>
       <c r="M34" s="11" t="inlineStr"/>
       <c r="N34" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>viernes 16 de octubre de 2026 10:26 h</t>
         </is>
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>SJF 12a Época — VERIFICADO</t>
+          <t>Semanario Judicial de la Federación — captura automática</t>
         </is>
       </c>
       <c r="P34" s="11" t="inlineStr"/>
       <c r="Q34" s="11" t="inlineStr">
         <is>
-          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
+          <t>Criterio publicado esta semana en el Semanario Judicial de la Federación. Ver texto íntegro en el SJF mediante el enlace directo.</t>
         </is>
       </c>
       <c r="R34" s="11" t="inlineStr">
         <is>
-          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
+          <t>Incorporada automáticamente en la actualización semanal. Pendiente de análisis editorial.</t>
         </is>
       </c>
       <c r="S34" s="11" t="inlineStr">
         <is>
-          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
+          <t>Tesis nueva detectada por el robot semanal. Revisa el texto completo en el SJF.</t>
         </is>
       </c>
       <c r="T34" s="11" t="inlineStr"/>
       <c r="U34" s="11" t="inlineStr">
         <is>
+          <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032779</t>
+        </is>
+      </c>
+      <c r="V34" s="11" t="inlineStr">
+        <is>
+          <t>Perspectiva de género · actualización automática</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="80" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>amp-gen-001</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Tribunales Colegiados</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>Constitucional / DDHH</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>Perspectiva de género interseccional</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>Acceso a la justicia para mujeres cuidadoras</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>tesis aislada</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>Duodécima Época</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>vigente</t>
+        </is>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="K35" s="14" t="inlineStr">
+        <is>
+          <t>ACCESO A LA JUSTICIA EN CONDICIONES DE IGUALDAD SUSTANTIVA. LAS MANIFESTACIONES DE MUJERES QUE AFIRMAN REALIZAR LABORES DE CUIDADO NO REMUNERADAS DEBEN VALORARSE CON PERSPECTIVA DE GÉNERO INTERSECCIONAL.</t>
+        </is>
+      </c>
+      <c r="L35" s="13" t="inlineStr">
+        <is>
+          <t>2032067</t>
+        </is>
+      </c>
+      <c r="M35" s="13" t="inlineStr"/>
+      <c r="N35" s="13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O35" s="13" t="inlineStr">
+        <is>
+          <t>SJF 12a Época — VERIFICADO</t>
+        </is>
+      </c>
+      <c r="P35" s="13" t="inlineStr"/>
+      <c r="Q35" s="13" t="inlineStr">
+        <is>
+          <t>En procesos donde las mujeres afirman dedicarse a labores de cuidado, sus manifestaciones deben valorarse con perspectiva de género interseccional (considerando clase, edad, etnia, discapacidad y otros factores).</t>
+        </is>
+      </c>
+      <c r="R35" s="13" t="inlineStr">
+        <is>
+          <t>Estándar probatorio favorable para mujeres en juicios civiles, familiares, laborales.</t>
+        </is>
+      </c>
+      <c r="S35" s="13" t="inlineStr">
+        <is>
+          <t>En alimentos, pensiones, compensación por trabajo doméstico y otros litigios, el juez debe creer y valorar con flexibilidad las declaraciones de mujeres cuidadoras.</t>
+        </is>
+      </c>
+      <c r="T35" s="13" t="inlineStr"/>
+      <c r="U35" s="13" t="inlineStr">
+        <is>
           <t>https://sjf2.scjn.gob.mx/detalle/tesis/2032067</t>
         </is>
       </c>
-      <c r="V34" s="11" t="inlineStr">
+      <c r="V35" s="13" t="inlineStr">
         <is>
           <t>perspectiva género · interseccional · acceso justicia · 12a Época</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V34"/>
+  <autoFilter ref="A1:V35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
